--- a/Results/Ammonia/ammonia land use results.xlsx
+++ b/Results/Ammonia/ammonia land use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.034540875799614</v>
+        <v>2.03454087579957</v>
       </c>
       <c r="C2" t="n">
-        <v>2.160839521846061</v>
+        <v>2.160839521846124</v>
       </c>
       <c r="D2" t="n">
-        <v>3.487128682813119</v>
+        <v>3.487128682813113</v>
       </c>
       <c r="E2" t="n">
-        <v>2.293344330278158</v>
+        <v>2.293344330277969</v>
       </c>
       <c r="F2" t="n">
-        <v>1.963683234590024</v>
+        <v>1.963683234590032</v>
       </c>
       <c r="G2" t="n">
-        <v>3.001897682874463</v>
+        <v>3.00189768287444</v>
       </c>
       <c r="H2" t="n">
-        <v>4.183935229767615</v>
+        <v>4.183935229767599</v>
       </c>
       <c r="I2" t="n">
-        <v>2.473722839237316</v>
+        <v>2.473722839237304</v>
       </c>
       <c r="J2" t="n">
-        <v>2.507382290067309</v>
+        <v>2.507382290067373</v>
       </c>
       <c r="K2" t="n">
-        <v>1.889124965872976</v>
+        <v>1.889124965873027</v>
       </c>
       <c r="L2" t="n">
-        <v>3.791963577715908</v>
+        <v>3.791963577715925</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.297834361873566</v>
+        <v>2.297834361873609</v>
       </c>
       <c r="C3" t="n">
-        <v>2.489495607326803</v>
+        <v>2.489495607326886</v>
       </c>
       <c r="D3" t="n">
-        <v>3.968611242596893</v>
+        <v>3.968611242596897</v>
       </c>
       <c r="E3" t="n">
-        <v>2.622598643166335</v>
+        <v>2.622598643166115</v>
       </c>
       <c r="F3" t="n">
-        <v>2.292937547478197</v>
+        <v>2.292937547478179</v>
       </c>
       <c r="G3" t="n">
         <v>3.410495077368632</v>
       </c>
       <c r="H3" t="n">
-        <v>4.770412203552384</v>
+        <v>4.770412203552381</v>
       </c>
       <c r="I3" t="n">
-        <v>2.801389504012093</v>
+        <v>2.801389504012087</v>
       </c>
       <c r="J3" t="n">
-        <v>2.81495615928061</v>
+        <v>2.814956159280682</v>
       </c>
       <c r="K3" t="n">
-        <v>2.166546175096772</v>
+        <v>2.16654617509671</v>
       </c>
       <c r="L3" t="n">
-        <v>4.319109289789157</v>
+        <v>4.31910928978918</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.977657381980793</v>
+        <v>1.342631218167288</v>
       </c>
       <c r="C4" t="n">
-        <v>2.428300688865523</v>
+        <v>1.461041414159784</v>
       </c>
       <c r="D4" t="n">
-        <v>3.841159281883671</v>
+        <v>2.206133118070199</v>
       </c>
       <c r="E4" t="n">
-        <v>2.631004281649989</v>
+        <v>1.496721853580923</v>
       </c>
       <c r="F4" t="n">
-        <v>2.631004281649995</v>
+        <v>1.496721853580913</v>
       </c>
       <c r="G4" t="n">
-        <v>3.548187963285581</v>
+        <v>1.916887968772217</v>
       </c>
       <c r="H4" t="n">
-        <v>4.255159033397332</v>
+        <v>2.620132869583897</v>
       </c>
       <c r="I4" t="n">
-        <v>3.211332925428054</v>
+        <v>1.598753963166573</v>
       </c>
       <c r="J4" t="n">
-        <v>3.152900781290737</v>
+        <v>1.517874617477262</v>
       </c>
       <c r="K4" t="n">
-        <v>3.033569053329297</v>
+        <v>1.398542889515835</v>
       </c>
       <c r="L4" t="n">
-        <v>4.022311348142433</v>
+        <v>2.387285184329005</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.51300205255183</v>
+        <v>6.01285185488101</v>
       </c>
       <c r="C5" t="n">
-        <v>56.32910955081459</v>
+        <v>10.94758372245895</v>
       </c>
       <c r="D5" t="n">
-        <v>120.1402699408918</v>
+        <v>22.6747764831441</v>
       </c>
       <c r="E5" t="n">
-        <v>56.32911514217909</v>
+        <v>10.94758931382356</v>
       </c>
       <c r="F5" t="n">
-        <v>56.32911514217909</v>
+        <v>10.94758931382356</v>
       </c>
       <c r="G5" t="n">
-        <v>92.12452131608512</v>
+        <v>17.5063225543919</v>
       </c>
       <c r="H5" t="n">
-        <v>183.7268163171917</v>
+        <v>34.20714438037398</v>
       </c>
       <c r="I5" t="n">
-        <v>56.32898682765813</v>
+        <v>10.94746099930199</v>
       </c>
       <c r="J5" t="n">
-        <v>50.70345515961707</v>
+        <v>9.886772142714452</v>
       </c>
       <c r="K5" t="n">
-        <v>35.83793490246306</v>
+        <v>7.172111247678508</v>
       </c>
       <c r="L5" t="n">
-        <v>161.4725892895026</v>
+        <v>4.329834688887507</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.54235210797405</v>
+        <v>1.713317068362165</v>
       </c>
       <c r="C6" t="n">
-        <v>5.187119666396388</v>
+        <v>1.946593551574203</v>
       </c>
       <c r="D6" t="n">
-        <v>6.032222268169012</v>
+        <v>2.591756768099708</v>
       </c>
       <c r="E6" t="n">
-        <v>5.15333168950621</v>
+        <v>1.940651474958118</v>
       </c>
       <c r="F6" t="n">
-        <v>5.336761350399519</v>
+        <v>1.972935095100406</v>
       </c>
       <c r="G6" t="n">
-        <v>17.11288268927876</v>
+        <v>4.304274227610707</v>
       </c>
       <c r="H6" t="n">
-        <v>21.05253287823214</v>
+        <v>5.576470650255395</v>
       </c>
       <c r="I6" t="n">
-        <v>16.77602765142124</v>
+        <v>1.969439813361441</v>
       </c>
       <c r="J6" t="n">
-        <v>5.408383607077264</v>
+        <v>1.914839592664316</v>
       </c>
       <c r="K6" t="n">
-        <v>4.979830402637565</v>
+        <v>1.741084885137856</v>
       </c>
       <c r="L6" t="n">
-        <v>6.182757432154102</v>
+        <v>2.767523693054589</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.720188985284727</v>
+        <v>2.001316776779682</v>
       </c>
       <c r="C7" t="n">
-        <v>6.953987251889028</v>
+        <v>2.257562244935885</v>
       </c>
       <c r="D7" t="n">
-        <v>7.583688055490704</v>
+        <v>2.864818178655878</v>
       </c>
       <c r="E7" t="n">
-        <v>6.906950654999041</v>
+        <v>2.249288411212476</v>
       </c>
       <c r="F7" t="n">
-        <v>6.906950654999041</v>
+        <v>2.249288411212476</v>
       </c>
       <c r="G7" t="n">
-        <v>7.290719566589481</v>
+        <v>2.575573527384537</v>
       </c>
       <c r="H7" t="n">
-        <v>7.997690636701309</v>
+        <v>3.278818428196293</v>
       </c>
       <c r="I7" t="n">
-        <v>6.953864528732012</v>
+        <v>2.257439521778871</v>
       </c>
       <c r="J7" t="n">
-        <v>6.895432384594722</v>
+        <v>2.176560176089673</v>
       </c>
       <c r="K7" t="n">
-        <v>6.776100656633261</v>
+        <v>2.05722844812819</v>
       </c>
       <c r="L7" t="n">
-        <v>7.764842951446431</v>
+        <v>3.045970742941273</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.72118665032924</v>
+        <v>3.761492356289728</v>
       </c>
       <c r="C8" t="n">
-        <v>25.9756358950075</v>
+        <v>5.605372387984482</v>
       </c>
       <c r="D8" t="n">
-        <v>28.52797881783733</v>
+        <v>6.551013332854944</v>
       </c>
       <c r="E8" t="n">
-        <v>23.50134069544075</v>
+        <v>5.169901042504414</v>
       </c>
       <c r="F8" t="n">
-        <v>17.21423908710344</v>
+        <v>4.063371165433022</v>
       </c>
       <c r="G8" t="n">
-        <v>26.35556054336573</v>
+        <v>5.930985521115673</v>
       </c>
       <c r="H8" t="n">
-        <v>27.06253161346803</v>
+        <v>6.63423042192554</v>
       </c>
       <c r="I8" t="n">
-        <v>26.01870550550831</v>
+        <v>5.612851515509712</v>
       </c>
       <c r="J8" t="n">
-        <v>25.96205466259972</v>
+        <v>5.532285678835194</v>
       </c>
       <c r="K8" t="n">
-        <v>16.60873277892942</v>
+        <v>3.78777169227522</v>
       </c>
       <c r="L8" t="n">
-        <v>36.29762617038661</v>
+        <v>8.067740562264063</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>516.0153637867816</v>
+        <v>91.63726705614121</v>
       </c>
       <c r="C9" t="n">
-        <v>658.2765697811394</v>
+        <v>116.8903361489344</v>
       </c>
       <c r="D9" t="n">
-        <v>658.9062751948459</v>
+        <v>117.4975928940328</v>
       </c>
       <c r="E9" t="n">
-        <v>822.1731917673349</v>
+        <v>145.736146069485</v>
       </c>
       <c r="F9" t="n">
-        <v>658.2765735605818</v>
+        <v>116.8903414214004</v>
       </c>
       <c r="G9" t="n">
-        <v>658.6133020958407</v>
+        <v>117.2083474313829</v>
       </c>
       <c r="H9" t="n">
-        <v>659.3202731659521</v>
+        <v>117.911592332195</v>
       </c>
       <c r="I9" t="n">
-        <v>658.2764470579825</v>
+        <v>116.8902134257775</v>
       </c>
       <c r="J9" t="n">
-        <v>658.218014913846</v>
+        <v>116.8093340800881</v>
       </c>
       <c r="K9" t="n">
-        <v>479.2608245925944</v>
+        <v>102.2067447057021</v>
       </c>
       <c r="L9" t="n">
-        <v>659.0874254806981</v>
+        <v>117.6787446469398</v>
       </c>
     </row>
   </sheetData>
@@ -911,34 +911,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.33305234846368</v>
+        <v>4.333052348463667</v>
       </c>
       <c r="C2" t="n">
-        <v>3.896312374844835</v>
+        <v>3.896312374844822</v>
       </c>
       <c r="D2" t="n">
-        <v>3.320463119343323</v>
+        <v>3.320463119343316</v>
       </c>
       <c r="E2" t="n">
-        <v>4.240951783453525</v>
+        <v>4.240951783453523</v>
       </c>
       <c r="F2" t="n">
-        <v>3.288212841558488</v>
+        <v>3.288212841558456</v>
       </c>
       <c r="G2" t="n">
-        <v>6.297699174291311</v>
+        <v>6.297699174291366</v>
       </c>
       <c r="H2" t="n">
-        <v>3.256980980456433</v>
+        <v>3.256980980456419</v>
       </c>
       <c r="I2" t="n">
-        <v>3.690431323484957</v>
+        <v>3.69043132348494</v>
       </c>
       <c r="J2" t="n">
-        <v>5.636067793629295</v>
+        <v>5.636067793629266</v>
       </c>
       <c r="K2" t="n">
-        <v>4.095788601684951</v>
+        <v>4.095788601684935</v>
       </c>
       <c r="L2" t="n">
         <v>3.739583637316328</v>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.017073987424368</v>
+        <v>5.017073987424378</v>
       </c>
       <c r="C3" t="n">
-        <v>4.482402260593832</v>
+        <v>4.482402260593801</v>
       </c>
       <c r="D3" t="n">
-        <v>3.852386616709065</v>
+        <v>3.852386616709071</v>
       </c>
       <c r="E3" t="n">
-        <v>4.828442447007958</v>
+        <v>4.828442447007942</v>
       </c>
       <c r="F3" t="n">
-        <v>3.875703505112901</v>
+        <v>3.875703505112862</v>
       </c>
       <c r="G3" t="n">
-        <v>7.276824812490376</v>
+        <v>7.276824812490137</v>
       </c>
       <c r="H3" t="n">
-        <v>3.780381230449861</v>
+        <v>3.780381230449851</v>
       </c>
       <c r="I3" t="n">
-        <v>4.274587792296445</v>
+        <v>4.274587792296416</v>
       </c>
       <c r="J3" t="n">
-        <v>6.27701083008224</v>
+        <v>6.277010830082216</v>
       </c>
       <c r="K3" t="n">
-        <v>4.687725750594431</v>
+        <v>4.687725750594433</v>
       </c>
       <c r="L3" t="n">
-        <v>4.334404630294944</v>
+        <v>4.334404630294943</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.442574373758704</v>
+        <v>3.316765672473941</v>
       </c>
       <c r="C4" t="n">
-        <v>6.862972631827239</v>
+        <v>2.723957303103706</v>
       </c>
       <c r="D4" t="n">
-        <v>7.840632984091997</v>
+        <v>2.714824282807205</v>
       </c>
       <c r="E4" t="n">
-        <v>7.272181189043327</v>
+        <v>2.795984097009836</v>
       </c>
       <c r="F4" t="n">
-        <v>7.272181189043323</v>
+        <v>2.795984097009841</v>
       </c>
       <c r="G4" t="n">
-        <v>9.600331976970061</v>
+        <v>4.482880024625511</v>
       </c>
       <c r="H4" t="n">
-        <v>7.803719372123224</v>
+        <v>2.677910670838431</v>
       </c>
       <c r="I4" t="n">
-        <v>7.998412799400366</v>
+        <v>2.92346440786836</v>
       </c>
       <c r="J4" t="n">
-        <v>8.272087123970522</v>
+        <v>3.146278422685781</v>
       </c>
       <c r="K4" t="n">
-        <v>8.078142137263724</v>
+        <v>2.952333435979058</v>
       </c>
       <c r="L4" t="n">
-        <v>8.090698788047826</v>
+        <v>2.964890086763025</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114.9591223983658</v>
+        <v>22.06367802322272</v>
       </c>
       <c r="C5" t="n">
-        <v>80.77807712401636</v>
+        <v>15.73301562323807</v>
       </c>
       <c r="D5" t="n">
-        <v>61.84519698559387</v>
+        <v>12.21962749556873</v>
       </c>
       <c r="E5" t="n">
-        <v>80.77808451264063</v>
+        <v>15.73302301186244</v>
       </c>
       <c r="F5" t="n">
-        <v>80.77808451264055</v>
+        <v>15.73302301186244</v>
       </c>
       <c r="G5" t="n">
-        <v>219.0685440437867</v>
+        <v>41.34928514862018</v>
       </c>
       <c r="H5" t="n">
-        <v>66.31444439701259</v>
+        <v>12.97579821941876</v>
       </c>
       <c r="I5" t="n">
-        <v>80.77767619726312</v>
+        <v>15.7326146964844</v>
       </c>
       <c r="J5" t="n">
-        <v>109.2690189040568</v>
+        <v>20.92173831966267</v>
       </c>
       <c r="K5" t="n">
-        <v>79.4346935138105</v>
+        <v>15.51108641020025</v>
       </c>
       <c r="L5" t="n">
-        <v>111.9851526803822</v>
+        <v>19.0394395728588</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.18937070781282</v>
+        <v>6.440201810342785</v>
       </c>
       <c r="C6" t="n">
-        <v>11.7274260383627</v>
+        <v>3.580101098014877</v>
       </c>
       <c r="D6" t="n">
-        <v>11.94385942355003</v>
+        <v>5.965579810861772</v>
       </c>
       <c r="E6" t="n">
-        <v>11.37174245241543</v>
+        <v>3.517506875453698</v>
       </c>
       <c r="F6" t="n">
-        <v>12.07420554628512</v>
+        <v>3.641140379304874</v>
       </c>
       <c r="G6" t="n">
-        <v>27.34712831102434</v>
+        <v>5.208268159239825</v>
       </c>
       <c r="H6" t="n">
-        <v>28.56874631924995</v>
+        <v>6.332555393729587</v>
       </c>
       <c r="I6" t="n">
-        <v>12.11993631385962</v>
+        <v>3.648852542482554</v>
       </c>
       <c r="J6" t="n">
-        <v>26.65044503452849</v>
+        <v>6.380869397416817</v>
       </c>
       <c r="K6" t="n">
-        <v>12.00902125216531</v>
+        <v>3.644168156452832</v>
       </c>
       <c r="L6" t="n">
-        <v>12.10442713442911</v>
+        <v>3.671306271898399</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.47656645980018</v>
+        <v>4.202748274816399</v>
       </c>
       <c r="C7" t="n">
-        <v>13.03280581219513</v>
+        <v>3.809847936964471</v>
       </c>
       <c r="D7" t="n">
-        <v>12.87462107475021</v>
+        <v>3.60080618196223</v>
       </c>
       <c r="E7" t="n">
-        <v>12.95584342586002</v>
+        <v>3.796308645269234</v>
       </c>
       <c r="F7" t="n">
-        <v>12.95584342585991</v>
+        <v>3.796308645269234</v>
       </c>
       <c r="G7" t="n">
-        <v>14.63432406301171</v>
+        <v>5.368862626968119</v>
       </c>
       <c r="H7" t="n">
-        <v>12.83771145816466</v>
+        <v>3.563893273180869</v>
       </c>
       <c r="I7" t="n">
-        <v>13.03240488544182</v>
+        <v>3.809447010210799</v>
       </c>
       <c r="J7" t="n">
-        <v>13.30607921001201</v>
+        <v>4.03226102502822</v>
       </c>
       <c r="K7" t="n">
-        <v>13.11213422330523</v>
+        <v>3.838316038321524</v>
       </c>
       <c r="L7" t="n">
-        <v>13.12469087408929</v>
+        <v>3.850872689105516</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.72824819700104</v>
+        <v>6.183044249833261</v>
       </c>
       <c r="C8" t="n">
-        <v>36.53007989803076</v>
+        <v>7.945368153662884</v>
       </c>
       <c r="D8" t="n">
-        <v>38.99700568990205</v>
+        <v>8.198345849316702</v>
       </c>
       <c r="E8" t="n">
-        <v>33.16909728582632</v>
+        <v>7.353841305346389</v>
       </c>
       <c r="F8" t="n">
-        <v>24.62900284783272</v>
+        <v>5.850784692404035</v>
       </c>
       <c r="G8" t="n">
-        <v>38.20274796221192</v>
+        <v>9.516905210750659</v>
       </c>
       <c r="H8" t="n">
-        <v>36.40613535726393</v>
+        <v>7.711935856945814</v>
       </c>
       <c r="I8" t="n">
-        <v>36.60082878464218</v>
+        <v>7.957489593993431</v>
       </c>
       <c r="J8" t="n">
-        <v>36.87692366033414</v>
+        <v>8.180729625806062</v>
       </c>
       <c r="K8" t="n">
-        <v>24.13502615543926</v>
+        <v>5.778345007864784</v>
       </c>
       <c r="L8" t="n">
-        <v>49.55898183093569</v>
+        <v>10.26330786276411</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>458.2905585163019</v>
+        <v>82.49001045255318</v>
       </c>
       <c r="C9" t="n">
-        <v>583.1115524434288</v>
+        <v>104.1437068003922</v>
       </c>
       <c r="D9" t="n">
-        <v>582.9533809560879</v>
+        <v>103.9346673774082</v>
       </c>
       <c r="E9" t="n">
-        <v>727.6644388702501</v>
+        <v>129.5850207618824</v>
       </c>
       <c r="F9" t="n">
-        <v>583.1115597798646</v>
+        <v>104.143714179831</v>
       </c>
       <c r="G9" t="n">
-        <v>584.7130706942455</v>
+        <v>105.7027214903957</v>
       </c>
       <c r="H9" t="n">
-        <v>582.916458089398</v>
+        <v>103.8977521366085</v>
       </c>
       <c r="I9" t="n">
-        <v>583.1111515166759</v>
+        <v>104.1433058736384</v>
       </c>
       <c r="J9" t="n">
-        <v>583.3848258412451</v>
+        <v>104.366119888456</v>
       </c>
       <c r="K9" t="n">
-        <v>510.6119939937733</v>
+        <v>91.39829088347101</v>
       </c>
       <c r="L9" t="n">
-        <v>583.2034375053228</v>
+        <v>104.1847315525333</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.135273322760252</v>
+        <v>1.135273322760242</v>
       </c>
       <c r="C2" t="n">
-        <v>1.069410793600631</v>
+        <v>1.069410793600672</v>
       </c>
       <c r="D2" t="n">
         <v>3.515181072680023</v>
       </c>
       <c r="E2" t="n">
-        <v>2.050830099395216</v>
+        <v>2.050830099395229</v>
       </c>
       <c r="F2" t="n">
-        <v>2.050830099395216</v>
+        <v>2.050830099395229</v>
       </c>
       <c r="G2" t="n">
-        <v>2.596383890047947</v>
+        <v>2.59638389004792</v>
       </c>
       <c r="H2" t="n">
-        <v>2.67440415264533</v>
+        <v>2.674404152645331</v>
       </c>
       <c r="I2" t="n">
-        <v>2.324609379172305</v>
+        <v>2.324609379172295</v>
       </c>
       <c r="J2" t="n">
-        <v>2.099222238570033</v>
+        <v>2.099222238570027</v>
       </c>
       <c r="K2" t="n">
-        <v>2.554713496395347</v>
+        <v>2.554713496395355</v>
       </c>
       <c r="L2" t="n">
-        <v>2.414926519461586</v>
+        <v>2.414926519461575</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.278456205216318</v>
+        <v>1.27845620521633</v>
       </c>
       <c r="C3" t="n">
-        <v>1.27399365331865</v>
+        <v>1.273993653318786</v>
       </c>
       <c r="D3" t="n">
-        <v>4.015843114029267</v>
+        <v>4.015843114029272</v>
       </c>
       <c r="E3" t="n">
-        <v>2.372661237664757</v>
+        <v>2.372661237664767</v>
       </c>
       <c r="F3" t="n">
-        <v>2.372661237664757</v>
+        <v>2.372661237664767</v>
       </c>
       <c r="G3" t="n">
-        <v>2.959036025739354</v>
+        <v>2.959036025739372</v>
       </c>
       <c r="H3" t="n">
-        <v>3.049048526427707</v>
+        <v>3.04904852642773</v>
       </c>
       <c r="I3" t="n">
-        <v>2.646420224118342</v>
+        <v>2.646420224118372</v>
       </c>
       <c r="J3" t="n">
-        <v>2.373966181118213</v>
+        <v>2.373966181118209</v>
       </c>
       <c r="K3" t="n">
-        <v>2.90431789216288</v>
+        <v>2.904317892162861</v>
       </c>
       <c r="L3" t="n">
-        <v>2.750254356121345</v>
+        <v>2.750254356121314</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.263378559489093</v>
+        <v>0.8324032894806326</v>
       </c>
       <c r="C4" t="n">
-        <v>1.854554026139699</v>
+        <v>0.9617375341531834</v>
       </c>
       <c r="D4" t="n">
-        <v>3.678132871570888</v>
+        <v>2.247157601562106</v>
       </c>
       <c r="E4" t="n">
-        <v>2.61429085787245</v>
+        <v>1.476744819943526</v>
       </c>
       <c r="F4" t="n">
-        <v>2.614290857872488</v>
+        <v>1.476744819943418</v>
       </c>
       <c r="G4" t="n">
-        <v>3.125899654439886</v>
+        <v>1.699907297668382</v>
       </c>
       <c r="H4" t="n">
-        <v>3.178360210807029</v>
+        <v>1.747384940798588</v>
       </c>
       <c r="I4" t="n">
-        <v>2.932642685448353</v>
+        <v>1.53272742100107</v>
       </c>
       <c r="J4" t="n">
-        <v>2.784042694549709</v>
+        <v>1.353067424541257</v>
       </c>
       <c r="K4" t="n">
-        <v>3.080309333769656</v>
+        <v>1.649334063761252</v>
       </c>
       <c r="L4" t="n">
-        <v>3.024232530426123</v>
+        <v>1.593257260417049</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-15.30626594777229</v>
+        <v>-2.259854127041767</v>
       </c>
       <c r="C5" t="n">
-        <v>8.01252022769636</v>
+        <v>2.045539579754586</v>
       </c>
       <c r="D5" t="n">
-        <v>121.5337671786346</v>
+        <v>22.98974912720954</v>
       </c>
       <c r="E5" t="n">
-        <v>53.37441219202181</v>
+        <v>10.41052612634508</v>
       </c>
       <c r="F5" t="n">
-        <v>53.37441219202181</v>
+        <v>10.41052612634508</v>
       </c>
       <c r="G5" t="n">
-        <v>70.54011520699198</v>
+        <v>13.56480917062638</v>
       </c>
       <c r="H5" t="n">
-        <v>82.30835162460345</v>
+        <v>15.67426335416243</v>
       </c>
       <c r="I5" t="n">
-        <v>53.37435476448258</v>
+        <v>10.41046869880655</v>
       </c>
       <c r="J5" t="n">
-        <v>36.49773586136469</v>
+        <v>7.286677389748855</v>
       </c>
       <c r="K5" t="n">
-        <v>63.81721439944258</v>
+        <v>12.33902929739644</v>
       </c>
       <c r="L5" t="n">
-        <v>66.63382510398067</v>
+        <v>12.78854549269991</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.26433280929745</v>
+        <v>1.134965539258544</v>
       </c>
       <c r="C6" t="n">
-        <v>4.038445016567814</v>
+        <v>1.346102346385798</v>
       </c>
       <c r="D6" t="n">
-        <v>5.501218598738266</v>
+        <v>2.568016508279712</v>
       </c>
       <c r="E6" t="n">
-        <v>4.559921093309734</v>
+        <v>1.819175739524676</v>
       </c>
       <c r="F6" t="n">
-        <v>4.676877234236985</v>
+        <v>1.83976002021636</v>
       </c>
       <c r="G6" t="n">
-        <v>15.12685390424844</v>
+        <v>3.812075234189672</v>
       </c>
       <c r="H6" t="n">
-        <v>18.14358998084623</v>
+        <v>4.38126536605352</v>
       </c>
       <c r="I6" t="n">
-        <v>14.93359693525642</v>
+        <v>3.644895357522372</v>
       </c>
       <c r="J6" t="n">
-        <v>15.0510058617868</v>
+        <v>3.512052930276226</v>
       </c>
       <c r="K6" t="n">
-        <v>4.728651227104384</v>
+        <v>1.93944223541615</v>
       </c>
       <c r="L6" t="n">
-        <v>4.766393768332513</v>
+        <v>1.89987763662731</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.570068570042991</v>
+        <v>1.414380728184639</v>
       </c>
       <c r="C7" t="n">
-        <v>5.806269086011646</v>
+        <v>1.657239380921979</v>
       </c>
       <c r="D7" t="n">
-        <v>6.984816814419862</v>
+        <v>2.829133972350108</v>
       </c>
       <c r="E7" t="n">
-        <v>6.258932248449723</v>
+        <v>2.118201701209035</v>
       </c>
       <c r="F7" t="n">
-        <v>6.258932248449723</v>
+        <v>2.118201701209035</v>
       </c>
       <c r="G7" t="n">
-        <v>6.43258966499389</v>
+        <v>2.281884736372377</v>
       </c>
       <c r="H7" t="n">
-        <v>6.485050221360861</v>
+        <v>2.329362379502576</v>
       </c>
       <c r="I7" t="n">
-        <v>6.239332696001806</v>
+        <v>2.114704859705098</v>
       </c>
       <c r="J7" t="n">
-        <v>6.090732705103592</v>
+        <v>1.935044863245238</v>
       </c>
       <c r="K7" t="n">
-        <v>6.386999344323604</v>
+        <v>2.231311502465244</v>
       </c>
       <c r="L7" t="n">
-        <v>6.330922540979484</v>
+        <v>2.175234699121095</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.82482990901047</v>
+        <v>3.043218715016782</v>
       </c>
       <c r="C8" t="n">
-        <v>23.29883438624054</v>
+        <v>4.735930857110525</v>
       </c>
       <c r="D8" t="n">
-        <v>26.16103327751324</v>
+        <v>6.204148051566709</v>
       </c>
       <c r="E8" t="n">
-        <v>21.48239225177672</v>
+        <v>4.797530647276296</v>
       </c>
       <c r="F8" t="n">
-        <v>15.76629488854165</v>
+        <v>3.79149751679814</v>
       </c>
       <c r="G8" t="n">
-        <v>23.9048484358479</v>
+        <v>5.357002263379666</v>
       </c>
       <c r="H8" t="n">
-        <v>23.95730899221984</v>
+        <v>5.404479906510815</v>
       </c>
       <c r="I8" t="n">
-        <v>23.71159146685494</v>
+        <v>5.189822386712216</v>
       </c>
       <c r="J8" t="n">
-        <v>23.56460644844492</v>
+        <v>5.010446625408855</v>
       </c>
       <c r="K8" t="n">
-        <v>15.4891164494438</v>
+        <v>3.833284104285865</v>
       </c>
       <c r="L8" t="n">
-        <v>32.38704451474781</v>
+        <v>6.761112141655221</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>473.2355620022018</v>
+        <v>83.72350712624402</v>
       </c>
       <c r="C9" t="n">
-        <v>603.8242703165752</v>
+        <v>106.9084070271864</v>
       </c>
       <c r="D9" t="n">
-        <v>605.0028264873283</v>
+        <v>108.0803031044676</v>
       </c>
       <c r="E9" t="n">
-        <v>754.6814231031852</v>
+        <v>133.8405593778909</v>
       </c>
       <c r="F9" t="n">
-        <v>604.2573909723226</v>
+        <v>107.3659298663149</v>
       </c>
       <c r="G9" t="n">
-        <v>604.4505908955573</v>
+        <v>107.533052382637</v>
       </c>
       <c r="H9" t="n">
-        <v>604.5030514519237</v>
+        <v>107.5805300257672</v>
       </c>
       <c r="I9" t="n">
-        <v>604.2573339265638</v>
+        <v>107.3658725059697</v>
       </c>
       <c r="J9" t="n">
-        <v>604.1087339356653</v>
+        <v>107.1862125095099</v>
       </c>
       <c r="K9" t="n">
-        <v>440.2679248009032</v>
+        <v>94.1897705249513</v>
       </c>
       <c r="L9" t="n">
-        <v>604.3489237715423</v>
+        <v>107.4264023453857</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.652795863624168</v>
+        <v>1.652795863624169</v>
       </c>
       <c r="C2" t="n">
-        <v>1.198197248071772</v>
+        <v>1.198197248071753</v>
       </c>
       <c r="D2" t="n">
         <v>4.133550328590724</v>
       </c>
       <c r="E2" t="n">
-        <v>2.654449382362736</v>
+        <v>2.654449382362734</v>
       </c>
       <c r="F2" t="n">
-        <v>2.654449382362736</v>
+        <v>2.654449382362734</v>
       </c>
       <c r="G2" t="n">
-        <v>3.064541002536505</v>
+        <v>3.064541002536497</v>
       </c>
       <c r="H2" t="n">
-        <v>2.349230174384084</v>
+        <v>2.349230174384083</v>
       </c>
       <c r="I2" t="n">
-        <v>2.909981911591219</v>
+        <v>2.90998191159124</v>
       </c>
       <c r="J2" t="n">
-        <v>2.112497141100961</v>
+        <v>2.112497141100963</v>
       </c>
       <c r="K2" t="n">
-        <v>3.369460885125011</v>
+        <v>3.369460885125013</v>
       </c>
       <c r="L2" t="n">
-        <v>3.071309827723725</v>
+        <v>3.071309827723724</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.884763022105659</v>
+        <v>1.88476302210566</v>
       </c>
       <c r="C3" t="n">
-        <v>1.436918581778164</v>
+        <v>1.436918581778065</v>
       </c>
       <c r="D3" t="n">
-        <v>4.738144543556473</v>
+        <v>4.738144543556478</v>
       </c>
       <c r="E3" t="n">
-        <v>3.075275432277669</v>
+        <v>3.075275432277677</v>
       </c>
       <c r="F3" t="n">
-        <v>3.075275432277668</v>
+        <v>3.075275432277676</v>
       </c>
       <c r="G3" t="n">
-        <v>3.508562373979353</v>
+        <v>3.508562373979347</v>
       </c>
       <c r="H3" t="n">
-        <v>2.686152970367992</v>
+        <v>2.686152970367989</v>
       </c>
       <c r="I3" t="n">
-        <v>3.333590625199746</v>
+        <v>3.333590625199722</v>
       </c>
       <c r="J3" t="n">
-        <v>2.393101665193348</v>
+        <v>2.393101665193345</v>
       </c>
       <c r="K3" t="n">
-        <v>3.841286741275968</v>
+        <v>3.841286741275976</v>
       </c>
       <c r="L3" t="n">
-        <v>3.516265145779677</v>
+        <v>3.516265145779678</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.001022182042437</v>
+        <v>1.192960371537017</v>
       </c>
       <c r="C4" t="n">
-        <v>2.44001357346579</v>
+        <v>1.117275055151871</v>
       </c>
       <c r="D4" t="n">
-        <v>4.475725592981423</v>
+        <v>2.667663782476006</v>
       </c>
       <c r="E4" t="n">
-        <v>3.79928130308248</v>
+        <v>1.949332339744931</v>
       </c>
       <c r="F4" t="n">
-        <v>3.799281303082484</v>
+        <v>1.94933233974493</v>
       </c>
       <c r="G4" t="n">
-        <v>3.834966875678819</v>
+        <v>2.031254113060786</v>
       </c>
       <c r="H4" t="n">
-        <v>3.415248744209192</v>
+        <v>1.607186933703795</v>
       </c>
       <c r="I4" t="n">
-        <v>3.715551149160549</v>
+        <v>1.934566168274934</v>
       </c>
       <c r="J4" t="n">
-        <v>3.19350871171682</v>
+        <v>1.385446901211479</v>
       </c>
       <c r="K4" t="n">
-        <v>3.950283470081799</v>
+        <v>2.142221659576314</v>
       </c>
       <c r="L4" t="n">
-        <v>3.844402562883406</v>
+        <v>2.036340752378061</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.112783330851871</v>
+        <v>2.268630327898877</v>
       </c>
       <c r="C5" t="n">
-        <v>10.69987833305101</v>
+        <v>2.571011244961896</v>
       </c>
       <c r="D5" t="n">
-        <v>143.5965824394484</v>
+        <v>27.15293445477823</v>
       </c>
       <c r="E5" t="n">
-        <v>77.47417767613567</v>
+        <v>14.91611403114027</v>
       </c>
       <c r="F5" t="n">
-        <v>77.47417767613567</v>
+        <v>14.91611403114027</v>
       </c>
       <c r="G5" t="n">
-        <v>87.655533899516</v>
+        <v>16.78367382931854</v>
       </c>
       <c r="H5" t="n">
-        <v>51.77339653530971</v>
+        <v>10.11822089881957</v>
       </c>
       <c r="I5" t="n">
-        <v>77.47414167557827</v>
+        <v>14.91607803058254</v>
       </c>
       <c r="J5" t="n">
-        <v>26.93317374808301</v>
+        <v>5.563627924972006</v>
       </c>
       <c r="K5" t="n">
-        <v>95.69344731231445</v>
+        <v>18.28901840831616</v>
       </c>
       <c r="L5" t="n">
-        <v>98.30110353765862</v>
+        <v>18.66072003385757</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.88957320541182</v>
+        <v>3.285345340312245</v>
       </c>
       <c r="C6" t="n">
-        <v>4.621244210383753</v>
+        <v>1.501171645169243</v>
       </c>
       <c r="D6" t="n">
-        <v>6.372365740499934</v>
+        <v>4.816557944208545</v>
       </c>
       <c r="E6" t="n">
-        <v>5.470782111328277</v>
+        <v>2.243516480402123</v>
       </c>
       <c r="F6" t="n">
-        <v>5.566555936908122</v>
+        <v>2.260372673612833</v>
       </c>
       <c r="G6" t="n">
-        <v>5.636637911821695</v>
+        <v>2.348348213703742</v>
       </c>
       <c r="H6" t="n">
-        <v>18.08511436935232</v>
+        <v>4.189083269738719</v>
       </c>
       <c r="I6" t="n">
-        <v>5.51722218530361</v>
+        <v>2.251660268917894</v>
       </c>
       <c r="J6" t="n">
-        <v>5.105976666966154</v>
+        <v>1.722041259511489</v>
       </c>
       <c r="K6" t="n">
-        <v>5.69459902851569</v>
+        <v>2.449221196197191</v>
       </c>
       <c r="L6" t="n">
-        <v>5.663281402771005</v>
+        <v>2.356463426463673</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.405836660667836</v>
+        <v>1.79220771652802</v>
       </c>
       <c r="C7" t="n">
-        <v>6.425520421853173</v>
+        <v>1.818724256667179</v>
       </c>
       <c r="D7" t="n">
-        <v>7.880518899005962</v>
+        <v>3.26690740108927</v>
       </c>
       <c r="E7" t="n">
-        <v>7.247554220822503</v>
+        <v>2.556228369978639</v>
       </c>
       <c r="F7" t="n">
-        <v>7.247554220822503</v>
+        <v>2.556228369978639</v>
       </c>
       <c r="G7" t="n">
-        <v>7.239781354304198</v>
+        <v>2.630501458051769</v>
       </c>
       <c r="H7" t="n">
-        <v>6.820063222834692</v>
+        <v>2.206434278694802</v>
       </c>
       <c r="I7" t="n">
-        <v>7.120365627786069</v>
+        <v>2.533813513265928</v>
       </c>
       <c r="J7" t="n">
-        <v>6.598323190342332</v>
+        <v>1.984694246202471</v>
       </c>
       <c r="K7" t="n">
-        <v>7.355097948707212</v>
+        <v>2.741469004567317</v>
       </c>
       <c r="L7" t="n">
-        <v>7.249217041508924</v>
+        <v>2.63558809736906</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.39222513945987</v>
+        <v>3.373812080225332</v>
       </c>
       <c r="C8" t="n">
-        <v>23.77946219090181</v>
+        <v>4.873017991503953</v>
       </c>
       <c r="D8" t="n">
-        <v>26.82081595004345</v>
+        <v>6.600399664008958</v>
       </c>
       <c r="E8" t="n">
-        <v>22.2065505913782</v>
+        <v>5.189011716930445</v>
       </c>
       <c r="F8" t="n">
-        <v>16.44398906310233</v>
+        <v>4.174800893449484</v>
       </c>
       <c r="G8" t="n">
-        <v>24.47053451011957</v>
+        <v>5.663113997042776</v>
       </c>
       <c r="H8" t="n">
-        <v>24.0508163786373</v>
+        <v>5.239046817683507</v>
       </c>
       <c r="I8" t="n">
-        <v>24.35111878360161</v>
+        <v>5.566426052256935</v>
       </c>
       <c r="J8" t="n">
-        <v>23.83069659579759</v>
+        <v>5.01759194912851</v>
       </c>
       <c r="K8" t="n">
-        <v>16.18834312095937</v>
+        <v>4.296120146459637</v>
       </c>
       <c r="L8" t="n">
-        <v>33.09189848158829</v>
+        <v>7.183900006177511</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>449.290780540753</v>
+        <v>79.73995741705512</v>
       </c>
       <c r="C9" t="n">
-        <v>572.8956983679172</v>
+        <v>101.5174750349464</v>
       </c>
       <c r="D9" t="n">
-        <v>574.3507212828837</v>
+        <v>102.9656624804237</v>
       </c>
       <c r="E9" t="n">
-        <v>716.2053224645091</v>
+        <v>127.3327949047525</v>
       </c>
       <c r="F9" t="n">
-        <v>573.5905797796644</v>
+        <v>102.232600328228</v>
       </c>
       <c r="G9" t="n">
-        <v>573.7099593003692</v>
+        <v>102.3292522363311</v>
       </c>
       <c r="H9" t="n">
-        <v>573.2902411688991</v>
+        <v>101.9051850569741</v>
       </c>
       <c r="I9" t="n">
-        <v>573.5905435738504</v>
+        <v>102.2325642915453</v>
       </c>
       <c r="J9" t="n">
-        <v>573.0685011364062</v>
+        <v>101.6834450244817</v>
       </c>
       <c r="K9" t="n">
-        <v>502.2195072935991</v>
+        <v>89.83760457732893</v>
       </c>
       <c r="L9" t="n">
-        <v>573.7193949875731</v>
+        <v>102.3343388756483</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.856951323175141</v>
+        <v>1.856951323175122</v>
       </c>
       <c r="C2" t="n">
-        <v>1.244393819063515</v>
+        <v>1.244393819063542</v>
       </c>
       <c r="D2" t="n">
-        <v>4.363666189926144</v>
+        <v>4.363666189926159</v>
       </c>
       <c r="E2" t="n">
-        <v>2.687761089547865</v>
+        <v>2.687761089547854</v>
       </c>
       <c r="F2" t="n">
-        <v>2.687761089547865</v>
+        <v>2.687761089547854</v>
       </c>
       <c r="G2" t="n">
-        <v>3.287372029795327</v>
+        <v>3.287372029795363</v>
       </c>
       <c r="H2" t="n">
-        <v>2.129123429097747</v>
+        <v>2.129123429097839</v>
       </c>
       <c r="I2" t="n">
-        <v>2.928122040832269</v>
+        <v>2.928122040832299</v>
       </c>
       <c r="J2" t="n">
-        <v>2.014131656183886</v>
+        <v>2.014131656183986</v>
       </c>
       <c r="K2" t="n">
-        <v>3.768348862195495</v>
+        <v>3.768348862195563</v>
       </c>
       <c r="L2" t="n">
-        <v>3.679551028913869</v>
+        <v>3.679551028913951</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.127792632210887</v>
+        <v>2.127792632210941</v>
       </c>
       <c r="C3" t="n">
-        <v>1.497691647368888</v>
+        <v>1.497691647368939</v>
       </c>
       <c r="D3" t="n">
-        <v>5.011033993394954</v>
+        <v>5.011033993394945</v>
       </c>
       <c r="E3" t="n">
-        <v>3.119521956983841</v>
+        <v>3.119521956983844</v>
       </c>
       <c r="F3" t="n">
-        <v>3.119521956983861</v>
+        <v>3.119521956983843</v>
       </c>
       <c r="G3" t="n">
-        <v>3.773072755580922</v>
+        <v>3.773072755580917</v>
       </c>
       <c r="H3" t="n">
-        <v>2.441228248980884</v>
+        <v>2.441228248980913</v>
       </c>
       <c r="I3" t="n">
-        <v>3.363845946667979</v>
+        <v>3.363845946667956</v>
       </c>
       <c r="J3" t="n">
-        <v>2.283265550370486</v>
+        <v>2.283265550370507</v>
       </c>
       <c r="K3" t="n">
-        <v>4.301187578428065</v>
+        <v>4.301187578428032</v>
       </c>
       <c r="L3" t="n">
-        <v>4.224058360722313</v>
+        <v>4.224058360722323</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.195392023680971</v>
+        <v>1.324602278145903</v>
       </c>
       <c r="C4" t="n">
-        <v>2.553134313945243</v>
+        <v>1.155368637418124</v>
       </c>
       <c r="D4" t="n">
-        <v>4.685527793445321</v>
+        <v>2.81473804791023</v>
       </c>
       <c r="E4" t="n">
-        <v>4.041563118629711</v>
+        <v>1.998295180520532</v>
       </c>
       <c r="F4" t="n">
-        <v>4.041563118629757</v>
+        <v>1.998295180520531</v>
       </c>
       <c r="G4" t="n">
-        <v>4.04022466093722</v>
+        <v>2.173960208675787</v>
       </c>
       <c r="H4" t="n">
-        <v>3.357517555390614</v>
+        <v>1.486727809855422</v>
       </c>
       <c r="I4" t="n">
-        <v>3.798053051593159</v>
+        <v>1.955384882234544</v>
       </c>
       <c r="J4" t="n">
-        <v>3.188634783543921</v>
+        <v>1.317845038008939</v>
       </c>
       <c r="K4" t="n">
-        <v>4.232269146065128</v>
+        <v>2.361479400530402</v>
       </c>
       <c r="L4" t="n">
-        <v>4.278904370257329</v>
+        <v>2.408114624722373</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.27460560853481</v>
+        <v>4.154543853745818</v>
       </c>
       <c r="C5" t="n">
-        <v>11.75775425568313</v>
+        <v>2.775381738385787</v>
       </c>
       <c r="D5" t="n">
-        <v>154.8824746147395</v>
+        <v>29.24940054521898</v>
       </c>
       <c r="E5" t="n">
-        <v>77.17631955789773</v>
+        <v>14.87001224408497</v>
       </c>
       <c r="F5" t="n">
-        <v>77.17631955789773</v>
+        <v>14.87001224408497</v>
       </c>
       <c r="G5" t="n">
-        <v>98.86864230699859</v>
+        <v>18.86376162394722</v>
       </c>
       <c r="H5" t="n">
-        <v>36.71004546017861</v>
+        <v>7.356772689290688</v>
       </c>
       <c r="I5" t="n">
-        <v>77.17625581187973</v>
+        <v>14.86994849806583</v>
       </c>
       <c r="J5" t="n">
-        <v>18.04486820720103</v>
+        <v>3.932542106404683</v>
       </c>
       <c r="K5" t="n">
-        <v>113.6874469347441</v>
+        <v>21.62559058695337</v>
       </c>
       <c r="L5" t="n">
-        <v>135.1865351478682</v>
+        <v>25.44785751673868</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.34005058761501</v>
+        <v>1.658809398744888</v>
       </c>
       <c r="C6" t="n">
-        <v>4.799749792581996</v>
+        <v>1.550772959517169</v>
       </c>
       <c r="D6" t="n">
-        <v>6.681340182521704</v>
+        <v>3.166001026484225</v>
       </c>
       <c r="E6" t="n">
-        <v>5.64514195315641</v>
+        <v>2.28052505386795</v>
       </c>
       <c r="F6" t="n">
-        <v>5.752525840968296</v>
+        <v>2.29942461802043</v>
       </c>
       <c r="G6" t="n">
-        <v>5.939128765539112</v>
+        <v>4.311420104346148</v>
       </c>
       <c r="H6" t="n">
-        <v>18.26424787156435</v>
+        <v>4.110312331285886</v>
       </c>
       <c r="I6" t="n">
-        <v>5.696957156195144</v>
+        <v>4.092844777904905</v>
       </c>
       <c r="J6" t="n">
-        <v>5.197947818781307</v>
+        <v>3.511099485503341</v>
       </c>
       <c r="K6" t="n">
-        <v>6.083744092069781</v>
+        <v>2.687338989261476</v>
       </c>
       <c r="L6" t="n">
-        <v>6.198923818871947</v>
+        <v>2.746038045847436</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.699311269655553</v>
+        <v>1.94129206209582</v>
       </c>
       <c r="C7" t="n">
-        <v>6.622244835454468</v>
+        <v>1.871532085323163</v>
       </c>
       <c r="D7" t="n">
-        <v>8.189437054750513</v>
+        <v>3.431426074558391</v>
       </c>
       <c r="E7" t="n">
-        <v>7.482155458253137</v>
+        <v>2.60383942901306</v>
       </c>
       <c r="F7" t="n">
-        <v>7.482155458253137</v>
+        <v>2.60383942901306</v>
       </c>
       <c r="G7" t="n">
-        <v>7.544143906911678</v>
+        <v>2.790649992625703</v>
       </c>
       <c r="H7" t="n">
-        <v>6.86143680136441</v>
+        <v>2.10341759380534</v>
       </c>
       <c r="I7" t="n">
-        <v>7.301972297567516</v>
+        <v>2.572074666184458</v>
       </c>
       <c r="J7" t="n">
-        <v>6.692554029517653</v>
+        <v>1.934534821958856</v>
       </c>
       <c r="K7" t="n">
-        <v>7.736188392038672</v>
+        <v>2.978169184480315</v>
       </c>
       <c r="L7" t="n">
-        <v>7.782823616231744</v>
+        <v>3.02480440867229</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.72049456317616</v>
+        <v>3.529020313152241</v>
       </c>
       <c r="C8" t="n">
-        <v>24.1987787845605</v>
+        <v>4.965002043572122</v>
       </c>
       <c r="D8" t="n">
-        <v>27.33008759653617</v>
+        <v>6.800180551658864</v>
       </c>
       <c r="E8" t="n">
-        <v>22.56789833761317</v>
+        <v>5.258930161393745</v>
       </c>
       <c r="F8" t="n">
-        <v>16.69635584254651</v>
+        <v>4.225538687861384</v>
       </c>
       <c r="G8" t="n">
-        <v>24.94682607277443</v>
+        <v>5.853522037221199</v>
       </c>
       <c r="H8" t="n">
-        <v>24.26411896722141</v>
+        <v>5.166289638399775</v>
       </c>
       <c r="I8" t="n">
-        <v>24.70465446343061</v>
+        <v>5.634946710779946</v>
       </c>
       <c r="J8" t="n">
-        <v>24.09688339434853</v>
+        <v>4.99769677357131</v>
       </c>
       <c r="K8" t="n">
-        <v>16.6016810411872</v>
+        <v>4.538495882275444</v>
       </c>
       <c r="L8" t="n">
-        <v>33.94068219884641</v>
+        <v>7.628587494266807</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>449.211958640997</v>
+        <v>79.82351757743905</v>
       </c>
       <c r="C9" t="n">
-        <v>572.6672307141085</v>
+        <v>101.4954490601437</v>
       </c>
       <c r="D9" t="n">
-        <v>574.2344367158679</v>
+        <v>103.0553454750924</v>
       </c>
       <c r="E9" t="n">
-        <v>715.9007251215259</v>
+        <v>127.2855070141485</v>
       </c>
       <c r="F9" t="n">
-        <v>573.3470222721984</v>
+        <v>102.1960554486167</v>
       </c>
       <c r="G9" t="n">
-        <v>573.5891297855662</v>
+        <v>102.4145669674462</v>
       </c>
       <c r="H9" t="n">
-        <v>572.9064226800184</v>
+        <v>101.7273345686259</v>
       </c>
       <c r="I9" t="n">
-        <v>573.3469581762213</v>
+        <v>102.1959916410051</v>
       </c>
       <c r="J9" t="n">
-        <v>572.7375399081719</v>
+        <v>101.5584517967794</v>
       </c>
       <c r="K9" t="n">
-        <v>499.3021605829781</v>
+        <v>75.22541556038325</v>
       </c>
       <c r="L9" t="n">
-        <v>573.8278094948868</v>
+        <v>102.6487213834929</v>
       </c>
     </row>
   </sheetData>
@@ -2495,34 +2495,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.590296889110095</v>
+        <v>1.59029688911009</v>
       </c>
       <c r="C2" t="n">
         <v>1.142942341538099</v>
       </c>
       <c r="D2" t="n">
-        <v>3.980225427145683</v>
+        <v>3.980225427145679</v>
       </c>
       <c r="E2" t="n">
-        <v>2.65295878631161</v>
+        <v>2.652958786311602</v>
       </c>
       <c r="F2" t="n">
-        <v>2.652958786311612</v>
+        <v>2.652958786311602</v>
       </c>
       <c r="G2" t="n">
-        <v>3.13879070518234</v>
+        <v>3.138790705182336</v>
       </c>
       <c r="H2" t="n">
-        <v>2.616483997858228</v>
+        <v>2.616483997858225</v>
       </c>
       <c r="I2" t="n">
-        <v>2.92397450831882</v>
+        <v>2.923974508318814</v>
       </c>
       <c r="J2" t="n">
-        <v>2.24694497911419</v>
+        <v>2.246944979114185</v>
       </c>
       <c r="K2" t="n">
-        <v>3.083473136545652</v>
+        <v>3.083473136545641</v>
       </c>
       <c r="L2" t="n">
         <v>3.02498762391818</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.801970770290029</v>
+        <v>1.801970770290024</v>
       </c>
       <c r="C3" t="n">
-        <v>1.364141799873198</v>
+        <v>1.364141799873196</v>
       </c>
       <c r="D3" t="n">
-        <v>4.550883661236153</v>
+        <v>4.550883661236146</v>
       </c>
       <c r="E3" t="n">
-        <v>3.064977406067658</v>
+        <v>3.064977406067662</v>
       </c>
       <c r="F3" t="n">
-        <v>3.064977406067659</v>
+        <v>3.064977406067662</v>
       </c>
       <c r="G3" t="n">
-        <v>3.583059428300756</v>
+        <v>3.583059428300747</v>
       </c>
       <c r="H3" t="n">
         <v>2.982611404602017</v>
       </c>
       <c r="I3" t="n">
-        <v>3.339352284428495</v>
+        <v>3.339352284428496</v>
       </c>
       <c r="J3" t="n">
-        <v>2.541957692728484</v>
+        <v>2.541957692728483</v>
       </c>
       <c r="K3" t="n">
         <v>3.505956736787569</v>
       </c>
       <c r="L3" t="n">
-        <v>3.452090958136524</v>
+        <v>3.452090958136521</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.741759864156409</v>
+        <v>1.117417564538238</v>
       </c>
       <c r="C4" t="n">
-        <v>2.050793642137208</v>
+        <v>1.028123656193833</v>
       </c>
       <c r="D4" t="n">
-        <v>4.162471110155929</v>
+        <v>2.538128810537759</v>
       </c>
       <c r="E4" t="n">
-        <v>3.696592204961235</v>
+        <v>1.938802345707361</v>
       </c>
       <c r="F4" t="n">
-        <v>3.696592204961231</v>
+        <v>1.938802345707361</v>
       </c>
       <c r="G4" t="n">
-        <v>3.657017010746714</v>
+        <v>2.037006324069662</v>
       </c>
       <c r="H4" t="n">
-        <v>3.351962362250915</v>
+        <v>1.727620062632723</v>
       </c>
       <c r="I4" t="n">
-        <v>3.501686550469806</v>
+        <v>1.904456487081296</v>
       </c>
       <c r="J4" t="n">
-        <v>3.071580413458953</v>
+        <v>1.447238113840772</v>
       </c>
       <c r="K4" t="n">
-        <v>3.576057337595377</v>
+        <v>1.951715037977195</v>
       </c>
       <c r="L4" t="n">
-        <v>3.594784706031461</v>
+        <v>1.97044240641329</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.89193789078822</v>
+        <v>1.671848894221187</v>
       </c>
       <c r="C5" t="n">
-        <v>8.719405603662901</v>
+        <v>2.20179935506268</v>
       </c>
       <c r="D5" t="n">
-        <v>142.6865178780632</v>
+        <v>26.91836090958266</v>
       </c>
       <c r="E5" t="n">
-        <v>82.57287585797177</v>
+        <v>15.82102819341494</v>
       </c>
       <c r="F5" t="n">
-        <v>82.57287585797177</v>
+        <v>15.82102819341494</v>
       </c>
       <c r="G5" t="n">
-        <v>96.91526570948017</v>
+        <v>18.45045800610869</v>
       </c>
       <c r="H5" t="n">
-        <v>72.11718042575386</v>
+        <v>13.83029837622963</v>
       </c>
       <c r="I5" t="n">
-        <v>82.57282432445066</v>
+        <v>15.82097665989383</v>
       </c>
       <c r="J5" t="n">
-        <v>38.66762280272133</v>
+        <v>7.712141540403913</v>
       </c>
       <c r="K5" t="n">
-        <v>86.16857029686491</v>
+        <v>16.48799724004224</v>
       </c>
       <c r="L5" t="n">
-        <v>100.699234879711</v>
+        <v>19.06082554437485</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.14113546762618</v>
+        <v>1.446514514614828</v>
       </c>
       <c r="C6" t="n">
-        <v>4.399619129862493</v>
+        <v>1.441516939793472</v>
       </c>
       <c r="D6" t="n">
-        <v>6.116098033677746</v>
+        <v>2.881967147214477</v>
       </c>
       <c r="E6" t="n">
-        <v>5.34612080316912</v>
+        <v>2.229119377418843</v>
       </c>
       <c r="F6" t="n">
-        <v>5.430596869289322</v>
+        <v>2.243987164975432</v>
       </c>
       <c r="G6" t="n">
-        <v>5.526886055404881</v>
+        <v>2.366103274146258</v>
       </c>
       <c r="H6" t="n">
-        <v>18.72949317147818</v>
+        <v>4.434065470391559</v>
       </c>
       <c r="I6" t="n">
-        <v>15.90106215393956</v>
+        <v>2.233553437157892</v>
       </c>
       <c r="J6" t="n">
-        <v>15.77995114556196</v>
+        <v>3.683911350571258</v>
       </c>
       <c r="K6" t="n">
-        <v>5.36939779226621</v>
+        <v>2.267342956288998</v>
       </c>
       <c r="L6" t="n">
-        <v>5.488356033744682</v>
+        <v>2.303710958284963</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.352383638935543</v>
+        <v>1.752887345456004</v>
       </c>
       <c r="C7" t="n">
-        <v>6.383409913088341</v>
+        <v>1.790664115749326</v>
       </c>
       <c r="D7" t="n">
-        <v>7.773102635729361</v>
+        <v>3.173599955595309</v>
       </c>
       <c r="E7" t="n">
-        <v>7.274034468481646</v>
+        <v>2.568432180675241</v>
       </c>
       <c r="F7" t="n">
-        <v>7.274034468481646</v>
+        <v>2.568432180675241</v>
       </c>
       <c r="G7" t="n">
-        <v>7.267640785525836</v>
+        <v>2.672476104987432</v>
       </c>
       <c r="H7" t="n">
-        <v>6.962586137030037</v>
+        <v>2.363089843550488</v>
       </c>
       <c r="I7" t="n">
-        <v>7.112310325248941</v>
+        <v>2.539926267999069</v>
       </c>
       <c r="J7" t="n">
-        <v>6.682204188238095</v>
+        <v>2.082707894758542</v>
       </c>
       <c r="K7" t="n">
-        <v>7.186681112374504</v>
+        <v>2.587184818894959</v>
       </c>
       <c r="L7" t="n">
-        <v>7.205408480810598</v>
+        <v>2.605912187331059</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.7488999659375</v>
+        <v>3.406674210047124</v>
       </c>
       <c r="C8" t="n">
-        <v>24.51316792237781</v>
+        <v>4.98150150809442</v>
       </c>
       <c r="D8" t="n">
-        <v>27.52519183760924</v>
+        <v>6.649967636289174</v>
       </c>
       <c r="E8" t="n">
-        <v>22.87989231673529</v>
+        <v>5.315063147084983</v>
       </c>
       <c r="F8" t="n">
-        <v>16.877198978592</v>
+        <v>4.258589125296345</v>
       </c>
       <c r="G8" t="n">
-        <v>25.24122652184334</v>
+        <v>5.835827177438391</v>
       </c>
       <c r="H8" t="n">
-        <v>24.93617187334256</v>
+        <v>5.526440916000542</v>
       </c>
       <c r="I8" t="n">
-        <v>25.08589606156644</v>
+        <v>5.703277340450033</v>
       </c>
       <c r="J8" t="n">
-        <v>24.65747556219101</v>
+        <v>5.24635563943167</v>
       </c>
       <c r="K8" t="n">
-        <v>16.42387397156625</v>
+        <v>4.212930753303416</v>
       </c>
       <c r="L8" t="n">
-        <v>34.13846041636437</v>
+        <v>7.346129302303174</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>474.7109543640008</v>
+        <v>84.18399534640604</v>
       </c>
       <c r="C9" t="n">
-        <v>605.4034634374611</v>
+        <v>107.2181929647689</v>
       </c>
       <c r="D9" t="n">
-        <v>606.7931517475172</v>
+        <v>108.601128028</v>
       </c>
       <c r="E9" t="n">
-        <v>756.9129991668248</v>
+        <v>134.5048892526721</v>
       </c>
       <c r="F9" t="n">
-        <v>606.1324154524364</v>
+        <v>107.9675066627352</v>
       </c>
       <c r="G9" t="n">
-        <v>606.2876943098981</v>
+        <v>108.1000049540071</v>
       </c>
       <c r="H9" t="n">
-        <v>605.9826396614026</v>
+        <v>107.79061869257</v>
       </c>
       <c r="I9" t="n">
-        <v>606.1323638496222</v>
+        <v>107.9674551170186</v>
       </c>
       <c r="J9" t="n">
-        <v>605.7022577126112</v>
+        <v>107.5102367437784</v>
       </c>
       <c r="K9" t="n">
-        <v>441.6806039350475</v>
+        <v>79.05811482131959</v>
       </c>
       <c r="L9" t="n">
-        <v>606.2254620051833</v>
+        <v>108.0334410363507</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.18923324918383</v>
+        <v>2.189233249183841</v>
       </c>
       <c r="C2" t="n">
-        <v>1.249427815835126</v>
+        <v>1.249427815835127</v>
       </c>
       <c r="D2" t="n">
-        <v>4.565909060869354</v>
+        <v>4.565909060869372</v>
       </c>
       <c r="E2" t="n">
-        <v>2.860880447784611</v>
+        <v>2.860880447784606</v>
       </c>
       <c r="F2" t="n">
-        <v>2.860880447784611</v>
+        <v>2.860880447784606</v>
       </c>
       <c r="G2" t="n">
-        <v>3.53671071748293</v>
+        <v>3.536710717482925</v>
       </c>
       <c r="H2" t="n">
         <v>2.008096804884554</v>
       </c>
       <c r="I2" t="n">
-        <v>3.120497692492174</v>
+        <v>3.120497692492183</v>
       </c>
       <c r="J2" t="n">
-        <v>2.196058817122139</v>
+        <v>2.196058817122145</v>
       </c>
       <c r="K2" t="n">
-        <v>3.889994059584934</v>
+        <v>3.889994059584933</v>
       </c>
       <c r="L2" t="n">
-        <v>3.887355239152647</v>
+        <v>3.887355239152645</v>
       </c>
     </row>
     <row r="3">
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.502624541167228</v>
+        <v>2.502624541167224</v>
       </c>
       <c r="C3" t="n">
-        <v>1.499905066905403</v>
+        <v>1.499905066905402</v>
       </c>
       <c r="D3" t="n">
-        <v>5.236294051516782</v>
+        <v>5.236294051516784</v>
       </c>
       <c r="E3" t="n">
-        <v>3.314175153580205</v>
+        <v>3.314175153580204</v>
       </c>
       <c r="F3" t="n">
         <v>3.314175153580204</v>
       </c>
       <c r="G3" t="n">
-        <v>4.052502758827842</v>
+        <v>4.052502758827845</v>
       </c>
       <c r="H3" t="n">
-        <v>2.294654202419203</v>
+        <v>2.294654202419205</v>
       </c>
       <c r="I3" t="n">
-        <v>3.578135638360646</v>
+        <v>3.578135638360659</v>
       </c>
       <c r="J3" t="n">
-        <v>2.489563816074792</v>
+        <v>2.489563816074795</v>
       </c>
       <c r="K3" t="n">
-        <v>4.436259543377189</v>
+        <v>4.436259543377196</v>
       </c>
       <c r="L3" t="n">
         <v>4.455722115113137</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.367803074017556</v>
+        <v>1.507905842299222</v>
       </c>
       <c r="C4" t="n">
-        <v>2.415606065859189</v>
+        <v>1.136520743110266</v>
       </c>
       <c r="D4" t="n">
-        <v>4.78063613576761</v>
+        <v>2.920738904049283</v>
       </c>
       <c r="E4" t="n">
-        <v>4.205326594043112</v>
+        <v>2.111542064756824</v>
       </c>
       <c r="F4" t="n">
-        <v>4.205326594043373</v>
+        <v>2.111542064756824</v>
       </c>
       <c r="G4" t="n">
-        <v>4.163135961717407</v>
+        <v>2.307923474670417</v>
       </c>
       <c r="H4" t="n">
-        <v>3.260542687689659</v>
+        <v>1.40064545597133</v>
       </c>
       <c r="I4" t="n">
-        <v>3.885838822751656</v>
+        <v>2.055247034705892</v>
       </c>
       <c r="J4" t="n">
-        <v>3.289101370389097</v>
+        <v>1.429204138670765</v>
       </c>
       <c r="K4" t="n">
-        <v>4.289422583401452</v>
+        <v>2.429525351683126</v>
       </c>
       <c r="L4" t="n">
-        <v>4.37733975530698</v>
+        <v>2.517442523588649</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.18106518736299</v>
+        <v>7.283039942954838</v>
       </c>
       <c r="C5" t="n">
-        <v>11.66690761215196</v>
+        <v>2.764749806435064</v>
       </c>
       <c r="D5" t="n">
-        <v>164.1553248871078</v>
+        <v>30.97068397229363</v>
       </c>
       <c r="E5" t="n">
-        <v>85.9969253111407</v>
+        <v>16.50686336096345</v>
       </c>
       <c r="F5" t="n">
-        <v>85.9969253111407</v>
+        <v>16.50686336096345</v>
       </c>
       <c r="G5" t="n">
-        <v>111.0682255739869</v>
+        <v>21.12321914447721</v>
       </c>
       <c r="H5" t="n">
-        <v>27.21831175528855</v>
+        <v>5.617212789020826</v>
       </c>
       <c r="I5" t="n">
-        <v>85.99684620603357</v>
+        <v>16.50678425585631</v>
       </c>
       <c r="J5" t="n">
-        <v>28.3241035565017</v>
+        <v>5.835364499551343</v>
       </c>
       <c r="K5" t="n">
-        <v>119.4964583874219</v>
+        <v>22.70596354332075</v>
       </c>
       <c r="L5" t="n">
-        <v>146.2472731307009</v>
+        <v>27.48655066236024</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.30813013383025</v>
+        <v>1.849403402975816</v>
       </c>
       <c r="C6" t="n">
-        <v>4.787024968450138</v>
+        <v>1.553890467704713</v>
       </c>
       <c r="D6" t="n">
-        <v>17.31605877203771</v>
+        <v>3.277045067127862</v>
       </c>
       <c r="E6" t="n">
-        <v>5.774422347641645</v>
+        <v>2.38770291589375</v>
       </c>
       <c r="F6" t="n">
-        <v>5.88238145874117</v>
+        <v>2.406703719344308</v>
       </c>
       <c r="G6" t="n">
-        <v>6.103463021530108</v>
+        <v>4.453382756786496</v>
       </c>
       <c r="H6" t="n">
-        <v>18.24548655232624</v>
+        <v>4.037995561856622</v>
       </c>
       <c r="I6" t="n">
-        <v>5.826165882564419</v>
+        <v>4.200706316821971</v>
       </c>
       <c r="J6" t="n">
-        <v>5.340419827983347</v>
+        <v>1.790236185251065</v>
       </c>
       <c r="K6" t="n">
-        <v>6.193121926482788</v>
+        <v>2.764576434249929</v>
       </c>
       <c r="L6" t="n">
-        <v>6.33898441647432</v>
+        <v>2.862691982083327</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.92332728058268</v>
+        <v>2.133678099263872</v>
       </c>
       <c r="C7" t="n">
-        <v>6.666918368599203</v>
+        <v>1.884751704338142</v>
       </c>
       <c r="D7" t="n">
-        <v>8.336167097701448</v>
+        <v>3.546512349958816</v>
       </c>
       <c r="E7" t="n">
-        <v>7.638437530268667</v>
+        <v>2.715769586258434</v>
       </c>
       <c r="F7" t="n">
-        <v>7.638437530268667</v>
+        <v>2.715769586258434</v>
       </c>
       <c r="G7" t="n">
-        <v>7.718660168282486</v>
+        <v>2.933695731635062</v>
       </c>
       <c r="H7" t="n">
-        <v>6.81606689425479</v>
+        <v>2.026417712935979</v>
       </c>
       <c r="I7" t="n">
-        <v>7.441363029316895</v>
+        <v>2.681019291670541</v>
       </c>
       <c r="J7" t="n">
-        <v>6.844625576954224</v>
+        <v>2.054976395635416</v>
       </c>
       <c r="K7" t="n">
-        <v>7.844946789966587</v>
+        <v>3.055297608647775</v>
       </c>
       <c r="L7" t="n">
-        <v>7.932863961872114</v>
+        <v>3.1432147805533</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.00334095224379</v>
+        <v>3.73176049681685</v>
       </c>
       <c r="C8" t="n">
-        <v>24.37409507364594</v>
+        <v>5.001214787539482</v>
       </c>
       <c r="D8" t="n">
-        <v>27.60292322474473</v>
+        <v>6.937461409944221</v>
       </c>
       <c r="E8" t="n">
-        <v>22.82104741218128</v>
+        <v>5.387908910995808</v>
       </c>
       <c r="F8" t="n">
-        <v>16.90641637816995</v>
+        <v>4.346933854650451</v>
       </c>
       <c r="G8" t="n">
-        <v>25.23590765576989</v>
+        <v>6.016731272727086</v>
       </c>
       <c r="H8" t="n">
-        <v>24.33331438172358</v>
+        <v>5.109453254024733</v>
       </c>
       <c r="I8" t="n">
-        <v>24.95861051680414</v>
+        <v>5.764054832762569</v>
       </c>
       <c r="J8" t="n">
-        <v>24.3635312179043</v>
+        <v>5.138303771735294</v>
       </c>
       <c r="K8" t="n">
-        <v>16.76823451188503</v>
+        <v>4.625796239195511</v>
       </c>
       <c r="L8" t="n">
-        <v>34.26350767609816</v>
+        <v>7.777408049146226</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>450.2598280538427</v>
+        <v>80.16090181255882</v>
       </c>
       <c r="C9" t="n">
-        <v>573.7715869378544</v>
+        <v>101.695172831694</v>
       </c>
       <c r="D9" t="n">
-        <v>575.4408332543142</v>
+        <v>103.3569330526894</v>
       </c>
       <c r="E9" t="n">
-        <v>717.3719567399845</v>
+        <v>127.628868290314</v>
       </c>
       <c r="F9" t="n">
-        <v>574.546111330167</v>
+        <v>102.4915196343953</v>
       </c>
       <c r="G9" t="n">
-        <v>574.8233287375385</v>
+        <v>102.7441168589909</v>
       </c>
       <c r="H9" t="n">
-        <v>573.920735463509</v>
+        <v>101.8368388402917</v>
       </c>
       <c r="I9" t="n">
-        <v>574.5460315985723</v>
+        <v>102.4914404190263</v>
       </c>
       <c r="J9" t="n">
-        <v>573.9492941462097</v>
+        <v>101.865397522991</v>
       </c>
       <c r="K9" t="n">
-        <v>503.2378546896385</v>
+        <v>75.43678470662127</v>
       </c>
       <c r="L9" t="n">
-        <v>575.0375325311278</v>
+        <v>102.9536359079091</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.503865761004841</v>
+        <v>2.503865761004822</v>
       </c>
       <c r="C2" t="n">
-        <v>1.354277175247724</v>
+        <v>1.354277175247718</v>
       </c>
       <c r="D2" t="n">
-        <v>4.716182648778428</v>
+        <v>4.716182648778431</v>
       </c>
       <c r="E2" t="n">
-        <v>2.888479158499021</v>
+        <v>2.888479158499015</v>
       </c>
       <c r="F2" t="n">
-        <v>2.88847915849902</v>
+        <v>2.888479158499015</v>
       </c>
       <c r="G2" t="n">
-        <v>3.822194224286536</v>
+        <v>3.822194224286521</v>
       </c>
       <c r="H2" t="n">
-        <v>2.11227113064272</v>
+        <v>2.112271130642724</v>
       </c>
       <c r="I2" t="n">
-        <v>3.12282621822641</v>
+        <v>3.122826218226431</v>
       </c>
       <c r="J2" t="n">
-        <v>2.323846367697971</v>
+        <v>2.323846367697973</v>
       </c>
       <c r="K2" t="n">
-        <v>4.143628035695972</v>
+        <v>4.143628035696046</v>
       </c>
       <c r="L2" t="n">
-        <v>4.359852903275698</v>
+        <v>4.359852903275707</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.888474644478753</v>
+        <v>2.88847464447877</v>
       </c>
       <c r="C3" t="n">
-        <v>1.642451479072602</v>
+        <v>1.642451479072592</v>
       </c>
       <c r="D3" t="n">
-        <v>5.433097345481089</v>
+        <v>5.433097345481104</v>
       </c>
       <c r="E3" t="n">
-        <v>3.366080191256958</v>
+        <v>3.366080191256962</v>
       </c>
       <c r="F3" t="n">
-        <v>3.366080191256969</v>
+        <v>3.366080191256962</v>
       </c>
       <c r="G3" t="n">
-        <v>4.40482546817118</v>
+        <v>4.404825468171178</v>
       </c>
       <c r="H3" t="n">
-        <v>2.438520815294706</v>
+        <v>2.438520815294715</v>
       </c>
       <c r="I3" t="n">
-        <v>3.603892133773174</v>
+        <v>3.603892133773172</v>
       </c>
       <c r="J3" t="n">
-        <v>2.648680951081254</v>
+        <v>2.648680951081266</v>
       </c>
       <c r="K3" t="n">
-        <v>4.744527533820796</v>
+        <v>4.744527533820884</v>
       </c>
       <c r="L3" t="n">
-        <v>5.023145037269395</v>
+        <v>5.023145037269386</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.881445824099896</v>
+        <v>1.747170824169766</v>
       </c>
       <c r="C4" t="n">
-        <v>2.636498426819403</v>
+        <v>1.215583709821892</v>
       </c>
       <c r="D4" t="n">
-        <v>5.196574470063209</v>
+        <v>3.062299470132575</v>
       </c>
       <c r="E4" t="n">
-        <v>4.391539357459483</v>
+        <v>2.14019937127919</v>
       </c>
       <c r="F4" t="n">
-        <v>4.391539357459481</v>
+        <v>2.140199371279189</v>
       </c>
       <c r="G4" t="n">
-        <v>4.658937528562006</v>
+        <v>2.529770261263772</v>
       </c>
       <c r="H4" t="n">
-        <v>3.649128182189962</v>
+        <v>1.514853182260114</v>
       </c>
       <c r="I4" t="n">
-        <v>4.211007753318057</v>
+        <v>2.108316175669279</v>
       </c>
       <c r="J4" t="n">
-        <v>3.644883924752378</v>
+        <v>1.510608924822279</v>
       </c>
       <c r="K4" t="n">
-        <v>4.737434410085071</v>
+        <v>2.603159410154902</v>
       </c>
       <c r="L4" t="n">
-        <v>4.984798882483554</v>
+        <v>2.850523882553659</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.16368814281347</v>
+        <v>10.0688454271715</v>
       </c>
       <c r="C5" t="n">
-        <v>14.14128790843299</v>
+        <v>3.240426647614291</v>
       </c>
       <c r="D5" t="n">
-        <v>169.713037860908</v>
+        <v>32.01719687002623</v>
       </c>
       <c r="E5" t="n">
-        <v>83.44283919911994</v>
+        <v>16.05322806802225</v>
       </c>
       <c r="F5" t="n">
-        <v>83.44283919911994</v>
+        <v>16.05322806802225</v>
       </c>
       <c r="G5" t="n">
-        <v>124.3959785611978</v>
+        <v>23.60348936881753</v>
       </c>
       <c r="H5" t="n">
-        <v>30.65266966042787</v>
+        <v>6.267476456677344</v>
       </c>
       <c r="I5" t="n">
-        <v>83.44270614881303</v>
+        <v>16.05309501771525</v>
       </c>
       <c r="J5" t="n">
-        <v>28.35013870605724</v>
+        <v>5.85873374277119</v>
       </c>
       <c r="K5" t="n">
-        <v>128.0366968313884</v>
+        <v>24.30382947871696</v>
       </c>
       <c r="L5" t="n">
-        <v>172.9819208890598</v>
+        <v>32.41801719549652</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.79664261109249</v>
+        <v>4.020245446363576</v>
       </c>
       <c r="C6" t="n">
-        <v>5.422875444037723</v>
+        <v>1.705986062195028</v>
       </c>
       <c r="D6" t="n">
-        <v>7.512020929452653</v>
+        <v>3.469818044777026</v>
       </c>
       <c r="E6" t="n">
-        <v>6.308873539516187</v>
+        <v>2.477650185492662</v>
       </c>
       <c r="F6" t="n">
-        <v>6.493217986539092</v>
+        <v>2.510094807992898</v>
       </c>
       <c r="G6" t="n">
-        <v>17.57413431555407</v>
+        <v>4.802844883457569</v>
       </c>
       <c r="H6" t="n">
-        <v>19.36495978713634</v>
+        <v>4.280839529742866</v>
       </c>
       <c r="I6" t="n">
-        <v>6.451881353691999</v>
+        <v>2.502709927198132</v>
       </c>
       <c r="J6" t="n">
-        <v>16.94470424605614</v>
+        <v>3.851377288688067</v>
       </c>
       <c r="K6" t="n">
-        <v>6.953921199544089</v>
+        <v>2.993261082985919</v>
       </c>
       <c r="L6" t="n">
-        <v>7.245357763696664</v>
+        <v>3.248382243491295</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.603050240418839</v>
+        <v>2.402173197892719</v>
       </c>
       <c r="C7" t="n">
-        <v>7.213172552656461</v>
+        <v>2.021078351604562</v>
       </c>
       <c r="D7" t="n">
-        <v>8.918222134799846</v>
+        <v>3.717309455577086</v>
       </c>
       <c r="E7" t="n">
-        <v>8.099210411655603</v>
+        <v>2.792749473281797</v>
       </c>
       <c r="F7" t="n">
-        <v>8.099210411655603</v>
+        <v>2.792749473281797</v>
       </c>
       <c r="G7" t="n">
-        <v>8.380541944880818</v>
+        <v>3.184772634986709</v>
       </c>
       <c r="H7" t="n">
-        <v>7.370732598509273</v>
+        <v>2.169855555983068</v>
       </c>
       <c r="I7" t="n">
-        <v>7.932612169636714</v>
+        <v>2.76331854939226</v>
       </c>
       <c r="J7" t="n">
-        <v>7.366488341071364</v>
+        <v>2.165611298545233</v>
       </c>
       <c r="K7" t="n">
-        <v>8.459038826404049</v>
+        <v>3.258161783877852</v>
       </c>
       <c r="L7" t="n">
-        <v>8.706403298802826</v>
+        <v>3.505526256276611</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.88451031827486</v>
+        <v>4.035710162743888</v>
       </c>
       <c r="C8" t="n">
-        <v>25.51028751198849</v>
+        <v>5.241370566997509</v>
       </c>
       <c r="D8" t="n">
-        <v>28.8906036623279</v>
+        <v>7.232448585374807</v>
       </c>
       <c r="E8" t="n">
-        <v>23.79114695682969</v>
+        <v>5.554530290267393</v>
       </c>
       <c r="F8" t="n">
-        <v>17.59416924385296</v>
+        <v>4.463862218693405</v>
       </c>
       <c r="G8" t="n">
-        <v>26.51685522574678</v>
+        <v>6.376763755123029</v>
       </c>
       <c r="H8" t="n">
-        <v>25.50704587934831</v>
+        <v>5.361846676114504</v>
       </c>
       <c r="I8" t="n">
-        <v>26.06892545050326</v>
+        <v>5.955309669528593</v>
       </c>
       <c r="J8" t="n">
-        <v>25.50454184491626</v>
+        <v>5.357908697924085</v>
       </c>
       <c r="K8" t="n">
-        <v>17.57601546044138</v>
+        <v>4.862749662773731</v>
       </c>
       <c r="L8" t="n">
-        <v>36.09235117270612</v>
+        <v>8.325453055966291</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>450.5335203539966</v>
+        <v>80.3579355154711</v>
       </c>
       <c r="C9" t="n">
-        <v>573.9255792808063</v>
+        <v>101.7624613952998</v>
       </c>
       <c r="D9" t="n">
-        <v>575.6305905954963</v>
+        <v>103.4586857642007</v>
       </c>
       <c r="E9" t="n">
-        <v>717.4868874582377</v>
+        <v>127.6449799569556</v>
       </c>
       <c r="F9" t="n">
-        <v>574.6451525523345</v>
+        <v>102.5048347497411</v>
       </c>
       <c r="G9" t="n">
-        <v>575.0929486730294</v>
+        <v>102.926155678682</v>
       </c>
       <c r="H9" t="n">
-        <v>574.0831393266577</v>
+        <v>101.9112385996781</v>
       </c>
       <c r="I9" t="n">
-        <v>574.6450188977855</v>
+        <v>102.5047015930875</v>
       </c>
       <c r="J9" t="n">
-        <v>574.0788950692209</v>
+        <v>101.9069943422404</v>
       </c>
       <c r="K9" t="n">
-        <v>503.4517074458552</v>
+        <v>89.86475313081193</v>
       </c>
       <c r="L9" t="n">
-        <v>575.4188100269515</v>
+        <v>103.2469092999718</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.026361381977849</v>
+        <v>2.026361381977853</v>
       </c>
       <c r="C2" t="n">
-        <v>1.204734193473636</v>
+        <v>1.204734193473642</v>
       </c>
       <c r="D2" t="n">
-        <v>4.310344192709469</v>
+        <v>4.310344192709476</v>
       </c>
       <c r="E2" t="n">
-        <v>2.948322956121447</v>
+        <v>2.948322956121448</v>
       </c>
       <c r="F2" t="n">
-        <v>2.948322956121447</v>
+        <v>2.948322956121449</v>
       </c>
       <c r="G2" t="n">
         <v>3.533967890329674</v>
       </c>
       <c r="H2" t="n">
-        <v>2.547836125612664</v>
+        <v>2.547836125612669</v>
       </c>
       <c r="I2" t="n">
-        <v>3.215597234265329</v>
+        <v>3.215597234265334</v>
       </c>
       <c r="J2" t="n">
-        <v>2.115963285352062</v>
+        <v>2.115963285352075</v>
       </c>
       <c r="K2" t="n">
-        <v>3.555458309925999</v>
+        <v>3.555458309926011</v>
       </c>
       <c r="L2" t="n">
-        <v>3.127767250422039</v>
+        <v>3.127767250422049</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.30596954144924</v>
+        <v>2.305969541449228</v>
       </c>
       <c r="C3" t="n">
-        <v>1.438706543346422</v>
+        <v>1.438706543346428</v>
       </c>
       <c r="D3" t="n">
-        <v>4.933022899404492</v>
+        <v>4.933022899404484</v>
       </c>
       <c r="E3" t="n">
-        <v>3.406580516781144</v>
+        <v>3.40658051678117</v>
       </c>
       <c r="F3" t="n">
-        <v>3.406580516781151</v>
+        <v>3.406580516781149</v>
       </c>
       <c r="G3" t="n">
-        <v>4.040029325801208</v>
+        <v>4.040029325801184</v>
       </c>
       <c r="H3" t="n">
         <v>2.906117743094367</v>
       </c>
       <c r="I3" t="n">
-        <v>3.677792240288158</v>
+        <v>3.677792240288156</v>
       </c>
       <c r="J3" t="n">
-        <v>2.392217275076555</v>
+        <v>2.39221727507657</v>
       </c>
       <c r="K3" t="n">
-        <v>4.04725640751946</v>
+        <v>4.047256407519466</v>
       </c>
       <c r="L3" t="n">
-        <v>3.572758189926843</v>
+        <v>3.572758189926842</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.151680071417643</v>
+        <v>1.39663381910096</v>
       </c>
       <c r="C4" t="n">
-        <v>2.185457966970953</v>
+        <v>1.079197574878241</v>
       </c>
       <c r="D4" t="n">
-        <v>4.509411071836216</v>
+        <v>2.754364819519548</v>
       </c>
       <c r="E4" t="n">
-        <v>4.114459708104457</v>
+        <v>2.148667735646567</v>
       </c>
       <c r="F4" t="n">
-        <v>4.114459708104424</v>
+        <v>2.148667735646567</v>
       </c>
       <c r="G4" t="n">
-        <v>4.042540837962907</v>
+        <v>2.291900859700932</v>
       </c>
       <c r="H4" t="n">
-        <v>3.461963564864065</v>
+        <v>1.70691731254743</v>
       </c>
       <c r="I4" t="n">
-        <v>3.825161399958284</v>
+        <v>2.097688560822094</v>
       </c>
       <c r="J4" t="n">
-        <v>3.138405658085183</v>
+        <v>1.383359405768549</v>
       </c>
       <c r="K4" t="n">
-        <v>3.991439879704014</v>
+        <v>2.236393627387355</v>
       </c>
       <c r="L4" t="n">
-        <v>3.806666059717566</v>
+        <v>2.051619807400997</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.94456407711274</v>
+        <v>5.936181379505308</v>
       </c>
       <c r="C5" t="n">
-        <v>9.954937698446656</v>
+        <v>2.446626000208416</v>
       </c>
       <c r="D5" t="n">
-        <v>158.9312266756019</v>
+        <v>29.93260421851421</v>
       </c>
       <c r="E5" t="n">
-        <v>96.740066707278</v>
+        <v>18.45077447916735</v>
       </c>
       <c r="F5" t="n">
-        <v>96.740066707278</v>
+        <v>18.45077447916735</v>
       </c>
       <c r="G5" t="n">
-        <v>117.5056956943062</v>
+        <v>22.26141600621026</v>
       </c>
       <c r="H5" t="n">
-        <v>64.47994120349001</v>
+        <v>12.44608131875428</v>
       </c>
       <c r="I5" t="n">
-        <v>96.73999064797383</v>
+        <v>18.45069841986304</v>
       </c>
       <c r="J5" t="n">
-        <v>27.16865389197212</v>
+        <v>5.612683072015596</v>
       </c>
       <c r="K5" t="n">
-        <v>109.1449331206336</v>
+        <v>20.74340833750873</v>
       </c>
       <c r="L5" t="n">
-        <v>104.3190382761376</v>
+        <v>19.74179722163481</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.89435688117229</v>
+        <v>1.746436428510728</v>
       </c>
       <c r="C6" t="n">
-        <v>4.660242048637429</v>
+        <v>1.514759570891406</v>
       </c>
       <c r="D6" t="n">
-        <v>6.571771028013892</v>
+        <v>3.117340169839979</v>
       </c>
       <c r="E6" t="n">
-        <v>5.776733956470748</v>
+        <v>2.441228001773777</v>
       </c>
       <c r="F6" t="n">
-        <v>5.873875400429305</v>
+        <v>2.45832489581783</v>
       </c>
       <c r="G6" t="n">
-        <v>16.78521764771748</v>
+        <v>4.53461196606539</v>
       </c>
       <c r="H6" t="n">
-        <v>19.17711867158812</v>
+        <v>4.472784596343748</v>
       </c>
       <c r="I6" t="n">
-        <v>5.812676236919841</v>
+        <v>4.340399667186543</v>
       </c>
       <c r="J6" t="n">
-        <v>16.20764199199127</v>
+        <v>3.683544988072247</v>
       </c>
       <c r="K6" t="n">
-        <v>5.910668191464043</v>
+        <v>2.574177808426798</v>
       </c>
       <c r="L6" t="n">
-        <v>5.809491291959608</v>
+        <v>2.404117046365524</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.938651823416755</v>
+        <v>2.063140843841277</v>
       </c>
       <c r="C7" t="n">
-        <v>6.750862643115449</v>
+        <v>1.882708793525774</v>
       </c>
       <c r="D7" t="n">
-        <v>8.296401736321872</v>
+        <v>3.420875172857474</v>
       </c>
       <c r="E7" t="n">
-        <v>7.801390221992251</v>
+        <v>2.79756750257469</v>
       </c>
       <c r="F7" t="n">
-        <v>7.801390221992251</v>
+        <v>2.79756750257469</v>
       </c>
       <c r="G7" t="n">
-        <v>7.8295125899621</v>
+        <v>2.958407884441244</v>
       </c>
       <c r="H7" t="n">
-        <v>7.24893531686325</v>
+        <v>2.373424337287735</v>
       </c>
       <c r="I7" t="n">
-        <v>7.612133151957504</v>
+        <v>2.764195585562407</v>
       </c>
       <c r="J7" t="n">
-        <v>6.925377410084346</v>
+        <v>2.04986643050887</v>
       </c>
       <c r="K7" t="n">
-        <v>7.778411631703175</v>
+        <v>2.902900652127671</v>
       </c>
       <c r="L7" t="n">
-        <v>7.59363781171682</v>
+        <v>2.718126832141312</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.43961345352685</v>
+        <v>3.735310081679862</v>
       </c>
       <c r="C8" t="n">
-        <v>25.24517071308777</v>
+        <v>5.13770699620342</v>
       </c>
       <c r="D8" t="n">
-        <v>28.43519370671446</v>
+        <v>6.965302540440759</v>
       </c>
       <c r="E8" t="n">
-        <v>23.67758104915409</v>
+        <v>5.591777073014494</v>
       </c>
       <c r="F8" t="n">
-        <v>17.5053058742158</v>
+        <v>4.505456648111677</v>
       </c>
       <c r="G8" t="n">
-        <v>26.14133424863128</v>
+        <v>6.181288478903573</v>
       </c>
       <c r="H8" t="n">
-        <v>25.56075697551844</v>
+        <v>5.596304931747646</v>
       </c>
       <c r="I8" t="n">
-        <v>25.92395481062686</v>
+        <v>5.987076180024729</v>
       </c>
       <c r="J8" t="n">
-        <v>25.23893065214186</v>
+        <v>5.273051783645845</v>
       </c>
       <c r="K8" t="n">
-        <v>17.1157070132585</v>
+        <v>4.54626463037672</v>
       </c>
       <c r="L8" t="n">
-        <v>35.10913951994795</v>
+        <v>7.560855106549281</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>475.7623368776941</v>
+        <v>84.576108966289</v>
       </c>
       <c r="C9" t="n">
-        <v>606.437532691138</v>
+        <v>107.4275621500721</v>
       </c>
       <c r="D9" t="n">
-        <v>607.9830570644428</v>
+        <v>108.9657259387013</v>
       </c>
       <c r="E9" t="n">
-        <v>758.311993491839</v>
+        <v>134.8874329623252</v>
       </c>
       <c r="F9" t="n">
-        <v>607.2988796619304</v>
+        <v>108.3091250722782</v>
       </c>
       <c r="G9" t="n">
-        <v>607.5161826379847</v>
+        <v>108.5032612409875</v>
       </c>
       <c r="H9" t="n">
-        <v>606.9356053648866</v>
+        <v>107.918277693834</v>
       </c>
       <c r="I9" t="n">
-        <v>607.2988031999802</v>
+        <v>108.3090489421087</v>
       </c>
       <c r="J9" t="n">
-        <v>606.6120474581069</v>
+        <v>107.594719787055</v>
       </c>
       <c r="K9" t="n">
-        <v>528.5663401839766</v>
+        <v>95.10298956119756</v>
       </c>
       <c r="L9" t="n">
-        <v>607.28030785974</v>
+        <v>108.2629801886874</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.408848796304432</v>
+        <v>3.408848796304413</v>
       </c>
       <c r="C2" t="n">
-        <v>1.456153717654475</v>
+        <v>1.456153717654471</v>
       </c>
       <c r="D2" t="n">
-        <v>4.78833394097073</v>
+        <v>4.788333940970719</v>
       </c>
       <c r="E2" t="n">
-        <v>3.567424598051968</v>
+        <v>3.567424598051957</v>
       </c>
       <c r="F2" t="n">
-        <v>3.567424598051968</v>
+        <v>3.567424598051956</v>
       </c>
       <c r="G2" t="n">
-        <v>4.334064947756579</v>
+        <v>4.334064947756565</v>
       </c>
       <c r="H2" t="n">
-        <v>2.239289385321004</v>
+        <v>2.239289385320994</v>
       </c>
       <c r="I2" t="n">
-        <v>3.797967778323356</v>
+        <v>3.797967778323359</v>
       </c>
       <c r="J2" t="n">
-        <v>2.754469601854733</v>
+        <v>2.754469601854725</v>
       </c>
       <c r="K2" t="n">
-        <v>4.597258838852603</v>
+        <v>4.597258838852593</v>
       </c>
       <c r="L2" t="n">
-        <v>4.129920670320217</v>
+        <v>4.129920670320206</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.925253393435487</v>
+        <v>3.925253393435495</v>
       </c>
       <c r="C3" t="n">
-        <v>1.759803019689773</v>
+        <v>1.75980301968977</v>
       </c>
       <c r="D3" t="n">
-        <v>5.511947069288611</v>
+        <v>5.511947069288585</v>
       </c>
       <c r="E3" t="n">
-        <v>4.142310020808645</v>
+        <v>4.142310020808629</v>
       </c>
       <c r="F3" t="n">
-        <v>4.142310020808645</v>
+        <v>4.14231002080863</v>
       </c>
       <c r="G3" t="n">
-        <v>4.989443625553858</v>
+        <v>4.989443625553848</v>
       </c>
       <c r="H3" t="n">
-        <v>2.580519588886073</v>
+        <v>2.58051958888606</v>
       </c>
       <c r="I3" t="n">
-        <v>4.37821315121362</v>
+        <v>4.378213151213601</v>
       </c>
       <c r="J3" t="n">
-        <v>3.138962007504068</v>
+        <v>3.138962007504054</v>
       </c>
       <c r="K3" t="n">
-        <v>5.257693236241178</v>
+        <v>5.257693236241164</v>
       </c>
       <c r="L3" t="n">
-        <v>4.754561949910892</v>
+        <v>4.754561949910865</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.793386069063505</v>
+        <v>2.332263804127121</v>
       </c>
       <c r="C4" t="n">
-        <v>3.045161345708855</v>
+        <v>1.332834441077833</v>
       </c>
       <c r="D4" t="n">
-        <v>5.613431533823603</v>
+        <v>3.152309268887218</v>
       </c>
       <c r="E4" t="n">
-        <v>5.454907577928944</v>
+        <v>2.639400508921478</v>
       </c>
       <c r="F4" t="n">
-        <v>5.454907577928942</v>
+        <v>2.639400508921479</v>
       </c>
       <c r="G4" t="n">
-        <v>5.339129511573701</v>
+        <v>2.881516130991638</v>
       </c>
       <c r="H4" t="n">
-        <v>4.09869793151401</v>
+        <v>1.637575666578223</v>
       </c>
       <c r="I4" t="n">
-        <v>4.999029038087891</v>
+        <v>2.559064902741679</v>
       </c>
       <c r="J4" t="n">
-        <v>4.271332301531136</v>
+        <v>1.810210036593527</v>
       </c>
       <c r="K4" t="n">
-        <v>5.36339630857891</v>
+        <v>2.902274043642759</v>
       </c>
       <c r="L4" t="n">
-        <v>5.22227842785911</v>
+        <v>2.761156162923009</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96.28274146723959</v>
+        <v>18.43439026695517</v>
       </c>
       <c r="C5" t="n">
-        <v>15.58839019388125</v>
+        <v>3.540442706393993</v>
       </c>
       <c r="D5" t="n">
-        <v>167.9284798853914</v>
+        <v>31.71975762396773</v>
       </c>
       <c r="E5" t="n">
-        <v>114.9295056864565</v>
+        <v>21.90692967161915</v>
       </c>
       <c r="F5" t="n">
-        <v>114.9295056864565</v>
+        <v>21.90692967161915</v>
       </c>
       <c r="G5" t="n">
-        <v>147.2909754894075</v>
+        <v>27.86504088771474</v>
       </c>
       <c r="H5" t="n">
-        <v>31.99132454558256</v>
+        <v>6.546677924053737</v>
       </c>
       <c r="I5" t="n">
-        <v>114.9293831335407</v>
+        <v>21.9068071187035</v>
       </c>
       <c r="J5" t="n">
-        <v>46.73033588743133</v>
+        <v>9.282994627220335</v>
       </c>
       <c r="K5" t="n">
-        <v>145.5393753608879</v>
+        <v>27.57324622316706</v>
       </c>
       <c r="L5" t="n">
-        <v>151.8276253462086</v>
+        <v>28.56369708073881</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.20725361721156</v>
+        <v>2.754905540507409</v>
       </c>
       <c r="C6" t="n">
-        <v>5.972160672482986</v>
+        <v>1.847986319798678</v>
       </c>
       <c r="D6" t="n">
-        <v>8.022572345774412</v>
+        <v>3.576314273665263</v>
       </c>
       <c r="E6" t="n">
-        <v>7.284826021873682</v>
+        <v>2.961466153310603</v>
       </c>
       <c r="F6" t="n">
-        <v>7.454518279155535</v>
+        <v>2.991331990430381</v>
       </c>
       <c r="G6" t="n">
-        <v>7.740503026745234</v>
+        <v>3.30415786737204</v>
       </c>
       <c r="H6" t="n">
-        <v>20.32301755346692</v>
+        <v>4.49305590456925</v>
       </c>
       <c r="I6" t="n">
-        <v>7.400402553261552</v>
+        <v>4.919905578423479</v>
       </c>
       <c r="J6" t="n">
-        <v>6.808045997029817</v>
+        <v>4.246140634988528</v>
       </c>
       <c r="K6" t="n">
-        <v>7.730774617445447</v>
+        <v>3.318932623745712</v>
       </c>
       <c r="L6" t="n">
-        <v>7.616601575990797</v>
+        <v>3.182557034710989</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.883196358037454</v>
+        <v>3.052070411086413</v>
       </c>
       <c r="C7" t="n">
-        <v>8.032641680067821</v>
+        <v>2.210630975168575</v>
       </c>
       <c r="D7" t="n">
-        <v>9.703284632959008</v>
+        <v>3.872123410434826</v>
       </c>
       <c r="E7" t="n">
-        <v>9.328863121419682</v>
+        <v>3.321216680881349</v>
       </c>
       <c r="F7" t="n">
-        <v>9.328863121419682</v>
+        <v>3.321216680881349</v>
       </c>
       <c r="G7" t="n">
-        <v>9.428939800547104</v>
+        <v>3.601322737950908</v>
       </c>
       <c r="H7" t="n">
-        <v>8.188508220488528</v>
+        <v>2.357382273537449</v>
       </c>
       <c r="I7" t="n">
-        <v>9.088839327063473</v>
+        <v>3.278871509700953</v>
       </c>
       <c r="J7" t="n">
-        <v>8.361142590503805</v>
+        <v>2.530016643552776</v>
       </c>
       <c r="K7" t="n">
-        <v>9.453206597553072</v>
+        <v>3.622080650601961</v>
       </c>
       <c r="L7" t="n">
-        <v>9.312088716833328</v>
+        <v>3.480962769882275</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.38420071368839</v>
+        <v>4.724247168620096</v>
       </c>
       <c r="C8" t="n">
-        <v>27.08015962040473</v>
+        <v>5.562994114502497</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45132460921054</v>
+        <v>7.523778426467277</v>
       </c>
       <c r="E8" t="n">
-        <v>25.56439386460171</v>
+        <v>6.17867007619732</v>
       </c>
       <c r="F8" t="n">
-        <v>19.02833905955579</v>
+        <v>5.028324436742635</v>
       </c>
       <c r="G8" t="n">
-        <v>28.24540176728141</v>
+        <v>6.913020026150341</v>
       </c>
       <c r="H8" t="n">
-        <v>27.00497018715195</v>
+        <v>5.669079561724509</v>
       </c>
       <c r="I8" t="n">
-        <v>27.90530129379474</v>
+        <v>6.590568797900477</v>
       </c>
       <c r="J8" t="n">
-        <v>27.17943530194418</v>
+        <v>5.842036142819451</v>
       </c>
       <c r="K8" t="n">
-        <v>18.78117154564524</v>
+        <v>5.26380247257014</v>
       </c>
       <c r="L8" t="n">
-        <v>37.85932509608931</v>
+        <v>8.50527634540563</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>452.9602957051264</v>
+        <v>81.20963947266912</v>
       </c>
       <c r="C9" t="n">
-        <v>576.3485464933231</v>
+        <v>102.2342296803132</v>
       </c>
       <c r="D9" t="n">
-        <v>578.0191525238475</v>
+        <v>103.895715617243</v>
       </c>
       <c r="E9" t="n">
-        <v>720.7738206152497</v>
+        <v>128.5355285213086</v>
       </c>
       <c r="F9" t="n">
-        <v>577.404867797124</v>
+        <v>103.3025929620458</v>
       </c>
       <c r="G9" t="n">
-        <v>577.7448446138028</v>
+        <v>103.6249214430955</v>
       </c>
       <c r="H9" t="n">
-        <v>576.504413033744</v>
+        <v>102.3809809786823</v>
       </c>
       <c r="I9" t="n">
-        <v>577.4047441403191</v>
+        <v>103.3024702148457</v>
       </c>
       <c r="J9" t="n">
-        <v>576.6770474037595</v>
+        <v>102.5536153486976</v>
       </c>
       <c r="K9" t="n">
-        <v>421.3302772545842</v>
+        <v>90.97641634158309</v>
       </c>
       <c r="L9" t="n">
-        <v>577.6279935300886</v>
+        <v>103.504561475027</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.195906808355477</v>
+        <v>3.195906808355486</v>
       </c>
       <c r="C2" t="n">
-        <v>1.564941827947345</v>
+        <v>1.564941827947353</v>
       </c>
       <c r="D2" t="n">
-        <v>4.850696481553382</v>
+        <v>4.850696481553391</v>
       </c>
       <c r="E2" t="n">
-        <v>3.401089187018416</v>
+        <v>3.401089187018425</v>
       </c>
       <c r="F2" t="n">
-        <v>3.401089187018415</v>
+        <v>3.401089187018425</v>
       </c>
       <c r="G2" t="n">
-        <v>4.350338274494318</v>
+        <v>4.350338274494332</v>
       </c>
       <c r="H2" t="n">
-        <v>2.358104150168588</v>
+        <v>2.358104150168598</v>
       </c>
       <c r="I2" t="n">
-        <v>3.614011429516007</v>
+        <v>3.614011429516011</v>
       </c>
       <c r="J2" t="n">
-        <v>3.080451140237876</v>
+        <v>3.080451140237886</v>
       </c>
       <c r="K2" t="n">
-        <v>4.665554180871866</v>
+        <v>4.665554180871872</v>
       </c>
       <c r="L2" t="n">
-        <v>4.52695040359187</v>
+        <v>4.526950403591878</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.72351415447697</v>
+        <v>3.723514154476977</v>
       </c>
       <c r="C3" t="n">
-        <v>1.926750017785695</v>
+        <v>1.926750017785704</v>
       </c>
       <c r="D3" t="n">
-        <v>5.626865067302672</v>
+        <v>5.626865067302685</v>
       </c>
       <c r="E3" t="n">
-        <v>3.991534104573654</v>
+        <v>3.99153410457366</v>
       </c>
       <c r="F3" t="n">
-        <v>3.991534104573654</v>
+        <v>3.991534104573659</v>
       </c>
       <c r="G3" t="n">
-        <v>5.05134948029441</v>
+        <v>5.051349480294427</v>
       </c>
       <c r="H3" t="n">
-        <v>2.760522386495127</v>
+        <v>2.760522386495137</v>
       </c>
       <c r="I3" t="n">
-        <v>4.207389220437412</v>
+        <v>4.207389220437419</v>
       </c>
       <c r="J3" t="n">
-        <v>3.537738801241948</v>
+        <v>3.537738801241959</v>
       </c>
       <c r="K3" t="n">
-        <v>5.372725548866609</v>
+        <v>5.372725548866611</v>
       </c>
       <c r="L3" t="n">
-        <v>5.254390943723873</v>
+        <v>5.254390943723875</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.286453902692467</v>
+        <v>2.294392843029744</v>
       </c>
       <c r="C4" t="n">
-        <v>3.530520339835852</v>
+        <v>1.447596892786811</v>
       </c>
       <c r="D4" t="n">
-        <v>6.27015624402192</v>
+        <v>3.278095184359379</v>
       </c>
       <c r="E4" t="n">
-        <v>5.588074738907364</v>
+        <v>2.552394597445983</v>
       </c>
       <c r="F4" t="n">
-        <v>5.588074738907372</v>
+        <v>2.552394597445987</v>
       </c>
       <c r="G4" t="n">
-        <v>5.968073162037563</v>
+        <v>2.979836558186911</v>
       </c>
       <c r="H4" t="n">
-        <v>4.788971209693307</v>
+        <v>1.796910150030756</v>
       </c>
       <c r="I4" t="n">
-        <v>5.507691884593666</v>
+        <v>2.538112931136235</v>
       </c>
       <c r="J4" t="n">
-        <v>5.008157741170523</v>
+        <v>2.016096681507713</v>
       </c>
       <c r="K4" t="n">
-        <v>5.997093860072115</v>
+        <v>3.005032800409188</v>
       </c>
       <c r="L4" t="n">
-        <v>6.077865998399038</v>
+        <v>3.085804938736363</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.61223429472713</v>
+        <v>15.37573012114523</v>
       </c>
       <c r="C5" t="n">
-        <v>16.64324191196174</v>
+        <v>3.755435876975699</v>
       </c>
       <c r="D5" t="n">
-        <v>166.8359866878649</v>
+        <v>31.53768118934826</v>
       </c>
       <c r="E5" t="n">
-        <v>100.2306259328688</v>
+        <v>19.20948351732474</v>
       </c>
       <c r="F5" t="n">
-        <v>100.2306259328688</v>
+        <v>19.20948351732474</v>
       </c>
       <c r="G5" t="n">
-        <v>143.5662494755232</v>
+        <v>27.19711545813646</v>
       </c>
       <c r="H5" t="n">
-        <v>34.22231479701267</v>
+        <v>6.9771785933291</v>
       </c>
       <c r="I5" t="n">
-        <v>100.2304629668156</v>
+        <v>19.2093205512727</v>
       </c>
       <c r="J5" t="n">
-        <v>53.32025005562133</v>
+        <v>10.51902488277706</v>
       </c>
       <c r="K5" t="n">
-        <v>142.3166555909088</v>
+        <v>26.99727553503202</v>
       </c>
       <c r="L5" t="n">
-        <v>171.6480912512022</v>
+        <v>32.2261644253297</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.77051722123224</v>
+        <v>2.787557605711465</v>
       </c>
       <c r="C6" t="n">
-        <v>7.03828562322158</v>
+        <v>2.064963579317477</v>
       </c>
       <c r="D6" t="n">
-        <v>9.111175093714271</v>
+        <v>3.778114499195767</v>
       </c>
       <c r="E6" t="n">
-        <v>8.050549679593727</v>
+        <v>2.985790184658348</v>
       </c>
       <c r="F6" t="n">
-        <v>8.341661481398782</v>
+        <v>3.037025861498438</v>
       </c>
       <c r="G6" t="n">
-        <v>20.45213648057729</v>
+        <v>5.52903168843682</v>
       </c>
       <c r="H6" t="n">
-        <v>22.1183337151402</v>
+        <v>4.846877934462816</v>
       </c>
       <c r="I6" t="n">
-        <v>8.309764415014333</v>
+        <v>5.08730806138614</v>
       </c>
       <c r="J6" t="n">
-        <v>20.01714227002878</v>
+        <v>2.543194181583347</v>
       </c>
       <c r="K6" t="n">
-        <v>8.78443832412561</v>
+        <v>3.495605423424401</v>
       </c>
       <c r="L6" t="n">
-        <v>8.879071914926557</v>
+        <v>3.578817177373722</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.548303636937252</v>
+        <v>3.044478392192379</v>
       </c>
       <c r="C7" t="n">
-        <v>8.882962276663811</v>
+        <v>2.389626668564094</v>
       </c>
       <c r="D7" t="n">
-        <v>10.53209168447105</v>
+        <v>4.028195817813864</v>
       </c>
       <c r="E7" t="n">
-        <v>9.913074443452093</v>
+        <v>3.313594541321201</v>
       </c>
       <c r="F7" t="n">
-        <v>9.913074443452093</v>
+        <v>3.313594541321201</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2299228962823</v>
+        <v>3.729922107349573</v>
       </c>
       <c r="H7" t="n">
-        <v>9.050820943938236</v>
+        <v>2.546995699193406</v>
       </c>
       <c r="I7" t="n">
-        <v>9.769541618838661</v>
+        <v>3.288198480298892</v>
       </c>
       <c r="J7" t="n">
-        <v>9.270007475415316</v>
+        <v>2.766182230670357</v>
       </c>
       <c r="K7" t="n">
-        <v>10.25894359431669</v>
+        <v>3.755118349571833</v>
       </c>
       <c r="L7" t="n">
-        <v>10.33971573264398</v>
+        <v>3.835890487899013</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.41381580742539</v>
+        <v>4.780808524789848</v>
       </c>
       <c r="C8" t="n">
-        <v>28.88426527101974</v>
+        <v>5.909855976496046</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46734190964118</v>
+        <v>7.888799836524831</v>
       </c>
       <c r="E8" t="n">
-        <v>27.02228984213979</v>
+        <v>6.324816435173705</v>
       </c>
       <c r="F8" t="n">
-        <v>20.03757904839165</v>
+        <v>5.095507342135148</v>
       </c>
       <c r="G8" t="n">
-        <v>30.09233624557221</v>
+        <v>7.225706837882326</v>
       </c>
       <c r="H8" t="n">
-        <v>28.91323429314649</v>
+        <v>6.042780429711809</v>
       </c>
       <c r="I8" t="n">
-        <v>29.63195496812811</v>
+        <v>6.78398321083166</v>
       </c>
       <c r="J8" t="n">
-        <v>29.13438548384179</v>
+        <v>6.262312741209353</v>
       </c>
       <c r="K8" t="n">
-        <v>19.93875819390453</v>
+        <v>5.458765709867888</v>
       </c>
       <c r="L8" t="n">
-        <v>40.64472827409043</v>
+        <v>9.169572666292627</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>452.8372503799623</v>
+        <v>81.06333259621158</v>
       </c>
       <c r="C9" t="n">
-        <v>576.3885407674467</v>
+        <v>102.2706079417264</v>
       </c>
       <c r="D9" t="n">
-        <v>578.0375907207257</v>
+        <v>103.9091631069793</v>
       </c>
       <c r="E9" t="n">
-        <v>720.6186492038793</v>
+        <v>128.3977750213745</v>
       </c>
       <c r="F9" t="n">
-        <v>577.2752840820701</v>
+        <v>103.1693428966391</v>
       </c>
       <c r="G9" t="n">
-        <v>577.735501387065</v>
+        <v>103.6109033805119</v>
       </c>
       <c r="H9" t="n">
-        <v>576.5563994347218</v>
+        <v>102.4279769723557</v>
       </c>
       <c r="I9" t="n">
-        <v>577.2751201096223</v>
+        <v>103.1691797534613</v>
       </c>
       <c r="J9" t="n">
-        <v>576.7755859661989</v>
+        <v>102.6471635038326</v>
       </c>
       <c r="K9" t="n">
-        <v>502.8729413975332</v>
+        <v>90.45518149314474</v>
       </c>
       <c r="L9" t="n">
-        <v>577.8452942234256</v>
+        <v>103.7168717610613</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.193281758731614</v>
+        <v>2.193281758731617</v>
       </c>
       <c r="C2" t="n">
-        <v>2.473335205096267</v>
+        <v>2.473335205096268</v>
       </c>
       <c r="D2" t="n">
-        <v>4.135646519226106</v>
+        <v>4.135646519226105</v>
       </c>
       <c r="E2" t="n">
-        <v>2.657185475044239</v>
+        <v>2.657185475044245</v>
       </c>
       <c r="F2" t="n">
-        <v>2.173807689924674</v>
+        <v>2.173807689924673</v>
       </c>
       <c r="G2" t="n">
-        <v>3.306674419127447</v>
+        <v>3.306674419127449</v>
       </c>
       <c r="H2" t="n">
-        <v>4.145421898297166</v>
+        <v>4.145421898297172</v>
       </c>
       <c r="I2" t="n">
-        <v>2.657634107617802</v>
+        <v>2.657634107617806</v>
       </c>
       <c r="J2" t="n">
-        <v>3.166096038948012</v>
+        <v>3.166096038948</v>
       </c>
       <c r="K2" t="n">
         <v>2.376695470611205</v>
       </c>
       <c r="L2" t="n">
-        <v>3.925159601393477</v>
+        <v>3.925159601393476</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.494397104131255</v>
+        <v>2.494397104131256</v>
       </c>
       <c r="C3" t="n">
-        <v>2.843007324505798</v>
+        <v>2.843007324505799</v>
       </c>
       <c r="D3" t="n">
-        <v>4.728518938347901</v>
+        <v>4.728518938347903</v>
       </c>
       <c r="E3" t="n">
-        <v>3.028026249662276</v>
+        <v>3.02802624966228</v>
       </c>
       <c r="F3" t="n">
         <v>2.54464846454271</v>
       </c>
       <c r="G3" t="n">
-        <v>3.775029302181239</v>
+        <v>3.77502930218124</v>
       </c>
       <c r="H3" t="n">
-        <v>4.740280379841106</v>
+        <v>4.740280379841118</v>
       </c>
       <c r="I3" t="n">
-        <v>3.024196622298816</v>
+        <v>3.024196622298822</v>
       </c>
       <c r="J3" t="n">
-        <v>3.535464445246478</v>
+        <v>3.535464445246483</v>
       </c>
       <c r="K3" t="n">
-        <v>2.723427858500084</v>
+        <v>2.723427858500086</v>
       </c>
       <c r="L3" t="n">
-        <v>4.486281194033266</v>
+        <v>4.486281194033271</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.994087791978838</v>
+        <v>1.574964347321308</v>
       </c>
       <c r="C4" t="n">
-        <v>3.035472978475857</v>
+        <v>1.633619886558799</v>
       </c>
       <c r="D4" t="n">
-        <v>5.148741337116273</v>
+        <v>2.729617892458672</v>
       </c>
       <c r="E4" t="n">
-        <v>3.325464605508936</v>
+        <v>1.684664806062048</v>
       </c>
       <c r="F4" t="n">
-        <v>3.325464605508931</v>
+        <v>1.684664806062047</v>
       </c>
       <c r="G4" t="n">
-        <v>4.650869626077013</v>
+        <v>2.235934510848359</v>
       </c>
       <c r="H4" t="n">
-        <v>5.154430543498339</v>
+        <v>2.73530709884077</v>
       </c>
       <c r="I4" t="n">
-        <v>4.239812386463512</v>
+        <v>1.845461729283945</v>
       </c>
       <c r="J4" t="n">
-        <v>4.264205111596416</v>
+        <v>1.845081666938954</v>
       </c>
       <c r="K4" t="n">
-        <v>4.174621134862091</v>
+        <v>1.75549769020456</v>
       </c>
       <c r="L4" t="n">
-        <v>5.023629619564339</v>
+        <v>2.604506174906828</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.24217609033904</v>
+        <v>6.018627863754307</v>
       </c>
       <c r="C5" t="n">
-        <v>54.38515566898469</v>
+        <v>10.67116399111748</v>
       </c>
       <c r="D5" t="n">
-        <v>141.3873342486284</v>
+        <v>26.70761011495771</v>
       </c>
       <c r="E5" t="n">
-        <v>54.38516342799171</v>
+        <v>10.6711717501247</v>
       </c>
       <c r="F5" t="n">
-        <v>54.38516342799166</v>
+        <v>10.6711717501247</v>
       </c>
       <c r="G5" t="n">
-        <v>95.93577948828371</v>
+        <v>18.30207855954067</v>
       </c>
       <c r="H5" t="n">
-        <v>160.1698041334994</v>
+        <v>30.01801270284701</v>
       </c>
       <c r="I5" t="n">
-        <v>54.38500774188277</v>
+        <v>10.67101606401553</v>
       </c>
       <c r="J5" t="n">
-        <v>59.03831513504787</v>
+        <v>11.48532497882976</v>
       </c>
       <c r="K5" t="n">
-        <v>47.1817885303314</v>
+        <v>9.324759110792344</v>
       </c>
       <c r="L5" t="n">
-        <v>33.93672429370617</v>
+        <v>7.693210809982219</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.74245684218576</v>
+        <v>3.994677287046664</v>
       </c>
       <c r="C6" t="n">
-        <v>6.307395148192118</v>
+        <v>2.209478185308525</v>
       </c>
       <c r="D6" t="n">
-        <v>7.88700011469903</v>
+        <v>3.211551434701986</v>
       </c>
       <c r="E6" t="n">
-        <v>6.220253786066301</v>
+        <v>2.194147699079458</v>
       </c>
       <c r="F6" t="n">
-        <v>6.509782497343584</v>
+        <v>2.245104751988136</v>
       </c>
       <c r="G6" t="n">
-        <v>6.933344146973235</v>
+        <v>4.655647450573245</v>
       </c>
       <c r="H6" t="n">
-        <v>7.47898384912288</v>
+        <v>5.735810470897867</v>
       </c>
       <c r="I6" t="n">
-        <v>17.98818143667046</v>
+        <v>4.265174669008889</v>
       </c>
       <c r="J6" t="n">
-        <v>18.67903298618569</v>
+        <v>4.382091359119561</v>
       </c>
       <c r="K6" t="n">
-        <v>6.261904396953141</v>
+        <v>2.122859542342021</v>
       </c>
       <c r="L6" t="n">
-        <v>7.323692758644937</v>
+        <v>3.009317285191431</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.995911206044829</v>
+        <v>2.279285264380742</v>
       </c>
       <c r="C7" t="n">
-        <v>8.241783727631432</v>
+        <v>2.549930573445063</v>
       </c>
       <c r="D7" t="n">
-        <v>9.150644526848605</v>
+        <v>3.433952850035266</v>
       </c>
       <c r="E7" t="n">
-        <v>8.096472099319621</v>
+        <v>2.524362120422718</v>
       </c>
       <c r="F7" t="n">
-        <v>8.096472099319621</v>
+        <v>2.524362120422718</v>
       </c>
       <c r="G7" t="n">
-        <v>8.6526930401429</v>
+        <v>2.940255427907526</v>
       </c>
       <c r="H7" t="n">
-        <v>9.156253957564212</v>
+        <v>3.439628015900198</v>
       </c>
       <c r="I7" t="n">
-        <v>8.241635800529458</v>
+        <v>2.549782646343111</v>
       </c>
       <c r="J7" t="n">
-        <v>8.266028525662446</v>
+        <v>2.549402583998336</v>
       </c>
       <c r="K7" t="n">
-        <v>8.176444548928114</v>
+        <v>2.459818607263859</v>
       </c>
       <c r="L7" t="n">
-        <v>9.025453033630409</v>
+        <v>3.30882709196617</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.04014834517488</v>
+        <v>4.04707099128874</v>
       </c>
       <c r="C8" t="n">
-        <v>27.85995081126722</v>
+        <v>6.002727961455633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.91952824426538</v>
+        <v>7.265276363540101</v>
       </c>
       <c r="E8" t="n">
-        <v>25.218634798875</v>
+        <v>5.537862739215511</v>
       </c>
       <c r="F8" t="n">
-        <v>18.50711697115701</v>
+        <v>4.356635607937736</v>
       </c>
       <c r="G8" t="n">
-        <v>28.40800243890263</v>
+        <v>6.417189863249111</v>
       </c>
       <c r="H8" t="n">
-        <v>28.91156335625796</v>
+        <v>6.916562451230107</v>
       </c>
       <c r="I8" t="n">
-        <v>27.9969451992893</v>
+        <v>6.026717081684741</v>
       </c>
       <c r="J8" t="n">
-        <v>28.02324641490758</v>
+        <v>6.026672913663497</v>
       </c>
       <c r="K8" t="n">
-        <v>18.04029353632326</v>
+        <v>4.195856019638317</v>
       </c>
       <c r="L8" t="n">
-        <v>38.92478942152893</v>
+        <v>8.571110267722009</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>484.1935669986195</v>
+        <v>86.09007222973605</v>
       </c>
       <c r="C9" t="n">
-        <v>617.5833097951706</v>
+        <v>109.7940385802185</v>
       </c>
       <c r="D9" t="n">
-        <v>618.4920937478997</v>
+        <v>110.6780473318267</v>
       </c>
       <c r="E9" t="n">
-        <v>771.2285217747975</v>
+        <v>136.8356021355273</v>
       </c>
       <c r="F9" t="n">
-        <v>617.5833162593907</v>
+        <v>109.7940461113436</v>
       </c>
       <c r="G9" t="n">
-        <v>617.994219107683</v>
+        <v>110.184363434681</v>
       </c>
       <c r="H9" t="n">
-        <v>618.4977800251033</v>
+        <v>110.6837360226735</v>
       </c>
       <c r="I9" t="n">
-        <v>617.5831618680686</v>
+        <v>109.7938906531169</v>
       </c>
       <c r="J9" t="n">
-        <v>617.6075545932024</v>
+        <v>109.7935105907717</v>
       </c>
       <c r="K9" t="n">
-        <v>540.3738905148116</v>
+        <v>96.1265685897164</v>
       </c>
       <c r="L9" t="n">
-        <v>618.3669791011689</v>
+        <v>110.5529350987397</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.548366858058741</v>
+        <v>2.548366858058734</v>
       </c>
       <c r="C2" t="n">
         <v>2.87576422950749</v>
       </c>
       <c r="D2" t="n">
-        <v>4.406438670816221</v>
+        <v>4.406438670816185</v>
       </c>
       <c r="E2" t="n">
-        <v>3.138402353223961</v>
+        <v>3.138402353223958</v>
       </c>
       <c r="F2" t="n">
-        <v>2.424679713448701</v>
+        <v>2.424679713448689</v>
       </c>
       <c r="G2" t="n">
-        <v>3.69902258242596</v>
+        <v>3.699022582425937</v>
       </c>
       <c r="H2" t="n">
-        <v>4.253591383298559</v>
+        <v>4.253591383298563</v>
       </c>
       <c r="I2" t="n">
-        <v>2.857090058197975</v>
+        <v>2.857090058197969</v>
       </c>
       <c r="J2" t="n">
-        <v>3.936252174296598</v>
+        <v>3.936252174296586</v>
       </c>
       <c r="K2" t="n">
-        <v>3.186858219720291</v>
+        <v>3.186858219720298</v>
       </c>
       <c r="L2" t="n">
-        <v>4.017392002445208</v>
+        <v>4.017392002445206</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.922498975976334</v>
+        <v>2.922498975976317</v>
       </c>
       <c r="C3" t="n">
-        <v>3.29505395262454</v>
+        <v>3.295053952624515</v>
       </c>
       <c r="D3" t="n">
-        <v>5.059666459063897</v>
+        <v>5.059666459063837</v>
       </c>
       <c r="E3" t="n">
-        <v>3.558909848339825</v>
+        <v>3.558909848339809</v>
       </c>
       <c r="F3" t="n">
-        <v>2.845187208564565</v>
+        <v>2.845187208564558</v>
       </c>
       <c r="G3" t="n">
-        <v>4.245991416613861</v>
+        <v>4.245991416613855</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8845938761078</v>
+        <v>4.884593876107771</v>
       </c>
       <c r="I3" t="n">
-        <v>3.274496968483069</v>
+        <v>3.274496968483073</v>
       </c>
       <c r="J3" t="n">
-        <v>4.360283662911366</v>
+        <v>4.360283662911336</v>
       </c>
       <c r="K3" t="n">
-        <v>3.634956617331166</v>
+        <v>3.63495661733115</v>
       </c>
       <c r="L3" t="n">
-        <v>4.612015557456098</v>
+        <v>4.612015557456096</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.655450348774357</v>
+        <v>2.001919714091984</v>
       </c>
       <c r="C4" t="n">
-        <v>4.761997634802418</v>
+        <v>1.995898484991</v>
       </c>
       <c r="D4" t="n">
-        <v>6.759995308278226</v>
+        <v>3.106464673594894</v>
       </c>
       <c r="E4" t="n">
-        <v>5.087207110183606</v>
+        <v>2.053141347056838</v>
       </c>
       <c r="F4" t="n">
-        <v>5.087207110183605</v>
+        <v>2.053141347056837</v>
       </c>
       <c r="G4" t="n">
-        <v>6.33359235470156</v>
+        <v>2.684901949411684</v>
       </c>
       <c r="H4" t="n">
-        <v>6.669104403194574</v>
+        <v>3.015573768511611</v>
       </c>
       <c r="I4" t="n">
-        <v>5.803786692076994</v>
+        <v>2.179103209715973</v>
       </c>
       <c r="J4" t="n">
-        <v>5.852931371397307</v>
+        <v>2.19940073671319</v>
       </c>
       <c r="K4" t="n">
-        <v>5.948178219873041</v>
+        <v>2.294647585190004</v>
       </c>
       <c r="L4" t="n">
-        <v>6.528844612999897</v>
+        <v>2.875313978316806</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>37.95506165618199</v>
+        <v>7.686651273392489</v>
       </c>
       <c r="C5" t="n">
-        <v>52.44600275767888</v>
+        <v>10.38828334114226</v>
       </c>
       <c r="D5" t="n">
-        <v>135.840037233004</v>
+        <v>25.82455192924608</v>
       </c>
       <c r="E5" t="n">
-        <v>52.44601003281096</v>
+        <v>10.3882906162744</v>
       </c>
       <c r="F5" t="n">
-        <v>52.44601003281096</v>
+        <v>10.3882906162744</v>
       </c>
       <c r="G5" t="n">
-        <v>101.1454479958789</v>
+        <v>19.37178845183924</v>
       </c>
       <c r="H5" t="n">
-        <v>146.4281878938511</v>
+        <v>27.61317232958237</v>
       </c>
       <c r="I5" t="n">
-        <v>52.44582053879334</v>
+        <v>10.38810112225676</v>
       </c>
       <c r="J5" t="n">
-        <v>59.26130928137739</v>
+        <v>11.59927519793567</v>
       </c>
       <c r="K5" t="n">
-        <v>61.56288991753346</v>
+        <v>12.08283679093973</v>
       </c>
       <c r="L5" t="n">
-        <v>137.3825625492124</v>
+        <v>10.99280833281544</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.366352146172344</v>
+        <v>4.56777720104412</v>
       </c>
       <c r="C6" t="n">
-        <v>8.301425535158629</v>
+        <v>2.618837792078247</v>
       </c>
       <c r="D6" t="n">
-        <v>9.859701935013788</v>
+        <v>3.652013036944155</v>
       </c>
       <c r="E6" t="n">
-        <v>8.110592137984341</v>
+        <v>2.585257109066451</v>
       </c>
       <c r="F6" t="n">
-        <v>8.500700581112984</v>
+        <v>2.653916194685044</v>
       </c>
       <c r="G6" t="n">
-        <v>9.044494152098883</v>
+        <v>5.250759436363571</v>
       </c>
       <c r="H6" t="n">
-        <v>24.1221451481697</v>
+        <v>6.087308922982817</v>
       </c>
       <c r="I6" t="n">
-        <v>8.514688489473961</v>
+        <v>4.744960696667818</v>
       </c>
       <c r="J6" t="n">
-        <v>8.742108172286938</v>
+        <v>4.876338898386825</v>
       </c>
       <c r="K6" t="n">
-        <v>8.438053863248543</v>
+        <v>2.732865696049513</v>
       </c>
       <c r="L6" t="n">
-        <v>9.20803319178647</v>
+        <v>3.34685116562834</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.8616660809747</v>
+        <v>2.742213678947794</v>
       </c>
       <c r="C7" t="n">
-        <v>10.0101846431624</v>
+        <v>2.9195793934573</v>
       </c>
       <c r="D7" t="n">
-        <v>10.96621961930202</v>
+        <v>3.846760148323769</v>
       </c>
       <c r="E7" t="n">
-        <v>9.914731997292373</v>
+        <v>2.902785722584098</v>
       </c>
       <c r="F7" t="n">
-        <v>9.914731997292373</v>
+        <v>2.902785722584098</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5398080869019</v>
+        <v>3.425195914267529</v>
       </c>
       <c r="H7" t="n">
-        <v>10.87532013539461</v>
+        <v>3.755867733367391</v>
       </c>
       <c r="I7" t="n">
-        <v>10.01000242427691</v>
+        <v>2.919397174571812</v>
       </c>
       <c r="J7" t="n">
-        <v>10.05914710359583</v>
+        <v>2.939694701569016</v>
       </c>
       <c r="K7" t="n">
-        <v>10.15439395207286</v>
+        <v>3.034941550045775</v>
       </c>
       <c r="L7" t="n">
-        <v>10.73506034519994</v>
+        <v>3.615607943172613</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.88986838312274</v>
+        <v>4.507177274562207</v>
       </c>
       <c r="C8" t="n">
-        <v>30.30521506845153</v>
+        <v>6.491504729006374</v>
       </c>
       <c r="D8" t="n">
-        <v>33.49788256170388</v>
+        <v>7.812332804698528</v>
       </c>
       <c r="E8" t="n">
-        <v>27.48239039957956</v>
+        <v>5.994693584632813</v>
       </c>
       <c r="F8" t="n">
-        <v>20.3097140877222</v>
+        <v>4.732302560586265</v>
       </c>
       <c r="G8" t="n">
-        <v>30.92408092141039</v>
+        <v>7.012827913701098</v>
       </c>
       <c r="H8" t="n">
-        <v>31.25959296977464</v>
+        <v>7.343499732778276</v>
       </c>
       <c r="I8" t="n">
-        <v>30.39427525878591</v>
+        <v>6.507029174005372</v>
       </c>
       <c r="J8" t="n">
-        <v>30.44545517541655</v>
+        <v>6.527684902767511</v>
       </c>
       <c r="K8" t="n">
-        <v>19.99022692984093</v>
+        <v>4.766048144752945</v>
       </c>
       <c r="L8" t="n">
-        <v>41.93711478524406</v>
+        <v>9.107169494863749</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>453.2314934813811</v>
+        <v>80.77530287858917</v>
       </c>
       <c r="C9" t="n">
-        <v>577.7303512441823</v>
+        <v>102.8383281738168</v>
       </c>
       <c r="D9" t="n">
-        <v>578.6863813521468</v>
+        <v>103.7655080718844</v>
       </c>
       <c r="E9" t="n">
-        <v>721.2280151344229</v>
+        <v>128.0939228763578</v>
       </c>
       <c r="F9" t="n">
-        <v>577.7303573004293</v>
+        <v>102.8383352344249</v>
       </c>
       <c r="G9" t="n">
-        <v>578.2599746879217</v>
+        <v>103.3439446946271</v>
       </c>
       <c r="H9" t="n">
-        <v>578.5954867364151</v>
+        <v>103.6746165137269</v>
       </c>
       <c r="I9" t="n">
-        <v>577.7301690252972</v>
+        <v>102.8381459549313</v>
       </c>
       <c r="J9" t="n">
-        <v>577.7793137046157</v>
+        <v>102.8584434819285</v>
       </c>
       <c r="K9" t="n">
-        <v>421.2952860807673</v>
+        <v>75.39573817260155</v>
       </c>
       <c r="L9" t="n">
-        <v>578.4552269462196</v>
+        <v>103.5343567235323</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.726532635910215</v>
+        <v>2.726532635910172</v>
       </c>
       <c r="C2" t="n">
-        <v>3.293750317934935</v>
+        <v>3.293750317934995</v>
       </c>
       <c r="D2" t="n">
-        <v>4.404545689765432</v>
+        <v>4.404545689765389</v>
       </c>
       <c r="E2" t="n">
-        <v>3.608036838548284</v>
+        <v>3.608036838548421</v>
       </c>
       <c r="F2" t="n">
-        <v>2.746959968616255</v>
+        <v>2.746959968616046</v>
       </c>
       <c r="G2" t="n">
-        <v>4.029984701439112</v>
+        <v>4.029984701439165</v>
       </c>
       <c r="H2" t="n">
-        <v>4.190500513912196</v>
+        <v>4.190500513911953</v>
       </c>
       <c r="I2" t="n">
-        <v>3.132290491828071</v>
+        <v>3.132290491827769</v>
       </c>
       <c r="J2" t="n">
-        <v>4.49181879469391</v>
+        <v>4.491818794693807</v>
       </c>
       <c r="K2" t="n">
-        <v>3.588449565388191</v>
+        <v>3.588449565388131</v>
       </c>
       <c r="L2" t="n">
-        <v>4.109926631486903</v>
+        <v>4.109926631486879</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.143942159112759</v>
+        <v>3.143942159112727</v>
       </c>
       <c r="C3" t="n">
-        <v>3.771252603706571</v>
+        <v>3.771252603706711</v>
       </c>
       <c r="D3" t="n">
-        <v>5.07400477040319</v>
+        <v>5.074004770403122</v>
       </c>
       <c r="E3" t="n">
-        <v>4.086422663348356</v>
+        <v>4.086422663348127</v>
       </c>
       <c r="F3" t="n">
-        <v>3.225345793416316</v>
+        <v>3.225345793416171</v>
       </c>
       <c r="G3" t="n">
-        <v>4.643182043752913</v>
+        <v>4.643182043752857</v>
       </c>
       <c r="H3" t="n">
-        <v>4.828575453602785</v>
+        <v>4.828575453602471</v>
       </c>
       <c r="I3" t="n">
-        <v>3.610837483527681</v>
+        <v>3.61083748352783</v>
       </c>
       <c r="J3" t="n">
-        <v>4.961774626230932</v>
+        <v>4.96177462623081</v>
       </c>
       <c r="K3" t="n">
-        <v>4.081694316818709</v>
+        <v>4.081694316818649</v>
       </c>
       <c r="L3" t="n">
-        <v>4.734940929144602</v>
+        <v>4.73494092914456</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.874857087831599</v>
+        <v>2.280503959169976</v>
       </c>
       <c r="C4" t="n">
-        <v>6.455016449549712</v>
+        <v>2.405454653477866</v>
       </c>
       <c r="D4" t="n">
-        <v>7.872364744904342</v>
+        <v>3.278011616242218</v>
       </c>
       <c r="E4" t="n">
-        <v>6.787504901197427</v>
+        <v>2.463976767189338</v>
       </c>
       <c r="F4" t="n">
-        <v>6.78750490119745</v>
+        <v>2.463976767189255</v>
       </c>
       <c r="G4" t="n">
-        <v>7.642844912717897</v>
+        <v>3.054143761666763</v>
       </c>
       <c r="H4" t="n">
-        <v>7.745196094165245</v>
+        <v>3.150842965502166</v>
       </c>
       <c r="I4" t="n">
-        <v>7.074380852526081</v>
+        <v>2.514307081707301</v>
       </c>
       <c r="J4" t="n">
-        <v>7.082813592291404</v>
+        <v>2.488460463628317</v>
       </c>
       <c r="K4" t="n">
-        <v>7.174981482428072</v>
+        <v>2.580628353765015</v>
       </c>
       <c r="L4" t="n">
-        <v>7.697429262642359</v>
+        <v>3.103076133979265</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.34969012790619</v>
+        <v>8.348074541345049</v>
       </c>
       <c r="C5" t="n">
-        <v>60.94885151655532</v>
+        <v>11.99636957329997</v>
       </c>
       <c r="D5" t="n">
-        <v>126.5966240421747</v>
+        <v>24.17348113933734</v>
       </c>
       <c r="E5" t="n">
-        <v>60.94885654876251</v>
+        <v>11.99637460550763</v>
       </c>
       <c r="F5" t="n">
-        <v>60.94885654876251</v>
+        <v>11.99637460550763</v>
       </c>
       <c r="G5" t="n">
-        <v>111.2533221312417</v>
+        <v>21.28958765331583</v>
       </c>
       <c r="H5" t="n">
-        <v>131.3798808073314</v>
+        <v>24.91054735711116</v>
       </c>
       <c r="I5" t="n">
-        <v>60.94866255283727</v>
+        <v>11.99618060958147</v>
       </c>
       <c r="J5" t="n">
-        <v>64.81015762127338</v>
+        <v>12.64847295767621</v>
       </c>
       <c r="K5" t="n">
-        <v>63.39078882651284</v>
+        <v>12.47461039271252</v>
       </c>
       <c r="L5" t="n">
-        <v>135.0103545149901</v>
+        <v>25.51015085697779</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.01065085986438</v>
+        <v>2.832403660056981</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06334843459111</v>
+        <v>3.040521079404229</v>
       </c>
       <c r="D6" t="n">
-        <v>24.34678912422808</v>
+        <v>6.17751029129214</v>
       </c>
       <c r="E6" t="n">
-        <v>9.793151041020039</v>
+        <v>2.992970484932151</v>
       </c>
       <c r="F6" t="n">
-        <v>10.22977938293014</v>
+        <v>3.069817072691693</v>
       </c>
       <c r="G6" t="n">
-        <v>10.77863868475023</v>
+        <v>3.606043462553821</v>
       </c>
       <c r="H6" t="n">
-        <v>26.30869670333611</v>
+        <v>6.418019055012717</v>
       </c>
       <c r="I6" t="n">
-        <v>22.82735115754938</v>
+        <v>5.286829840368269</v>
       </c>
       <c r="J6" t="n">
-        <v>23.41731623631782</v>
+        <v>3.077362065200118</v>
       </c>
       <c r="K6" t="n">
-        <v>10.08051328522741</v>
+        <v>3.092001948286862</v>
       </c>
       <c r="L6" t="n">
-        <v>10.78438528618211</v>
+        <v>3.646380391178594</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.47027260131999</v>
+        <v>3.089297085161377</v>
       </c>
       <c r="C7" t="n">
-        <v>11.66998532973257</v>
+        <v>3.323289171416855</v>
       </c>
       <c r="D7" t="n">
-        <v>12.46769863574346</v>
+        <v>4.086790376647562</v>
       </c>
       <c r="E7" t="n">
-        <v>11.70172644653888</v>
+        <v>3.328879754482994</v>
       </c>
       <c r="F7" t="n">
-        <v>11.70172644653888</v>
+        <v>3.328879754482994</v>
       </c>
       <c r="G7" t="n">
-        <v>12.23826042620564</v>
+        <v>3.862936887658157</v>
       </c>
       <c r="H7" t="n">
-        <v>12.34061160765251</v>
+        <v>3.959636091493383</v>
       </c>
       <c r="I7" t="n">
-        <v>11.66979636601436</v>
+        <v>3.323100207698602</v>
       </c>
       <c r="J7" t="n">
-        <v>11.67822910577868</v>
+        <v>3.29725358961973</v>
       </c>
       <c r="K7" t="n">
-        <v>11.7703969959155</v>
+        <v>3.389421479756415</v>
       </c>
       <c r="L7" t="n">
-        <v>12.29284477612963</v>
+        <v>3.911869259970575</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21.92117493025077</v>
+        <v>4.928655885086398</v>
       </c>
       <c r="C8" t="n">
-        <v>33.36111482466797</v>
+        <v>7.140927941838822</v>
       </c>
       <c r="D8" t="n">
-        <v>36.45018314076081</v>
+        <v>8.307707626658704</v>
       </c>
       <c r="E8" t="n">
-        <v>30.29244247091188</v>
+        <v>6.600845757043316</v>
       </c>
       <c r="F8" t="n">
-        <v>22.49513533971776</v>
+        <v>5.228519709389178</v>
       </c>
       <c r="G8" t="n">
-        <v>33.89670617289467</v>
+        <v>7.674823318420186</v>
       </c>
       <c r="H8" t="n">
-        <v>33.99905735420678</v>
+        <v>7.771522522231852</v>
       </c>
       <c r="I8" t="n">
-        <v>33.32824211270312</v>
+        <v>7.134986638460945</v>
       </c>
       <c r="J8" t="n">
-        <v>33.33887742037479</v>
+        <v>7.109527672331307</v>
       </c>
       <c r="K8" t="n">
-        <v>22.01311345531286</v>
+        <v>5.192139566842187</v>
       </c>
       <c r="L8" t="n">
-        <v>45.65850674822406</v>
+        <v>9.784225735239113</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>454.4806337019452</v>
+        <v>81.05912021638352</v>
       </c>
       <c r="C9" t="n">
-        <v>579.1849795491361</v>
+        <v>103.2059276128071</v>
       </c>
       <c r="D9" t="n">
-        <v>579.9827788032285</v>
+        <v>103.9694439449002</v>
       </c>
       <c r="E9" t="n">
-        <v>722.8606936701661</v>
+        <v>128.4928573076276</v>
       </c>
       <c r="F9" t="n">
-        <v>579.1849833688252</v>
+        <v>103.2059324316112</v>
       </c>
       <c r="G9" t="n">
-        <v>579.753254645611</v>
+        <v>103.7455753290489</v>
       </c>
       <c r="H9" t="n">
-        <v>579.8556058270569</v>
+        <v>103.8422745328841</v>
       </c>
       <c r="I9" t="n">
-        <v>579.1847905854183</v>
+        <v>103.2057386490893</v>
       </c>
       <c r="J9" t="n">
-        <v>579.1932233251829</v>
+        <v>103.1798920310101</v>
       </c>
       <c r="K9" t="n">
-        <v>507.1469196381175</v>
+        <v>90.57568899235643</v>
       </c>
       <c r="L9" t="n">
-        <v>579.8078389955338</v>
+        <v>103.7945077013611</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.753135266312106</v>
+        <v>2.753135266312112</v>
       </c>
       <c r="C2" t="n">
-        <v>2.851378727542472</v>
+        <v>2.851378727542481</v>
       </c>
       <c r="D2" t="n">
-        <v>3.15008204272348</v>
+        <v>3.150082042723487</v>
       </c>
       <c r="E2" t="n">
         <v>3.119094101456278</v>
       </c>
       <c r="F2" t="n">
-        <v>2.393199491483585</v>
+        <v>2.393199491483586</v>
       </c>
       <c r="G2" t="n">
-        <v>4.604507579115397</v>
+        <v>4.604507579115404</v>
       </c>
       <c r="H2" t="n">
-        <v>3.301158321392578</v>
+        <v>3.301158321392576</v>
       </c>
       <c r="I2" t="n">
         <v>2.830745686487175</v>
       </c>
       <c r="J2" t="n">
-        <v>4.047345164784452</v>
+        <v>4.047345164784445</v>
       </c>
       <c r="K2" t="n">
-        <v>3.202690435361147</v>
+        <v>3.20269043536115</v>
       </c>
       <c r="L2" t="n">
-        <v>2.797524801416948</v>
+        <v>2.797524801416953</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.166408464994274</v>
+        <v>3.166408464994273</v>
       </c>
       <c r="C3" t="n">
-        <v>3.275323524739529</v>
+        <v>3.275323524739528</v>
       </c>
       <c r="D3" t="n">
-        <v>3.622979485144369</v>
+        <v>3.622979485144372</v>
       </c>
       <c r="E3" t="n">
-        <v>3.544006527562844</v>
+        <v>3.544006527562847</v>
       </c>
       <c r="F3" t="n">
-        <v>2.818111917590152</v>
+        <v>2.818111917590151</v>
       </c>
       <c r="G3" t="n">
-        <v>5.295870135337271</v>
+        <v>5.295870135337281</v>
       </c>
       <c r="H3" t="n">
         <v>3.797476420770371</v>
       </c>
       <c r="I3" t="n">
-        <v>3.253813841439526</v>
+        <v>3.253813841439525</v>
       </c>
       <c r="J3" t="n">
-        <v>4.490962754368979</v>
+        <v>4.490962754368968</v>
       </c>
       <c r="K3" t="n">
         <v>3.657934168807959</v>
       </c>
       <c r="L3" t="n">
-        <v>3.217362905995953</v>
+        <v>3.217362905995955</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.360717383220217</v>
+        <v>2.226448187841663</v>
       </c>
       <c r="C4" t="n">
-        <v>5.49167894182076</v>
+        <v>2.111448645278816</v>
       </c>
       <c r="D4" t="n">
-        <v>6.596685421734889</v>
+        <v>2.462416226356587</v>
       </c>
       <c r="E4" t="n">
-        <v>5.827629997410304</v>
+        <v>2.170580915708846</v>
       </c>
       <c r="F4" t="n">
-        <v>5.827629997410305</v>
+        <v>2.170580915708845</v>
       </c>
       <c r="G4" t="n">
-        <v>7.45330016139917</v>
+        <v>3.325606166714123</v>
       </c>
       <c r="H4" t="n">
-        <v>6.686893805319116</v>
+        <v>2.552624609940323</v>
       </c>
       <c r="I4" t="n">
-        <v>6.357987377157825</v>
+        <v>2.263673653496914</v>
       </c>
       <c r="J4" t="n">
-        <v>6.480807902649365</v>
+        <v>2.34653870727083</v>
       </c>
       <c r="K4" t="n">
-        <v>6.52681936024887</v>
+        <v>2.392550164870049</v>
       </c>
       <c r="L4" t="n">
-        <v>6.387758876217192</v>
+        <v>2.253489680838532</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.55000098626078</v>
+        <v>9.651762061741811</v>
       </c>
       <c r="C5" t="n">
-        <v>52.46836018971175</v>
+        <v>10.37934450010716</v>
       </c>
       <c r="D5" t="n">
-        <v>67.83711435592564</v>
+        <v>13.24073166037032</v>
       </c>
       <c r="E5" t="n">
-        <v>52.46836611806931</v>
+        <v>10.37935042846475</v>
       </c>
       <c r="F5" t="n">
-        <v>52.46836611806931</v>
+        <v>10.37935042846475</v>
       </c>
       <c r="G5" t="n">
-        <v>151.245723503653</v>
+        <v>28.63307253781967</v>
       </c>
       <c r="H5" t="n">
-        <v>84.46674586002977</v>
+        <v>16.24187849739321</v>
       </c>
       <c r="I5" t="n">
-        <v>52.4680625251792</v>
+        <v>10.37904683557467</v>
       </c>
       <c r="J5" t="n">
-        <v>64.86993993864982</v>
+        <v>12.62302588992275</v>
       </c>
       <c r="K5" t="n">
-        <v>62.79252164409017</v>
+        <v>12.29531371316684</v>
       </c>
       <c r="L5" t="n">
-        <v>34.87450912675968</v>
+        <v>11.49760712547448</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.582002008203791</v>
+        <v>2.793394278766665</v>
       </c>
       <c r="C6" t="n">
-        <v>9.231038353436993</v>
+        <v>2.769575898157147</v>
       </c>
       <c r="D6" t="n">
-        <v>9.975311875970544</v>
+        <v>5.499809784182816</v>
       </c>
       <c r="E6" t="n">
-        <v>9.013697308758735</v>
+        <v>2.7313287594677</v>
       </c>
       <c r="F6" t="n">
-        <v>9.511598046354036</v>
+        <v>2.818959288809633</v>
       </c>
       <c r="G6" t="n">
-        <v>24.16999648970828</v>
+        <v>3.89255225763926</v>
       </c>
       <c r="H6" t="n">
-        <v>26.40419609002333</v>
+        <v>6.022869793244339</v>
       </c>
       <c r="I6" t="n">
-        <v>23.07468370546711</v>
+        <v>2.830619744421912</v>
       </c>
       <c r="J6" t="n">
-        <v>23.59364934586164</v>
+        <v>5.358398784955909</v>
       </c>
       <c r="K6" t="n">
-        <v>9.483666663112462</v>
+        <v>2.912955287354263</v>
       </c>
       <c r="L6" t="n">
-        <v>9.494820160652614</v>
+        <v>2.800332463936408</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.32962200626189</v>
+        <v>3.100975396758102</v>
       </c>
       <c r="C7" t="n">
-        <v>11.32718966473233</v>
+        <v>3.138498526946086</v>
       </c>
       <c r="D7" t="n">
-        <v>11.56552719540865</v>
+        <v>3.33693237378424</v>
       </c>
       <c r="E7" t="n">
-        <v>11.30817883628943</v>
+        <v>3.13515750612491</v>
       </c>
       <c r="F7" t="n">
-        <v>11.30817883628943</v>
+        <v>3.13515750612491</v>
       </c>
       <c r="G7" t="n">
-        <v>12.4222047844412</v>
+        <v>4.200133375630882</v>
       </c>
       <c r="H7" t="n">
-        <v>11.65579842836068</v>
+        <v>3.427151818857364</v>
       </c>
       <c r="I7" t="n">
-        <v>11.32689200019986</v>
+        <v>3.138200862413612</v>
       </c>
       <c r="J7" t="n">
-        <v>11.44971252569104</v>
+        <v>3.221065916187596</v>
       </c>
       <c r="K7" t="n">
-        <v>11.4957239832903</v>
+        <v>3.267077373786646</v>
       </c>
       <c r="L7" t="n">
-        <v>11.35666349925897</v>
+        <v>3.128016889755494</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22.60360334989352</v>
+        <v>5.085196102485556</v>
       </c>
       <c r="C8" t="n">
-        <v>34.35420448105116</v>
+        <v>7.191253112582443</v>
       </c>
       <c r="D8" t="n">
-        <v>37.04869065570733</v>
+        <v>7.821969118494154</v>
       </c>
       <c r="E8" t="n">
-        <v>31.13717421730238</v>
+        <v>6.625060674272797</v>
       </c>
       <c r="F8" t="n">
-        <v>22.96292234035574</v>
+        <v>5.186392351725761</v>
       </c>
       <c r="G8" t="n">
-        <v>35.4649711550201</v>
+        <v>8.255660234877629</v>
       </c>
       <c r="H8" t="n">
-        <v>34.69856479884848</v>
+        <v>7.482678678087634</v>
       </c>
       <c r="I8" t="n">
-        <v>34.36965837077889</v>
+        <v>7.193727721660223</v>
       </c>
       <c r="J8" t="n">
-        <v>34.49479177250905</v>
+        <v>7.276999841649948</v>
       </c>
       <c r="K8" t="n">
-        <v>22.55109410557912</v>
+        <v>5.212822504766125</v>
       </c>
       <c r="L8" t="n">
-        <v>46.69290989424196</v>
+        <v>9.347196221573006</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>488.9503077985724</v>
+        <v>87.16221564071027</v>
       </c>
       <c r="C9" t="n">
-        <v>623.040823075855</v>
+        <v>110.8000974239282</v>
       </c>
       <c r="D9" t="n">
-        <v>623.2792300094582</v>
+        <v>110.9985434856812</v>
       </c>
       <c r="E9" t="n">
-        <v>777.7812527125129</v>
+        <v>138.0344177773745</v>
       </c>
       <c r="F9" t="n">
-        <v>623.0408285735928</v>
+        <v>110.8001032764968</v>
       </c>
       <c r="G9" t="n">
-        <v>624.1358381955633</v>
+        <v>111.8617322726128</v>
       </c>
       <c r="H9" t="n">
-        <v>623.3694318394832</v>
+        <v>111.0887507158394</v>
       </c>
       <c r="I9" t="n">
-        <v>623.0405254113209</v>
+        <v>110.7997997593956</v>
       </c>
       <c r="J9" t="n">
-        <v>623.1633459368134</v>
+        <v>110.882664813169</v>
       </c>
       <c r="K9" t="n">
-        <v>454.3623991373043</v>
+        <v>97.25453626656706</v>
       </c>
       <c r="L9" t="n">
-        <v>623.0702969103816</v>
+        <v>110.7896157867372</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.663688246752086</v>
+        <v>6.663688246752091</v>
       </c>
       <c r="C2" t="n">
-        <v>4.183008194757096</v>
+        <v>4.183008194757093</v>
       </c>
       <c r="D2" t="n">
-        <v>3.326477260265669</v>
+        <v>3.326477260265686</v>
       </c>
       <c r="E2" t="n">
-        <v>4.536706013602578</v>
+        <v>4.536706013602569</v>
       </c>
       <c r="F2" t="n">
-        <v>3.555807620361388</v>
+        <v>3.555807620361378</v>
       </c>
       <c r="G2" t="n">
-        <v>7.183710931247479</v>
+        <v>7.183710931247481</v>
       </c>
       <c r="H2" t="n">
-        <v>3.24500926649428</v>
+        <v>3.245009266494278</v>
       </c>
       <c r="I2" t="n">
-        <v>3.962655712289133</v>
+        <v>3.962655712289141</v>
       </c>
       <c r="J2" t="n">
-        <v>6.059058002239947</v>
+        <v>6.059058002239946</v>
       </c>
       <c r="K2" t="n">
-        <v>5.869461799387661</v>
+        <v>5.869461799387647</v>
       </c>
       <c r="L2" t="n">
-        <v>3.253574893815276</v>
+        <v>3.253574893815277</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.724349232667818</v>
+        <v>7.724349232667835</v>
       </c>
       <c r="C3" t="n">
-        <v>4.836324364838432</v>
+        <v>4.836324364838429</v>
       </c>
       <c r="D3" t="n">
-        <v>3.885865297035213</v>
+        <v>3.885865297035217</v>
       </c>
       <c r="E3" t="n">
-        <v>5.191632268837607</v>
+        <v>5.191632268837622</v>
       </c>
       <c r="F3" t="n">
-        <v>4.210733875596416</v>
+        <v>4.210733875596418</v>
       </c>
       <c r="G3" t="n">
-        <v>8.322483042212074</v>
+        <v>8.322483042212102</v>
       </c>
       <c r="H3" t="n">
-        <v>3.793354844476819</v>
+        <v>3.793354844476818</v>
       </c>
       <c r="I3" t="n">
-        <v>4.612863854785347</v>
+        <v>4.612863854785344</v>
       </c>
       <c r="J3" t="n">
-        <v>6.782305275934881</v>
+        <v>6.782305275934867</v>
       </c>
       <c r="K3" t="n">
         <v>6.745189698674543</v>
       </c>
       <c r="L3" t="n">
-        <v>3.802018538181507</v>
+        <v>3.802018538181511</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.12687172035307</v>
+        <v>4.748579597815321</v>
       </c>
       <c r="C4" t="n">
-        <v>7.125530486246384</v>
+        <v>2.897215249642537</v>
       </c>
       <c r="D4" t="n">
-        <v>8.143041198511709</v>
+        <v>2.764749075974171</v>
       </c>
       <c r="E4" t="n">
-        <v>7.564920281269295</v>
+        <v>2.974554740740924</v>
       </c>
       <c r="F4" t="n">
-        <v>7.564920281269298</v>
+        <v>2.974554740740924</v>
       </c>
       <c r="G4" t="n">
-        <v>10.42442332899929</v>
+        <v>5.055672996326682</v>
       </c>
       <c r="H4" t="n">
-        <v>8.095635361240872</v>
+        <v>2.717343238703226</v>
       </c>
       <c r="I4" t="n">
-        <v>8.450063230759934</v>
+        <v>3.129927623830127</v>
       </c>
       <c r="J4" t="n">
-        <v>8.791528127742694</v>
+        <v>3.413236005204811</v>
       </c>
       <c r="K4" t="n">
-        <v>9.394983230504447</v>
+        <v>4.016691107966762</v>
       </c>
       <c r="L4" t="n">
-        <v>8.100980077730661</v>
+        <v>2.722687955192268</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>235.1099834550851</v>
+        <v>44.34560704856752</v>
       </c>
       <c r="C5" t="n">
-        <v>89.41165436440505</v>
+        <v>17.3795729737243</v>
       </c>
       <c r="D5" t="n">
-        <v>56.7817432315318</v>
+        <v>11.32516058739982</v>
       </c>
       <c r="E5" t="n">
-        <v>89.41166272313488</v>
+        <v>17.37958133245414</v>
       </c>
       <c r="F5" t="n">
-        <v>89.41166272313491</v>
+        <v>17.37958133245414</v>
       </c>
       <c r="G5" t="n">
-        <v>251.2127271628228</v>
+        <v>47.43441424144585</v>
       </c>
       <c r="H5" t="n">
-        <v>57.59576249191313</v>
+        <v>11.42936556649442</v>
       </c>
       <c r="I5" t="n">
-        <v>89.41116238918288</v>
+        <v>17.37908099850204</v>
       </c>
       <c r="J5" t="n">
-        <v>120.4560598665499</v>
+        <v>23.06619348474322</v>
       </c>
       <c r="K5" t="n">
-        <v>161.9374584490378</v>
+        <v>30.86416660095262</v>
       </c>
       <c r="L5" t="n">
-        <v>32.27910129640673</v>
+        <v>6.978037266621131</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.72567484830793</v>
+        <v>8.036078820485615</v>
       </c>
       <c r="C6" t="n">
-        <v>12.45236492986876</v>
+        <v>3.834738106640016</v>
       </c>
       <c r="D6" t="n">
-        <v>12.52307349712591</v>
+        <v>3.535628984063945</v>
       </c>
       <c r="E6" t="n">
-        <v>12.06829496724873</v>
+        <v>3.76714868117855</v>
       </c>
       <c r="F6" t="n">
-        <v>12.88251368313204</v>
+        <v>3.910451174397514</v>
       </c>
       <c r="G6" t="n">
-        <v>15.02322645695374</v>
+        <v>5.865062342460784</v>
       </c>
       <c r="H6" t="n">
-        <v>30.30187027346767</v>
+        <v>3.505474400862159</v>
       </c>
       <c r="I6" t="n">
-        <v>13.04886635871417</v>
+        <v>3.939316969964306</v>
       </c>
       <c r="J6" t="n">
-        <v>13.55998788241789</v>
+        <v>6.815770589723337</v>
       </c>
       <c r="K6" t="n">
-        <v>13.87672374888921</v>
+        <v>4.80547743492824</v>
       </c>
       <c r="L6" t="n">
-        <v>12.46936937357144</v>
+        <v>3.491524467094274</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.44137975547268</v>
+        <v>5.683933006928251</v>
       </c>
       <c r="C7" t="n">
-        <v>13.76506324110164</v>
+        <v>4.065773008165112</v>
       </c>
       <c r="D7" t="n">
-        <v>13.45757160459134</v>
+        <v>3.700106422375794</v>
       </c>
       <c r="E7" t="n">
-        <v>13.64986572333593</v>
+        <v>4.045505132741597</v>
       </c>
       <c r="F7" t="n">
-        <v>13.64986572333594</v>
+        <v>4.045505132741597</v>
       </c>
       <c r="G7" t="n">
-        <v>15.73893136411855</v>
+        <v>5.991026405439387</v>
       </c>
       <c r="H7" t="n">
-        <v>13.41014339636048</v>
+        <v>3.652696647815913</v>
       </c>
       <c r="I7" t="n">
-        <v>13.76457126587936</v>
+        <v>4.065281032942832</v>
       </c>
       <c r="J7" t="n">
-        <v>14.10603616286192</v>
+        <v>4.348589414317464</v>
       </c>
       <c r="K7" t="n">
-        <v>14.70949126562391</v>
+        <v>4.952044517079479</v>
       </c>
       <c r="L7" t="n">
-        <v>13.41548811285003</v>
+        <v>3.658041364305014</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.06989266904195</v>
+        <v>7.730551268626279</v>
       </c>
       <c r="C8" t="n">
-        <v>38.13870880742283</v>
+        <v>8.355534604593107</v>
       </c>
       <c r="D8" t="n">
-        <v>40.60393631180576</v>
+        <v>8.477866584956637</v>
       </c>
       <c r="E8" t="n">
-        <v>34.63500354304576</v>
+        <v>7.738889368997543</v>
       </c>
       <c r="F8" t="n">
-        <v>25.73225822215299</v>
+        <v>6.172006201010734</v>
       </c>
       <c r="G8" t="n">
-        <v>40.22021310157383</v>
+        <v>10.29973196788429</v>
       </c>
       <c r="H8" t="n">
-        <v>37.89142513382158</v>
+        <v>7.961402210261855</v>
       </c>
       <c r="I8" t="n">
-        <v>38.24585300333457</v>
+        <v>8.373986595387786</v>
       </c>
       <c r="J8" t="n">
-        <v>38.58984379471558</v>
+        <v>8.657739534174059</v>
       </c>
       <c r="K8" t="n">
-        <v>26.09925740381042</v>
+        <v>6.956643346538068</v>
       </c>
       <c r="L8" t="n">
-        <v>51.32256157688523</v>
+        <v>10.32968625782426</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>462.0182446420284</v>
+        <v>84.28146080107307</v>
       </c>
       <c r="C9" t="n">
-        <v>586.2233053180156</v>
+        <v>104.818423067763</v>
       </c>
       <c r="D9" t="n">
-        <v>585.9158023167757</v>
+        <v>104.4527544817817</v>
       </c>
       <c r="E9" t="n">
-        <v>731.4877641220895</v>
+        <v>130.3849745663387</v>
       </c>
       <c r="F9" t="n">
-        <v>586.2233139444751</v>
+        <v>104.8184314736134</v>
       </c>
       <c r="G9" t="n">
-        <v>588.1971734410314</v>
+        <v>106.7436764650376</v>
       </c>
       <c r="H9" t="n">
-        <v>585.8683854732745</v>
+        <v>104.4053467074141</v>
       </c>
       <c r="I9" t="n">
-        <v>586.222813342793</v>
+        <v>104.8179310925408</v>
       </c>
       <c r="J9" t="n">
-        <v>586.5642782397754</v>
+        <v>105.1012394739157</v>
       </c>
       <c r="K9" t="n">
-        <v>511.2724610760045</v>
+        <v>92.34712673014704</v>
       </c>
       <c r="L9" t="n">
-        <v>585.8737301897642</v>
+        <v>104.4106914239027</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.164103649758951</v>
+        <v>9.164103649758953</v>
       </c>
       <c r="C2" t="n">
-        <v>4.655598054898277</v>
+        <v>4.655598054898284</v>
       </c>
       <c r="D2" t="n">
-        <v>3.704576288219672</v>
+        <v>3.704576288219678</v>
       </c>
       <c r="E2" t="n">
-        <v>5.046991607285166</v>
+        <v>5.046991607285172</v>
       </c>
       <c r="F2" t="n">
-        <v>3.954435572511772</v>
+        <v>3.954435572511774</v>
       </c>
       <c r="G2" t="n">
-        <v>7.306999063580052</v>
+        <v>7.306999063580057</v>
       </c>
       <c r="H2" t="n">
-        <v>3.123529969447763</v>
+        <v>3.123529969447767</v>
       </c>
       <c r="I2" t="n">
-        <v>4.332930930510667</v>
+        <v>4.332930930510673</v>
       </c>
       <c r="J2" t="n">
-        <v>6.811529182161204</v>
+        <v>6.811529182161212</v>
       </c>
       <c r="K2" t="n">
-        <v>5.927920076794805</v>
+        <v>5.927920076794812</v>
       </c>
       <c r="L2" t="n">
-        <v>3.712676468503032</v>
+        <v>3.712676468503033</v>
       </c>
     </row>
     <row r="3">
@@ -6894,34 +6894,34 @@
         <v>10.66182463239614</v>
       </c>
       <c r="C3" t="n">
-        <v>5.425724705675027</v>
+        <v>5.425724705675036</v>
       </c>
       <c r="D3" t="n">
-        <v>4.382237228940104</v>
+        <v>4.382237228940109</v>
       </c>
       <c r="E3" t="n">
-        <v>5.819037365561011</v>
+        <v>5.819037365561019</v>
       </c>
       <c r="F3" t="n">
-        <v>4.726481330787617</v>
+        <v>4.726481330787621</v>
       </c>
       <c r="G3" t="n">
-        <v>8.525769660234314</v>
+        <v>8.525769660234337</v>
       </c>
       <c r="H3" t="n">
-        <v>3.715226663718636</v>
+        <v>3.715226663718641</v>
       </c>
       <c r="I3" t="n">
-        <v>5.099358195607856</v>
+        <v>5.099358195607863</v>
       </c>
       <c r="J3" t="n">
-        <v>7.670615320164231</v>
+        <v>7.670615320164247</v>
       </c>
       <c r="K3" t="n">
-        <v>6.860216042893632</v>
+        <v>6.860216042893642</v>
       </c>
       <c r="L3" t="n">
-        <v>4.391530204445521</v>
+        <v>4.391530204445525</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.26171684081452</v>
+        <v>6.328824609833422</v>
       </c>
       <c r="C4" t="n">
-        <v>7.786635032340967</v>
+        <v>3.174738901144817</v>
       </c>
       <c r="D4" t="n">
-        <v>9.016259164177523</v>
+        <v>3.083366933196123</v>
       </c>
       <c r="E4" t="n">
-        <v>8.277352524350761</v>
+        <v>3.26111301244106</v>
       </c>
       <c r="F4" t="n">
-        <v>8.277352524350762</v>
+        <v>3.261113012441061</v>
       </c>
       <c r="G4" t="n">
-        <v>11.14658603371128</v>
+        <v>5.222890320741237</v>
       </c>
       <c r="H4" t="n">
-        <v>8.671927904232001</v>
+        <v>2.739035673250023</v>
       </c>
       <c r="I4" t="n">
-        <v>9.321731062545185</v>
+        <v>3.444542603606116</v>
       </c>
       <c r="J4" t="n">
-        <v>9.734264882246856</v>
+        <v>3.801372651265276</v>
       </c>
       <c r="K4" t="n">
-        <v>10.02399903152175</v>
+        <v>4.091106800539722</v>
       </c>
       <c r="L4" t="n">
-        <v>9.022286170932702</v>
+        <v>3.089393939951293</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>358.1866815616135</v>
+        <v>67.21161807079382</v>
       </c>
       <c r="C5" t="n">
-        <v>105.7481920317266</v>
+        <v>20.41597283961308</v>
       </c>
       <c r="D5" t="n">
-        <v>73.13011829871888</v>
+        <v>14.367406079732</v>
       </c>
       <c r="E5" t="n">
-        <v>105.7482015380014</v>
+        <v>20.41598234588804</v>
       </c>
       <c r="F5" t="n">
-        <v>105.7482015380014</v>
+        <v>20.41598234588804</v>
       </c>
       <c r="G5" t="n">
-        <v>260.9739898105921</v>
+        <v>49.19251314721851</v>
       </c>
       <c r="H5" t="n">
-        <v>49.27418241764547</v>
+        <v>9.885032428889934</v>
       </c>
       <c r="I5" t="n">
-        <v>105.7477391222724</v>
+        <v>20.41551993015914</v>
       </c>
       <c r="J5" t="n">
-        <v>144.9532471171606</v>
+        <v>27.59991339565517</v>
       </c>
       <c r="K5" t="n">
-        <v>153.1654428815947</v>
+        <v>29.28400078164244</v>
       </c>
       <c r="L5" t="n">
-        <v>145.0399667558218</v>
+        <v>16.81209708942294</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.23778668770254</v>
+        <v>7.204612898139748</v>
       </c>
       <c r="C6" t="n">
-        <v>13.69486133917514</v>
+        <v>4.214586725513128</v>
       </c>
       <c r="D6" t="n">
-        <v>29.32994324150397</v>
+        <v>3.917261072258421</v>
       </c>
       <c r="E6" t="n">
-        <v>13.25107332188954</v>
+        <v>4.136487868064568</v>
       </c>
       <c r="F6" t="n">
-        <v>14.13508264571403</v>
+        <v>4.292073508214623</v>
       </c>
       <c r="G6" t="n">
-        <v>16.12265588059807</v>
+        <v>8.65346826581653</v>
       </c>
       <c r="H6" t="n">
-        <v>32.06632144768113</v>
+        <v>6.856448914586593</v>
       </c>
       <c r="I6" t="n">
-        <v>14.29780090943288</v>
+        <v>4.320330891912791</v>
       </c>
       <c r="J6" t="n">
-        <v>14.92064109708259</v>
+        <v>7.364038323673608</v>
       </c>
       <c r="K6" t="n">
-        <v>14.86365574233151</v>
+        <v>4.942886377026865</v>
       </c>
       <c r="L6" t="n">
-        <v>13.77083544429562</v>
+        <v>3.925138607534205</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.74539407589256</v>
+        <v>7.293951797977191</v>
       </c>
       <c r="C7" t="n">
-        <v>14.80586120707707</v>
+        <v>4.410122701204344</v>
       </c>
       <c r="D7" t="n">
-        <v>14.49998708039192</v>
+        <v>4.048503041220264</v>
       </c>
       <c r="E7" t="n">
-        <v>14.64216752732117</v>
+        <v>4.381320446893896</v>
       </c>
       <c r="F7" t="n">
-        <v>14.64216752732117</v>
+        <v>4.381320446893896</v>
       </c>
       <c r="G7" t="n">
-        <v>16.63026326878957</v>
+        <v>6.18801750888534</v>
       </c>
       <c r="H7" t="n">
-        <v>14.15560513931002</v>
+        <v>3.704162861394565</v>
       </c>
       <c r="I7" t="n">
-        <v>14.80540829762293</v>
+        <v>4.409669791750148</v>
       </c>
       <c r="J7" t="n">
-        <v>15.21794211732489</v>
+        <v>4.766499839409336</v>
       </c>
       <c r="K7" t="n">
-        <v>15.50767626659824</v>
+        <v>5.056233988683936</v>
       </c>
       <c r="L7" t="n">
-        <v>14.50596340601075</v>
+        <v>4.054521128094971</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.70115422513268</v>
+        <v>9.398165572841434</v>
       </c>
       <c r="C8" t="n">
-        <v>40.07939851755756</v>
+        <v>8.85826524382369</v>
       </c>
       <c r="D8" t="n">
-        <v>42.72085178259743</v>
+        <v>9.015375201894889</v>
       </c>
       <c r="E8" t="n">
-        <v>36.41134565179863</v>
+        <v>8.212695776041222</v>
       </c>
       <c r="F8" t="n">
-        <v>27.09097612645567</v>
+        <v>6.572310748469478</v>
       </c>
       <c r="G8" t="n">
-        <v>42.05773210040908</v>
+        <v>10.663251999001</v>
       </c>
       <c r="H8" t="n">
-        <v>39.58307397099751</v>
+        <v>8.179397351522155</v>
       </c>
       <c r="I8" t="n">
-        <v>40.23287712924383</v>
+        <v>8.884904281865918</v>
       </c>
       <c r="J8" t="n">
-        <v>40.64805847469928</v>
+        <v>9.242200294055225</v>
       </c>
       <c r="K8" t="n">
-        <v>27.21319251558515</v>
+        <v>7.116404837342311</v>
       </c>
       <c r="L8" t="n">
-        <v>54.00575839364083</v>
+        <v>11.00648500824848</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>463.4016589165251</v>
+        <v>85.72945398491785</v>
       </c>
       <c r="C9" t="n">
-        <v>586.2678000539867</v>
+        <v>104.9874233932719</v>
       </c>
       <c r="D9" t="n">
-        <v>585.9618867100888</v>
+        <v>104.6257968310583</v>
       </c>
       <c r="E9" t="n">
-        <v>731.4449008616167</v>
+        <v>130.5386008301334</v>
       </c>
       <c r="F9" t="n">
-        <v>586.2678100772144</v>
+        <v>104.9874329905302</v>
       </c>
       <c r="G9" t="n">
-        <v>588.0922021156981</v>
+        <v>106.7653182009529</v>
       </c>
       <c r="H9" t="n">
-        <v>585.6175439862193</v>
+        <v>104.2814635534617</v>
       </c>
       <c r="I9" t="n">
-        <v>586.2673471445339</v>
+        <v>104.9869704838178</v>
       </c>
       <c r="J9" t="n">
-        <v>586.6798809642339</v>
+        <v>105.3438005314772</v>
       </c>
       <c r="K9" t="n">
-        <v>514.0773183389341</v>
+        <v>92.28399990888974</v>
       </c>
       <c r="L9" t="n">
-        <v>585.9679022529189</v>
+        <v>104.6318218201627</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.773395820393467</v>
+        <v>2.773395820393471</v>
       </c>
       <c r="C2" t="n">
-        <v>2.508716982468831</v>
+        <v>2.508716982468842</v>
       </c>
       <c r="D2" t="n">
-        <v>4.262681263883191</v>
+        <v>4.262681263883218</v>
       </c>
       <c r="E2" t="n">
-        <v>2.718043266309492</v>
+        <v>2.718043266309512</v>
       </c>
       <c r="F2" t="n">
-        <v>2.161296037406784</v>
+        <v>2.161296037406796</v>
       </c>
       <c r="G2" t="n">
-        <v>4.344862340915585</v>
+        <v>4.344862340915565</v>
       </c>
       <c r="H2" t="n">
-        <v>4.843809795215688</v>
+        <v>4.843809795215715</v>
       </c>
       <c r="I2" t="n">
-        <v>2.644159205901505</v>
+        <v>2.644159205901502</v>
       </c>
       <c r="J2" t="n">
-        <v>3.223204145324943</v>
+        <v>3.223204145324988</v>
       </c>
       <c r="K2" t="n">
-        <v>2.404245183558392</v>
+        <v>2.404245183558408</v>
       </c>
       <c r="L2" t="n">
-        <v>3.77325223071015</v>
+        <v>3.773252230710167</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.169678365871794</v>
+        <v>3.169678365871811</v>
       </c>
       <c r="C3" t="n">
-        <v>2.884469838366551</v>
+        <v>2.88446983836655</v>
       </c>
       <c r="D3" t="n">
-        <v>4.882665130435221</v>
+        <v>4.882665130435225</v>
       </c>
       <c r="E3" t="n">
-        <v>3.094871180751908</v>
+        <v>3.09487118075194</v>
       </c>
       <c r="F3" t="n">
-        <v>2.538123951849195</v>
+        <v>2.538123951849217</v>
       </c>
       <c r="G3" t="n">
-        <v>4.977190392781251</v>
+        <v>4.977190392781252</v>
       </c>
       <c r="H3" t="n">
-        <v>5.551657247573201</v>
+        <v>5.551657247573218</v>
       </c>
       <c r="I3" t="n">
-        <v>3.017386411611354</v>
+        <v>3.017386411611363</v>
       </c>
       <c r="J3" t="n">
-        <v>3.586188086538607</v>
+        <v>3.586188086538659</v>
       </c>
       <c r="K3" t="n">
-        <v>2.751910903426094</v>
+        <v>2.751910903426125</v>
       </c>
       <c r="L3" t="n">
-        <v>4.319642760013302</v>
+        <v>4.31964276001331</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.999186445020308</v>
+        <v>2.019690820472727</v>
       </c>
       <c r="C4" t="n">
-        <v>3.809493229953322</v>
+        <v>1.74685655265834</v>
       </c>
       <c r="D4" t="n">
-        <v>5.884503534797512</v>
+        <v>2.905007910249996</v>
       </c>
       <c r="E4" t="n">
-        <v>4.11000666055928</v>
+        <v>1.799752646912052</v>
       </c>
       <c r="F4" t="n">
-        <v>4.110006660559281</v>
+        <v>1.799752646912042</v>
       </c>
       <c r="G4" t="n">
-        <v>5.925660293405684</v>
+        <v>2.952506510194554</v>
       </c>
       <c r="H4" t="n">
-        <v>6.229923714548844</v>
+        <v>3.250428090001315</v>
       </c>
       <c r="I4" t="n">
-        <v>4.875038080231796</v>
+        <v>1.934163333799814</v>
       </c>
       <c r="J4" t="n">
-        <v>4.867404373820417</v>
+        <v>1.887908749272854</v>
       </c>
       <c r="K4" t="n">
-        <v>4.806781204151723</v>
+        <v>1.827285579604151</v>
       </c>
       <c r="L4" t="n">
-        <v>5.593897155599991</v>
+        <v>2.614401531052418</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56.50180033539878</v>
+        <v>11.08415081606263</v>
       </c>
       <c r="C5" t="n">
-        <v>48.82739653417209</v>
+        <v>9.67000749126842</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8531330089035</v>
+        <v>26.13148657183756</v>
       </c>
       <c r="E5" t="n">
-        <v>48.82740348897018</v>
+        <v>9.67001444606653</v>
       </c>
       <c r="F5" t="n">
-        <v>48.82740348897018</v>
+        <v>9.67001444606653</v>
       </c>
       <c r="G5" t="n">
-        <v>147.7489751563577</v>
+        <v>27.91340979082082</v>
       </c>
       <c r="H5" t="n">
-        <v>184.8595123107687</v>
+        <v>34.6892355125817</v>
       </c>
       <c r="I5" t="n">
-        <v>48.82711848624599</v>
+        <v>9.669729443342355</v>
       </c>
       <c r="J5" t="n">
-        <v>47.64033790117593</v>
+        <v>9.41594500929603</v>
       </c>
       <c r="K5" t="n">
-        <v>38.77637961438988</v>
+        <v>7.805934867410164</v>
       </c>
       <c r="L5" t="n">
-        <v>134.6491346487231</v>
+        <v>25.3281232067655</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.560026653439454</v>
+        <v>2.470398694712319</v>
       </c>
       <c r="C6" t="n">
-        <v>7.124070303743809</v>
+        <v>2.330222114484428</v>
       </c>
       <c r="D6" t="n">
-        <v>8.828705975512539</v>
+        <v>3.423187537008034</v>
       </c>
       <c r="E6" t="n">
-        <v>6.99666711315494</v>
+        <v>2.307804883815956</v>
       </c>
       <c r="F6" t="n">
-        <v>7.385370955937939</v>
+        <v>2.376216759775072</v>
       </c>
       <c r="G6" t="n">
-        <v>20.50827764890129</v>
+        <v>5.519047150854746</v>
       </c>
       <c r="H6" t="n">
-        <v>24.33036369974905</v>
+        <v>6.436105510134611</v>
       </c>
       <c r="I6" t="n">
-        <v>7.435878288650988</v>
+        <v>4.500703974460011</v>
       </c>
       <c r="J6" t="n">
-        <v>20.19446528382207</v>
+        <v>4.585471454816155</v>
       </c>
       <c r="K6" t="n">
-        <v>7.061711468178736</v>
+        <v>2.224153303922438</v>
       </c>
       <c r="L6" t="n">
-        <v>8.119605480881063</v>
+        <v>3.058926193893178</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.295451822396442</v>
+        <v>2.775833522793713</v>
       </c>
       <c r="C7" t="n">
-        <v>9.171581505533961</v>
+        <v>2.690584084046891</v>
       </c>
       <c r="D7" t="n">
-        <v>10.18078875828297</v>
+        <v>3.661154105486176</v>
       </c>
       <c r="E7" t="n">
-        <v>9.07948237326147</v>
+        <v>2.674380367608406</v>
       </c>
       <c r="F7" t="n">
-        <v>9.079482373261436</v>
+        <v>2.674380367608406</v>
       </c>
       <c r="G7" t="n">
-        <v>10.22192567078183</v>
+        <v>3.708649212515533</v>
       </c>
       <c r="H7" t="n">
-        <v>10.52618909192509</v>
+        <v>4.006570792322274</v>
       </c>
       <c r="I7" t="n">
-        <v>9.171303457608017</v>
+        <v>2.690306036120792</v>
       </c>
       <c r="J7" t="n">
-        <v>9.163669751196617</v>
+        <v>2.644051451593838</v>
       </c>
       <c r="K7" t="n">
-        <v>9.103046581527906</v>
+        <v>2.583428281925132</v>
       </c>
       <c r="L7" t="n">
-        <v>9.890162532976165</v>
+        <v>3.370544233373398</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.79037720562084</v>
+        <v>4.622940380232504</v>
       </c>
       <c r="C8" t="n">
-        <v>29.97579672892602</v>
+        <v>6.352125943571988</v>
       </c>
       <c r="D8" t="n">
-        <v>33.22656036621293</v>
+        <v>7.717209886503743</v>
       </c>
       <c r="E8" t="n">
-        <v>27.14189443462397</v>
+        <v>5.853364873182613</v>
       </c>
       <c r="F8" t="n">
-        <v>19.94107208537977</v>
+        <v>4.58602014658283</v>
       </c>
       <c r="G8" t="n">
-        <v>31.11217830151105</v>
+        <v>7.385333655601436</v>
       </c>
       <c r="H8" t="n">
-        <v>31.41644172260682</v>
+        <v>7.68325523539982</v>
       </c>
       <c r="I8" t="n">
-        <v>30.06155608833703</v>
+        <v>6.366990479206694</v>
       </c>
       <c r="J8" t="n">
-        <v>30.05596534406521</v>
+        <v>6.321095456014388</v>
       </c>
       <c r="K8" t="n">
-        <v>19.40487342575041</v>
+        <v>4.396549796683755</v>
       </c>
       <c r="L8" t="n">
-        <v>41.63920370022124</v>
+        <v>8.958375448530406</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>486.6553921872228</v>
+        <v>86.79118257175739</v>
       </c>
       <c r="C9" t="n">
-        <v>620.1700107547194</v>
+        <v>110.22630704921</v>
       </c>
       <c r="D9" t="n">
-        <v>621.1792024753781</v>
+        <v>111.1968743370015</v>
       </c>
       <c r="E9" t="n">
-        <v>774.386001740958</v>
+        <v>137.3683270464699</v>
       </c>
       <c r="F9" t="n">
-        <v>620.1700157517882</v>
+        <v>110.2263136594482</v>
       </c>
       <c r="G9" t="n">
-        <v>621.2203549199663</v>
+        <v>111.2443721776787</v>
       </c>
       <c r="H9" t="n">
-        <v>621.5246183411102</v>
+        <v>111.5422937574856</v>
       </c>
       <c r="I9" t="n">
-        <v>620.1697327067923</v>
+        <v>110.226029001284</v>
       </c>
       <c r="J9" t="n">
-        <v>620.1620990003814</v>
+        <v>110.179774416757</v>
       </c>
       <c r="K9" t="n">
-        <v>539.52935234458</v>
+        <v>96.49135454774851</v>
       </c>
       <c r="L9" t="n">
-        <v>620.8885917821619</v>
+        <v>110.9062671985365</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.346590480423521</v>
+        <v>4.346590480423525</v>
       </c>
       <c r="C2" t="n">
-        <v>3.218608060821611</v>
+        <v>3.218608060821618</v>
       </c>
       <c r="D2" t="n">
-        <v>4.387931967854262</v>
+        <v>4.387931967854298</v>
       </c>
       <c r="E2" t="n">
-        <v>3.520394577797945</v>
+        <v>3.520394577797941</v>
       </c>
       <c r="F2" t="n">
-        <v>2.692736247028573</v>
+        <v>2.692736247028578</v>
       </c>
       <c r="G2" t="n">
-        <v>6.296277450770925</v>
+        <v>6.296277450770948</v>
       </c>
       <c r="H2" t="n">
-        <v>3.427812815904559</v>
+        <v>3.427812815904568</v>
       </c>
       <c r="I2" t="n">
         <v>3.143039661658932</v>
       </c>
       <c r="J2" t="n">
-        <v>5.154897537103388</v>
+        <v>5.154897537103381</v>
       </c>
       <c r="K2" t="n">
-        <v>3.552739630706152</v>
+        <v>3.552739630706165</v>
       </c>
       <c r="L2" t="n">
-        <v>4.034680882266207</v>
+        <v>4.034680882266204</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.008573998930297</v>
+        <v>5.008573998930308</v>
       </c>
       <c r="C3" t="n">
-        <v>3.698345952020502</v>
+        <v>3.698345952020509</v>
       </c>
       <c r="D3" t="n">
-        <v>5.056125273338908</v>
+        <v>5.056125273339018</v>
       </c>
       <c r="E3" t="n">
-        <v>4.001552686687934</v>
+        <v>4.001552686687938</v>
       </c>
       <c r="F3" t="n">
-        <v>3.173894355918566</v>
+        <v>3.17389435591857</v>
       </c>
       <c r="G3" t="n">
-        <v>7.251117891269014</v>
+        <v>7.251117891269029</v>
       </c>
       <c r="H3" t="n">
-        <v>3.952758156779784</v>
+        <v>3.952758156779806</v>
       </c>
       <c r="I3" t="n">
-        <v>3.619531622325482</v>
+        <v>3.61953162232549</v>
       </c>
       <c r="J3" t="n">
-        <v>5.745303116283944</v>
+        <v>5.745303116283941</v>
       </c>
       <c r="K3" t="n">
-        <v>4.063686660949148</v>
+        <v>4.06368666094916</v>
       </c>
       <c r="L3" t="n">
-        <v>4.649764842492983</v>
+        <v>4.649764842492994</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.55524708265756</v>
+        <v>3.186658525543494</v>
       </c>
       <c r="C4" t="n">
-        <v>5.534350544157052</v>
+        <v>2.241293482235625</v>
       </c>
       <c r="D4" t="n">
-        <v>7.579822845147695</v>
+        <v>3.211234288033654</v>
       </c>
       <c r="E4" t="n">
-        <v>5.911738797912153</v>
+        <v>2.307720294430245</v>
       </c>
       <c r="F4" t="n">
-        <v>5.911738797912154</v>
+        <v>2.30772029443024</v>
       </c>
       <c r="G4" t="n">
-        <v>8.702805604945004</v>
+        <v>4.343650007305289</v>
       </c>
       <c r="H4" t="n">
-        <v>7.009847131876006</v>
+        <v>2.641258574761937</v>
       </c>
       <c r="I4" t="n">
-        <v>6.768734802373319</v>
+        <v>2.458155427763828</v>
       </c>
       <c r="J4" t="n">
-        <v>7.271971272606929</v>
+        <v>2.903382715492841</v>
       </c>
       <c r="K4" t="n">
-        <v>6.957507276749866</v>
+        <v>2.588918719635776</v>
       </c>
       <c r="L4" t="n">
-        <v>7.370664076085034</v>
+        <v>3.002075518970963</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122.0352461977838</v>
+        <v>23.33513826062905</v>
       </c>
       <c r="C5" t="n">
-        <v>57.16388436681453</v>
+        <v>11.32809138578559</v>
       </c>
       <c r="D5" t="n">
-        <v>117.502881524113</v>
+        <v>22.55769251070111</v>
       </c>
       <c r="E5" t="n">
-        <v>57.16389223076303</v>
+        <v>11.32809924973413</v>
       </c>
       <c r="F5" t="n">
-        <v>57.16389223076308</v>
+        <v>11.32809924973413</v>
       </c>
       <c r="G5" t="n">
-        <v>221.130383818678</v>
+        <v>41.7309035703356</v>
       </c>
       <c r="H5" t="n">
-        <v>78.2096610205068</v>
+        <v>15.17242575125951</v>
       </c>
       <c r="I5" t="n">
-        <v>57.16341145086764</v>
+        <v>11.32761846983872</v>
       </c>
       <c r="J5" t="n">
-        <v>104.8068631373803</v>
+        <v>20.06952359067648</v>
       </c>
       <c r="K5" t="n">
-        <v>66.5752975363625</v>
+        <v>13.08164974847166</v>
       </c>
       <c r="L5" t="n">
-        <v>122.7482683688612</v>
+        <v>15.75684772655336</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.05260967080902</v>
+        <v>6.097671738106618</v>
       </c>
       <c r="C6" t="n">
-        <v>9.78378602972265</v>
+        <v>2.989194123642553</v>
       </c>
       <c r="D6" t="n">
-        <v>11.19235683602147</v>
+        <v>3.847040266982135</v>
       </c>
       <c r="E6" t="n">
-        <v>9.521712295850437</v>
+        <v>2.943075626624598</v>
       </c>
       <c r="F6" t="n">
-        <v>10.16759925630587</v>
+        <v>3.056751731048844</v>
       </c>
       <c r="G6" t="n">
-        <v>25.24265349322224</v>
+        <v>4.959185819484559</v>
       </c>
       <c r="H6" t="n">
-        <v>26.55070692625432</v>
+        <v>6.080449879936896</v>
       </c>
       <c r="I6" t="n">
-        <v>23.30858269065039</v>
+        <v>5.369168640326985</v>
       </c>
       <c r="J6" t="n">
-        <v>24.43115905413248</v>
+        <v>3.54995404956294</v>
       </c>
       <c r="K6" t="n">
-        <v>10.10930063631879</v>
+        <v>3.143634347914115</v>
       </c>
       <c r="L6" t="n">
-        <v>10.7538163773313</v>
+        <v>3.597510320763841</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.32736656750465</v>
+        <v>4.026551550325526</v>
       </c>
       <c r="C7" t="n">
-        <v>11.54132720316725</v>
+        <v>3.298521368492716</v>
       </c>
       <c r="D7" t="n">
-        <v>12.35195789910198</v>
+        <v>4.05113005297854</v>
       </c>
       <c r="E7" t="n">
-        <v>11.43026104352576</v>
+        <v>3.278980204395376</v>
       </c>
       <c r="F7" t="n">
-        <v>11.43026104352581</v>
+        <v>3.278980204395376</v>
       </c>
       <c r="G7" t="n">
-        <v>13.47492508979217</v>
+        <v>5.183543032087312</v>
       </c>
       <c r="H7" t="n">
-        <v>11.78196661672316</v>
+        <v>3.48115159954401</v>
       </c>
       <c r="I7" t="n">
-        <v>11.54085428722044</v>
+        <v>3.298048452545882</v>
       </c>
       <c r="J7" t="n">
-        <v>12.04409075745418</v>
+        <v>3.743275740274905</v>
       </c>
       <c r="K7" t="n">
-        <v>11.72962676159704</v>
+        <v>3.428811744417862</v>
       </c>
       <c r="L7" t="n">
-        <v>12.14278356093219</v>
+        <v>3.841968543752953</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23.26102744533663</v>
+        <v>5.950875854396809</v>
       </c>
       <c r="C8" t="n">
-        <v>34.00750756438305</v>
+        <v>7.252569090702406</v>
       </c>
       <c r="D8" t="n">
-        <v>37.33494187249947</v>
+        <v>8.448135208470889</v>
       </c>
       <c r="E8" t="n">
-        <v>30.83606901370785</v>
+        <v>6.694402388640601</v>
       </c>
       <c r="F8" t="n">
-        <v>22.77758299553866</v>
+        <v>5.276108857127944</v>
       </c>
       <c r="G8" t="n">
-        <v>36.04503178901739</v>
+        <v>9.15588178962641</v>
       </c>
       <c r="H8" t="n">
-        <v>34.35207331585605</v>
+        <v>7.453490357066837</v>
       </c>
       <c r="I8" t="n">
-        <v>34.11096098644566</v>
+        <v>7.270387210084926</v>
       </c>
       <c r="J8" t="n">
-        <v>34.6164843180569</v>
+        <v>7.716016985414316</v>
       </c>
       <c r="K8" t="n">
-        <v>22.44713468734655</v>
+        <v>5.315093129128746</v>
       </c>
       <c r="L8" t="n">
-        <v>46.86813091223899</v>
+        <v>9.953629644466316</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>458.0008468978282</v>
+        <v>82.46508366343488</v>
       </c>
       <c r="C9" t="n">
-        <v>582.5091070138687</v>
+        <v>103.788850070659</v>
       </c>
       <c r="D9" t="n">
-        <v>583.3197312170273</v>
+        <v>104.5414576124159</v>
       </c>
       <c r="E9" t="n">
-        <v>727.096087577636</v>
+        <v>129.2361649918869</v>
       </c>
       <c r="F9" t="n">
-        <v>582.5091145282039</v>
+        <v>103.7888578730755</v>
       </c>
       <c r="G9" t="n">
-        <v>584.4427049004943</v>
+        <v>105.6738717342537</v>
       </c>
       <c r="H9" t="n">
-        <v>582.7497464274253</v>
+        <v>103.9714803017103</v>
       </c>
       <c r="I9" t="n">
-        <v>582.5086340979227</v>
+        <v>103.7883771547122</v>
       </c>
       <c r="J9" t="n">
-        <v>583.0118705681565</v>
+        <v>104.2336044424412</v>
       </c>
       <c r="K9" t="n">
-        <v>510.1014012021381</v>
+        <v>76.15199189517324</v>
       </c>
       <c r="L9" t="n">
-        <v>583.1105633716344</v>
+        <v>104.3322972459193</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia land use results.xlsx
+++ b/Results/Ammonia/ammonia land use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.03454087579957</v>
+        <v>1.972813910297351</v>
       </c>
       <c r="C2" t="n">
-        <v>2.160839521846124</v>
+        <v>1.73461303836888</v>
       </c>
       <c r="D2" t="n">
-        <v>3.487128682813113</v>
+        <v>2.04926072150871</v>
       </c>
       <c r="E2" t="n">
-        <v>2.293344330277969</v>
+        <v>1.845830299160797</v>
       </c>
       <c r="F2" t="n">
-        <v>1.963683234590032</v>
+        <v>1.571461648110051</v>
       </c>
       <c r="G2" t="n">
-        <v>3.00189768287444</v>
+        <v>2.02372397772833</v>
       </c>
       <c r="H2" t="n">
-        <v>4.183935229767599</v>
+        <v>2.08585527590391</v>
       </c>
       <c r="I2" t="n">
-        <v>2.473722839237304</v>
+        <v>1.995924576606493</v>
       </c>
       <c r="J2" t="n">
-        <v>2.507382290067373</v>
+        <v>2.136528440098751</v>
       </c>
       <c r="K2" t="n">
-        <v>1.889124965873027</v>
+        <v>1.778435616624019</v>
       </c>
       <c r="L2" t="n">
-        <v>3.791963577715925</v>
+        <v>2.065491891569371</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.297834361873609</v>
+        <v>2.086688790018075</v>
       </c>
       <c r="C3" t="n">
-        <v>2.489495607326886</v>
+        <v>1.821066235967175</v>
       </c>
       <c r="D3" t="n">
-        <v>3.968611242596897</v>
+        <v>2.63107006093739</v>
       </c>
       <c r="E3" t="n">
-        <v>2.622598643166115</v>
+        <v>2.003334787007283</v>
       </c>
       <c r="F3" t="n">
-        <v>2.292937547478179</v>
+        <v>1.550418810714317</v>
       </c>
       <c r="G3" t="n">
-        <v>3.410495077368632</v>
+        <v>2.449891688207928</v>
       </c>
       <c r="H3" t="n">
-        <v>4.770412203552381</v>
+        <v>2.897975112621411</v>
       </c>
       <c r="I3" t="n">
-        <v>2.801389504012087</v>
+        <v>2.251096797362064</v>
       </c>
       <c r="J3" t="n">
-        <v>2.814956159280682</v>
+        <v>2.442628112678687</v>
       </c>
       <c r="K3" t="n">
-        <v>2.16654617509671</v>
+        <v>1.79304499029498</v>
       </c>
       <c r="L3" t="n">
-        <v>4.31910928978918</v>
+        <v>2.752077511995881</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.342631218167288</v>
+        <v>1.342631218167339</v>
       </c>
       <c r="C4" t="n">
-        <v>1.461041414159784</v>
+        <v>1.461041414159781</v>
       </c>
       <c r="D4" t="n">
-        <v>2.206133118070199</v>
+        <v>2.20613311807025</v>
       </c>
       <c r="E4" t="n">
-        <v>1.496721853580923</v>
+        <v>1.496721853580889</v>
       </c>
       <c r="F4" t="n">
-        <v>1.496721853580913</v>
+        <v>1.496721853580888</v>
       </c>
       <c r="G4" t="n">
-        <v>1.916887968772217</v>
+        <v>1.91688796877218</v>
       </c>
       <c r="H4" t="n">
-        <v>2.620132869583897</v>
+        <v>2.620132869583879</v>
       </c>
       <c r="I4" t="n">
-        <v>1.598753963166573</v>
+        <v>1.59875396316653</v>
       </c>
       <c r="J4" t="n">
-        <v>1.517874617477262</v>
+        <v>1.51787461747731</v>
       </c>
       <c r="K4" t="n">
-        <v>1.398542889515835</v>
+        <v>1.398542889515846</v>
       </c>
       <c r="L4" t="n">
-        <v>2.387285184329005</v>
+        <v>2.38728518432901</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.01285185488101</v>
+        <v>6.012851854881514</v>
       </c>
       <c r="C5" t="n">
-        <v>10.94758372245895</v>
+        <v>10.94758372245903</v>
       </c>
       <c r="D5" t="n">
-        <v>22.6747764831441</v>
+        <v>22.6747764831442</v>
       </c>
       <c r="E5" t="n">
-        <v>10.94758931382356</v>
+        <v>10.94758931382362</v>
       </c>
       <c r="F5" t="n">
-        <v>10.94758931382356</v>
+        <v>10.94758931382362</v>
       </c>
       <c r="G5" t="n">
-        <v>17.5063225543919</v>
+        <v>17.50632255439184</v>
       </c>
       <c r="H5" t="n">
-        <v>34.20714438037398</v>
+        <v>34.20714438037429</v>
       </c>
       <c r="I5" t="n">
-        <v>10.94746099930199</v>
+        <v>10.94746099930197</v>
       </c>
       <c r="J5" t="n">
-        <v>9.886772142714452</v>
+        <v>9.886772142715079</v>
       </c>
       <c r="K5" t="n">
-        <v>7.172111247678508</v>
+        <v>7.172111247678652</v>
       </c>
       <c r="L5" t="n">
-        <v>4.329834688887507</v>
+        <v>30.09853395185228</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.713317068362165</v>
+        <v>1.71331706836223</v>
       </c>
       <c r="C6" t="n">
-        <v>1.946593551574203</v>
+        <v>1.946593551574193</v>
       </c>
       <c r="D6" t="n">
-        <v>2.591756768099708</v>
+        <v>2.591760201566888</v>
       </c>
       <c r="E6" t="n">
-        <v>1.940651474958118</v>
+        <v>1.940651474958114</v>
       </c>
       <c r="F6" t="n">
-        <v>1.972935095100406</v>
+        <v>1.972935095100391</v>
       </c>
       <c r="G6" t="n">
-        <v>4.304274227610707</v>
+        <v>4.30427422761068</v>
       </c>
       <c r="H6" t="n">
-        <v>5.576470650255395</v>
+        <v>5.576470650255578</v>
       </c>
       <c r="I6" t="n">
-        <v>1.969439813361441</v>
+        <v>3.98614022200503</v>
       </c>
       <c r="J6" t="n">
-        <v>1.914839592664316</v>
+        <v>3.977485880211481</v>
       </c>
       <c r="K6" t="n">
-        <v>1.741084885137856</v>
+        <v>1.741084885137992</v>
       </c>
       <c r="L6" t="n">
-        <v>2.767523693054589</v>
+        <v>2.76752369305469</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.001316776779682</v>
+        <v>2.001316776779667</v>
       </c>
       <c r="C7" t="n">
-        <v>2.257562244935885</v>
+        <v>2.257562244935888</v>
       </c>
       <c r="D7" t="n">
-        <v>2.864818178655878</v>
+        <v>2.864818178655917</v>
       </c>
       <c r="E7" t="n">
-        <v>2.249288411212476</v>
+        <v>2.249288411212459</v>
       </c>
       <c r="F7" t="n">
-        <v>2.249288411212476</v>
+        <v>2.24928841121246</v>
       </c>
       <c r="G7" t="n">
-        <v>2.575573527384537</v>
+        <v>2.57557352738451</v>
       </c>
       <c r="H7" t="n">
-        <v>3.278818428196293</v>
+        <v>3.278818428196224</v>
       </c>
       <c r="I7" t="n">
-        <v>2.257439521778871</v>
+        <v>2.257439521778858</v>
       </c>
       <c r="J7" t="n">
-        <v>2.176560176089673</v>
+        <v>2.176560176089642</v>
       </c>
       <c r="K7" t="n">
-        <v>2.05722844812819</v>
+        <v>2.057228448128176</v>
       </c>
       <c r="L7" t="n">
-        <v>3.045970742941273</v>
+        <v>3.045970742941343</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.761492356289728</v>
+        <v>3.761492356289808</v>
       </c>
       <c r="C8" t="n">
-        <v>5.605372387984482</v>
+        <v>5.605372388014422</v>
       </c>
       <c r="D8" t="n">
-        <v>6.551013332854944</v>
+        <v>6.551013332854904</v>
       </c>
       <c r="E8" t="n">
-        <v>5.169901042504414</v>
+        <v>5.169901042504548</v>
       </c>
       <c r="F8" t="n">
-        <v>4.063371165433022</v>
+        <v>4.063371165433042</v>
       </c>
       <c r="G8" t="n">
-        <v>5.930985521115673</v>
+        <v>5.930985521115486</v>
       </c>
       <c r="H8" t="n">
-        <v>6.63423042192554</v>
+        <v>6.634230421925549</v>
       </c>
       <c r="I8" t="n">
-        <v>5.612851515509712</v>
+        <v>5.612851515509841</v>
       </c>
       <c r="J8" t="n">
-        <v>5.532285678835194</v>
+        <v>5.532285678835168</v>
       </c>
       <c r="K8" t="n">
-        <v>3.78777169227522</v>
+        <v>3.787771692275165</v>
       </c>
       <c r="L8" t="n">
-        <v>8.067740562264063</v>
+        <v>8.067740562263847</v>
       </c>
     </row>
     <row r="9">
@@ -795,25 +795,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91.63726705614121</v>
+        <v>91.6372670561412</v>
       </c>
       <c r="C9" t="n">
-        <v>116.8903361489344</v>
+        <v>116.8903361489345</v>
       </c>
       <c r="D9" t="n">
-        <v>117.4975928940328</v>
+        <v>117.4975928940329</v>
       </c>
       <c r="E9" t="n">
         <v>145.736146069485</v>
       </c>
       <c r="F9" t="n">
-        <v>116.8903414214004</v>
+        <v>116.8903414214003</v>
       </c>
       <c r="G9" t="n">
-        <v>117.2083474313829</v>
+        <v>117.2083474313831</v>
       </c>
       <c r="H9" t="n">
-        <v>117.911592332195</v>
+        <v>117.9115923321949</v>
       </c>
       <c r="I9" t="n">
         <v>116.8902134257775</v>
@@ -822,10 +822,10 @@
         <v>116.8093340800881</v>
       </c>
       <c r="K9" t="n">
-        <v>102.2067447057021</v>
+        <v>85.21453941026073</v>
       </c>
       <c r="L9" t="n">
-        <v>117.6787446469398</v>
+        <v>117.6787446469399</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.333052348463667</v>
+        <v>3.00722594657343</v>
       </c>
       <c r="C2" t="n">
-        <v>3.896312374844822</v>
+        <v>3.141343276769969</v>
       </c>
       <c r="D2" t="n">
-        <v>3.320463119343316</v>
+        <v>2.953935386609053</v>
       </c>
       <c r="E2" t="n">
-        <v>4.240951783453523</v>
+        <v>3.431709616498897</v>
       </c>
       <c r="F2" t="n">
-        <v>3.288212841558456</v>
+        <v>2.638728747130486</v>
       </c>
       <c r="G2" t="n">
-        <v>6.297699174291366</v>
+        <v>3.110621406913849</v>
       </c>
       <c r="H2" t="n">
-        <v>3.256980980456419</v>
+        <v>2.946616948728508</v>
       </c>
       <c r="I2" t="n">
-        <v>3.69043132348494</v>
+        <v>2.973404430548579</v>
       </c>
       <c r="J2" t="n">
-        <v>5.636067793629266</v>
+        <v>4.315441881135378</v>
       </c>
       <c r="K2" t="n">
-        <v>4.095788601684935</v>
+        <v>3.287755333027833</v>
       </c>
       <c r="L2" t="n">
-        <v>3.739583637316328</v>
+        <v>2.972728671856427</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.017073987424378</v>
+        <v>3.500102219702519</v>
       </c>
       <c r="C3" t="n">
-        <v>4.482402260593801</v>
+        <v>3.540487103635279</v>
       </c>
       <c r="D3" t="n">
-        <v>3.852386616709071</v>
+        <v>3.121312960924441</v>
       </c>
       <c r="E3" t="n">
-        <v>4.828442447007942</v>
+        <v>4.016048526736564</v>
       </c>
       <c r="F3" t="n">
-        <v>3.875703505112862</v>
+        <v>2.707055935165118</v>
       </c>
       <c r="G3" t="n">
-        <v>7.276824812490137</v>
+        <v>4.235399383528092</v>
       </c>
       <c r="H3" t="n">
-        <v>3.780381230449851</v>
+        <v>3.096657609927387</v>
       </c>
       <c r="I3" t="n">
-        <v>4.274587792296416</v>
+        <v>3.259559698893</v>
       </c>
       <c r="J3" t="n">
-        <v>6.277010830082216</v>
+        <v>5.58035906571382</v>
       </c>
       <c r="K3" t="n">
-        <v>4.687725750594433</v>
+        <v>3.785950883450704</v>
       </c>
       <c r="L3" t="n">
-        <v>4.334404630294943</v>
+        <v>3.280597389411766</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.316765672473941</v>
+        <v>3.316765672474105</v>
       </c>
       <c r="C4" t="n">
-        <v>2.723957303103706</v>
+        <v>2.723957303103719</v>
       </c>
       <c r="D4" t="n">
-        <v>2.714824282807205</v>
+        <v>2.714824282807095</v>
       </c>
       <c r="E4" t="n">
-        <v>2.795984097009836</v>
+        <v>2.795984097009956</v>
       </c>
       <c r="F4" t="n">
-        <v>2.795984097009841</v>
+        <v>2.795984097009974</v>
       </c>
       <c r="G4" t="n">
-        <v>4.482880024625511</v>
+        <v>4.482880024625585</v>
       </c>
       <c r="H4" t="n">
-        <v>2.677910670838431</v>
+        <v>2.677910670838448</v>
       </c>
       <c r="I4" t="n">
-        <v>2.92346440786836</v>
+        <v>2.923464407868313</v>
       </c>
       <c r="J4" t="n">
-        <v>3.146278422685781</v>
+        <v>3.146278422685535</v>
       </c>
       <c r="K4" t="n">
-        <v>2.952333435979058</v>
+        <v>2.952333435978795</v>
       </c>
       <c r="L4" t="n">
-        <v>2.964890086763025</v>
+        <v>2.96489008676299</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.06367802322272</v>
+        <v>22.06367802322258</v>
       </c>
       <c r="C5" t="n">
-        <v>15.73301562323807</v>
+        <v>15.73301562323812</v>
       </c>
       <c r="D5" t="n">
-        <v>12.21962749556873</v>
+        <v>12.21962749556886</v>
       </c>
       <c r="E5" t="n">
-        <v>15.73302301186244</v>
+        <v>15.73302301186249</v>
       </c>
       <c r="F5" t="n">
-        <v>15.73302301186244</v>
+        <v>15.73302301186249</v>
       </c>
       <c r="G5" t="n">
-        <v>41.34928514862018</v>
+        <v>41.34928514862026</v>
       </c>
       <c r="H5" t="n">
-        <v>12.97579821941876</v>
+        <v>12.9757982194191</v>
       </c>
       <c r="I5" t="n">
-        <v>15.7326146964844</v>
+        <v>15.73261469648451</v>
       </c>
       <c r="J5" t="n">
-        <v>20.92173831966267</v>
+        <v>20.92173831966482</v>
       </c>
       <c r="K5" t="n">
-        <v>15.51108641020025</v>
+        <v>15.51108641020023</v>
       </c>
       <c r="L5" t="n">
-        <v>19.0394395728588</v>
+        <v>19.03943957285883</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.440201810342785</v>
+        <v>4.042153807088144</v>
       </c>
       <c r="C6" t="n">
-        <v>3.580101098014877</v>
+        <v>3.580101098014864</v>
       </c>
       <c r="D6" t="n">
-        <v>5.965579810861772</v>
+        <v>5.965579810861835</v>
       </c>
       <c r="E6" t="n">
-        <v>3.517506875453698</v>
+        <v>3.517506875453761</v>
       </c>
       <c r="F6" t="n">
-        <v>3.641140379304874</v>
+        <v>3.641140379304812</v>
       </c>
       <c r="G6" t="n">
-        <v>5.208268159239825</v>
+        <v>7.606316162494299</v>
       </c>
       <c r="H6" t="n">
-        <v>6.332555393729587</v>
+        <v>6.332555393729323</v>
       </c>
       <c r="I6" t="n">
-        <v>3.648852542482554</v>
+        <v>3.648852542482538</v>
       </c>
       <c r="J6" t="n">
-        <v>6.380869397416817</v>
+        <v>3.91549758920047</v>
       </c>
       <c r="K6" t="n">
-        <v>3.644168156452832</v>
+        <v>3.644168156452893</v>
       </c>
       <c r="L6" t="n">
-        <v>3.671306271898399</v>
+        <v>3.671306271898352</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.202748274816399</v>
+        <v>4.202748274816485</v>
       </c>
       <c r="C7" t="n">
-        <v>3.809847936964471</v>
+        <v>3.809847936964568</v>
       </c>
       <c r="D7" t="n">
-        <v>3.60080618196223</v>
+        <v>3.600806181962282</v>
       </c>
       <c r="E7" t="n">
-        <v>3.796308645269234</v>
+        <v>3.796308645269256</v>
       </c>
       <c r="F7" t="n">
-        <v>3.796308645269234</v>
+        <v>3.796308645269231</v>
       </c>
       <c r="G7" t="n">
-        <v>5.368862626968119</v>
+        <v>5.368862626968064</v>
       </c>
       <c r="H7" t="n">
-        <v>3.563893273180869</v>
+        <v>3.563893273180901</v>
       </c>
       <c r="I7" t="n">
-        <v>3.809447010210799</v>
+        <v>3.809447010210815</v>
       </c>
       <c r="J7" t="n">
-        <v>4.03226102502822</v>
+        <v>4.03226102502826</v>
       </c>
       <c r="K7" t="n">
-        <v>3.838316038321524</v>
+        <v>3.838316038321442</v>
       </c>
       <c r="L7" t="n">
-        <v>3.850872689105516</v>
+        <v>3.850872689105465</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.183044249833261</v>
+        <v>6.183044249833452</v>
       </c>
       <c r="C8" t="n">
-        <v>7.945368153662884</v>
+        <v>7.945368153734792</v>
       </c>
       <c r="D8" t="n">
-        <v>8.198345849316702</v>
+        <v>8.198345849316517</v>
       </c>
       <c r="E8" t="n">
-        <v>7.353841305346389</v>
+        <v>7.353841305346746</v>
       </c>
       <c r="F8" t="n">
-        <v>5.850784692404035</v>
+        <v>5.850784692404185</v>
       </c>
       <c r="G8" t="n">
-        <v>9.516905210750659</v>
+        <v>9.516905210750773</v>
       </c>
       <c r="H8" t="n">
-        <v>7.711935856945814</v>
+        <v>7.711935856945793</v>
       </c>
       <c r="I8" t="n">
-        <v>7.957489593993431</v>
+        <v>7.957489593993424</v>
       </c>
       <c r="J8" t="n">
-        <v>8.180729625806062</v>
+        <v>8.180729625805741</v>
       </c>
       <c r="K8" t="n">
-        <v>5.778345007864784</v>
+        <v>5.77834500786485</v>
       </c>
       <c r="L8" t="n">
-        <v>10.26330786276411</v>
+        <v>10.2633078627639</v>
       </c>
     </row>
     <row r="9">
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.49001045255318</v>
+        <v>82.49001045255329</v>
       </c>
       <c r="C9" t="n">
-        <v>104.1437068003922</v>
+        <v>104.1437068003921</v>
       </c>
       <c r="D9" t="n">
         <v>103.9346673774082</v>
@@ -1203,7 +1203,7 @@
         <v>129.5850207618824</v>
       </c>
       <c r="F9" t="n">
-        <v>104.143714179831</v>
+        <v>104.1437141798311</v>
       </c>
       <c r="G9" t="n">
         <v>105.7027214903957</v>
@@ -1212,16 +1212,16 @@
         <v>103.8977521366085</v>
       </c>
       <c r="I9" t="n">
-        <v>104.1433058736384</v>
+        <v>104.1433058736385</v>
       </c>
       <c r="J9" t="n">
         <v>104.366119888456</v>
       </c>
       <c r="K9" t="n">
-        <v>91.39829088347101</v>
+        <v>91.39829088347088</v>
       </c>
       <c r="L9" t="n">
-        <v>104.1847315525333</v>
+        <v>104.1847315525332</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.135273322760242</v>
+        <v>1.772294963007987</v>
       </c>
       <c r="C2" t="n">
-        <v>1.069410793600672</v>
+        <v>1.396332714307164</v>
       </c>
       <c r="D2" t="n">
-        <v>3.515181072680023</v>
+        <v>1.897544781008754</v>
       </c>
       <c r="E2" t="n">
-        <v>2.050830099395229</v>
+        <v>1.607010434533247</v>
       </c>
       <c r="F2" t="n">
-        <v>2.050830099395229</v>
+        <v>1.607040140493425</v>
       </c>
       <c r="G2" t="n">
-        <v>2.59638389004792</v>
+        <v>1.849190310165006</v>
       </c>
       <c r="H2" t="n">
-        <v>2.674404152645331</v>
+        <v>1.852680117210147</v>
       </c>
       <c r="I2" t="n">
-        <v>2.324609379172295</v>
+        <v>1.834887874986597</v>
       </c>
       <c r="J2" t="n">
-        <v>2.099222238570027</v>
+        <v>1.891709008692344</v>
       </c>
       <c r="K2" t="n">
-        <v>2.554713496395355</v>
+        <v>1.882237367056786</v>
       </c>
       <c r="L2" t="n">
-        <v>2.414926519461575</v>
+        <v>1.839178658042666</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.27845620521633</v>
+        <v>1.610726415972917</v>
       </c>
       <c r="C3" t="n">
-        <v>1.273993653318786</v>
+        <v>1.109633881999831</v>
       </c>
       <c r="D3" t="n">
-        <v>4.015843114029272</v>
+        <v>2.502649782466694</v>
       </c>
       <c r="E3" t="n">
-        <v>2.372661237664767</v>
+        <v>1.680403451326347</v>
       </c>
       <c r="F3" t="n">
-        <v>2.372661237664767</v>
+        <v>1.680433157286536</v>
       </c>
       <c r="G3" t="n">
-        <v>2.959036025739372</v>
+        <v>2.158902455435142</v>
       </c>
       <c r="H3" t="n">
-        <v>3.04904852642773</v>
+        <v>2.189883807154166</v>
       </c>
       <c r="I3" t="n">
-        <v>2.646420224118372</v>
+        <v>2.056567464168059</v>
       </c>
       <c r="J3" t="n">
-        <v>2.373966181118209</v>
+        <v>2.060466872530112</v>
       </c>
       <c r="K3" t="n">
-        <v>2.904317892162861</v>
+        <v>2.187886322831228</v>
       </c>
       <c r="L3" t="n">
-        <v>2.750254356121314</v>
+        <v>2.092611926697607</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8324032894806326</v>
+        <v>0.8324032894806511</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9617375341531834</v>
+        <v>0.961737534153176</v>
       </c>
       <c r="D4" t="n">
-        <v>2.247157601562106</v>
+        <v>2.247157601562173</v>
       </c>
       <c r="E4" t="n">
-        <v>1.476744819943526</v>
+        <v>1.476744819943252</v>
       </c>
       <c r="F4" t="n">
-        <v>1.476744819943418</v>
+        <v>1.476744819943252</v>
       </c>
       <c r="G4" t="n">
-        <v>1.699907297668382</v>
+        <v>1.699907297668358</v>
       </c>
       <c r="H4" t="n">
-        <v>1.747384940798588</v>
+        <v>1.747384940798602</v>
       </c>
       <c r="I4" t="n">
-        <v>1.53272742100107</v>
+        <v>1.532727421001099</v>
       </c>
       <c r="J4" t="n">
-        <v>1.353067424541257</v>
+        <v>1.353067424541239</v>
       </c>
       <c r="K4" t="n">
-        <v>1.649334063761252</v>
+        <v>1.649334063761228</v>
       </c>
       <c r="L4" t="n">
-        <v>1.593257260417049</v>
+        <v>1.593257260417106</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.259854127041767</v>
+        <v>-2.259854127041728</v>
       </c>
       <c r="C5" t="n">
-        <v>2.045539579754586</v>
+        <v>2.045539579754418</v>
       </c>
       <c r="D5" t="n">
-        <v>22.98974912720954</v>
+        <v>22.98974912721001</v>
       </c>
       <c r="E5" t="n">
-        <v>10.41052612634508</v>
+        <v>10.41052612634473</v>
       </c>
       <c r="F5" t="n">
-        <v>10.41052612634508</v>
+        <v>10.41052612634473</v>
       </c>
       <c r="G5" t="n">
-        <v>13.56480917062638</v>
+        <v>13.56480917062619</v>
       </c>
       <c r="H5" t="n">
-        <v>15.67426335416243</v>
+        <v>15.67426335416228</v>
       </c>
       <c r="I5" t="n">
-        <v>10.41046869880655</v>
+        <v>10.41046869880595</v>
       </c>
       <c r="J5" t="n">
-        <v>7.286677389748855</v>
+        <v>7.286677389748745</v>
       </c>
       <c r="K5" t="n">
-        <v>12.33902929739644</v>
+        <v>12.33902929739643</v>
       </c>
       <c r="L5" t="n">
-        <v>12.78854549269991</v>
+        <v>12.78854549269987</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.134965539258544</v>
+        <v>2.944571226001958</v>
       </c>
       <c r="C6" t="n">
-        <v>1.346102346385798</v>
+        <v>1.346102346385795</v>
       </c>
       <c r="D6" t="n">
-        <v>2.568016508279712</v>
+        <v>2.568020687805001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.819175739524676</v>
+        <v>1.819175739524684</v>
       </c>
       <c r="F6" t="n">
-        <v>1.83976002021636</v>
+        <v>1.83976002021634</v>
       </c>
       <c r="G6" t="n">
-        <v>3.812075234189672</v>
+        <v>2.002469547446271</v>
       </c>
       <c r="H6" t="n">
-        <v>4.38126536605352</v>
+        <v>4.381265366053512</v>
       </c>
       <c r="I6" t="n">
-        <v>3.644895357522372</v>
+        <v>1.835289670778994</v>
       </c>
       <c r="J6" t="n">
-        <v>3.512052930276226</v>
+        <v>3.512052930276242</v>
       </c>
       <c r="K6" t="n">
-        <v>1.93944223541615</v>
+        <v>1.93944223541616</v>
       </c>
       <c r="L6" t="n">
-        <v>1.89987763662731</v>
+        <v>1.899877636627306</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.414380728184639</v>
+        <v>1.414380728184658</v>
       </c>
       <c r="C7" t="n">
-        <v>1.657239380921979</v>
+        <v>1.657239380921995</v>
       </c>
       <c r="D7" t="n">
-        <v>2.829133972350108</v>
+        <v>2.829133972350176</v>
       </c>
       <c r="E7" t="n">
-        <v>2.118201701209035</v>
+        <v>2.118201701209014</v>
       </c>
       <c r="F7" t="n">
-        <v>2.118201701209035</v>
+        <v>2.118201701209014</v>
       </c>
       <c r="G7" t="n">
-        <v>2.281884736372377</v>
+        <v>2.281884736372392</v>
       </c>
       <c r="H7" t="n">
-        <v>2.329362379502576</v>
+        <v>2.3293623795026</v>
       </c>
       <c r="I7" t="n">
-        <v>2.114704859705098</v>
+        <v>2.114704859705132</v>
       </c>
       <c r="J7" t="n">
-        <v>1.935044863245238</v>
+        <v>1.935044863245257</v>
       </c>
       <c r="K7" t="n">
-        <v>2.231311502465244</v>
+        <v>2.231311502465223</v>
       </c>
       <c r="L7" t="n">
-        <v>2.175234699121095</v>
+        <v>2.175234699121107</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.043218715016782</v>
+        <v>3.043218715016854</v>
       </c>
       <c r="C8" t="n">
-        <v>4.735930857110525</v>
+        <v>4.735930857110566</v>
       </c>
       <c r="D8" t="n">
-        <v>6.204148051566709</v>
+        <v>6.204148051566723</v>
       </c>
       <c r="E8" t="n">
-        <v>4.797530647276296</v>
+        <v>4.797530647276368</v>
       </c>
       <c r="F8" t="n">
-        <v>3.79149751679814</v>
+        <v>3.791497516798267</v>
       </c>
       <c r="G8" t="n">
-        <v>5.357002263379666</v>
+        <v>5.357002263379675</v>
       </c>
       <c r="H8" t="n">
-        <v>5.404479906510815</v>
+        <v>5.404479906510913</v>
       </c>
       <c r="I8" t="n">
-        <v>5.189822386712216</v>
+        <v>5.189822386712395</v>
       </c>
       <c r="J8" t="n">
-        <v>5.010446625408855</v>
+        <v>5.010446625408917</v>
       </c>
       <c r="K8" t="n">
-        <v>3.833284104285865</v>
+        <v>3.833284104285877</v>
       </c>
       <c r="L8" t="n">
-        <v>6.761112141655221</v>
+        <v>6.761112141655226</v>
       </c>
     </row>
     <row r="9">
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.72350712624402</v>
+        <v>83.723507126244</v>
       </c>
       <c r="C9" t="n">
         <v>106.9084070271864</v>
       </c>
       <c r="D9" t="n">
-        <v>108.0803031044676</v>
+        <v>108.0803031044677</v>
       </c>
       <c r="E9" t="n">
         <v>133.8405593778909</v>
@@ -1602,19 +1602,19 @@
         <v>107.3659298663149</v>
       </c>
       <c r="G9" t="n">
-        <v>107.533052382637</v>
+        <v>107.5330523826371</v>
       </c>
       <c r="H9" t="n">
         <v>107.5805300257672</v>
       </c>
       <c r="I9" t="n">
-        <v>107.3658725059697</v>
+        <v>107.3658725059698</v>
       </c>
       <c r="J9" t="n">
         <v>107.1862125095099</v>
       </c>
       <c r="K9" t="n">
-        <v>94.1897705249513</v>
+        <v>94.18977052495124</v>
       </c>
       <c r="L9" t="n">
         <v>107.4264023453857</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.652795863624169</v>
+        <v>1.937592001108358</v>
       </c>
       <c r="C2" t="n">
-        <v>1.198197248071753</v>
+        <v>1.521442119900674</v>
       </c>
       <c r="D2" t="n">
-        <v>4.133550328590724</v>
+        <v>2.068149181424319</v>
       </c>
       <c r="E2" t="n">
-        <v>2.654449382362734</v>
+        <v>1.790991015696335</v>
       </c>
       <c r="F2" t="n">
-        <v>2.654449382362734</v>
+        <v>1.791021560539828</v>
       </c>
       <c r="G2" t="n">
-        <v>3.064541002536497</v>
+        <v>2.011889343817621</v>
       </c>
       <c r="H2" t="n">
-        <v>2.349230174384083</v>
+        <v>1.972989363853962</v>
       </c>
       <c r="I2" t="n">
-        <v>2.90998191159124</v>
+        <v>2.00376240906474</v>
       </c>
       <c r="J2" t="n">
-        <v>2.112497141100963</v>
+        <v>2.067751517836616</v>
       </c>
       <c r="K2" t="n">
-        <v>3.369460885125013</v>
+        <v>2.121359276694321</v>
       </c>
       <c r="L2" t="n">
-        <v>3.071309827723724</v>
+        <v>2.011814713200061</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.88476302210566</v>
+        <v>1.898130082930233</v>
       </c>
       <c r="C3" t="n">
-        <v>1.436918581778065</v>
+        <v>1.225991291601237</v>
       </c>
       <c r="D3" t="n">
-        <v>4.738144543556478</v>
+        <v>2.82761094868918</v>
       </c>
       <c r="E3" t="n">
-        <v>3.075275432277677</v>
+        <v>2.0180548732323</v>
       </c>
       <c r="F3" t="n">
-        <v>3.075275432277676</v>
+        <v>2.018085418075792</v>
       </c>
       <c r="G3" t="n">
-        <v>3.508562373979347</v>
+        <v>2.427762795416994</v>
       </c>
       <c r="H3" t="n">
-        <v>2.686152970367989</v>
+        <v>2.159594853752808</v>
       </c>
       <c r="I3" t="n">
-        <v>3.333590625199722</v>
+        <v>2.369299043837365</v>
       </c>
       <c r="J3" t="n">
-        <v>2.393101665193345</v>
+        <v>2.206264468286784</v>
       </c>
       <c r="K3" t="n">
-        <v>3.841286741275976</v>
+        <v>2.661057772503905</v>
       </c>
       <c r="L3" t="n">
-        <v>3.516265145779678</v>
+        <v>2.433425513283269</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.192960371537017</v>
+        <v>1.192960371537012</v>
       </c>
       <c r="C4" t="n">
-        <v>1.117275055151871</v>
+        <v>1.11727505515187</v>
       </c>
       <c r="D4" t="n">
-        <v>2.667663782476006</v>
+        <v>2.667663782475998</v>
       </c>
       <c r="E4" t="n">
-        <v>1.949332339744931</v>
+        <v>1.949332339744921</v>
       </c>
       <c r="F4" t="n">
-        <v>1.94933233974493</v>
+        <v>1.949332339744922</v>
       </c>
       <c r="G4" t="n">
-        <v>2.031254113060786</v>
+        <v>2.031254113060772</v>
       </c>
       <c r="H4" t="n">
-        <v>1.607186933703795</v>
+        <v>1.607186933703794</v>
       </c>
       <c r="I4" t="n">
-        <v>1.934566168274934</v>
+        <v>1.934566168274925</v>
       </c>
       <c r="J4" t="n">
-        <v>1.385446901211479</v>
+        <v>1.38544690121147</v>
       </c>
       <c r="K4" t="n">
-        <v>2.142221659576314</v>
+        <v>2.142221659576315</v>
       </c>
       <c r="L4" t="n">
-        <v>2.036340752378061</v>
+        <v>2.036340752378059</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.268630327898877</v>
+        <v>2.268630327898859</v>
       </c>
       <c r="C5" t="n">
-        <v>2.571011244961896</v>
+        <v>2.571011244961906</v>
       </c>
       <c r="D5" t="n">
-        <v>27.15293445477823</v>
+        <v>27.15293445477818</v>
       </c>
       <c r="E5" t="n">
-        <v>14.91611403114027</v>
+        <v>14.91611403114026</v>
       </c>
       <c r="F5" t="n">
-        <v>14.91611403114027</v>
+        <v>14.91611403114026</v>
       </c>
       <c r="G5" t="n">
-        <v>16.78367382931854</v>
+        <v>16.78367382931863</v>
       </c>
       <c r="H5" t="n">
         <v>10.11822089881957</v>
       </c>
       <c r="I5" t="n">
-        <v>14.91607803058254</v>
+        <v>14.91607803058255</v>
       </c>
       <c r="J5" t="n">
-        <v>5.563627924972006</v>
+        <v>5.563627924972005</v>
       </c>
       <c r="K5" t="n">
-        <v>18.28901840831616</v>
+        <v>18.28901840831615</v>
       </c>
       <c r="L5" t="n">
-        <v>18.66072003385757</v>
+        <v>18.66072003385755</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.285345340312245</v>
+        <v>3.28534534031224</v>
       </c>
       <c r="C6" t="n">
-        <v>1.501171645169243</v>
+        <v>1.501171645169233</v>
       </c>
       <c r="D6" t="n">
         <v>4.816557944208545</v>
       </c>
       <c r="E6" t="n">
-        <v>2.243516480402123</v>
+        <v>2.243516480402114</v>
       </c>
       <c r="F6" t="n">
-        <v>2.260372673612833</v>
+        <v>2.26037267361283</v>
       </c>
       <c r="G6" t="n">
-        <v>2.348348213703742</v>
+        <v>4.123639081835994</v>
       </c>
       <c r="H6" t="n">
-        <v>4.189083269738719</v>
+        <v>4.189083269738711</v>
       </c>
       <c r="I6" t="n">
-        <v>2.251660268917894</v>
+        <v>2.25166026891789</v>
       </c>
       <c r="J6" t="n">
-        <v>1.722041259511489</v>
+        <v>1.722041259511494</v>
       </c>
       <c r="K6" t="n">
-        <v>2.449221196197191</v>
+        <v>2.449221196197176</v>
       </c>
       <c r="L6" t="n">
-        <v>2.356463426463673</v>
+        <v>2.356463426463668</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.79220771652802</v>
+        <v>1.792207716528008</v>
       </c>
       <c r="C7" t="n">
-        <v>1.818724256667179</v>
+        <v>1.81872425666718</v>
       </c>
       <c r="D7" t="n">
-        <v>3.26690740108927</v>
+        <v>3.266907401089265</v>
       </c>
       <c r="E7" t="n">
-        <v>2.556228369978639</v>
+        <v>2.556228369978635</v>
       </c>
       <c r="F7" t="n">
-        <v>2.556228369978639</v>
+        <v>2.556228369978634</v>
       </c>
       <c r="G7" t="n">
-        <v>2.630501458051769</v>
+        <v>2.630501458051768</v>
       </c>
       <c r="H7" t="n">
-        <v>2.206434278694802</v>
+        <v>2.206434278694791</v>
       </c>
       <c r="I7" t="n">
-        <v>2.533813513265928</v>
+        <v>2.533813513265919</v>
       </c>
       <c r="J7" t="n">
-        <v>1.984694246202471</v>
+        <v>1.984694246202468</v>
       </c>
       <c r="K7" t="n">
-        <v>2.741469004567317</v>
+        <v>2.74146900456731</v>
       </c>
       <c r="L7" t="n">
-        <v>2.63558809736906</v>
+        <v>2.635588097369053</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.373812080225332</v>
+        <v>3.373812080225315</v>
       </c>
       <c r="C8" t="n">
-        <v>4.873017991503953</v>
+        <v>4.873017991469712</v>
       </c>
       <c r="D8" t="n">
-        <v>6.600399664008958</v>
+        <v>6.600399664008962</v>
       </c>
       <c r="E8" t="n">
-        <v>5.189011716930445</v>
+        <v>5.189011716930427</v>
       </c>
       <c r="F8" t="n">
-        <v>4.174800893449484</v>
+        <v>4.174800893449478</v>
       </c>
       <c r="G8" t="n">
-        <v>5.663113997042776</v>
+        <v>5.663113997042769</v>
       </c>
       <c r="H8" t="n">
-        <v>5.239046817683507</v>
+        <v>5.239046817683505</v>
       </c>
       <c r="I8" t="n">
-        <v>5.566426052256935</v>
+        <v>5.566426052256922</v>
       </c>
       <c r="J8" t="n">
-        <v>5.01759194912851</v>
+        <v>5.017591949128503</v>
       </c>
       <c r="K8" t="n">
-        <v>4.296120146459637</v>
+        <v>4.296120146459645</v>
       </c>
       <c r="L8" t="n">
-        <v>7.183900006177511</v>
+        <v>7.183900006177518</v>
       </c>
     </row>
     <row r="9">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.73995741705512</v>
+        <v>79.73995741705511</v>
       </c>
       <c r="C9" t="n">
         <v>101.5174750349464</v>
@@ -2010,7 +2010,7 @@
         <v>101.6834450244817</v>
       </c>
       <c r="K9" t="n">
-        <v>89.83760457732893</v>
+        <v>89.83760457732892</v>
       </c>
       <c r="L9" t="n">
         <v>102.3343388756483</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.856951323175122</v>
+        <v>1.989437071365105</v>
       </c>
       <c r="C2" t="n">
-        <v>1.244393819063542</v>
+        <v>1.56782597086129</v>
       </c>
       <c r="D2" t="n">
-        <v>4.363666189926159</v>
+        <v>2.121360496065476</v>
       </c>
       <c r="E2" t="n">
-        <v>2.687761089547854</v>
+        <v>1.845663378480743</v>
       </c>
       <c r="F2" t="n">
-        <v>2.687761089547854</v>
+        <v>1.845694469040583</v>
       </c>
       <c r="G2" t="n">
-        <v>3.287372029795363</v>
+        <v>2.064717272110185</v>
       </c>
       <c r="H2" t="n">
-        <v>2.129123429097839</v>
+        <v>2.002166648737079</v>
       </c>
       <c r="I2" t="n">
-        <v>2.928122040832299</v>
+        <v>2.045818387313133</v>
       </c>
       <c r="J2" t="n">
-        <v>2.014131656183986</v>
+        <v>2.129132556208221</v>
       </c>
       <c r="K2" t="n">
-        <v>3.768348862195563</v>
+        <v>2.220369328907213</v>
       </c>
       <c r="L2" t="n">
-        <v>3.679551028913951</v>
+        <v>2.085159045622216</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.127792632210941</v>
+        <v>1.994814399720846</v>
       </c>
       <c r="C3" t="n">
-        <v>1.497691647368939</v>
+        <v>1.267122051412741</v>
       </c>
       <c r="D3" t="n">
-        <v>5.011033993394945</v>
+        <v>2.933925819924446</v>
       </c>
       <c r="E3" t="n">
-        <v>3.119521956983844</v>
+        <v>2.065748033598122</v>
       </c>
       <c r="F3" t="n">
-        <v>3.119521956983843</v>
+        <v>2.065779124157901</v>
       </c>
       <c r="G3" t="n">
-        <v>3.773072755580917</v>
+        <v>2.53145768501934</v>
       </c>
       <c r="H3" t="n">
-        <v>2.441228248980913</v>
+        <v>2.096276024740953</v>
       </c>
       <c r="I3" t="n">
-        <v>3.363845946667956</v>
+        <v>2.396164167418507</v>
       </c>
       <c r="J3" t="n">
-        <v>2.283265550370507</v>
+        <v>2.22192751409542</v>
       </c>
       <c r="K3" t="n">
-        <v>4.301187578428032</v>
+        <v>2.877961809952951</v>
       </c>
       <c r="L3" t="n">
-        <v>4.224058360722323</v>
+        <v>2.683339784820585</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.324602278145903</v>
+        <v>1.32460227814599</v>
       </c>
       <c r="C4" t="n">
-        <v>1.155368637418124</v>
+        <v>1.155368637418115</v>
       </c>
       <c r="D4" t="n">
-        <v>2.81473804791023</v>
+        <v>2.814738047910189</v>
       </c>
       <c r="E4" t="n">
-        <v>1.998295180520532</v>
+        <v>1.998295180520536</v>
       </c>
       <c r="F4" t="n">
-        <v>1.998295180520531</v>
+        <v>1.998295180520538</v>
       </c>
       <c r="G4" t="n">
-        <v>2.173960208675787</v>
+        <v>2.173960208675793</v>
       </c>
       <c r="H4" t="n">
-        <v>1.486727809855422</v>
+        <v>1.486727809855513</v>
       </c>
       <c r="I4" t="n">
-        <v>1.955384882234544</v>
+        <v>1.955384882234536</v>
       </c>
       <c r="J4" t="n">
-        <v>1.317845038008939</v>
+        <v>1.317845038008809</v>
       </c>
       <c r="K4" t="n">
-        <v>2.361479400530402</v>
+        <v>2.361479400530393</v>
       </c>
       <c r="L4" t="n">
-        <v>2.408114624722373</v>
+        <v>2.408114624722344</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.154543853745818</v>
+        <v>4.154543853745926</v>
       </c>
       <c r="C5" t="n">
-        <v>2.775381738385787</v>
+        <v>2.775381738385766</v>
       </c>
       <c r="D5" t="n">
         <v>29.24940054521898</v>
       </c>
       <c r="E5" t="n">
-        <v>14.87001224408497</v>
+        <v>14.87001224408493</v>
       </c>
       <c r="F5" t="n">
-        <v>14.87001224408497</v>
+        <v>14.87001224408493</v>
       </c>
       <c r="G5" t="n">
-        <v>18.86376162394722</v>
+        <v>18.86376162394719</v>
       </c>
       <c r="H5" t="n">
-        <v>7.356772689290688</v>
+        <v>7.356772689290605</v>
       </c>
       <c r="I5" t="n">
-        <v>14.86994849806583</v>
+        <v>14.86994849806581</v>
       </c>
       <c r="J5" t="n">
-        <v>3.932542106404683</v>
+        <v>3.932542106404494</v>
       </c>
       <c r="K5" t="n">
-        <v>21.62559058695337</v>
+        <v>21.62559058695332</v>
       </c>
       <c r="L5" t="n">
-        <v>25.44785751673868</v>
+        <v>25.44785751673864</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.658809398744888</v>
+        <v>1.658809398744791</v>
       </c>
       <c r="C6" t="n">
-        <v>1.550772959517169</v>
+        <v>1.550772959517152</v>
       </c>
       <c r="D6" t="n">
-        <v>3.166001026484225</v>
+        <v>3.165996968110802</v>
       </c>
       <c r="E6" t="n">
-        <v>2.28052505386795</v>
+        <v>2.280525053867934</v>
       </c>
       <c r="F6" t="n">
-        <v>2.29942461802043</v>
+        <v>2.299424618020414</v>
       </c>
       <c r="G6" t="n">
-        <v>4.311420104346148</v>
+        <v>4.311420104346106</v>
       </c>
       <c r="H6" t="n">
-        <v>4.110312331285886</v>
+        <v>4.110312331285845</v>
       </c>
       <c r="I6" t="n">
-        <v>4.092844777904905</v>
+        <v>4.092844777904886</v>
       </c>
       <c r="J6" t="n">
-        <v>3.511099485503341</v>
+        <v>3.511099485503396</v>
       </c>
       <c r="K6" t="n">
-        <v>2.687338989261476</v>
+        <v>2.687338989261427</v>
       </c>
       <c r="L6" t="n">
-        <v>2.746038045847436</v>
+        <v>2.746038045847419</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.94129206209582</v>
+        <v>1.941292062095784</v>
       </c>
       <c r="C7" t="n">
-        <v>1.871532085323163</v>
+        <v>1.871532085323154</v>
       </c>
       <c r="D7" t="n">
-        <v>3.431426074558391</v>
+        <v>3.431426074558253</v>
       </c>
       <c r="E7" t="n">
-        <v>2.60383942901306</v>
+        <v>2.603839429013044</v>
       </c>
       <c r="F7" t="n">
-        <v>2.60383942901306</v>
+        <v>2.603839429013044</v>
       </c>
       <c r="G7" t="n">
-        <v>2.790649992625703</v>
+        <v>2.7906499926257</v>
       </c>
       <c r="H7" t="n">
-        <v>2.10341759380534</v>
+        <v>2.10341759380537</v>
       </c>
       <c r="I7" t="n">
-        <v>2.572074666184458</v>
+        <v>2.572074666184437</v>
       </c>
       <c r="J7" t="n">
-        <v>1.934534821958856</v>
+        <v>1.934534821958934</v>
       </c>
       <c r="K7" t="n">
-        <v>2.978169184480315</v>
+        <v>2.978169184480296</v>
       </c>
       <c r="L7" t="n">
-        <v>3.02480440867229</v>
+        <v>3.024804408672363</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.529020313152241</v>
+        <v>3.529020313152333</v>
       </c>
       <c r="C8" t="n">
-        <v>4.965002043572122</v>
+        <v>4.965002043603786</v>
       </c>
       <c r="D8" t="n">
-        <v>6.800180551658864</v>
+        <v>6.800180551658726</v>
       </c>
       <c r="E8" t="n">
-        <v>5.258930161393745</v>
+        <v>5.258930161393699</v>
       </c>
       <c r="F8" t="n">
-        <v>4.225538687861384</v>
+        <v>4.225538687861365</v>
       </c>
       <c r="G8" t="n">
-        <v>5.853522037221199</v>
+        <v>5.85352203722116</v>
       </c>
       <c r="H8" t="n">
-        <v>5.166289638399775</v>
+        <v>5.166289638399793</v>
       </c>
       <c r="I8" t="n">
-        <v>5.634946710779946</v>
+        <v>5.634946710779937</v>
       </c>
       <c r="J8" t="n">
-        <v>4.99769677357131</v>
+        <v>4.997696773571329</v>
       </c>
       <c r="K8" t="n">
-        <v>4.538495882275444</v>
+        <v>4.538495882275407</v>
       </c>
       <c r="L8" t="n">
-        <v>7.628587494266807</v>
+        <v>7.628587494266781</v>
       </c>
     </row>
     <row r="9">
@@ -2379,16 +2379,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.82351757743905</v>
+        <v>79.82351757743913</v>
       </c>
       <c r="C9" t="n">
-        <v>101.4954490601437</v>
+        <v>101.4954490601436</v>
       </c>
       <c r="D9" t="n">
         <v>103.0553454750924</v>
       </c>
       <c r="E9" t="n">
-        <v>127.2855070141485</v>
+        <v>127.2855070141484</v>
       </c>
       <c r="F9" t="n">
         <v>102.1960554486167</v>
@@ -2397,19 +2397,19 @@
         <v>102.4145669674462</v>
       </c>
       <c r="H9" t="n">
-        <v>101.7273345686259</v>
+        <v>101.727334568626</v>
       </c>
       <c r="I9" t="n">
-        <v>102.1959916410051</v>
+        <v>102.195991641005</v>
       </c>
       <c r="J9" t="n">
         <v>101.5584517967794</v>
       </c>
       <c r="K9" t="n">
-        <v>75.22541556038325</v>
+        <v>89.49377982129151</v>
       </c>
       <c r="L9" t="n">
-        <v>102.6487213834929</v>
+        <v>102.6487213834927</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.59029688911009</v>
+        <v>1.919561962595367</v>
       </c>
       <c r="C2" t="n">
-        <v>1.142942341538099</v>
+        <v>1.494693253459964</v>
       </c>
       <c r="D2" t="n">
-        <v>3.980225427145679</v>
+        <v>2.045339154771771</v>
       </c>
       <c r="E2" t="n">
-        <v>2.652958786311602</v>
+        <v>1.764127840126369</v>
       </c>
       <c r="F2" t="n">
-        <v>2.652958786311602</v>
+        <v>1.764157294919545</v>
       </c>
       <c r="G2" t="n">
-        <v>3.138790705182336</v>
+        <v>2.001056116578809</v>
       </c>
       <c r="H2" t="n">
-        <v>2.616483997858225</v>
+        <v>1.972442615613486</v>
       </c>
       <c r="I2" t="n">
-        <v>2.923974508318814</v>
+        <v>1.989756661838153</v>
       </c>
       <c r="J2" t="n">
-        <v>2.246944979114185</v>
+        <v>2.033514949334591</v>
       </c>
       <c r="K2" t="n">
-        <v>3.083473136545641</v>
+        <v>2.068100375731222</v>
       </c>
       <c r="L2" t="n">
-        <v>3.02498762391818</v>
+        <v>1.994554044155844</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.801970770290024</v>
+        <v>1.867640036210311</v>
       </c>
       <c r="C3" t="n">
-        <v>1.364141799873196</v>
+        <v>1.186613150167662</v>
       </c>
       <c r="D3" t="n">
-        <v>4.550883661236146</v>
+        <v>2.763118949684575</v>
       </c>
       <c r="E3" t="n">
-        <v>3.064977406067662</v>
+        <v>1.995040976326514</v>
       </c>
       <c r="F3" t="n">
-        <v>3.064977406067662</v>
+        <v>1.995070431119664</v>
       </c>
       <c r="G3" t="n">
-        <v>3.583059428300747</v>
+        <v>2.448613720038242</v>
       </c>
       <c r="H3" t="n">
-        <v>2.982611404602017</v>
+        <v>2.253514755166607</v>
       </c>
       <c r="I3" t="n">
-        <v>3.339352284428496</v>
+        <v>2.367514944691019</v>
       </c>
       <c r="J3" t="n">
-        <v>2.541957692728483</v>
+        <v>2.215755986912038</v>
       </c>
       <c r="K3" t="n">
-        <v>3.505956736787569</v>
+        <v>2.516751135648717</v>
       </c>
       <c r="L3" t="n">
-        <v>3.452090958136521</v>
+        <v>2.408853833719458</v>
       </c>
     </row>
     <row r="4">
@@ -2578,34 +2578,34 @@
         <v>1.117417564538238</v>
       </c>
       <c r="C4" t="n">
-        <v>1.028123656193833</v>
+        <v>1.028123656193835</v>
       </c>
       <c r="D4" t="n">
-        <v>2.538128810537759</v>
+        <v>2.538128810537757</v>
       </c>
       <c r="E4" t="n">
-        <v>1.938802345707361</v>
+        <v>1.938802345707343</v>
       </c>
       <c r="F4" t="n">
-        <v>1.938802345707361</v>
+        <v>1.938802345707343</v>
       </c>
       <c r="G4" t="n">
-        <v>2.037006324069662</v>
+        <v>2.037006324069667</v>
       </c>
       <c r="H4" t="n">
-        <v>1.727620062632723</v>
+        <v>1.727620062632724</v>
       </c>
       <c r="I4" t="n">
-        <v>1.904456487081296</v>
+        <v>1.90445648708129</v>
       </c>
       <c r="J4" t="n">
-        <v>1.447238113840772</v>
+        <v>1.447238113840777</v>
       </c>
       <c r="K4" t="n">
-        <v>1.951715037977195</v>
+        <v>1.951715037977193</v>
       </c>
       <c r="L4" t="n">
-        <v>1.97044240641329</v>
+        <v>1.970442406413296</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.671848894221187</v>
+        <v>1.671848894221186</v>
       </c>
       <c r="C5" t="n">
-        <v>2.20179935506268</v>
+        <v>2.201799355062678</v>
       </c>
       <c r="D5" t="n">
-        <v>26.91836090958266</v>
+        <v>26.91836090958265</v>
       </c>
       <c r="E5" t="n">
-        <v>15.82102819341494</v>
+        <v>15.82102819341451</v>
       </c>
       <c r="F5" t="n">
-        <v>15.82102819341494</v>
+        <v>15.82102819341451</v>
       </c>
       <c r="G5" t="n">
-        <v>18.45045800610869</v>
+        <v>18.45045800610877</v>
       </c>
       <c r="H5" t="n">
-        <v>13.83029837622963</v>
+        <v>13.83029837622964</v>
       </c>
       <c r="I5" t="n">
-        <v>15.82097665989383</v>
+        <v>15.82097665989361</v>
       </c>
       <c r="J5" t="n">
-        <v>7.712141540403913</v>
+        <v>7.712141540403909</v>
       </c>
       <c r="K5" t="n">
-        <v>16.48799724004224</v>
+        <v>16.48799724004226</v>
       </c>
       <c r="L5" t="n">
-        <v>19.06082554437485</v>
+        <v>19.06082554437486</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.446514514614828</v>
+        <v>1.446514514614829</v>
       </c>
       <c r="C6" t="n">
-        <v>1.441516939793472</v>
+        <v>1.441516939793473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.881967147214477</v>
+        <v>2.881963172557008</v>
       </c>
       <c r="E6" t="n">
-        <v>2.229119377418843</v>
+        <v>2.229119377418824</v>
       </c>
       <c r="F6" t="n">
-        <v>2.243987164975432</v>
+        <v>2.243987164975408</v>
       </c>
       <c r="G6" t="n">
         <v>2.366103274146258</v>
       </c>
       <c r="H6" t="n">
-        <v>4.434065470391559</v>
+        <v>4.434065470391567</v>
       </c>
       <c r="I6" t="n">
-        <v>2.233553437157892</v>
+        <v>4.086746581466985</v>
       </c>
       <c r="J6" t="n">
-        <v>3.683911350571258</v>
+        <v>1.797254131087179</v>
       </c>
       <c r="K6" t="n">
         <v>2.267342956288998</v>
       </c>
       <c r="L6" t="n">
-        <v>2.303710958284963</v>
+        <v>2.303710958284966</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.752887345456004</v>
+        <v>1.752887345456005</v>
       </c>
       <c r="C7" t="n">
         <v>1.790664115749326</v>
       </c>
       <c r="D7" t="n">
-        <v>3.173599955595309</v>
+        <v>3.17359995559531</v>
       </c>
       <c r="E7" t="n">
-        <v>2.568432180675241</v>
+        <v>2.568432180675247</v>
       </c>
       <c r="F7" t="n">
-        <v>2.568432180675241</v>
+        <v>2.568432180675247</v>
       </c>
       <c r="G7" t="n">
-        <v>2.672476104987432</v>
+        <v>2.672476104987434</v>
       </c>
       <c r="H7" t="n">
-        <v>2.363089843550488</v>
+        <v>2.363089843550493</v>
       </c>
       <c r="I7" t="n">
-        <v>2.539926267999069</v>
+        <v>2.539926267999066</v>
       </c>
       <c r="J7" t="n">
-        <v>2.082707894758542</v>
+        <v>2.082707894758545</v>
       </c>
       <c r="K7" t="n">
-        <v>2.587184818894959</v>
+        <v>2.587184818894965</v>
       </c>
       <c r="L7" t="n">
-        <v>2.605912187331059</v>
+        <v>2.605912187331062</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.406674210047124</v>
+        <v>3.406674210047139</v>
       </c>
       <c r="C8" t="n">
-        <v>4.98150150809442</v>
+        <v>4.981501508125223</v>
       </c>
       <c r="D8" t="n">
-        <v>6.649967636289174</v>
+        <v>6.649967636289114</v>
       </c>
       <c r="E8" t="n">
-        <v>5.315063147084983</v>
+        <v>5.315063147084988</v>
       </c>
       <c r="F8" t="n">
-        <v>4.258589125296345</v>
+        <v>4.258589125296344</v>
       </c>
       <c r="G8" t="n">
-        <v>5.835827177438391</v>
+        <v>5.835827177438372</v>
       </c>
       <c r="H8" t="n">
-        <v>5.526440916000542</v>
+        <v>5.526440916000555</v>
       </c>
       <c r="I8" t="n">
-        <v>5.703277340450033</v>
+        <v>5.703277340450012</v>
       </c>
       <c r="J8" t="n">
-        <v>5.24635563943167</v>
+        <v>5.246355639431712</v>
       </c>
       <c r="K8" t="n">
-        <v>4.212930753303416</v>
+        <v>4.21293075330344</v>
       </c>
       <c r="L8" t="n">
-        <v>7.346129302303174</v>
+        <v>7.346129302303161</v>
       </c>
     </row>
     <row r="9">
@@ -2781,7 +2781,7 @@
         <v>107.2181929647689</v>
       </c>
       <c r="D9" t="n">
-        <v>108.601128028</v>
+        <v>108.6011280280001</v>
       </c>
       <c r="E9" t="n">
         <v>134.5048892526721</v>
@@ -2802,10 +2802,10 @@
         <v>107.5102367437784</v>
       </c>
       <c r="K9" t="n">
-        <v>79.05811482131959</v>
+        <v>94.69049736173754</v>
       </c>
       <c r="L9" t="n">
-        <v>108.0334410363507</v>
+        <v>108.0334410363506</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.189233249183841</v>
+        <v>2.04069478697947</v>
       </c>
       <c r="C2" t="n">
-        <v>1.249427815835127</v>
+        <v>1.581517577693152</v>
       </c>
       <c r="D2" t="n">
-        <v>4.565909060869372</v>
+        <v>2.165774514490114</v>
       </c>
       <c r="E2" t="n">
-        <v>2.860880447784606</v>
+        <v>1.87355422285623</v>
       </c>
       <c r="F2" t="n">
-        <v>2.860880447784606</v>
+        <v>1.873584819784228</v>
       </c>
       <c r="G2" t="n">
-        <v>3.536710717482925</v>
+        <v>2.11160984983024</v>
       </c>
       <c r="H2" t="n">
-        <v>2.008096804884554</v>
+        <v>2.029297574151531</v>
       </c>
       <c r="I2" t="n">
-        <v>3.120497692492183</v>
+        <v>2.089712685454777</v>
       </c>
       <c r="J2" t="n">
-        <v>2.196058817122145</v>
+        <v>2.149608066087261</v>
       </c>
       <c r="K2" t="n">
-        <v>3.889994059584933</v>
+        <v>2.247481203462237</v>
       </c>
       <c r="L2" t="n">
-        <v>3.887355239152645</v>
+        <v>2.129797306032992</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.502624541167224</v>
+        <v>2.147632073482424</v>
       </c>
       <c r="C3" t="n">
-        <v>1.499905066905402</v>
+        <v>1.271138146798536</v>
       </c>
       <c r="D3" t="n">
-        <v>5.236294051516784</v>
+        <v>3.037822524715679</v>
       </c>
       <c r="E3" t="n">
-        <v>3.314175153580204</v>
+        <v>2.139544961840199</v>
       </c>
       <c r="F3" t="n">
-        <v>3.314175153580204</v>
+        <v>2.139575558768195</v>
       </c>
       <c r="G3" t="n">
-        <v>4.052502758827845</v>
+        <v>2.653127052384626</v>
       </c>
       <c r="H3" t="n">
-        <v>2.294654202419205</v>
+        <v>2.07840437726986</v>
       </c>
       <c r="I3" t="n">
-        <v>3.578135638360659</v>
+        <v>2.496389519928893</v>
       </c>
       <c r="J3" t="n">
-        <v>2.489563816074795</v>
+        <v>2.289079340448711</v>
       </c>
       <c r="K3" t="n">
-        <v>4.436259543377196</v>
+        <v>2.934921549791764</v>
       </c>
       <c r="L3" t="n">
-        <v>4.455722115113137</v>
+        <v>2.78976732534479</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.507905842299222</v>
+        <v>1.507905842299223</v>
       </c>
       <c r="C4" t="n">
         <v>1.136520743110266</v>
       </c>
       <c r="D4" t="n">
-        <v>2.920738904049283</v>
+        <v>2.920738904049278</v>
       </c>
       <c r="E4" t="n">
-        <v>2.111542064756824</v>
+        <v>2.111542064756827</v>
       </c>
       <c r="F4" t="n">
-        <v>2.111542064756824</v>
+        <v>2.111542064756827</v>
       </c>
       <c r="G4" t="n">
-        <v>2.307923474670417</v>
+        <v>2.307923474670406</v>
       </c>
       <c r="H4" t="n">
-        <v>1.40064545597133</v>
+        <v>1.400645455971329</v>
       </c>
       <c r="I4" t="n">
-        <v>2.055247034705892</v>
+        <v>2.055247034705883</v>
       </c>
       <c r="J4" t="n">
-        <v>1.429204138670765</v>
+        <v>1.429204138670766</v>
       </c>
       <c r="K4" t="n">
-        <v>2.429525351683126</v>
+        <v>2.429525351683122</v>
       </c>
       <c r="L4" t="n">
-        <v>2.517442523588649</v>
+        <v>2.517442523588651</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.283039942954838</v>
+        <v>7.283039942954857</v>
       </c>
       <c r="C5" t="n">
         <v>2.764749806435064</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97068397229363</v>
+        <v>30.97068397229365</v>
       </c>
       <c r="E5" t="n">
-        <v>16.50686336096345</v>
+        <v>16.50686336096342</v>
       </c>
       <c r="F5" t="n">
-        <v>16.50686336096345</v>
+        <v>16.50686336096342</v>
       </c>
       <c r="G5" t="n">
-        <v>21.12321914447721</v>
+        <v>21.12321914447728</v>
       </c>
       <c r="H5" t="n">
-        <v>5.617212789020826</v>
+        <v>5.617212789020811</v>
       </c>
       <c r="I5" t="n">
-        <v>16.50678425585631</v>
+        <v>16.50678425585633</v>
       </c>
       <c r="J5" t="n">
-        <v>5.835364499551343</v>
+        <v>5.835364499551337</v>
       </c>
       <c r="K5" t="n">
-        <v>22.70596354332075</v>
+        <v>22.7059635433207</v>
       </c>
       <c r="L5" t="n">
-        <v>27.48655066236024</v>
+        <v>27.48655066236026</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.849403402975816</v>
+        <v>1.84940340297582</v>
       </c>
       <c r="C6" t="n">
-        <v>1.553890467704713</v>
+        <v>1.553890467704712</v>
       </c>
       <c r="D6" t="n">
-        <v>3.277045067127862</v>
+        <v>5.126973276078086</v>
       </c>
       <c r="E6" t="n">
-        <v>2.38770291589375</v>
+        <v>2.387702915893747</v>
       </c>
       <c r="F6" t="n">
-        <v>2.406703719344308</v>
+        <v>2.406703719344311</v>
       </c>
       <c r="G6" t="n">
-        <v>4.453382756786496</v>
+        <v>2.649421035347007</v>
       </c>
       <c r="H6" t="n">
-        <v>4.037995561856622</v>
+        <v>4.037995561856617</v>
       </c>
       <c r="I6" t="n">
-        <v>4.200706316821971</v>
+        <v>4.200706316821976</v>
       </c>
       <c r="J6" t="n">
-        <v>1.790236185251065</v>
+        <v>3.631922528966369</v>
       </c>
       <c r="K6" t="n">
-        <v>2.764576434249929</v>
+        <v>2.764576434249932</v>
       </c>
       <c r="L6" t="n">
-        <v>2.862691982083327</v>
+        <v>2.86269198208333</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.133678099263872</v>
+        <v>2.133678099263868</v>
       </c>
       <c r="C7" t="n">
-        <v>1.884751704338142</v>
+        <v>1.884751704338143</v>
       </c>
       <c r="D7" t="n">
-        <v>3.546512349958816</v>
+        <v>3.546512349958814</v>
       </c>
       <c r="E7" t="n">
-        <v>2.715769586258434</v>
+        <v>2.71576958625843</v>
       </c>
       <c r="F7" t="n">
-        <v>2.715769586258434</v>
+        <v>2.71576958625843</v>
       </c>
       <c r="G7" t="n">
-        <v>2.933695731635062</v>
+        <v>2.933695731635065</v>
       </c>
       <c r="H7" t="n">
         <v>2.026417712935979</v>
       </c>
       <c r="I7" t="n">
-        <v>2.681019291670541</v>
+        <v>2.681019291670542</v>
       </c>
       <c r="J7" t="n">
-        <v>2.054976395635416</v>
+        <v>2.054976395635417</v>
       </c>
       <c r="K7" t="n">
-        <v>3.055297608647775</v>
+        <v>3.055297608647776</v>
       </c>
       <c r="L7" t="n">
-        <v>3.1432147805533</v>
+        <v>3.143214780553303</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.73176049681685</v>
+        <v>3.73176049681684</v>
       </c>
       <c r="C8" t="n">
-        <v>5.001214787539482</v>
+        <v>5.001214787507017</v>
       </c>
       <c r="D8" t="n">
-        <v>6.937461409944221</v>
+        <v>6.937461409944184</v>
       </c>
       <c r="E8" t="n">
-        <v>5.387908910995808</v>
+        <v>5.387908910995786</v>
       </c>
       <c r="F8" t="n">
-        <v>4.346933854650451</v>
+        <v>4.346933854650473</v>
       </c>
       <c r="G8" t="n">
-        <v>6.016731272727086</v>
+        <v>6.016731272727076</v>
       </c>
       <c r="H8" t="n">
-        <v>5.109453254024733</v>
+        <v>5.109453254024685</v>
       </c>
       <c r="I8" t="n">
-        <v>5.764054832762569</v>
+        <v>5.764054832762557</v>
       </c>
       <c r="J8" t="n">
-        <v>5.138303771735294</v>
+        <v>5.1383037717353</v>
       </c>
       <c r="K8" t="n">
-        <v>4.625796239195511</v>
+        <v>4.625796239195459</v>
       </c>
       <c r="L8" t="n">
-        <v>7.777408049146226</v>
+        <v>7.777408049146159</v>
       </c>
     </row>
     <row r="9">
@@ -3198,10 +3198,10 @@
         <v>101.865397522991</v>
       </c>
       <c r="K9" t="n">
-        <v>75.43678470662127</v>
+        <v>90.24444892654664</v>
       </c>
       <c r="L9" t="n">
-        <v>102.9536359079091</v>
+        <v>102.953635907909</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.503865761004822</v>
+        <v>2.142958888695045</v>
       </c>
       <c r="C2" t="n">
-        <v>1.354277175247718</v>
+        <v>1.681956317098958</v>
       </c>
       <c r="D2" t="n">
-        <v>4.716182648778431</v>
+        <v>2.259388732483314</v>
       </c>
       <c r="E2" t="n">
-        <v>2.888479158499015</v>
+        <v>1.980406555735123</v>
       </c>
       <c r="F2" t="n">
-        <v>2.888479158499015</v>
+        <v>1.980439703579328</v>
       </c>
       <c r="G2" t="n">
-        <v>3.822194224286521</v>
+        <v>2.212339897306332</v>
       </c>
       <c r="H2" t="n">
-        <v>2.112271130642724</v>
+        <v>2.120226104009111</v>
       </c>
       <c r="I2" t="n">
-        <v>3.122826218226431</v>
+        <v>2.175540507744903</v>
       </c>
       <c r="J2" t="n">
-        <v>2.323846367697973</v>
+        <v>2.30341105828705</v>
       </c>
       <c r="K2" t="n">
-        <v>4.143628035696046</v>
+        <v>2.385059117820312</v>
       </c>
       <c r="L2" t="n">
-        <v>4.359852903275707</v>
+        <v>2.240418590026839</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.88847464447877</v>
+        <v>2.311614151660407</v>
       </c>
       <c r="C3" t="n">
-        <v>1.642451479072592</v>
+        <v>1.3683333757628</v>
       </c>
       <c r="D3" t="n">
-        <v>5.433097345481104</v>
+        <v>3.140048283792935</v>
       </c>
       <c r="E3" t="n">
-        <v>3.366080191256962</v>
+        <v>2.22102125804017</v>
       </c>
       <c r="F3" t="n">
-        <v>3.366080191256962</v>
+        <v>2.221054405884378</v>
       </c>
       <c r="G3" t="n">
-        <v>4.404825468171178</v>
+        <v>2.80616249012456</v>
       </c>
       <c r="H3" t="n">
-        <v>2.438520815294715</v>
+        <v>2.163252007320234</v>
       </c>
       <c r="I3" t="n">
-        <v>3.603892133773172</v>
+        <v>2.543151244373677</v>
       </c>
       <c r="J3" t="n">
-        <v>2.648680951081266</v>
+        <v>2.461517916591307</v>
       </c>
       <c r="K3" t="n">
-        <v>4.744527533820884</v>
+        <v>3.125265273481516</v>
       </c>
       <c r="L3" t="n">
-        <v>5.023145037269386</v>
+        <v>3.014017422875131</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.747170824169766</v>
+        <v>1.747170824169849</v>
       </c>
       <c r="C4" t="n">
-        <v>1.215583709821892</v>
+        <v>1.215583709821896</v>
       </c>
       <c r="D4" t="n">
-        <v>3.062299470132575</v>
+        <v>3.062299470132635</v>
       </c>
       <c r="E4" t="n">
-        <v>2.14019937127919</v>
+        <v>2.140199371279196</v>
       </c>
       <c r="F4" t="n">
-        <v>2.140199371279189</v>
+        <v>2.140199371279195</v>
       </c>
       <c r="G4" t="n">
-        <v>2.529770261263772</v>
+        <v>2.529770261263925</v>
       </c>
       <c r="H4" t="n">
-        <v>1.514853182260114</v>
+        <v>1.514853182260052</v>
       </c>
       <c r="I4" t="n">
-        <v>2.108316175669279</v>
+        <v>2.108316175669285</v>
       </c>
       <c r="J4" t="n">
-        <v>1.510608924822279</v>
+        <v>1.510608924822334</v>
       </c>
       <c r="K4" t="n">
-        <v>2.603159410154902</v>
+        <v>2.603159410154907</v>
       </c>
       <c r="L4" t="n">
-        <v>2.850523882553659</v>
+        <v>2.850523882553603</v>
       </c>
     </row>
     <row r="5">
@@ -3407,34 +3407,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.0688454271715</v>
+        <v>10.06884542717154</v>
       </c>
       <c r="C5" t="n">
-        <v>3.240426647614291</v>
+        <v>3.240426647614294</v>
       </c>
       <c r="D5" t="n">
-        <v>32.01719687002623</v>
+        <v>32.0171968700262</v>
       </c>
       <c r="E5" t="n">
-        <v>16.05322806802225</v>
+        <v>16.0532280680224</v>
       </c>
       <c r="F5" t="n">
-        <v>16.05322806802225</v>
+        <v>16.0532280680224</v>
       </c>
       <c r="G5" t="n">
         <v>23.60348936881753</v>
       </c>
       <c r="H5" t="n">
-        <v>6.267476456677344</v>
+        <v>6.267476456677367</v>
       </c>
       <c r="I5" t="n">
-        <v>16.05309501771525</v>
+        <v>16.05309501771544</v>
       </c>
       <c r="J5" t="n">
-        <v>5.85873374277119</v>
+        <v>5.858733742771178</v>
       </c>
       <c r="K5" t="n">
-        <v>24.30382947871696</v>
+        <v>24.30382947871693</v>
       </c>
       <c r="L5" t="n">
         <v>32.41801719549652</v>
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.020245446363576</v>
+        <v>4.020245446363542</v>
       </c>
       <c r="C6" t="n">
-        <v>1.705986062195028</v>
+        <v>1.705986062195034</v>
       </c>
       <c r="D6" t="n">
-        <v>3.469818044777026</v>
+        <v>3.469818044776952</v>
       </c>
       <c r="E6" t="n">
-        <v>2.477650185492662</v>
+        <v>2.477650185492671</v>
       </c>
       <c r="F6" t="n">
-        <v>2.510094807992898</v>
+        <v>2.510094807992902</v>
       </c>
       <c r="G6" t="n">
-        <v>4.802844883457569</v>
+        <v>4.802844883457505</v>
       </c>
       <c r="H6" t="n">
-        <v>4.280839529742866</v>
+        <v>1.904969112871789</v>
       </c>
       <c r="I6" t="n">
-        <v>2.502709927198132</v>
+        <v>4.381390797863129</v>
       </c>
       <c r="J6" t="n">
-        <v>3.851377288688067</v>
+        <v>1.927396154394219</v>
       </c>
       <c r="K6" t="n">
-        <v>2.993261082985919</v>
+        <v>2.993261082985886</v>
       </c>
       <c r="L6" t="n">
-        <v>3.248382243491295</v>
+        <v>3.248382243491263</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.402173197892719</v>
+        <v>2.402173197892723</v>
       </c>
       <c r="C7" t="n">
-        <v>2.021078351604562</v>
+        <v>2.021078351604566</v>
       </c>
       <c r="D7" t="n">
-        <v>3.717309455577086</v>
+        <v>3.717309455577059</v>
       </c>
       <c r="E7" t="n">
-        <v>2.792749473281797</v>
+        <v>2.792749473281801</v>
       </c>
       <c r="F7" t="n">
-        <v>2.792749473281797</v>
+        <v>2.792749473281801</v>
       </c>
       <c r="G7" t="n">
-        <v>3.184772634986709</v>
+        <v>3.184772634986723</v>
       </c>
       <c r="H7" t="n">
-        <v>2.169855555983068</v>
+        <v>2.169855555983009</v>
       </c>
       <c r="I7" t="n">
-        <v>2.76331854939226</v>
+        <v>2.763318549392265</v>
       </c>
       <c r="J7" t="n">
-        <v>2.165611298545233</v>
+        <v>2.165611298545238</v>
       </c>
       <c r="K7" t="n">
-        <v>3.258161783877852</v>
+        <v>3.258161783877789</v>
       </c>
       <c r="L7" t="n">
-        <v>3.505526256276611</v>
+        <v>3.505526256276564</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.035710162743888</v>
+        <v>4.035710162743844</v>
       </c>
       <c r="C8" t="n">
-        <v>5.241370566997509</v>
+        <v>5.241370567029243</v>
       </c>
       <c r="D8" t="n">
-        <v>7.232448585374807</v>
+        <v>7.232448585374788</v>
       </c>
       <c r="E8" t="n">
-        <v>5.554530290267393</v>
+        <v>5.554530290267392</v>
       </c>
       <c r="F8" t="n">
-        <v>4.463862218693405</v>
+        <v>4.46386221869341</v>
       </c>
       <c r="G8" t="n">
-        <v>6.376763755123029</v>
+        <v>6.376763755123005</v>
       </c>
       <c r="H8" t="n">
-        <v>5.361846676114504</v>
+        <v>5.361846676114507</v>
       </c>
       <c r="I8" t="n">
-        <v>5.955309669528593</v>
+        <v>5.955309669528586</v>
       </c>
       <c r="J8" t="n">
-        <v>5.357908697924085</v>
+        <v>5.357908697924035</v>
       </c>
       <c r="K8" t="n">
-        <v>4.862749662773731</v>
+        <v>4.862749662773676</v>
       </c>
       <c r="L8" t="n">
-        <v>8.325453055966291</v>
+        <v>8.325453055966239</v>
       </c>
     </row>
     <row r="9">
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.3579355154711</v>
+        <v>80.35793551547111</v>
       </c>
       <c r="C9" t="n">
         <v>101.7624613952998</v>
       </c>
       <c r="D9" t="n">
-        <v>103.4586857642007</v>
+        <v>103.4586857642006</v>
       </c>
       <c r="E9" t="n">
         <v>127.6449799569556</v>
@@ -3594,10 +3594,10 @@
         <v>101.9069943422404</v>
       </c>
       <c r="K9" t="n">
-        <v>89.86475313081193</v>
+        <v>90.37687098883958</v>
       </c>
       <c r="L9" t="n">
-        <v>103.2469092999718</v>
+        <v>103.2469092999717</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.026361381977853</v>
+        <v>2.009175704834395</v>
       </c>
       <c r="C2" t="n">
-        <v>1.204734193473642</v>
+        <v>1.558594237844284</v>
       </c>
       <c r="D2" t="n">
-        <v>4.310344192709476</v>
+        <v>2.129377183808915</v>
       </c>
       <c r="E2" t="n">
-        <v>2.948322956121448</v>
+        <v>1.849257714759266</v>
       </c>
       <c r="F2" t="n">
-        <v>2.948322956121449</v>
+        <v>1.84928753407067</v>
       </c>
       <c r="G2" t="n">
-        <v>3.533967890329674</v>
+        <v>2.088518041022148</v>
       </c>
       <c r="H2" t="n">
-        <v>2.547836125612669</v>
+        <v>2.03510369374084</v>
       </c>
       <c r="I2" t="n">
-        <v>3.215597234265334</v>
+        <v>2.071769018118306</v>
       </c>
       <c r="J2" t="n">
-        <v>2.115963285352075</v>
+        <v>2.101169449555225</v>
       </c>
       <c r="K2" t="n">
-        <v>3.555458309926011</v>
+        <v>2.180448530347711</v>
       </c>
       <c r="L2" t="n">
-        <v>3.127767250422049</v>
+        <v>2.066333410197887</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.305969541449228</v>
+        <v>2.072386194003992</v>
       </c>
       <c r="C3" t="n">
-        <v>1.438706543346428</v>
+        <v>1.243310875637343</v>
       </c>
       <c r="D3" t="n">
-        <v>4.933022899404484</v>
+        <v>2.927929186876664</v>
       </c>
       <c r="E3" t="n">
-        <v>3.40658051678117</v>
+        <v>2.150610742052317</v>
       </c>
       <c r="F3" t="n">
-        <v>3.406580516781149</v>
+        <v>2.150640561363512</v>
       </c>
       <c r="G3" t="n">
-        <v>4.040029325801184</v>
+        <v>2.63800068994719</v>
       </c>
       <c r="H3" t="n">
-        <v>2.906117743094367</v>
+        <v>2.268237654527558</v>
       </c>
       <c r="I3" t="n">
-        <v>3.677792240288156</v>
+        <v>2.517943853522439</v>
       </c>
       <c r="J3" t="n">
-        <v>2.39221727507657</v>
+        <v>2.217651562918063</v>
       </c>
       <c r="K3" t="n">
-        <v>4.047256407519466</v>
+        <v>2.761475562511511</v>
       </c>
       <c r="L3" t="n">
-        <v>3.572758189926842</v>
+        <v>2.488356449965583</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.39663381910096</v>
+        <v>1.396633819100956</v>
       </c>
       <c r="C4" t="n">
-        <v>1.079197574878241</v>
+        <v>1.079197574878243</v>
       </c>
       <c r="D4" t="n">
-        <v>2.754364819519548</v>
+        <v>2.754364819519545</v>
       </c>
       <c r="E4" t="n">
         <v>2.148667735646567</v>
       </c>
       <c r="F4" t="n">
-        <v>2.148667735646567</v>
+        <v>2.148667735646566</v>
       </c>
       <c r="G4" t="n">
-        <v>2.291900859700932</v>
+        <v>2.291900859700927</v>
       </c>
       <c r="H4" t="n">
-        <v>1.70691731254743</v>
+        <v>1.706917312547433</v>
       </c>
       <c r="I4" t="n">
-        <v>2.097688560822094</v>
+        <v>2.097688560822087</v>
       </c>
       <c r="J4" t="n">
-        <v>1.383359405768549</v>
+        <v>1.383359405768537</v>
       </c>
       <c r="K4" t="n">
-        <v>2.236393627387355</v>
+        <v>2.236393627387356</v>
       </c>
       <c r="L4" t="n">
-        <v>2.051619807400997</v>
+        <v>2.051619807400991</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.936181379505308</v>
+        <v>5.936181379505296</v>
       </c>
       <c r="C5" t="n">
-        <v>2.446626000208416</v>
+        <v>2.446626000208407</v>
       </c>
       <c r="D5" t="n">
-        <v>29.93260421851421</v>
+        <v>29.93260421851417</v>
       </c>
       <c r="E5" t="n">
-        <v>18.45077447916735</v>
+        <v>18.45077447916647</v>
       </c>
       <c r="F5" t="n">
-        <v>18.45077447916735</v>
+        <v>18.45077447916647</v>
       </c>
       <c r="G5" t="n">
-        <v>22.26141600621026</v>
+        <v>22.26141600620851</v>
       </c>
       <c r="H5" t="n">
-        <v>12.44608131875428</v>
+        <v>12.44608131875431</v>
       </c>
       <c r="I5" t="n">
-        <v>18.45069841986304</v>
+        <v>18.45069841986234</v>
       </c>
       <c r="J5" t="n">
-        <v>5.612683072015596</v>
+        <v>5.612683072015598</v>
       </c>
       <c r="K5" t="n">
-        <v>20.74340833750873</v>
+        <v>20.74340833750877</v>
       </c>
       <c r="L5" t="n">
-        <v>19.74179722163481</v>
+        <v>19.74179722163482</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.746436428510728</v>
+        <v>1.746436428510742</v>
       </c>
       <c r="C6" t="n">
-        <v>1.514759570891406</v>
+        <v>1.514759570891395</v>
       </c>
       <c r="D6" t="n">
         <v>3.117340169839979</v>
       </c>
       <c r="E6" t="n">
-        <v>2.441228001773777</v>
+        <v>2.441228001773771</v>
       </c>
       <c r="F6" t="n">
-        <v>2.45832489581783</v>
+        <v>2.45832489581782</v>
       </c>
       <c r="G6" t="n">
-        <v>4.53461196606539</v>
+        <v>2.641703469110704</v>
       </c>
       <c r="H6" t="n">
-        <v>4.472784596343748</v>
+        <v>4.47278459634373</v>
       </c>
       <c r="I6" t="n">
-        <v>4.340399667186543</v>
+        <v>2.447491170231863</v>
       </c>
       <c r="J6" t="n">
-        <v>3.683544988072247</v>
+        <v>1.753558954076001</v>
       </c>
       <c r="K6" t="n">
-        <v>2.574177808426798</v>
+        <v>2.574177808426794</v>
       </c>
       <c r="L6" t="n">
-        <v>2.404117046365524</v>
+        <v>2.404117046365536</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.063140843841277</v>
+        <v>2.063140843841287</v>
       </c>
       <c r="C7" t="n">
-        <v>1.882708793525774</v>
+        <v>1.882708793525778</v>
       </c>
       <c r="D7" t="n">
-        <v>3.420875172857474</v>
+        <v>3.420875172857462</v>
       </c>
       <c r="E7" t="n">
-        <v>2.79756750257469</v>
+        <v>2.79756750257468</v>
       </c>
       <c r="F7" t="n">
-        <v>2.79756750257469</v>
+        <v>2.79756750257468</v>
       </c>
       <c r="G7" t="n">
-        <v>2.958407884441244</v>
+        <v>2.958407884441255</v>
       </c>
       <c r="H7" t="n">
-        <v>2.373424337287735</v>
+        <v>2.373424337287733</v>
       </c>
       <c r="I7" t="n">
-        <v>2.764195585562407</v>
+        <v>2.764195585562398</v>
       </c>
       <c r="J7" t="n">
-        <v>2.04986643050887</v>
+        <v>2.049866430508867</v>
       </c>
       <c r="K7" t="n">
-        <v>2.902900652127671</v>
+        <v>2.902900652127663</v>
       </c>
       <c r="L7" t="n">
-        <v>2.718126832141312</v>
+        <v>2.718126832141301</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.735310081679862</v>
+        <v>3.735310081679854</v>
       </c>
       <c r="C8" t="n">
-        <v>5.13770699620342</v>
+        <v>5.137706996172044</v>
       </c>
       <c r="D8" t="n">
-        <v>6.965302540440759</v>
+        <v>6.965302540440745</v>
       </c>
       <c r="E8" t="n">
-        <v>5.591777073014494</v>
+        <v>5.59177707301447</v>
       </c>
       <c r="F8" t="n">
-        <v>4.505456648111677</v>
+        <v>4.505456648111657</v>
       </c>
       <c r="G8" t="n">
-        <v>6.181288478903573</v>
+        <v>6.181288478903562</v>
       </c>
       <c r="H8" t="n">
-        <v>5.596304931747646</v>
+        <v>5.596304931747613</v>
       </c>
       <c r="I8" t="n">
-        <v>5.987076180024729</v>
+        <v>5.987076180024718</v>
       </c>
       <c r="J8" t="n">
-        <v>5.273051783645845</v>
+        <v>5.273051783645847</v>
       </c>
       <c r="K8" t="n">
-        <v>4.54626463037672</v>
+        <v>4.546264630376701</v>
       </c>
       <c r="L8" t="n">
-        <v>7.560855106549281</v>
+        <v>7.56085510654923</v>
       </c>
     </row>
     <row r="9">
@@ -3984,13 +3984,13 @@
         <v>107.918277693834</v>
       </c>
       <c r="I9" t="n">
-        <v>108.3090489421087</v>
+        <v>108.3090489421086</v>
       </c>
       <c r="J9" t="n">
         <v>107.594719787055</v>
       </c>
       <c r="K9" t="n">
-        <v>95.10298956119756</v>
+        <v>95.10298956119755</v>
       </c>
       <c r="L9" t="n">
         <v>108.2629801886874</v>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.408848796304413</v>
+        <v>2.324485404451763</v>
       </c>
       <c r="C2" t="n">
-        <v>1.456153717654471</v>
+        <v>1.798427838480095</v>
       </c>
       <c r="D2" t="n">
-        <v>4.788333940970719</v>
+        <v>2.39708496773736</v>
       </c>
       <c r="E2" t="n">
-        <v>3.567424598051957</v>
+        <v>2.152971531682257</v>
       </c>
       <c r="F2" t="n">
-        <v>3.567424598051956</v>
+        <v>2.153004405439015</v>
       </c>
       <c r="G2" t="n">
-        <v>4.334064947756565</v>
+        <v>2.373177692875399</v>
       </c>
       <c r="H2" t="n">
-        <v>2.239289385320994</v>
+        <v>2.260437402065861</v>
       </c>
       <c r="I2" t="n">
-        <v>3.797967778323359</v>
+        <v>2.344975305985646</v>
       </c>
       <c r="J2" t="n">
-        <v>2.754469601854725</v>
+        <v>2.464570505134691</v>
       </c>
       <c r="K2" t="n">
-        <v>4.597258838852593</v>
+        <v>2.566007469251197</v>
       </c>
       <c r="L2" t="n">
-        <v>4.129920670320206</v>
+        <v>2.36156874106114</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.925253393435495</v>
+        <v>2.744358438739562</v>
       </c>
       <c r="C3" t="n">
-        <v>1.75980301968977</v>
+        <v>1.47057454423976</v>
       </c>
       <c r="D3" t="n">
-        <v>5.511947069288585</v>
+        <v>3.260153863939713</v>
       </c>
       <c r="E3" t="n">
-        <v>4.142310020808629</v>
+        <v>2.572421761483219</v>
       </c>
       <c r="F3" t="n">
-        <v>4.14231002080863</v>
+        <v>2.572454635239987</v>
       </c>
       <c r="G3" t="n">
-        <v>4.989443625553848</v>
+        <v>3.091305989605996</v>
       </c>
       <c r="H3" t="n">
-        <v>2.58051958888606</v>
+        <v>2.303642370098916</v>
       </c>
       <c r="I3" t="n">
-        <v>4.378213151213601</v>
+        <v>2.889406460585554</v>
       </c>
       <c r="J3" t="n">
-        <v>3.138962007504054</v>
+        <v>2.722183754424604</v>
       </c>
       <c r="K3" t="n">
-        <v>5.257693236241164</v>
+        <v>3.418077837468691</v>
       </c>
       <c r="L3" t="n">
-        <v>4.754561949910865</v>
+        <v>3.019375959753951</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.332263804127121</v>
+        <v>2.332263804127045</v>
       </c>
       <c r="C4" t="n">
-        <v>1.332834441077833</v>
+        <v>1.33283444107782</v>
       </c>
       <c r="D4" t="n">
-        <v>3.152309268887218</v>
+        <v>3.152309268887081</v>
       </c>
       <c r="E4" t="n">
-        <v>2.639400508921478</v>
+        <v>2.639400508921482</v>
       </c>
       <c r="F4" t="n">
-        <v>2.639400508921479</v>
+        <v>2.639400508921484</v>
       </c>
       <c r="G4" t="n">
-        <v>2.881516130991638</v>
+        <v>2.881516130991556</v>
       </c>
       <c r="H4" t="n">
-        <v>1.637575666578223</v>
+        <v>1.637575666578102</v>
       </c>
       <c r="I4" t="n">
-        <v>2.559064902741679</v>
+        <v>2.559064902741676</v>
       </c>
       <c r="J4" t="n">
-        <v>1.810210036593527</v>
+        <v>1.810210036593373</v>
       </c>
       <c r="K4" t="n">
-        <v>2.902274043642759</v>
+        <v>2.902274043642612</v>
       </c>
       <c r="L4" t="n">
-        <v>2.761156162923009</v>
+        <v>2.761156162922878</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.43439026695517</v>
+        <v>18.43439026695512</v>
       </c>
       <c r="C5" t="n">
-        <v>3.540442706393993</v>
+        <v>3.540442706393989</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71975762396773</v>
+        <v>31.71975762396753</v>
       </c>
       <c r="E5" t="n">
-        <v>21.90692967161915</v>
+        <v>21.90692967161911</v>
       </c>
       <c r="F5" t="n">
-        <v>21.90692967161915</v>
+        <v>21.90692967161911</v>
       </c>
       <c r="G5" t="n">
-        <v>27.86504088771474</v>
+        <v>27.86504088771451</v>
       </c>
       <c r="H5" t="n">
-        <v>6.546677924053737</v>
+        <v>6.546677924053694</v>
       </c>
       <c r="I5" t="n">
-        <v>21.9068071187035</v>
+        <v>21.90680711870349</v>
       </c>
       <c r="J5" t="n">
-        <v>9.282994627220335</v>
+        <v>9.282994627220129</v>
       </c>
       <c r="K5" t="n">
-        <v>27.57324622316706</v>
+        <v>27.57324622316689</v>
       </c>
       <c r="L5" t="n">
-        <v>28.56369708073881</v>
+        <v>28.56369708073863</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.754905540507409</v>
+        <v>4.693104479808857</v>
       </c>
       <c r="C6" t="n">
-        <v>1.847986319798678</v>
+        <v>1.847986319798669</v>
       </c>
       <c r="D6" t="n">
-        <v>3.576314273665263</v>
+        <v>3.576318049493132</v>
       </c>
       <c r="E6" t="n">
-        <v>2.961466153310603</v>
+        <v>2.961466153310595</v>
       </c>
       <c r="F6" t="n">
-        <v>2.991331990430381</v>
+        <v>2.991331990430368</v>
       </c>
       <c r="G6" t="n">
-        <v>3.30415786737204</v>
+        <v>3.3041578673719</v>
       </c>
       <c r="H6" t="n">
-        <v>4.49305590456925</v>
+        <v>4.493055904569099</v>
       </c>
       <c r="I6" t="n">
-        <v>4.919905578423479</v>
+        <v>4.919905578423485</v>
       </c>
       <c r="J6" t="n">
-        <v>4.246140634988528</v>
+        <v>2.256671644582392</v>
       </c>
       <c r="K6" t="n">
-        <v>3.318932623745712</v>
+        <v>3.3189326237456</v>
       </c>
       <c r="L6" t="n">
-        <v>3.182557034710989</v>
+        <v>3.182557034710829</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.052070411086413</v>
+        <v>3.052070411086335</v>
       </c>
       <c r="C7" t="n">
-        <v>2.210630975168575</v>
+        <v>2.210630975168582</v>
       </c>
       <c r="D7" t="n">
-        <v>3.872123410434826</v>
+        <v>3.872123410434744</v>
       </c>
       <c r="E7" t="n">
-        <v>3.321216680881349</v>
+        <v>3.321216680881342</v>
       </c>
       <c r="F7" t="n">
-        <v>3.321216680881349</v>
+        <v>3.321216680881343</v>
       </c>
       <c r="G7" t="n">
-        <v>3.601322737950908</v>
+        <v>3.601322737950822</v>
       </c>
       <c r="H7" t="n">
-        <v>2.357382273537449</v>
+        <v>2.357382273537421</v>
       </c>
       <c r="I7" t="n">
-        <v>3.278871509700953</v>
+        <v>3.278871509700961</v>
       </c>
       <c r="J7" t="n">
-        <v>2.530016643552776</v>
+        <v>2.530016643552678</v>
       </c>
       <c r="K7" t="n">
-        <v>3.622080650601961</v>
+        <v>3.6220806506019</v>
       </c>
       <c r="L7" t="n">
-        <v>3.480962769882275</v>
+        <v>3.480962769882186</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.724247168620096</v>
+        <v>4.724247168619905</v>
       </c>
       <c r="C8" t="n">
-        <v>5.562994114502497</v>
+        <v>5.562994114502457</v>
       </c>
       <c r="D8" t="n">
-        <v>7.523778426467277</v>
+        <v>7.523778426467109</v>
       </c>
       <c r="E8" t="n">
-        <v>6.17867007619732</v>
+        <v>6.178670076197256</v>
       </c>
       <c r="F8" t="n">
-        <v>5.028324436742635</v>
+        <v>5.028324436742619</v>
       </c>
       <c r="G8" t="n">
-        <v>6.913020026150341</v>
+        <v>6.913020026150298</v>
       </c>
       <c r="H8" t="n">
-        <v>5.669079561724509</v>
+        <v>5.66907956172442</v>
       </c>
       <c r="I8" t="n">
-        <v>6.590568797900477</v>
+        <v>6.59056879790041</v>
       </c>
       <c r="J8" t="n">
-        <v>5.842036142819451</v>
+        <v>5.842036142819273</v>
       </c>
       <c r="K8" t="n">
-        <v>5.26380247257014</v>
+        <v>5.263802472569955</v>
       </c>
       <c r="L8" t="n">
-        <v>8.50527634540563</v>
+        <v>8.505276345405342</v>
       </c>
     </row>
     <row r="9">
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.20963947266912</v>
+        <v>81.20963947266898</v>
       </c>
       <c r="C9" t="n">
         <v>102.2342296803132</v>
       </c>
       <c r="D9" t="n">
-        <v>103.895715617243</v>
+        <v>103.8957156172429</v>
       </c>
       <c r="E9" t="n">
         <v>128.5355285213086</v>
@@ -4374,22 +4374,22 @@
         <v>103.3025929620458</v>
       </c>
       <c r="G9" t="n">
-        <v>103.6249214430955</v>
+        <v>103.6249214430954</v>
       </c>
       <c r="H9" t="n">
-        <v>102.3809809786823</v>
+        <v>102.380980978682</v>
       </c>
       <c r="I9" t="n">
-        <v>103.3024702148457</v>
+        <v>103.3024702148456</v>
       </c>
       <c r="J9" t="n">
-        <v>102.5536153486976</v>
+        <v>102.5536153486973</v>
       </c>
       <c r="K9" t="n">
-        <v>90.97641634158309</v>
+        <v>76.1124446934426</v>
       </c>
       <c r="L9" t="n">
-        <v>103.504561475027</v>
+        <v>103.5045614750268</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.195906808355486</v>
+        <v>2.453811580503018</v>
       </c>
       <c r="C2" t="n">
-        <v>1.564941827947353</v>
+        <v>1.950331742748079</v>
       </c>
       <c r="D2" t="n">
-        <v>4.850696481553391</v>
+        <v>2.54089987432641</v>
       </c>
       <c r="E2" t="n">
-        <v>3.401089187018425</v>
+        <v>2.298450213926274</v>
       </c>
       <c r="F2" t="n">
-        <v>3.401089187018425</v>
+        <v>2.298487759418436</v>
       </c>
       <c r="G2" t="n">
-        <v>4.350338274494332</v>
+        <v>2.514567015680354</v>
       </c>
       <c r="H2" t="n">
-        <v>2.358104150168598</v>
+        <v>2.407151301194206</v>
       </c>
       <c r="I2" t="n">
-        <v>3.614011429516011</v>
+        <v>2.475827953177876</v>
       </c>
       <c r="J2" t="n">
-        <v>3.080451140237886</v>
+        <v>2.72274685116534</v>
       </c>
       <c r="K2" t="n">
-        <v>4.665554180871872</v>
+        <v>2.744965049187179</v>
       </c>
       <c r="L2" t="n">
-        <v>4.526950403591878</v>
+        <v>2.523216797397982</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.723514154476977</v>
+        <v>2.749636331424294</v>
       </c>
       <c r="C3" t="n">
-        <v>1.926750017785704</v>
+        <v>1.603958597982812</v>
       </c>
       <c r="D3" t="n">
-        <v>5.626865067302685</v>
+        <v>3.368803895443079</v>
       </c>
       <c r="E3" t="n">
-        <v>3.99153410457366</v>
+        <v>2.612862506258287</v>
       </c>
       <c r="F3" t="n">
-        <v>3.991534104573659</v>
+        <v>2.612900051750431</v>
       </c>
       <c r="G3" t="n">
-        <v>5.051349480294427</v>
+        <v>3.182642190705077</v>
       </c>
       <c r="H3" t="n">
-        <v>2.760522386495137</v>
+        <v>2.433456082747488</v>
       </c>
       <c r="I3" t="n">
-        <v>4.207389220437419</v>
+        <v>2.905687957412448</v>
       </c>
       <c r="J3" t="n">
-        <v>3.537738801241959</v>
+        <v>3.05851703814486</v>
       </c>
       <c r="K3" t="n">
-        <v>5.372725548866611</v>
+        <v>3.573578481045022</v>
       </c>
       <c r="L3" t="n">
-        <v>5.254390943723875</v>
+        <v>3.254536948710795</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.294392843029744</v>
+        <v>2.294392843029729</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447596892786811</v>
+        <v>1.447596892786807</v>
       </c>
       <c r="D4" t="n">
-        <v>3.278095184359379</v>
+        <v>3.278095184359378</v>
       </c>
       <c r="E4" t="n">
-        <v>2.552394597445983</v>
+        <v>2.552394597445951</v>
       </c>
       <c r="F4" t="n">
-        <v>2.552394597445987</v>
+        <v>2.552394597445951</v>
       </c>
       <c r="G4" t="n">
-        <v>2.979836558186911</v>
+        <v>2.979836558186904</v>
       </c>
       <c r="H4" t="n">
-        <v>1.796910150030756</v>
+        <v>1.796910150030731</v>
       </c>
       <c r="I4" t="n">
-        <v>2.538112931136235</v>
+        <v>2.538112931136198</v>
       </c>
       <c r="J4" t="n">
-        <v>2.016096681507713</v>
+        <v>2.016096681507721</v>
       </c>
       <c r="K4" t="n">
-        <v>3.005032800409188</v>
+        <v>3.005032800409199</v>
       </c>
       <c r="L4" t="n">
-        <v>3.085804938736363</v>
+        <v>3.08580493873637</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.37573012114523</v>
+        <v>15.37573012114525</v>
       </c>
       <c r="C5" t="n">
-        <v>3.755435876975699</v>
+        <v>3.755435876975678</v>
       </c>
       <c r="D5" t="n">
-        <v>31.53768118934826</v>
+        <v>31.53768118934816</v>
       </c>
       <c r="E5" t="n">
-        <v>19.20948351732474</v>
+        <v>19.20948351732483</v>
       </c>
       <c r="F5" t="n">
-        <v>19.20948351732474</v>
+        <v>19.20948351732483</v>
       </c>
       <c r="G5" t="n">
-        <v>27.19711545813646</v>
+        <v>27.19711545813644</v>
       </c>
       <c r="H5" t="n">
-        <v>6.9771785933291</v>
+        <v>6.977178593329095</v>
       </c>
       <c r="I5" t="n">
-        <v>19.2093205512727</v>
+        <v>19.2093205512726</v>
       </c>
       <c r="J5" t="n">
-        <v>10.51902488277706</v>
+        <v>10.51902488277705</v>
       </c>
       <c r="K5" t="n">
-        <v>26.99727553503202</v>
+        <v>26.99727553503199</v>
       </c>
       <c r="L5" t="n">
-        <v>32.2261644253297</v>
+        <v>32.22616442532969</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.787557605711465</v>
+        <v>4.843587973279688</v>
       </c>
       <c r="C6" t="n">
-        <v>2.064963579317477</v>
+        <v>2.064963579317471</v>
       </c>
       <c r="D6" t="n">
-        <v>3.778114499195767</v>
+        <v>3.778109550622033</v>
       </c>
       <c r="E6" t="n">
-        <v>2.985790184658348</v>
+        <v>2.98579018465833</v>
       </c>
       <c r="F6" t="n">
-        <v>3.037025861498438</v>
+        <v>3.037025861498426</v>
       </c>
       <c r="G6" t="n">
-        <v>5.52903168843682</v>
+        <v>3.473001320868691</v>
       </c>
       <c r="H6" t="n">
-        <v>4.846877934462816</v>
+        <v>4.846877934462817</v>
       </c>
       <c r="I6" t="n">
-        <v>5.08730806138614</v>
+        <v>3.031277693817951</v>
       </c>
       <c r="J6" t="n">
-        <v>2.543194181583347</v>
+        <v>4.657677944273111</v>
       </c>
       <c r="K6" t="n">
-        <v>3.495605423424401</v>
+        <v>3.495605423424457</v>
       </c>
       <c r="L6" t="n">
-        <v>3.578817177373722</v>
+        <v>3.578817177373744</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.044478392192379</v>
+        <v>3.044478392192426</v>
       </c>
       <c r="C7" t="n">
-        <v>2.389626668564094</v>
+        <v>2.389626668564078</v>
       </c>
       <c r="D7" t="n">
-        <v>4.028195817813864</v>
+        <v>4.028195817813881</v>
       </c>
       <c r="E7" t="n">
-        <v>3.313594541321201</v>
+        <v>3.31359454132119</v>
       </c>
       <c r="F7" t="n">
-        <v>3.313594541321201</v>
+        <v>3.31359454132119</v>
       </c>
       <c r="G7" t="n">
-        <v>3.729922107349573</v>
+        <v>3.729922107349589</v>
       </c>
       <c r="H7" t="n">
-        <v>2.546995699193406</v>
+        <v>2.546995699193438</v>
       </c>
       <c r="I7" t="n">
-        <v>3.288198480298892</v>
+        <v>3.288198480298876</v>
       </c>
       <c r="J7" t="n">
-        <v>2.766182230670357</v>
+        <v>2.766182230670376</v>
       </c>
       <c r="K7" t="n">
-        <v>3.755118349571833</v>
+        <v>3.755118349571882</v>
       </c>
       <c r="L7" t="n">
-        <v>3.835890487899013</v>
+        <v>3.835890487899033</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.780808524789848</v>
+        <v>4.780808524789852</v>
       </c>
       <c r="C8" t="n">
-        <v>5.909855976496046</v>
+        <v>5.909855976454936</v>
       </c>
       <c r="D8" t="n">
-        <v>7.888799836524831</v>
+        <v>7.888799836524732</v>
       </c>
       <c r="E8" t="n">
-        <v>6.324816435173705</v>
+        <v>6.324816435173627</v>
       </c>
       <c r="F8" t="n">
-        <v>5.095507342135148</v>
+        <v>5.095507342135086</v>
       </c>
       <c r="G8" t="n">
-        <v>7.225706837882326</v>
+        <v>7.225706837882294</v>
       </c>
       <c r="H8" t="n">
-        <v>6.042780429711809</v>
+        <v>6.042780429711741</v>
       </c>
       <c r="I8" t="n">
-        <v>6.78398321083166</v>
+        <v>6.783983210831594</v>
       </c>
       <c r="J8" t="n">
-        <v>6.262312741209353</v>
+        <v>6.262312741209371</v>
       </c>
       <c r="K8" t="n">
-        <v>5.458765709867888</v>
+        <v>5.458765709867918</v>
       </c>
       <c r="L8" t="n">
-        <v>9.169572666292627</v>
+        <v>9.169572666292593</v>
       </c>
     </row>
     <row r="9">
@@ -4758,7 +4758,7 @@
         <v>81.06333259621158</v>
       </c>
       <c r="C9" t="n">
-        <v>102.2706079417264</v>
+        <v>102.2706079417263</v>
       </c>
       <c r="D9" t="n">
         <v>103.9091631069793</v>
@@ -4776,13 +4776,13 @@
         <v>102.4279769723557</v>
       </c>
       <c r="I9" t="n">
-        <v>103.1691797534613</v>
+        <v>103.1691797534612</v>
       </c>
       <c r="J9" t="n">
         <v>102.6471635038326</v>
       </c>
       <c r="K9" t="n">
-        <v>90.45518149314474</v>
+        <v>90.45518149314476</v>
       </c>
       <c r="L9" t="n">
         <v>103.7168717610613</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.193281758731617</v>
+        <v>2.186412480120625</v>
       </c>
       <c r="C2" t="n">
-        <v>2.473335205096268</v>
+        <v>2.056321765943951</v>
       </c>
       <c r="D2" t="n">
-        <v>4.135646519226105</v>
+        <v>2.288635279618303</v>
       </c>
       <c r="E2" t="n">
-        <v>2.657185475044245</v>
+        <v>2.210604090154175</v>
       </c>
       <c r="F2" t="n">
-        <v>2.173807689924673</v>
+        <v>1.808291183717773</v>
       </c>
       <c r="G2" t="n">
-        <v>3.306674419127449</v>
+        <v>2.245008124461318</v>
       </c>
       <c r="H2" t="n">
-        <v>4.145421898297172</v>
+        <v>2.288635323309075</v>
       </c>
       <c r="I2" t="n">
-        <v>2.657634107617806</v>
+        <v>2.210842148542885</v>
       </c>
       <c r="J2" t="n">
-        <v>3.166096038948</v>
+        <v>2.641844413366441</v>
       </c>
       <c r="K2" t="n">
-        <v>2.376695470611205</v>
+        <v>2.102277483678052</v>
       </c>
       <c r="L2" t="n">
-        <v>3.925159601393476</v>
+        <v>2.277467509755342</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.494397104131256</v>
+        <v>2.28212779430367</v>
       </c>
       <c r="C3" t="n">
-        <v>2.843007324505799</v>
+        <v>2.202093015901323</v>
       </c>
       <c r="D3" t="n">
-        <v>4.728518938347903</v>
+        <v>3.009641643804626</v>
       </c>
       <c r="E3" t="n">
-        <v>3.02802624966228</v>
+        <v>2.455081289418647</v>
       </c>
       <c r="F3" t="n">
-        <v>2.54464846454271</v>
+        <v>1.790966757787572</v>
       </c>
       <c r="G3" t="n">
-        <v>3.77502930218124</v>
+        <v>2.699914038867654</v>
       </c>
       <c r="H3" t="n">
-        <v>4.740280379841118</v>
+        <v>3.018491658897884</v>
       </c>
       <c r="I3" t="n">
-        <v>3.024196622298822</v>
+        <v>2.455477187139466</v>
       </c>
       <c r="J3" t="n">
-        <v>3.535464445246483</v>
+        <v>3.165747554973916</v>
       </c>
       <c r="K3" t="n">
-        <v>2.723427858500086</v>
+        <v>2.230742142159478</v>
       </c>
       <c r="L3" t="n">
-        <v>4.486281194033271</v>
+        <v>2.937762591272028</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.574964347321308</v>
+        <v>1.574964347321575</v>
       </c>
       <c r="C4" t="n">
         <v>1.633619886558799</v>
       </c>
       <c r="D4" t="n">
-        <v>2.729617892458672</v>
+        <v>2.729617892458904</v>
       </c>
       <c r="E4" t="n">
-        <v>1.684664806062048</v>
+        <v>1.68466480606205</v>
       </c>
       <c r="F4" t="n">
-        <v>1.684664806062047</v>
+        <v>1.68466480606205</v>
       </c>
       <c r="G4" t="n">
-        <v>2.235934510848359</v>
+        <v>2.235934510848354</v>
       </c>
       <c r="H4" t="n">
-        <v>2.73530709884077</v>
+        <v>2.735307098841018</v>
       </c>
       <c r="I4" t="n">
-        <v>1.845461729283945</v>
+        <v>1.845461729283947</v>
       </c>
       <c r="J4" t="n">
-        <v>1.845081666938954</v>
+        <v>1.845081666939057</v>
       </c>
       <c r="K4" t="n">
-        <v>1.75549769020456</v>
+        <v>1.755497690204746</v>
       </c>
       <c r="L4" t="n">
-        <v>2.604506174906828</v>
+        <v>2.60450617490707</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.018627863754307</v>
+        <v>6.018627863754572</v>
       </c>
       <c r="C5" t="n">
-        <v>10.67116399111748</v>
+        <v>10.67116399111746</v>
       </c>
       <c r="D5" t="n">
-        <v>26.70761011495771</v>
+        <v>26.70761011495779</v>
       </c>
       <c r="E5" t="n">
-        <v>10.6711717501247</v>
+        <v>10.67117175012468</v>
       </c>
       <c r="F5" t="n">
-        <v>10.6711717501247</v>
+        <v>10.67117175012468</v>
       </c>
       <c r="G5" t="n">
-        <v>18.30207855954067</v>
+        <v>18.30207855954085</v>
       </c>
       <c r="H5" t="n">
-        <v>30.01801270284701</v>
+        <v>30.01801270284707</v>
       </c>
       <c r="I5" t="n">
         <v>10.67101606401553</v>
       </c>
       <c r="J5" t="n">
-        <v>11.48532497882976</v>
+        <v>11.48532497882977</v>
       </c>
       <c r="K5" t="n">
-        <v>9.324759110792344</v>
+        <v>9.324759110792492</v>
       </c>
       <c r="L5" t="n">
-        <v>7.693210809982219</v>
+        <v>7.693210809982289</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.994677287046664</v>
+        <v>1.976679860822631</v>
       </c>
       <c r="C6" t="n">
-        <v>2.209478185308525</v>
+        <v>2.209478185308533</v>
       </c>
       <c r="D6" t="n">
-        <v>3.211551434701986</v>
+        <v>3.211558908462123</v>
       </c>
       <c r="E6" t="n">
-        <v>2.194147699079458</v>
+        <v>2.194147699079455</v>
       </c>
       <c r="F6" t="n">
         <v>2.245104751988136</v>
       </c>
       <c r="G6" t="n">
-        <v>4.655647450573245</v>
+        <v>2.637650024349402</v>
       </c>
       <c r="H6" t="n">
-        <v>5.735810470897867</v>
+        <v>5.735810470898129</v>
       </c>
       <c r="I6" t="n">
-        <v>4.265174669008889</v>
+        <v>4.265174669008928</v>
       </c>
       <c r="J6" t="n">
-        <v>4.382091359119561</v>
+        <v>2.275298227424139</v>
       </c>
       <c r="K6" t="n">
-        <v>2.122859542342021</v>
+        <v>2.122859542341955</v>
       </c>
       <c r="L6" t="n">
-        <v>3.009317285191431</v>
+        <v>3.00931728519178</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.279285264380742</v>
+        <v>2.279285264380589</v>
       </c>
       <c r="C7" t="n">
-        <v>2.549930573445063</v>
+        <v>2.549930573445066</v>
       </c>
       <c r="D7" t="n">
-        <v>3.433952850035266</v>
+        <v>3.433952850035303</v>
       </c>
       <c r="E7" t="n">
-        <v>2.524362120422718</v>
+        <v>2.524362120422725</v>
       </c>
       <c r="F7" t="n">
-        <v>2.524362120422718</v>
+        <v>2.524362120422725</v>
       </c>
       <c r="G7" t="n">
-        <v>2.940255427907526</v>
+        <v>2.940255427907527</v>
       </c>
       <c r="H7" t="n">
-        <v>3.439628015900198</v>
+        <v>3.439628015900031</v>
       </c>
       <c r="I7" t="n">
-        <v>2.549782646343111</v>
+        <v>2.549782646343132</v>
       </c>
       <c r="J7" t="n">
-        <v>2.549402583998336</v>
+        <v>2.549402583998182</v>
       </c>
       <c r="K7" t="n">
-        <v>2.459818607263859</v>
+        <v>2.459818607263763</v>
       </c>
       <c r="L7" t="n">
-        <v>3.30882709196617</v>
+        <v>3.30882709196603</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.04707099128874</v>
+        <v>4.047070991288758</v>
       </c>
       <c r="C8" t="n">
-        <v>6.002727961455633</v>
+        <v>6.002727961489911</v>
       </c>
       <c r="D8" t="n">
-        <v>7.265276363540101</v>
+        <v>7.265276363540244</v>
       </c>
       <c r="E8" t="n">
-        <v>5.537862739215511</v>
+        <v>5.53786273921551</v>
       </c>
       <c r="F8" t="n">
-        <v>4.356635607937736</v>
+        <v>4.356635607937741</v>
       </c>
       <c r="G8" t="n">
-        <v>6.417189863249111</v>
+        <v>6.417189863249214</v>
       </c>
       <c r="H8" t="n">
-        <v>6.916562451230107</v>
+        <v>6.916562451230325</v>
       </c>
       <c r="I8" t="n">
-        <v>6.026717081684741</v>
+        <v>6.026717081684718</v>
       </c>
       <c r="J8" t="n">
-        <v>6.026672913663497</v>
+        <v>6.026672913663522</v>
       </c>
       <c r="K8" t="n">
-        <v>4.195856019638317</v>
+        <v>4.195856019638637</v>
       </c>
       <c r="L8" t="n">
-        <v>8.571110267722009</v>
+        <v>8.571110267721862</v>
       </c>
     </row>
     <row r="9">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.09007222973605</v>
+        <v>86.09007222973629</v>
       </c>
       <c r="C9" t="n">
         <v>109.7940385802185</v>
@@ -5160,13 +5160,13 @@
         <v>110.6780473318267</v>
       </c>
       <c r="E9" t="n">
-        <v>136.8356021355273</v>
+        <v>136.8356021355275</v>
       </c>
       <c r="F9" t="n">
-        <v>109.7940461113436</v>
+        <v>109.7940461113435</v>
       </c>
       <c r="G9" t="n">
-        <v>110.184363434681</v>
+        <v>110.1843634346812</v>
       </c>
       <c r="H9" t="n">
         <v>110.6837360226735</v>
@@ -5178,10 +5178,10 @@
         <v>109.7935105907717</v>
       </c>
       <c r="K9" t="n">
-        <v>96.1265685897164</v>
+        <v>96.1265685897166</v>
       </c>
       <c r="L9" t="n">
-        <v>110.5529350987397</v>
+        <v>110.5529350987395</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.548366858058734</v>
+        <v>2.48137007097328</v>
       </c>
       <c r="C2" t="n">
-        <v>2.87576422950749</v>
+        <v>2.511389919554013</v>
       </c>
       <c r="D2" t="n">
-        <v>4.406438670816185</v>
+        <v>2.57915670005084</v>
       </c>
       <c r="E2" t="n">
-        <v>3.138402353223958</v>
+        <v>2.731784777107086</v>
       </c>
       <c r="F2" t="n">
-        <v>2.424679713448689</v>
+        <v>2.137746239496603</v>
       </c>
       <c r="G2" t="n">
-        <v>3.699022582425937</v>
+        <v>2.541926796360383</v>
       </c>
       <c r="H2" t="n">
-        <v>4.253591383298563</v>
+        <v>2.570097814073917</v>
       </c>
       <c r="I2" t="n">
-        <v>2.857090058197969</v>
+        <v>2.49761859178715</v>
       </c>
       <c r="J2" t="n">
-        <v>3.936252174296586</v>
+        <v>3.377570442099203</v>
       </c>
       <c r="K2" t="n">
-        <v>3.186858219720298</v>
+        <v>2.628863880071552</v>
       </c>
       <c r="L2" t="n">
-        <v>4.017392002445206</v>
+        <v>2.558159889118463</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.922498975976317</v>
+        <v>2.580818684540833</v>
       </c>
       <c r="C3" t="n">
-        <v>3.295053952624515</v>
+        <v>2.720543947508868</v>
       </c>
       <c r="D3" t="n">
-        <v>5.059666459063837</v>
+        <v>3.276029446226292</v>
       </c>
       <c r="E3" t="n">
-        <v>3.558909848339809</v>
+        <v>3.082263187950501</v>
       </c>
       <c r="F3" t="n">
-        <v>2.845187208564558</v>
+        <v>2.101666242437226</v>
       </c>
       <c r="G3" t="n">
-        <v>4.245991416613855</v>
+        <v>3.01222045137372</v>
       </c>
       <c r="H3" t="n">
-        <v>4.884593876107771</v>
+        <v>3.224141191460485</v>
       </c>
       <c r="I3" t="n">
-        <v>3.274496968483073</v>
+        <v>2.69574642978455</v>
       </c>
       <c r="J3" t="n">
-        <v>4.360283662911336</v>
+        <v>4.156890989262109</v>
       </c>
       <c r="K3" t="n">
-        <v>3.63495661733115</v>
+        <v>2.96495890472744</v>
       </c>
       <c r="L3" t="n">
-        <v>4.612015557456096</v>
+        <v>3.137489176817766</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.001919714091984</v>
+        <v>2.001919714092069</v>
       </c>
       <c r="C4" t="n">
-        <v>1.995898484991</v>
+        <v>1.995898484991012</v>
       </c>
       <c r="D4" t="n">
-        <v>3.106464673594894</v>
+        <v>3.106464673595036</v>
       </c>
       <c r="E4" t="n">
-        <v>2.053141347056838</v>
+        <v>2.053141347056841</v>
       </c>
       <c r="F4" t="n">
-        <v>2.053141347056837</v>
+        <v>2.053141347056839</v>
       </c>
       <c r="G4" t="n">
-        <v>2.684901949411684</v>
+        <v>2.68490194941189</v>
       </c>
       <c r="H4" t="n">
-        <v>3.015573768511611</v>
+        <v>3.015573768511747</v>
       </c>
       <c r="I4" t="n">
-        <v>2.179103209715973</v>
+        <v>2.179103209715992</v>
       </c>
       <c r="J4" t="n">
-        <v>2.19940073671319</v>
+        <v>2.199400736713259</v>
       </c>
       <c r="K4" t="n">
-        <v>2.294647585190004</v>
+        <v>2.294647585190067</v>
       </c>
       <c r="L4" t="n">
-        <v>2.875313978316806</v>
+        <v>2.875313978316906</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.686651273392489</v>
+        <v>7.686651273392665</v>
       </c>
       <c r="C5" t="n">
-        <v>10.38828334114226</v>
+        <v>10.38828334114225</v>
       </c>
       <c r="D5" t="n">
-        <v>25.82455192924608</v>
+        <v>25.82455192924635</v>
       </c>
       <c r="E5" t="n">
-        <v>10.3882906162744</v>
+        <v>10.38829061627438</v>
       </c>
       <c r="F5" t="n">
-        <v>10.3882906162744</v>
+        <v>10.38829061627439</v>
       </c>
       <c r="G5" t="n">
-        <v>19.37178845183924</v>
+        <v>19.3717884518394</v>
       </c>
       <c r="H5" t="n">
-        <v>27.61317232958237</v>
+        <v>27.61317232958252</v>
       </c>
       <c r="I5" t="n">
-        <v>10.38810112225676</v>
+        <v>10.38810112225677</v>
       </c>
       <c r="J5" t="n">
-        <v>11.59927519793567</v>
+        <v>11.59927519793571</v>
       </c>
       <c r="K5" t="n">
-        <v>12.08283679093973</v>
+        <v>12.0828367909399</v>
       </c>
       <c r="L5" t="n">
-        <v>10.99280833281544</v>
+        <v>10.99280833281553</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.56777720104412</v>
+        <v>2.479038427848697</v>
       </c>
       <c r="C6" t="n">
-        <v>2.618837792078247</v>
+        <v>2.61883779207824</v>
       </c>
       <c r="D6" t="n">
-        <v>3.652013036944155</v>
+        <v>3.652013036944563</v>
       </c>
       <c r="E6" t="n">
-        <v>2.585257109066451</v>
+        <v>2.585257109066446</v>
       </c>
       <c r="F6" t="n">
-        <v>2.653916194685044</v>
+        <v>2.65391619468505</v>
       </c>
       <c r="G6" t="n">
-        <v>5.250759436363571</v>
+        <v>3.162020663168342</v>
       </c>
       <c r="H6" t="n">
-        <v>6.087308922982817</v>
+        <v>6.087308922983087</v>
       </c>
       <c r="I6" t="n">
-        <v>4.744960696667818</v>
+        <v>4.744960696667844</v>
       </c>
       <c r="J6" t="n">
-        <v>4.876338898386825</v>
+        <v>2.707895850914821</v>
       </c>
       <c r="K6" t="n">
-        <v>2.732865696049513</v>
+        <v>2.732865696049777</v>
       </c>
       <c r="L6" t="n">
-        <v>3.34685116562834</v>
+        <v>3.346851165628586</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.742213678947794</v>
+        <v>2.742213678947949</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9195793934573</v>
+        <v>2.919579393457308</v>
       </c>
       <c r="D7" t="n">
-        <v>3.846760148323769</v>
+        <v>3.846760148323903</v>
       </c>
       <c r="E7" t="n">
-        <v>2.902785722584098</v>
+        <v>2.902785722584101</v>
       </c>
       <c r="F7" t="n">
-        <v>2.902785722584098</v>
+        <v>2.902785722584101</v>
       </c>
       <c r="G7" t="n">
-        <v>3.425195914267529</v>
+        <v>3.425195914267634</v>
       </c>
       <c r="H7" t="n">
-        <v>3.755867733367391</v>
+        <v>3.755867733367681</v>
       </c>
       <c r="I7" t="n">
-        <v>2.919397174571812</v>
+        <v>2.919397174571821</v>
       </c>
       <c r="J7" t="n">
-        <v>2.939694701569016</v>
+        <v>2.939694701569085</v>
       </c>
       <c r="K7" t="n">
-        <v>3.034941550045775</v>
+        <v>3.034941550046011</v>
       </c>
       <c r="L7" t="n">
-        <v>3.615607943172613</v>
+        <v>3.615607943172785</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.507177274562207</v>
+        <v>4.507177274562327</v>
       </c>
       <c r="C8" t="n">
-        <v>6.491504729006374</v>
+        <v>6.491504729006409</v>
       </c>
       <c r="D8" t="n">
-        <v>7.812332804698528</v>
+        <v>7.812332804698715</v>
       </c>
       <c r="E8" t="n">
-        <v>5.994693584632813</v>
+        <v>5.994693584632819</v>
       </c>
       <c r="F8" t="n">
-        <v>4.732302560586265</v>
+        <v>4.732302560586297</v>
       </c>
       <c r="G8" t="n">
-        <v>7.012827913701098</v>
+        <v>7.012827913701139</v>
       </c>
       <c r="H8" t="n">
-        <v>7.343499732778276</v>
+        <v>7.343499732778538</v>
       </c>
       <c r="I8" t="n">
-        <v>6.507029174005372</v>
+        <v>6.507029174005425</v>
       </c>
       <c r="J8" t="n">
-        <v>6.527684902767511</v>
+        <v>6.527684902767516</v>
       </c>
       <c r="K8" t="n">
-        <v>4.766048144752945</v>
+        <v>4.766048144753142</v>
       </c>
       <c r="L8" t="n">
-        <v>9.107169494863749</v>
+        <v>9.107169494863928</v>
       </c>
     </row>
     <row r="9">
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.77530287858917</v>
+        <v>80.77530287858922</v>
       </c>
       <c r="C9" t="n">
         <v>102.8383281738168</v>
@@ -5556,28 +5556,28 @@
         <v>103.7655080718844</v>
       </c>
       <c r="E9" t="n">
-        <v>128.0939228763578</v>
+        <v>128.0939228763577</v>
       </c>
       <c r="F9" t="n">
-        <v>102.8383352344249</v>
+        <v>102.838335234425</v>
       </c>
       <c r="G9" t="n">
-        <v>103.3439446946271</v>
+        <v>103.343944694627</v>
       </c>
       <c r="H9" t="n">
         <v>103.6746165137269</v>
       </c>
       <c r="I9" t="n">
-        <v>102.8381459549313</v>
+        <v>102.8381459549314</v>
       </c>
       <c r="J9" t="n">
-        <v>102.8584434819285</v>
+        <v>102.8584434819284</v>
       </c>
       <c r="K9" t="n">
-        <v>75.39573817260155</v>
+        <v>90.27305349239795</v>
       </c>
       <c r="L9" t="n">
-        <v>103.5343567235323</v>
+        <v>103.5343567235322</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.726532635910172</v>
+        <v>2.66741859014407</v>
       </c>
       <c r="C2" t="n">
-        <v>3.293750317934995</v>
+        <v>2.820870460774244</v>
       </c>
       <c r="D2" t="n">
-        <v>4.404545689765389</v>
+        <v>2.755729084366104</v>
       </c>
       <c r="E2" t="n">
-        <v>3.608036838548421</v>
+        <v>3.084671145759667</v>
       </c>
       <c r="F2" t="n">
-        <v>2.746959968616046</v>
+        <v>2.367982382428724</v>
       </c>
       <c r="G2" t="n">
-        <v>4.029984701439165</v>
+        <v>2.736016683488532</v>
       </c>
       <c r="H2" t="n">
-        <v>4.190500513911953</v>
+        <v>2.743023548966368</v>
       </c>
       <c r="I2" t="n">
-        <v>3.132290491827769</v>
+        <v>2.688782830512921</v>
       </c>
       <c r="J2" t="n">
-        <v>4.491818794693807</v>
+        <v>3.864015363592732</v>
       </c>
       <c r="K2" t="n">
-        <v>3.588449565388131</v>
+        <v>2.991183108464239</v>
       </c>
       <c r="L2" t="n">
-        <v>4.109926631486879</v>
+        <v>2.739388032479699</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.143942159112727</v>
+        <v>2.746360715353101</v>
       </c>
       <c r="C3" t="n">
-        <v>3.771252603706711</v>
+        <v>3.117959548399251</v>
       </c>
       <c r="D3" t="n">
-        <v>5.074004770403122</v>
+        <v>3.37313060059005</v>
       </c>
       <c r="E3" t="n">
-        <v>4.086422663348127</v>
+        <v>3.551110109329896</v>
       </c>
       <c r="F3" t="n">
-        <v>3.225345793416171</v>
+        <v>2.368054601590151</v>
       </c>
       <c r="G3" t="n">
-        <v>4.643182043752857</v>
+        <v>3.23447884779328</v>
       </c>
       <c r="H3" t="n">
-        <v>4.828575453602471</v>
+        <v>3.297094257119677</v>
       </c>
       <c r="I3" t="n">
-        <v>3.61083748352783</v>
+        <v>2.897656441219409</v>
       </c>
       <c r="J3" t="n">
-        <v>4.96177462623081</v>
+        <v>4.823771121199623</v>
       </c>
       <c r="K3" t="n">
-        <v>4.081694316818649</v>
+        <v>3.424287836689051</v>
       </c>
       <c r="L3" t="n">
-        <v>4.73494092914456</v>
+        <v>3.270293346373867</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.280503959169976</v>
+        <v>2.280503959169972</v>
       </c>
       <c r="C4" t="n">
-        <v>2.405454653477866</v>
+        <v>2.405454653478035</v>
       </c>
       <c r="D4" t="n">
-        <v>3.278011616242218</v>
+        <v>3.278011616242277</v>
       </c>
       <c r="E4" t="n">
-        <v>2.463976767189338</v>
+        <v>2.463976767189663</v>
       </c>
       <c r="F4" t="n">
-        <v>2.463976767189255</v>
+        <v>2.463976767189661</v>
       </c>
       <c r="G4" t="n">
-        <v>3.054143761666763</v>
+        <v>3.054143761666807</v>
       </c>
       <c r="H4" t="n">
-        <v>3.150842965502166</v>
+        <v>3.150842965502212</v>
       </c>
       <c r="I4" t="n">
-        <v>2.514307081707301</v>
+        <v>2.514307081707243</v>
       </c>
       <c r="J4" t="n">
-        <v>2.488460463628317</v>
+        <v>2.48846046362836</v>
       </c>
       <c r="K4" t="n">
-        <v>2.580628353765015</v>
+        <v>2.580628353765112</v>
       </c>
       <c r="L4" t="n">
-        <v>3.103076133979265</v>
+        <v>3.103076133979323</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.348074541345049</v>
+        <v>8.34807454134514</v>
       </c>
       <c r="C5" t="n">
-        <v>11.99636957329997</v>
+        <v>11.99636957330163</v>
       </c>
       <c r="D5" t="n">
-        <v>24.17348113933734</v>
+        <v>24.17348113933751</v>
       </c>
       <c r="E5" t="n">
-        <v>11.99637460550763</v>
+        <v>11.99637460550879</v>
       </c>
       <c r="F5" t="n">
-        <v>11.99637460550763</v>
+        <v>11.99637460550879</v>
       </c>
       <c r="G5" t="n">
-        <v>21.28958765331583</v>
+        <v>21.28958765331613</v>
       </c>
       <c r="H5" t="n">
-        <v>24.91054735711116</v>
+        <v>24.91054735711251</v>
       </c>
       <c r="I5" t="n">
-        <v>11.99618060958147</v>
+        <v>11.99618060958345</v>
       </c>
       <c r="J5" t="n">
-        <v>12.64847295767621</v>
+        <v>12.6484729576762</v>
       </c>
       <c r="K5" t="n">
-        <v>12.47461039271252</v>
+        <v>12.47461039271266</v>
       </c>
       <c r="L5" t="n">
-        <v>25.51015085697779</v>
+        <v>9.993050151228156</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.832403660056981</v>
+        <v>2.832403660057061</v>
       </c>
       <c r="C6" t="n">
-        <v>3.040521079404229</v>
+        <v>3.040521079404148</v>
       </c>
       <c r="D6" t="n">
-        <v>6.17751029129214</v>
+        <v>3.890031515975434</v>
       </c>
       <c r="E6" t="n">
-        <v>2.992970484932151</v>
+        <v>2.99297048493203</v>
       </c>
       <c r="F6" t="n">
-        <v>3.069817072691693</v>
+        <v>3.069817072691805</v>
       </c>
       <c r="G6" t="n">
-        <v>3.606043462553821</v>
+        <v>5.826666520327691</v>
       </c>
       <c r="H6" t="n">
-        <v>6.418019055012717</v>
+        <v>6.418019055012863</v>
       </c>
       <c r="I6" t="n">
-        <v>5.286829840368269</v>
+        <v>3.066206782594345</v>
       </c>
       <c r="J6" t="n">
-        <v>3.077362065200118</v>
+        <v>5.363332913399389</v>
       </c>
       <c r="K6" t="n">
-        <v>3.092001948286862</v>
+        <v>3.092001948286935</v>
       </c>
       <c r="L6" t="n">
-        <v>3.646380391178594</v>
+        <v>3.646380391178618</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.089297085161377</v>
+        <v>3.089297085161383</v>
       </c>
       <c r="C7" t="n">
-        <v>3.323289171416855</v>
+        <v>3.323289171416827</v>
       </c>
       <c r="D7" t="n">
-        <v>4.086790376647562</v>
+        <v>4.086790376647595</v>
       </c>
       <c r="E7" t="n">
-        <v>3.328879754482994</v>
+        <v>3.328879754483184</v>
       </c>
       <c r="F7" t="n">
-        <v>3.328879754482994</v>
+        <v>3.328879754483184</v>
       </c>
       <c r="G7" t="n">
-        <v>3.862936887658157</v>
+        <v>3.862936887658206</v>
       </c>
       <c r="H7" t="n">
-        <v>3.959636091493383</v>
+        <v>3.959636091493626</v>
       </c>
       <c r="I7" t="n">
-        <v>3.323100207698602</v>
+        <v>3.323100207698665</v>
       </c>
       <c r="J7" t="n">
-        <v>3.29725358961973</v>
+        <v>3.297253589619772</v>
       </c>
       <c r="K7" t="n">
-        <v>3.389421479756415</v>
+        <v>3.389421479756523</v>
       </c>
       <c r="L7" t="n">
-        <v>3.911869259970575</v>
+        <v>3.911869259970734</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.928655885086398</v>
+        <v>4.928655885086526</v>
       </c>
       <c r="C8" t="n">
-        <v>7.140927941838822</v>
+        <v>7.140927941839175</v>
       </c>
       <c r="D8" t="n">
-        <v>8.307707626658704</v>
+        <v>8.307707626658972</v>
       </c>
       <c r="E8" t="n">
-        <v>6.600845757043316</v>
+        <v>6.600845757043336</v>
       </c>
       <c r="F8" t="n">
-        <v>5.228519709389178</v>
+        <v>5.228519709389264</v>
       </c>
       <c r="G8" t="n">
-        <v>7.674823318420186</v>
+        <v>7.674823318420337</v>
       </c>
       <c r="H8" t="n">
-        <v>7.771522522231852</v>
+        <v>7.771522522231915</v>
       </c>
       <c r="I8" t="n">
-        <v>7.134986638460945</v>
+        <v>7.134986638460771</v>
       </c>
       <c r="J8" t="n">
-        <v>7.109527672331307</v>
+        <v>7.109527672331359</v>
       </c>
       <c r="K8" t="n">
-        <v>5.192139566842187</v>
+        <v>5.192139566842291</v>
       </c>
       <c r="L8" t="n">
-        <v>9.784225735239113</v>
+        <v>9.784225735239302</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.05912021638352</v>
+        <v>81.05912021638358</v>
       </c>
       <c r="C9" t="n">
-        <v>103.2059276128071</v>
+        <v>103.2059276128074</v>
       </c>
       <c r="D9" t="n">
-        <v>103.9694439449002</v>
+        <v>103.9694439449003</v>
       </c>
       <c r="E9" t="n">
-        <v>128.4928573076276</v>
+        <v>128.4928573076275</v>
       </c>
       <c r="F9" t="n">
-        <v>103.2059324316112</v>
+        <v>103.2059324316113</v>
       </c>
       <c r="G9" t="n">
         <v>103.7455753290489</v>
       </c>
       <c r="H9" t="n">
-        <v>103.8422745328841</v>
+        <v>103.8422745328843</v>
       </c>
       <c r="I9" t="n">
         <v>103.2057386490893</v>
       </c>
       <c r="J9" t="n">
-        <v>103.1798920310101</v>
+        <v>103.1798920310103</v>
       </c>
       <c r="K9" t="n">
-        <v>90.57568899235643</v>
+        <v>90.57568899235653</v>
       </c>
       <c r="L9" t="n">
-        <v>103.7945077013611</v>
+        <v>103.7945077013613</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.753135266312112</v>
+        <v>2.575539149645702</v>
       </c>
       <c r="C2" t="n">
-        <v>2.851378727542481</v>
+        <v>2.594641470816309</v>
       </c>
       <c r="D2" t="n">
-        <v>3.150082042723487</v>
+        <v>2.596429670088433</v>
       </c>
       <c r="E2" t="n">
-        <v>3.119094101456278</v>
+        <v>2.81978275187267</v>
       </c>
       <c r="F2" t="n">
-        <v>2.393199491483586</v>
+        <v>2.215611782808611</v>
       </c>
       <c r="G2" t="n">
-        <v>4.604507579115404</v>
+        <v>2.67297319734695</v>
       </c>
       <c r="H2" t="n">
-        <v>3.301158321392576</v>
+        <v>2.602088365237283</v>
       </c>
       <c r="I2" t="n">
-        <v>2.830745686487175</v>
+        <v>2.579617180714953</v>
       </c>
       <c r="J2" t="n">
-        <v>4.047345164784445</v>
+        <v>3.495278964831739</v>
       </c>
       <c r="K2" t="n">
-        <v>3.20269043536115</v>
+        <v>2.731861591005939</v>
       </c>
       <c r="L2" t="n">
-        <v>2.797524801416953</v>
+        <v>2.575633389051221</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.166408464994273</v>
+        <v>2.699182962392957</v>
       </c>
       <c r="C3" t="n">
-        <v>3.275323524739528</v>
+        <v>2.755474067125283</v>
       </c>
       <c r="D3" t="n">
-        <v>3.622979485144372</v>
+        <v>2.846710488814306</v>
       </c>
       <c r="E3" t="n">
-        <v>3.544006527562847</v>
+        <v>3.124449606801837</v>
       </c>
       <c r="F3" t="n">
-        <v>2.818111917590151</v>
+        <v>2.127127784593178</v>
       </c>
       <c r="G3" t="n">
-        <v>5.295870135337281</v>
+        <v>3.391290241053145</v>
       </c>
       <c r="H3" t="n">
-        <v>3.797476420770371</v>
+        <v>2.903710596737839</v>
       </c>
       <c r="I3" t="n">
-        <v>3.253813841439525</v>
+        <v>2.728045627665201</v>
       </c>
       <c r="J3" t="n">
-        <v>4.490962754368968</v>
+        <v>4.276971323894783</v>
       </c>
       <c r="K3" t="n">
-        <v>3.657934168807959</v>
+        <v>3.037006080456594</v>
       </c>
       <c r="L3" t="n">
-        <v>3.217362905995955</v>
+        <v>2.716368994467784</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.226448187841663</v>
+        <v>2.226448187841719</v>
       </c>
       <c r="C4" t="n">
-        <v>2.111448645278816</v>
+        <v>2.111448645278813</v>
       </c>
       <c r="D4" t="n">
-        <v>2.462416226356587</v>
+        <v>2.462416226356556</v>
       </c>
       <c r="E4" t="n">
-        <v>2.170580915708846</v>
+        <v>2.170580915708837</v>
       </c>
       <c r="F4" t="n">
-        <v>2.170580915708845</v>
+        <v>2.170580915708837</v>
       </c>
       <c r="G4" t="n">
-        <v>3.325606166714123</v>
+        <v>3.325606166714297</v>
       </c>
       <c r="H4" t="n">
-        <v>2.552624609940323</v>
+        <v>2.552624609940636</v>
       </c>
       <c r="I4" t="n">
-        <v>2.263673653496914</v>
+        <v>2.263673653496913</v>
       </c>
       <c r="J4" t="n">
-        <v>2.34653870727083</v>
+        <v>2.34653870727097</v>
       </c>
       <c r="K4" t="n">
-        <v>2.392550164870049</v>
+        <v>2.392550164870248</v>
       </c>
       <c r="L4" t="n">
-        <v>2.253489680838532</v>
+        <v>2.25348968083884</v>
       </c>
     </row>
     <row r="5">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.651762061741811</v>
+        <v>9.651762061742106</v>
       </c>
       <c r="C5" t="n">
-        <v>10.37934450010716</v>
+        <v>10.37934450010717</v>
       </c>
       <c r="D5" t="n">
-        <v>13.24073166037032</v>
+        <v>13.2407316603707</v>
       </c>
       <c r="E5" t="n">
         <v>10.37935042846475</v>
@@ -6194,22 +6194,22 @@
         <v>10.37935042846475</v>
       </c>
       <c r="G5" t="n">
-        <v>28.63307253781967</v>
+        <v>28.63307253781983</v>
       </c>
       <c r="H5" t="n">
-        <v>16.24187849739321</v>
+        <v>16.24187849739309</v>
       </c>
       <c r="I5" t="n">
-        <v>10.37904683557467</v>
+        <v>10.37904683557468</v>
       </c>
       <c r="J5" t="n">
-        <v>12.62302588992275</v>
+        <v>12.62302588992284</v>
       </c>
       <c r="K5" t="n">
-        <v>12.29531371316684</v>
+        <v>12.29531371316724</v>
       </c>
       <c r="L5" t="n">
-        <v>11.49760712547448</v>
+        <v>11.49760712547457</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.793394278766665</v>
+        <v>5.168586725681795</v>
       </c>
       <c r="C6" t="n">
-        <v>2.769575898157147</v>
+        <v>2.769575898157138</v>
       </c>
       <c r="D6" t="n">
-        <v>5.499809784182816</v>
+        <v>5.499809784182991</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7313287594677</v>
+        <v>2.73132875946769</v>
       </c>
       <c r="F6" t="n">
-        <v>2.818959288809633</v>
+        <v>2.81895928880963</v>
       </c>
       <c r="G6" t="n">
-        <v>3.89255225763926</v>
+        <v>6.267744704554372</v>
       </c>
       <c r="H6" t="n">
-        <v>6.022869793244339</v>
+        <v>3.109409762223642</v>
       </c>
       <c r="I6" t="n">
-        <v>2.830619744421912</v>
+        <v>5.205812191336979</v>
       </c>
       <c r="J6" t="n">
-        <v>5.358398784955909</v>
+        <v>5.358398784956208</v>
       </c>
       <c r="K6" t="n">
-        <v>2.912955287354263</v>
+        <v>2.912955287354285</v>
       </c>
       <c r="L6" t="n">
-        <v>2.800332463936408</v>
+        <v>2.800332463936307</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.100975396758102</v>
+        <v>3.100975396758398</v>
       </c>
       <c r="C7" t="n">
-        <v>3.138498526946086</v>
+        <v>3.138498526946075</v>
       </c>
       <c r="D7" t="n">
-        <v>3.33693237378424</v>
+        <v>3.336932373784399</v>
       </c>
       <c r="E7" t="n">
-        <v>3.13515750612491</v>
+        <v>3.135157506124906</v>
       </c>
       <c r="F7" t="n">
-        <v>3.13515750612491</v>
+        <v>3.135157506124909</v>
       </c>
       <c r="G7" t="n">
-        <v>4.200133375630882</v>
+        <v>4.200133375630977</v>
       </c>
       <c r="H7" t="n">
-        <v>3.427151818857364</v>
+        <v>3.427151818857315</v>
       </c>
       <c r="I7" t="n">
-        <v>3.138200862413612</v>
+        <v>3.138200862413588</v>
       </c>
       <c r="J7" t="n">
-        <v>3.221065916187596</v>
+        <v>3.221065916187647</v>
       </c>
       <c r="K7" t="n">
-        <v>3.267077373786646</v>
+        <v>3.267077373786926</v>
       </c>
       <c r="L7" t="n">
-        <v>3.128016889755494</v>
+        <v>3.128016889755515</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.085196102485556</v>
+        <v>5.085196102485798</v>
       </c>
       <c r="C8" t="n">
-        <v>7.191253112582443</v>
+        <v>7.191253112582442</v>
       </c>
       <c r="D8" t="n">
-        <v>7.821969118494154</v>
+        <v>7.821969118494453</v>
       </c>
       <c r="E8" t="n">
-        <v>6.625060674272797</v>
+        <v>6.625060674272796</v>
       </c>
       <c r="F8" t="n">
-        <v>5.186392351725761</v>
+        <v>5.186392351725754</v>
       </c>
       <c r="G8" t="n">
-        <v>8.255660234877629</v>
+        <v>8.255660234877626</v>
       </c>
       <c r="H8" t="n">
-        <v>7.482678678087634</v>
+        <v>7.482678678087723</v>
       </c>
       <c r="I8" t="n">
-        <v>7.193727721660223</v>
+        <v>7.193727721660218</v>
       </c>
       <c r="J8" t="n">
-        <v>7.276999841649948</v>
+        <v>7.276999841649992</v>
       </c>
       <c r="K8" t="n">
-        <v>5.212822504766125</v>
+        <v>5.212822504766479</v>
       </c>
       <c r="L8" t="n">
-        <v>9.347196221573006</v>
+        <v>9.347196221573173</v>
       </c>
     </row>
     <row r="9">
@@ -6339,34 +6339,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87.16221564071027</v>
+        <v>87.16221564071043</v>
       </c>
       <c r="C9" t="n">
-        <v>110.8000974239282</v>
+        <v>110.8000974239281</v>
       </c>
       <c r="D9" t="n">
-        <v>110.9985434856812</v>
+        <v>110.9985434856814</v>
       </c>
       <c r="E9" t="n">
         <v>138.0344177773745</v>
       </c>
       <c r="F9" t="n">
-        <v>110.8001032764968</v>
+        <v>110.8001032764967</v>
       </c>
       <c r="G9" t="n">
         <v>111.8617322726128</v>
       </c>
       <c r="H9" t="n">
-        <v>111.0887507158394</v>
+        <v>111.0887507158393</v>
       </c>
       <c r="I9" t="n">
-        <v>110.7997997593956</v>
+        <v>110.7997997593955</v>
       </c>
       <c r="J9" t="n">
-        <v>110.882664813169</v>
+        <v>110.8826648131695</v>
       </c>
       <c r="K9" t="n">
-        <v>97.25453626656706</v>
+        <v>97.25453626656703</v>
       </c>
       <c r="L9" t="n">
         <v>110.7896157867372</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.663688246752091</v>
+        <v>3.243627526575014</v>
       </c>
       <c r="C2" t="n">
-        <v>4.183008194757093</v>
+        <v>3.281041143868645</v>
       </c>
       <c r="D2" t="n">
-        <v>3.326477260265686</v>
+        <v>3.067996740591123</v>
       </c>
       <c r="E2" t="n">
-        <v>4.536706013602569</v>
+        <v>3.579450248218374</v>
       </c>
       <c r="F2" t="n">
-        <v>3.555807620361378</v>
+        <v>2.763031492617896</v>
       </c>
       <c r="G2" t="n">
-        <v>7.183710931247481</v>
+        <v>3.270995287611761</v>
       </c>
       <c r="H2" t="n">
-        <v>3.245009266494278</v>
+        <v>3.059024692965955</v>
       </c>
       <c r="I2" t="n">
-        <v>3.962655712289141</v>
+        <v>3.101470424796838</v>
       </c>
       <c r="J2" t="n">
-        <v>6.059058002239946</v>
+        <v>4.491902618235989</v>
       </c>
       <c r="K2" t="n">
-        <v>5.869461799387647</v>
+        <v>3.542545209151462</v>
       </c>
       <c r="L2" t="n">
-        <v>3.253574893815277</v>
+        <v>3.059709468406917</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.724349232667835</v>
+        <v>4.43710233700309</v>
       </c>
       <c r="C3" t="n">
-        <v>4.836324364838429</v>
+        <v>3.72599260691097</v>
       </c>
       <c r="D3" t="n">
-        <v>3.885865297035217</v>
+        <v>3.187605028305518</v>
       </c>
       <c r="E3" t="n">
-        <v>5.191632268837622</v>
+        <v>4.214274831428244</v>
       </c>
       <c r="F3" t="n">
-        <v>4.210733875596418</v>
+        <v>2.866592949124765</v>
       </c>
       <c r="G3" t="n">
-        <v>8.322483042212102</v>
+        <v>4.627841264828061</v>
       </c>
       <c r="H3" t="n">
-        <v>3.793354844476818</v>
+        <v>3.154695448185691</v>
       </c>
       <c r="I3" t="n">
-        <v>4.612863854785344</v>
+        <v>3.425311040280732</v>
       </c>
       <c r="J3" t="n">
-        <v>6.782305275934867</v>
+        <v>5.853525596275559</v>
       </c>
       <c r="K3" t="n">
-        <v>6.745189698674543</v>
+        <v>4.573996153646988</v>
       </c>
       <c r="L3" t="n">
-        <v>3.802018538181511</v>
+        <v>3.159731511361637</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.748579597815321</v>
+        <v>4.748579597815481</v>
       </c>
       <c r="C4" t="n">
-        <v>2.897215249642537</v>
+        <v>2.897215249642527</v>
       </c>
       <c r="D4" t="n">
-        <v>2.764749075974171</v>
+        <v>2.764749075974222</v>
       </c>
       <c r="E4" t="n">
-        <v>2.974554740740924</v>
+        <v>2.974554740740912</v>
       </c>
       <c r="F4" t="n">
-        <v>2.974554740740924</v>
+        <v>2.974554740740929</v>
       </c>
       <c r="G4" t="n">
-        <v>5.055672996326682</v>
+        <v>5.055672996326772</v>
       </c>
       <c r="H4" t="n">
-        <v>2.717343238703226</v>
+        <v>2.717343238703238</v>
       </c>
       <c r="I4" t="n">
-        <v>3.129927623830127</v>
+        <v>3.129927623830139</v>
       </c>
       <c r="J4" t="n">
-        <v>3.413236005204811</v>
+        <v>3.413236005204879</v>
       </c>
       <c r="K4" t="n">
-        <v>4.016691107966762</v>
+        <v>4.016691107966739</v>
       </c>
       <c r="L4" t="n">
-        <v>2.722687955192268</v>
+        <v>2.722687955192409</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.34560704856752</v>
+        <v>44.34560704856756</v>
       </c>
       <c r="C5" t="n">
-        <v>17.3795729737243</v>
+        <v>17.37957297372431</v>
       </c>
       <c r="D5" t="n">
-        <v>11.32516058739982</v>
+        <v>11.32516058740015</v>
       </c>
       <c r="E5" t="n">
-        <v>17.37958133245414</v>
+        <v>17.37958133245415</v>
       </c>
       <c r="F5" t="n">
-        <v>17.37958133245414</v>
+        <v>17.37958133245415</v>
       </c>
       <c r="G5" t="n">
-        <v>47.43441424144585</v>
+        <v>47.43441424144682</v>
       </c>
       <c r="H5" t="n">
-        <v>11.42936556649442</v>
+        <v>11.42936556649446</v>
       </c>
       <c r="I5" t="n">
         <v>17.37908099850204</v>
       </c>
       <c r="J5" t="n">
-        <v>23.06619348474322</v>
+        <v>23.06619348474317</v>
       </c>
       <c r="K5" t="n">
         <v>30.86416660095262</v>
       </c>
       <c r="L5" t="n">
-        <v>6.978037266621131</v>
+        <v>6.978037266621136</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.036078820485615</v>
+        <v>8.036078820485491</v>
       </c>
       <c r="C6" t="n">
-        <v>3.834738106640016</v>
+        <v>3.834738106640029</v>
       </c>
       <c r="D6" t="n">
-        <v>3.535628984063945</v>
+        <v>3.535634756353013</v>
       </c>
       <c r="E6" t="n">
-        <v>3.76714868117855</v>
+        <v>3.767148681178561</v>
       </c>
       <c r="F6" t="n">
-        <v>3.910451174397514</v>
+        <v>3.910451174397523</v>
       </c>
       <c r="G6" t="n">
-        <v>5.865062342460784</v>
+        <v>8.343172218996546</v>
       </c>
       <c r="H6" t="n">
-        <v>3.505474400862159</v>
+        <v>6.625640562077613</v>
       </c>
       <c r="I6" t="n">
-        <v>3.939316969964306</v>
+        <v>6.417426846500178</v>
       </c>
       <c r="J6" t="n">
-        <v>6.815770589723337</v>
+        <v>4.252484917480051</v>
       </c>
       <c r="K6" t="n">
-        <v>4.80547743492824</v>
+        <v>4.805477434928227</v>
       </c>
       <c r="L6" t="n">
-        <v>3.491524467094274</v>
+        <v>3.491524467094428</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.683933006928251</v>
+        <v>5.683933006928272</v>
       </c>
       <c r="C7" t="n">
-        <v>4.065773008165112</v>
+        <v>4.065773008165104</v>
       </c>
       <c r="D7" t="n">
-        <v>3.700106422375794</v>
+        <v>3.700106422375859</v>
       </c>
       <c r="E7" t="n">
-        <v>4.045505132741597</v>
+        <v>4.045505132741617</v>
       </c>
       <c r="F7" t="n">
-        <v>4.045505132741597</v>
+        <v>4.045505132741622</v>
       </c>
       <c r="G7" t="n">
-        <v>5.991026405439387</v>
+        <v>5.991026405439507</v>
       </c>
       <c r="H7" t="n">
-        <v>3.652696647815913</v>
+        <v>3.652696647816013</v>
       </c>
       <c r="I7" t="n">
         <v>4.065281032942832</v>
       </c>
       <c r="J7" t="n">
-        <v>4.348589414317464</v>
+        <v>4.348589414317668</v>
       </c>
       <c r="K7" t="n">
-        <v>4.952044517079479</v>
+        <v>4.952044517079505</v>
       </c>
       <c r="L7" t="n">
-        <v>3.658041364305014</v>
+        <v>3.658041364305022</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.730551268626279</v>
+        <v>7.730551268626462</v>
       </c>
       <c r="C8" t="n">
-        <v>8.355534604593107</v>
+        <v>8.355534604593087</v>
       </c>
       <c r="D8" t="n">
-        <v>8.477866584956637</v>
+        <v>8.477866584956805</v>
       </c>
       <c r="E8" t="n">
-        <v>7.738889368997543</v>
+        <v>7.738889368997549</v>
       </c>
       <c r="F8" t="n">
-        <v>6.172006201010734</v>
+        <v>6.172006201010722</v>
       </c>
       <c r="G8" t="n">
-        <v>10.29973196788429</v>
+        <v>10.29973196788434</v>
       </c>
       <c r="H8" t="n">
-        <v>7.961402210261855</v>
+        <v>7.961402210261873</v>
       </c>
       <c r="I8" t="n">
-        <v>8.373986595387786</v>
+        <v>8.373986595387759</v>
       </c>
       <c r="J8" t="n">
-        <v>8.657739534174059</v>
+        <v>8.657739534173913</v>
       </c>
       <c r="K8" t="n">
-        <v>6.956643346538068</v>
+        <v>6.956643346538065</v>
       </c>
       <c r="L8" t="n">
-        <v>10.32968625782426</v>
+        <v>10.32968625782417</v>
       </c>
     </row>
     <row r="9">
@@ -6735,7 +6735,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.28146080107307</v>
+        <v>84.28146080107308</v>
       </c>
       <c r="C9" t="n">
         <v>104.818423067763</v>
@@ -6747,10 +6747,10 @@
         <v>130.3849745663387</v>
       </c>
       <c r="F9" t="n">
-        <v>104.8184314736134</v>
+        <v>104.8184314736133</v>
       </c>
       <c r="G9" t="n">
-        <v>106.7436764650376</v>
+        <v>106.7436764650375</v>
       </c>
       <c r="H9" t="n">
         <v>104.4053467074141</v>
@@ -6762,10 +6762,10 @@
         <v>105.1012394739157</v>
       </c>
       <c r="K9" t="n">
-        <v>92.34712673014704</v>
+        <v>92.8679305409278</v>
       </c>
       <c r="L9" t="n">
-        <v>104.4106914239027</v>
+        <v>104.4106914239029</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.164103649758953</v>
+        <v>3.502524713190255</v>
       </c>
       <c r="C2" t="n">
-        <v>4.655598054898284</v>
+        <v>3.512691648452546</v>
       </c>
       <c r="D2" t="n">
-        <v>3.704576288219678</v>
+        <v>3.215200631647173</v>
       </c>
       <c r="E2" t="n">
-        <v>5.046991607285172</v>
+        <v>3.842666548900696</v>
       </c>
       <c r="F2" t="n">
-        <v>3.954435572511774</v>
+        <v>2.933311323701778</v>
       </c>
       <c r="G2" t="n">
-        <v>7.306999063580057</v>
+        <v>3.404788987326452</v>
       </c>
       <c r="H2" t="n">
-        <v>3.123529969447767</v>
+        <v>3.179707132314693</v>
       </c>
       <c r="I2" t="n">
-        <v>4.332930930510673</v>
+        <v>3.248270199275821</v>
       </c>
       <c r="J2" t="n">
-        <v>6.811529182161212</v>
+        <v>4.859535671432601</v>
       </c>
       <c r="K2" t="n">
-        <v>5.927920076794812</v>
+        <v>3.744006339698271</v>
       </c>
       <c r="L2" t="n">
-        <v>3.712676468503033</v>
+        <v>3.211331184641697</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.66182463239614</v>
+        <v>5.45031030193956</v>
       </c>
       <c r="C3" t="n">
-        <v>5.425724705675036</v>
+        <v>4.08427373810933</v>
       </c>
       <c r="D3" t="n">
-        <v>4.382237228940109</v>
+        <v>3.408457612007028</v>
       </c>
       <c r="E3" t="n">
-        <v>5.819037365561019</v>
+        <v>4.624555508879479</v>
       </c>
       <c r="F3" t="n">
-        <v>4.726481330787621</v>
+        <v>3.123462404271839</v>
       </c>
       <c r="G3" t="n">
-        <v>8.525769660234337</v>
+        <v>4.755676241933158</v>
       </c>
       <c r="H3" t="n">
-        <v>3.715226663718641</v>
+        <v>3.188984345496258</v>
       </c>
       <c r="I3" t="n">
-        <v>5.099358195607863</v>
+        <v>3.643422924474266</v>
       </c>
       <c r="J3" t="n">
-        <v>7.670615320164247</v>
+        <v>6.472508555605565</v>
       </c>
       <c r="K3" t="n">
-        <v>6.860216042893642</v>
+        <v>4.765212499541765</v>
       </c>
       <c r="L3" t="n">
-        <v>4.391530204445525</v>
+        <v>3.412374495577732</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.328824609833422</v>
+        <v>6.328824609832988</v>
       </c>
       <c r="C4" t="n">
-        <v>3.174738901144817</v>
+        <v>3.174738901144815</v>
       </c>
       <c r="D4" t="n">
-        <v>3.083366933196123</v>
+        <v>3.083366933196231</v>
       </c>
       <c r="E4" t="n">
-        <v>3.26111301244106</v>
+        <v>3.261113012441065</v>
       </c>
       <c r="F4" t="n">
-        <v>3.261113012441061</v>
+        <v>3.261113012441064</v>
       </c>
       <c r="G4" t="n">
-        <v>5.222890320741237</v>
+        <v>5.222890320741079</v>
       </c>
       <c r="H4" t="n">
-        <v>2.739035673250023</v>
+        <v>2.739035673250259</v>
       </c>
       <c r="I4" t="n">
-        <v>3.444542603606116</v>
+        <v>3.444542603606113</v>
       </c>
       <c r="J4" t="n">
-        <v>3.801372651265276</v>
+        <v>3.801372651265292</v>
       </c>
       <c r="K4" t="n">
-        <v>4.091106800539722</v>
+        <v>4.091106800539849</v>
       </c>
       <c r="L4" t="n">
-        <v>3.089393939951293</v>
+        <v>3.089393939951008</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.21161807079382</v>
+        <v>67.21161807079372</v>
       </c>
       <c r="C5" t="n">
-        <v>20.41597283961308</v>
+        <v>20.41597283961327</v>
       </c>
       <c r="D5" t="n">
-        <v>14.367406079732</v>
+        <v>14.36740607973177</v>
       </c>
       <c r="E5" t="n">
-        <v>20.41598234588804</v>
+        <v>20.41598234588812</v>
       </c>
       <c r="F5" t="n">
-        <v>20.41598234588804</v>
+        <v>20.41598234588812</v>
       </c>
       <c r="G5" t="n">
-        <v>49.19251314721851</v>
+        <v>49.19251314721822</v>
       </c>
       <c r="H5" t="n">
-        <v>9.885032428889934</v>
+        <v>9.885032428889767</v>
       </c>
       <c r="I5" t="n">
-        <v>20.41551993015914</v>
+        <v>20.41551993015908</v>
       </c>
       <c r="J5" t="n">
-        <v>27.59991339565517</v>
+        <v>27.59991339565536</v>
       </c>
       <c r="K5" t="n">
-        <v>29.28400078164244</v>
+        <v>29.28400078164231</v>
       </c>
       <c r="L5" t="n">
-        <v>16.81209708942294</v>
+        <v>27.02850559317512</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.204612898139748</v>
+        <v>7.204612898139715</v>
       </c>
       <c r="C6" t="n">
-        <v>4.214586725513128</v>
+        <v>4.21458672551312</v>
       </c>
       <c r="D6" t="n">
-        <v>3.917261072258421</v>
+        <v>3.917261072258426</v>
       </c>
       <c r="E6" t="n">
         <v>4.136487868064568</v>
       </c>
       <c r="F6" t="n">
-        <v>4.292073508214623</v>
+        <v>4.292073508214626</v>
       </c>
       <c r="G6" t="n">
-        <v>8.65346826581653</v>
+        <v>6.09867860904781</v>
       </c>
       <c r="H6" t="n">
-        <v>6.856448914586593</v>
+        <v>6.856448914586919</v>
       </c>
       <c r="I6" t="n">
-        <v>4.320330891912791</v>
+        <v>4.320330891912789</v>
       </c>
       <c r="J6" t="n">
-        <v>7.364038323673608</v>
+        <v>4.714174860130197</v>
       </c>
       <c r="K6" t="n">
-        <v>4.942886377026865</v>
+        <v>4.942886377027049</v>
       </c>
       <c r="L6" t="n">
-        <v>3.925138607534205</v>
+        <v>3.925138607534376</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.293951797977191</v>
+        <v>7.293951797977127</v>
       </c>
       <c r="C7" t="n">
-        <v>4.410122701204344</v>
+        <v>4.41012270120433</v>
       </c>
       <c r="D7" t="n">
-        <v>4.048503041220264</v>
+        <v>4.048503041220347</v>
       </c>
       <c r="E7" t="n">
-        <v>4.381320446893896</v>
+        <v>4.381320446893894</v>
       </c>
       <c r="F7" t="n">
-        <v>4.381320446893896</v>
+        <v>4.381320446893894</v>
       </c>
       <c r="G7" t="n">
-        <v>6.18801750888534</v>
+        <v>6.188017508885211</v>
       </c>
       <c r="H7" t="n">
-        <v>3.704162861394565</v>
+        <v>3.704162861394409</v>
       </c>
       <c r="I7" t="n">
-        <v>4.409669791750148</v>
+        <v>4.409669791750146</v>
       </c>
       <c r="J7" t="n">
-        <v>4.766499839409336</v>
+        <v>4.766499839409407</v>
       </c>
       <c r="K7" t="n">
-        <v>5.056233988683936</v>
+        <v>5.056233988683783</v>
       </c>
       <c r="L7" t="n">
-        <v>4.054521128094971</v>
+        <v>4.054521128095149</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.398165572841434</v>
+        <v>9.398165572841288</v>
       </c>
       <c r="C8" t="n">
-        <v>8.85826524382369</v>
+        <v>8.858265243823675</v>
       </c>
       <c r="D8" t="n">
-        <v>9.015375201894889</v>
+        <v>9.015375201894715</v>
       </c>
       <c r="E8" t="n">
-        <v>8.212695776041222</v>
+        <v>8.212695776041228</v>
       </c>
       <c r="F8" t="n">
-        <v>6.572310748469478</v>
+        <v>6.572310748469461</v>
       </c>
       <c r="G8" t="n">
-        <v>10.663251999001</v>
+        <v>10.66325199900083</v>
       </c>
       <c r="H8" t="n">
-        <v>8.179397351522155</v>
+        <v>8.179397351521841</v>
       </c>
       <c r="I8" t="n">
-        <v>8.884904281865918</v>
+        <v>8.884904281865909</v>
       </c>
       <c r="J8" t="n">
-        <v>9.242200294055225</v>
+        <v>9.242200294055079</v>
       </c>
       <c r="K8" t="n">
-        <v>7.116404837342311</v>
+        <v>7.116404837342204</v>
       </c>
       <c r="L8" t="n">
-        <v>11.00648500824848</v>
+        <v>11.00648500824811</v>
       </c>
     </row>
     <row r="9">
@@ -7131,7 +7131,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.72945398491785</v>
+        <v>85.72945398491764</v>
       </c>
       <c r="C9" t="n">
         <v>104.9874233932719</v>
@@ -7146,22 +7146,22 @@
         <v>104.9874329905302</v>
       </c>
       <c r="G9" t="n">
-        <v>106.7653182009529</v>
+        <v>106.7653182009528</v>
       </c>
       <c r="H9" t="n">
-        <v>104.2814635534617</v>
+        <v>104.2814635534618</v>
       </c>
       <c r="I9" t="n">
         <v>104.9869704838178</v>
       </c>
       <c r="J9" t="n">
-        <v>105.3438005314772</v>
+        <v>105.3438005314769</v>
       </c>
       <c r="K9" t="n">
-        <v>92.28399990888974</v>
+        <v>92.28399990888971</v>
       </c>
       <c r="L9" t="n">
-        <v>104.6318218201627</v>
+        <v>104.6318218201625</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.773395820393471</v>
+        <v>2.365731899565676</v>
       </c>
       <c r="C2" t="n">
-        <v>2.508716982468842</v>
+        <v>2.244522307314802</v>
       </c>
       <c r="D2" t="n">
-        <v>4.262681263883218</v>
+        <v>2.444110034497397</v>
       </c>
       <c r="E2" t="n">
-        <v>2.718043266309512</v>
+        <v>2.420670749150823</v>
       </c>
       <c r="F2" t="n">
-        <v>2.161296037406796</v>
+        <v>1.957289265669868</v>
       </c>
       <c r="G2" t="n">
-        <v>4.344862340915565</v>
+        <v>2.44843506135685</v>
       </c>
       <c r="H2" t="n">
-        <v>4.843809795215715</v>
+        <v>2.473662602708226</v>
       </c>
       <c r="I2" t="n">
-        <v>2.644159205901502</v>
+        <v>2.358915588919579</v>
       </c>
       <c r="J2" t="n">
-        <v>3.223204145324988</v>
+        <v>2.912995251630631</v>
       </c>
       <c r="K2" t="n">
-        <v>2.404245183558408</v>
+        <v>2.310837346447159</v>
       </c>
       <c r="L2" t="n">
-        <v>3.773252230710167</v>
+        <v>2.417154442280834</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.169678365871811</v>
+        <v>2.587361297968568</v>
       </c>
       <c r="C3" t="n">
-        <v>2.88446983836655</v>
+        <v>2.352347336043604</v>
       </c>
       <c r="D3" t="n">
-        <v>4.882665130435225</v>
+        <v>3.143707342781675</v>
       </c>
       <c r="E3" t="n">
-        <v>3.09487118075194</v>
+        <v>2.640726843973155</v>
       </c>
       <c r="F3" t="n">
-        <v>2.538123951849217</v>
+        <v>1.875806204502014</v>
       </c>
       <c r="G3" t="n">
-        <v>4.977190392781252</v>
+        <v>3.176120835228071</v>
       </c>
       <c r="H3" t="n">
-        <v>5.551657247573218</v>
+        <v>3.364577543856208</v>
       </c>
       <c r="I3" t="n">
-        <v>3.017386411611363</v>
+        <v>2.538802665367113</v>
       </c>
       <c r="J3" t="n">
-        <v>3.586188086538659</v>
+        <v>3.428191948041207</v>
       </c>
       <c r="K3" t="n">
-        <v>2.751910903426125</v>
+        <v>2.403940686465435</v>
       </c>
       <c r="L3" t="n">
-        <v>4.31964276001331</v>
+        <v>2.967294929057807</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.019690820472727</v>
+        <v>2.01969082047271</v>
       </c>
       <c r="C4" t="n">
-        <v>1.74685655265834</v>
+        <v>1.746856552658335</v>
       </c>
       <c r="D4" t="n">
-        <v>2.905007910249996</v>
+        <v>2.905007910249942</v>
       </c>
       <c r="E4" t="n">
-        <v>1.799752646912052</v>
+        <v>1.799752646912045</v>
       </c>
       <c r="F4" t="n">
-        <v>1.799752646912042</v>
+        <v>1.799752646912045</v>
       </c>
       <c r="G4" t="n">
-        <v>2.952506510194554</v>
+        <v>2.952506510194436</v>
       </c>
       <c r="H4" t="n">
-        <v>3.250428090001315</v>
+        <v>3.250428090001255</v>
       </c>
       <c r="I4" t="n">
-        <v>1.934163333799814</v>
+        <v>1.934163333799773</v>
       </c>
       <c r="J4" t="n">
-        <v>1.887908749272854</v>
+        <v>1.887908749272822</v>
       </c>
       <c r="K4" t="n">
-        <v>1.827285579604151</v>
+        <v>1.827285579604092</v>
       </c>
       <c r="L4" t="n">
-        <v>2.614401531052418</v>
+        <v>2.614401531052374</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.08415081606263</v>
+        <v>11.08415081606257</v>
       </c>
       <c r="C5" t="n">
-        <v>9.67000749126842</v>
+        <v>9.670007491268406</v>
       </c>
       <c r="D5" t="n">
-        <v>26.13148657183756</v>
+        <v>26.13148657183739</v>
       </c>
       <c r="E5" t="n">
-        <v>9.67001444606653</v>
+        <v>9.670014446066535</v>
       </c>
       <c r="F5" t="n">
-        <v>9.67001444606653</v>
+        <v>9.670014446066535</v>
       </c>
       <c r="G5" t="n">
-        <v>27.91340979082082</v>
+        <v>27.91340979082069</v>
       </c>
       <c r="H5" t="n">
-        <v>34.6892355125817</v>
+        <v>34.68923551258133</v>
       </c>
       <c r="I5" t="n">
-        <v>9.669729443342355</v>
+        <v>9.669729443342337</v>
       </c>
       <c r="J5" t="n">
-        <v>9.41594500929603</v>
+        <v>9.41594500929588</v>
       </c>
       <c r="K5" t="n">
-        <v>7.805934867410164</v>
+        <v>7.805934867410041</v>
       </c>
       <c r="L5" t="n">
-        <v>25.3281232067655</v>
+        <v>6.096473655408602</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.470398694712319</v>
+        <v>2.470398694712343</v>
       </c>
       <c r="C6" t="n">
-        <v>2.330222114484428</v>
+        <v>2.330222114484422</v>
       </c>
       <c r="D6" t="n">
-        <v>3.423187537008034</v>
+        <v>3.423187537007972</v>
       </c>
       <c r="E6" t="n">
-        <v>2.307804883815956</v>
+        <v>2.307804883816006</v>
       </c>
       <c r="F6" t="n">
-        <v>2.376216759775072</v>
+        <v>2.376216759775054</v>
       </c>
       <c r="G6" t="n">
-        <v>5.519047150854746</v>
+        <v>5.519047150854671</v>
       </c>
       <c r="H6" t="n">
-        <v>6.436105510134611</v>
+        <v>6.436105510134664</v>
       </c>
       <c r="I6" t="n">
-        <v>4.500703974460011</v>
+        <v>4.500703974459959</v>
       </c>
       <c r="J6" t="n">
-        <v>4.585471454816155</v>
+        <v>4.585471454816214</v>
       </c>
       <c r="K6" t="n">
-        <v>2.224153303922438</v>
+        <v>2.224153303922356</v>
       </c>
       <c r="L6" t="n">
-        <v>3.058926193893178</v>
+        <v>3.05892619389315</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.775833522793713</v>
+        <v>2.775833522793662</v>
       </c>
       <c r="C7" t="n">
-        <v>2.690584084046891</v>
+        <v>2.690584084046879</v>
       </c>
       <c r="D7" t="n">
-        <v>3.661154105486176</v>
+        <v>3.661154105486091</v>
       </c>
       <c r="E7" t="n">
-        <v>2.674380367608406</v>
+        <v>2.674380367608387</v>
       </c>
       <c r="F7" t="n">
-        <v>2.674380367608406</v>
+        <v>2.674380367608387</v>
       </c>
       <c r="G7" t="n">
-        <v>3.708649212515533</v>
+        <v>3.70864921251552</v>
       </c>
       <c r="H7" t="n">
-        <v>4.006570792322274</v>
+        <v>4.006570792322166</v>
       </c>
       <c r="I7" t="n">
-        <v>2.690306036120792</v>
+        <v>2.690306036120794</v>
       </c>
       <c r="J7" t="n">
-        <v>2.644051451593838</v>
+        <v>2.644051451593748</v>
       </c>
       <c r="K7" t="n">
-        <v>2.583428281925132</v>
+        <v>2.583428281925072</v>
       </c>
       <c r="L7" t="n">
-        <v>3.370544233373398</v>
+        <v>3.370544233373325</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.622940380232504</v>
+        <v>4.622940380232438</v>
       </c>
       <c r="C8" t="n">
-        <v>6.352125943571988</v>
+        <v>6.352125943523443</v>
       </c>
       <c r="D8" t="n">
-        <v>7.717209886503743</v>
+        <v>7.717209886503674</v>
       </c>
       <c r="E8" t="n">
-        <v>5.853364873182613</v>
+        <v>5.853364873182529</v>
       </c>
       <c r="F8" t="n">
-        <v>4.58602014658283</v>
+        <v>4.586020146582821</v>
       </c>
       <c r="G8" t="n">
-        <v>7.385333655601436</v>
+        <v>7.385333655601377</v>
       </c>
       <c r="H8" t="n">
-        <v>7.68325523539982</v>
+        <v>7.683255235399801</v>
       </c>
       <c r="I8" t="n">
-        <v>6.366990479206694</v>
+        <v>6.366990479206686</v>
       </c>
       <c r="J8" t="n">
-        <v>6.321095456014388</v>
+        <v>6.321095456014146</v>
       </c>
       <c r="K8" t="n">
-        <v>4.396549796683755</v>
+        <v>4.396549796683611</v>
       </c>
       <c r="L8" t="n">
-        <v>8.958375448530406</v>
+        <v>8.958375448530182</v>
       </c>
     </row>
     <row r="9">
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.79118257175739</v>
+        <v>86.79118257175729</v>
       </c>
       <c r="C9" t="n">
         <v>110.22630704921</v>
       </c>
       <c r="D9" t="n">
-        <v>111.1968743370015</v>
+        <v>111.1968743370014</v>
       </c>
       <c r="E9" t="n">
         <v>137.3683270464699</v>
@@ -7545,7 +7545,7 @@
         <v>111.2443721776787</v>
       </c>
       <c r="H9" t="n">
-        <v>111.5422937574856</v>
+        <v>111.5422937574854</v>
       </c>
       <c r="I9" t="n">
         <v>110.226029001284</v>
@@ -7554,10 +7554,10 @@
         <v>110.179774416757</v>
       </c>
       <c r="K9" t="n">
-        <v>96.49135454774851</v>
+        <v>96.49135454774844</v>
       </c>
       <c r="L9" t="n">
-        <v>110.9062671985365</v>
+        <v>110.9062671985364</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.346590480423525</v>
+        <v>2.86657960124458</v>
       </c>
       <c r="C2" t="n">
-        <v>3.218608060821618</v>
+        <v>2.863100221457772</v>
       </c>
       <c r="D2" t="n">
-        <v>4.387931967854298</v>
+        <v>2.86875532161723</v>
       </c>
       <c r="E2" t="n">
-        <v>3.520394577797941</v>
+        <v>3.11759724438665</v>
       </c>
       <c r="F2" t="n">
-        <v>2.692736247028578</v>
+        <v>2.428726431143924</v>
       </c>
       <c r="G2" t="n">
-        <v>6.296277450770948</v>
+        <v>2.969187754103729</v>
       </c>
       <c r="H2" t="n">
-        <v>3.427812815904568</v>
+        <v>2.814457181872804</v>
       </c>
       <c r="I2" t="n">
-        <v>3.143039661658932</v>
+        <v>2.803223880831255</v>
       </c>
       <c r="J2" t="n">
-        <v>5.154897537103381</v>
+        <v>3.910958496440774</v>
       </c>
       <c r="K2" t="n">
-        <v>3.552739630706165</v>
+        <v>2.98984903413485</v>
       </c>
       <c r="L2" t="n">
-        <v>4.034680882266204</v>
+        <v>2.847200094433782</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.008573998930308</v>
+        <v>3.422214422749116</v>
       </c>
       <c r="C3" t="n">
-        <v>3.698345952020509</v>
+        <v>3.073900952439436</v>
       </c>
       <c r="D3" t="n">
-        <v>5.056125273339018</v>
+        <v>3.435403683904058</v>
       </c>
       <c r="E3" t="n">
-        <v>4.001552686687938</v>
+        <v>3.490228687336907</v>
       </c>
       <c r="F3" t="n">
-        <v>3.17389435591857</v>
+        <v>2.353090902024408</v>
       </c>
       <c r="G3" t="n">
-        <v>7.251117891269029</v>
+        <v>4.150479392787475</v>
       </c>
       <c r="H3" t="n">
-        <v>3.952758156779806</v>
+        <v>3.076628100520431</v>
       </c>
       <c r="I3" t="n">
-        <v>3.61953162232549</v>
+        <v>2.971319860317506</v>
       </c>
       <c r="J3" t="n">
-        <v>5.745303116283941</v>
+        <v>5.011928329265666</v>
       </c>
       <c r="K3" t="n">
-        <v>4.06368666094916</v>
+        <v>3.335977049171766</v>
       </c>
       <c r="L3" t="n">
-        <v>4.649764842492994</v>
+        <v>3.308795621125664</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.186658525543494</v>
+        <v>3.186658525543561</v>
       </c>
       <c r="C4" t="n">
-        <v>2.241293482235625</v>
+        <v>2.241293482235605</v>
       </c>
       <c r="D4" t="n">
-        <v>3.211234288033654</v>
+        <v>3.211234288033848</v>
       </c>
       <c r="E4" t="n">
         <v>2.307720294430245</v>
       </c>
       <c r="F4" t="n">
-        <v>2.30772029443024</v>
+        <v>2.307720294430236</v>
       </c>
       <c r="G4" t="n">
-        <v>4.343650007305289</v>
+        <v>4.343650007305279</v>
       </c>
       <c r="H4" t="n">
-        <v>2.641258574761937</v>
+        <v>2.641258574761686</v>
       </c>
       <c r="I4" t="n">
-        <v>2.458155427763828</v>
+        <v>2.458155427763822</v>
       </c>
       <c r="J4" t="n">
-        <v>2.903382715492841</v>
+        <v>2.903382715492835</v>
       </c>
       <c r="K4" t="n">
-        <v>2.588918719635776</v>
+        <v>2.588918719635676</v>
       </c>
       <c r="L4" t="n">
-        <v>3.002075518970963</v>
+        <v>3.002075518970744</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.33513826062905</v>
+        <v>23.33513826062912</v>
       </c>
       <c r="C5" t="n">
-        <v>11.32809138578559</v>
+        <v>11.32809138578557</v>
       </c>
       <c r="D5" t="n">
-        <v>22.55769251070111</v>
+        <v>22.55769251070133</v>
       </c>
       <c r="E5" t="n">
-        <v>11.32809924973413</v>
+        <v>11.32809924973417</v>
       </c>
       <c r="F5" t="n">
-        <v>11.32809924973413</v>
+        <v>11.32809924973417</v>
       </c>
       <c r="G5" t="n">
-        <v>41.7309035703356</v>
+        <v>41.73090357033798</v>
       </c>
       <c r="H5" t="n">
-        <v>15.17242575125951</v>
+        <v>15.17242575125963</v>
       </c>
       <c r="I5" t="n">
-        <v>11.32761846983872</v>
+        <v>11.32761846983871</v>
       </c>
       <c r="J5" t="n">
-        <v>20.06952359067648</v>
+        <v>20.06952359067639</v>
       </c>
       <c r="K5" t="n">
-        <v>13.08164974847166</v>
+        <v>13.08164974847165</v>
       </c>
       <c r="L5" t="n">
-        <v>15.75684772655336</v>
+        <v>23.30853376446682</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.097671738106618</v>
+        <v>6.097671738106554</v>
       </c>
       <c r="C6" t="n">
-        <v>2.989194123642553</v>
+        <v>2.98919412364258</v>
       </c>
       <c r="D6" t="n">
-        <v>3.847040266982135</v>
+        <v>3.847046322760681</v>
       </c>
       <c r="E6" t="n">
-        <v>2.943075626624598</v>
+        <v>2.943075626624626</v>
       </c>
       <c r="F6" t="n">
-        <v>3.056751731048844</v>
+        <v>3.056751731048829</v>
       </c>
       <c r="G6" t="n">
-        <v>4.959185819484559</v>
+        <v>7.254663219868656</v>
       </c>
       <c r="H6" t="n">
-        <v>6.080449879936896</v>
+        <v>6.080449879936689</v>
       </c>
       <c r="I6" t="n">
-        <v>5.369168640326985</v>
+        <v>5.369168640326971</v>
       </c>
       <c r="J6" t="n">
-        <v>3.54995404956294</v>
+        <v>3.549954049562998</v>
       </c>
       <c r="K6" t="n">
-        <v>3.143634347914115</v>
+        <v>3.143634347914221</v>
       </c>
       <c r="L6" t="n">
-        <v>3.597510320763841</v>
+        <v>3.597510320763806</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.026551550325526</v>
+        <v>4.026551550325677</v>
       </c>
       <c r="C7" t="n">
-        <v>3.298521368492716</v>
+        <v>3.298521368492718</v>
       </c>
       <c r="D7" t="n">
-        <v>4.05113005297854</v>
+        <v>4.051130052978659</v>
       </c>
       <c r="E7" t="n">
-        <v>3.278980204395376</v>
+        <v>3.278980204395328</v>
       </c>
       <c r="F7" t="n">
-        <v>3.278980204395376</v>
+        <v>3.278980204395328</v>
       </c>
       <c r="G7" t="n">
-        <v>5.183543032087312</v>
+        <v>5.183543032087414</v>
       </c>
       <c r="H7" t="n">
-        <v>3.48115159954401</v>
+        <v>3.481151599543886</v>
       </c>
       <c r="I7" t="n">
-        <v>3.298048452545882</v>
+        <v>3.298048452545852</v>
       </c>
       <c r="J7" t="n">
-        <v>3.743275740274905</v>
+        <v>3.74327574027481</v>
       </c>
       <c r="K7" t="n">
-        <v>3.428811744417862</v>
+        <v>3.428811744417933</v>
       </c>
       <c r="L7" t="n">
-        <v>3.841968543752953</v>
+        <v>3.841968543753112</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.950875854396809</v>
+        <v>5.95087585439688</v>
       </c>
       <c r="C8" t="n">
-        <v>7.252569090702406</v>
+        <v>7.252569090702395</v>
       </c>
       <c r="D8" t="n">
-        <v>8.448135208470889</v>
+        <v>8.448135208471079</v>
       </c>
       <c r="E8" t="n">
-        <v>6.694402388640601</v>
+        <v>6.694402388640485</v>
       </c>
       <c r="F8" t="n">
-        <v>5.276108857127944</v>
+        <v>5.276108857127985</v>
       </c>
       <c r="G8" t="n">
-        <v>9.15588178962641</v>
+        <v>9.155881789626545</v>
       </c>
       <c r="H8" t="n">
-        <v>7.453490357066837</v>
+        <v>7.453490357066752</v>
       </c>
       <c r="I8" t="n">
-        <v>7.270387210084926</v>
+        <v>7.270387210085107</v>
       </c>
       <c r="J8" t="n">
-        <v>7.716016985414316</v>
+        <v>7.716016985414381</v>
       </c>
       <c r="K8" t="n">
-        <v>5.315093129128746</v>
+        <v>5.315093129128809</v>
       </c>
       <c r="L8" t="n">
-        <v>9.953629644466316</v>
+        <v>9.953629644466483</v>
       </c>
     </row>
     <row r="9">
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.46508366343488</v>
+        <v>82.46508366343497</v>
       </c>
       <c r="C9" t="n">
         <v>103.788850070659</v>
@@ -7938,19 +7938,19 @@
         <v>103.7888578730755</v>
       </c>
       <c r="G9" t="n">
-        <v>105.6738717342537</v>
+        <v>105.6738717342538</v>
       </c>
       <c r="H9" t="n">
-        <v>103.9714803017103</v>
+        <v>103.9714803017102</v>
       </c>
       <c r="I9" t="n">
         <v>103.7883771547122</v>
       </c>
       <c r="J9" t="n">
-        <v>104.2336044424412</v>
+        <v>104.2336044424411</v>
       </c>
       <c r="K9" t="n">
-        <v>76.15199189517324</v>
+        <v>91.142243570669</v>
       </c>
       <c r="L9" t="n">
         <v>104.3322972459193</v>

--- a/Results/Ammonia/ammonia land use results.xlsx
+++ b/Results/Ammonia/ammonia land use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.972813910297351</v>
+        <v>1.972813910297354</v>
       </c>
       <c r="C2" t="n">
         <v>1.73461303836888</v>
       </c>
       <c r="D2" t="n">
-        <v>2.04926072150871</v>
+        <v>2.049260721508714</v>
       </c>
       <c r="E2" t="n">
-        <v>1.845830299160797</v>
+        <v>1.845830299160794</v>
       </c>
       <c r="F2" t="n">
-        <v>1.571461648110051</v>
+        <v>1.571461648110055</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02372397772833</v>
+        <v>2.023723977728333</v>
       </c>
       <c r="H2" t="n">
-        <v>2.08585527590391</v>
+        <v>2.085855275903913</v>
       </c>
       <c r="I2" t="n">
-        <v>1.995924576606493</v>
+        <v>1.995924576606494</v>
       </c>
       <c r="J2" t="n">
-        <v>2.136528440098751</v>
+        <v>2.136528440098754</v>
       </c>
       <c r="K2" t="n">
-        <v>1.778435616624019</v>
+        <v>1.778435616624021</v>
       </c>
       <c r="L2" t="n">
-        <v>2.065491891569371</v>
+        <v>2.065491891569372</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.086688790018075</v>
+        <v>2.086688790018076</v>
       </c>
       <c r="C3" t="n">
-        <v>1.821066235967175</v>
+        <v>1.821066235967173</v>
       </c>
       <c r="D3" t="n">
-        <v>2.63107006093739</v>
+        <v>2.631070060937391</v>
       </c>
       <c r="E3" t="n">
-        <v>2.003334787007283</v>
+        <v>2.003334787007282</v>
       </c>
       <c r="F3" t="n">
-        <v>1.550418810714317</v>
+        <v>1.550418810714318</v>
       </c>
       <c r="G3" t="n">
-        <v>2.449891688207928</v>
+        <v>2.44989168820793</v>
       </c>
       <c r="H3" t="n">
-        <v>2.897975112621411</v>
+        <v>2.897975112621417</v>
       </c>
       <c r="I3" t="n">
-        <v>2.251096797362064</v>
+        <v>2.251096797362067</v>
       </c>
       <c r="J3" t="n">
-        <v>2.442628112678687</v>
+        <v>2.442628112678682</v>
       </c>
       <c r="K3" t="n">
-        <v>1.79304499029498</v>
+        <v>1.793044990294981</v>
       </c>
       <c r="L3" t="n">
-        <v>2.752077511995881</v>
+        <v>2.752077511995887</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.342631218167339</v>
+        <v>1.342631218167333</v>
       </c>
       <c r="C4" t="n">
-        <v>1.461041414159781</v>
+        <v>1.461041414159776</v>
       </c>
       <c r="D4" t="n">
-        <v>2.20613311807025</v>
+        <v>2.206133118070246</v>
       </c>
       <c r="E4" t="n">
-        <v>1.496721853580889</v>
+        <v>1.496721853580887</v>
       </c>
       <c r="F4" t="n">
-        <v>1.496721853580888</v>
+        <v>1.496721853580887</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91688796877218</v>
+        <v>1.916887968772176</v>
       </c>
       <c r="H4" t="n">
-        <v>2.620132869583879</v>
+        <v>2.620132869583886</v>
       </c>
       <c r="I4" t="n">
-        <v>1.59875396316653</v>
+        <v>1.598753963166528</v>
       </c>
       <c r="J4" t="n">
-        <v>1.51787461747731</v>
+        <v>1.517874617477309</v>
       </c>
       <c r="K4" t="n">
-        <v>1.398542889515846</v>
+        <v>1.398542889515847</v>
       </c>
       <c r="L4" t="n">
-        <v>2.38728518432901</v>
+        <v>2.387285184329011</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.012851854881514</v>
+        <v>6.012851854881482</v>
       </c>
       <c r="C5" t="n">
-        <v>10.94758372245903</v>
+        <v>10.94758372245905</v>
       </c>
       <c r="D5" t="n">
-        <v>22.6747764831442</v>
+        <v>22.67477648314417</v>
       </c>
       <c r="E5" t="n">
-        <v>10.94758931382362</v>
+        <v>10.94758931382354</v>
       </c>
       <c r="F5" t="n">
-        <v>10.94758931382362</v>
+        <v>10.94758931382354</v>
       </c>
       <c r="G5" t="n">
-        <v>17.50632255439184</v>
+        <v>17.50632255439179</v>
       </c>
       <c r="H5" t="n">
-        <v>34.20714438037429</v>
+        <v>34.20714438037409</v>
       </c>
       <c r="I5" t="n">
-        <v>10.94746099930197</v>
+        <v>10.94746099930202</v>
       </c>
       <c r="J5" t="n">
-        <v>9.886772142715079</v>
+        <v>9.886772142715024</v>
       </c>
       <c r="K5" t="n">
-        <v>7.172111247678652</v>
+        <v>7.17211124767866</v>
       </c>
       <c r="L5" t="n">
-        <v>30.09853395185228</v>
+        <v>30.09853395185223</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.71331706836223</v>
+        <v>1.713317068362229</v>
       </c>
       <c r="C6" t="n">
-        <v>1.946593551574193</v>
+        <v>1.946593551574199</v>
       </c>
       <c r="D6" t="n">
-        <v>2.591760201566888</v>
+        <v>2.591760201566897</v>
       </c>
       <c r="E6" t="n">
-        <v>1.940651474958114</v>
+        <v>1.940651474958106</v>
       </c>
       <c r="F6" t="n">
-        <v>1.972935095100391</v>
+        <v>1.972935095100394</v>
       </c>
       <c r="G6" t="n">
-        <v>4.30427422761068</v>
+        <v>4.304274227610675</v>
       </c>
       <c r="H6" t="n">
-        <v>5.576470650255578</v>
+        <v>5.576470650255588</v>
       </c>
       <c r="I6" t="n">
-        <v>3.98614022200503</v>
+        <v>3.986140222005031</v>
       </c>
       <c r="J6" t="n">
-        <v>3.977485880211481</v>
+        <v>3.977485880211474</v>
       </c>
       <c r="K6" t="n">
-        <v>1.741084885137992</v>
+        <v>1.741084885137995</v>
       </c>
       <c r="L6" t="n">
-        <v>2.76752369305469</v>
+        <v>2.767523693054693</v>
       </c>
     </row>
     <row r="7">
@@ -718,34 +718,34 @@
         <v>2.001316776779667</v>
       </c>
       <c r="C7" t="n">
-        <v>2.257562244935888</v>
+        <v>2.257562244935887</v>
       </c>
       <c r="D7" t="n">
-        <v>2.864818178655917</v>
+        <v>2.864818178655915</v>
       </c>
       <c r="E7" t="n">
-        <v>2.249288411212459</v>
+        <v>2.249288411212458</v>
       </c>
       <c r="F7" t="n">
-        <v>2.24928841121246</v>
+        <v>2.249288411212458</v>
       </c>
       <c r="G7" t="n">
-        <v>2.57557352738451</v>
+        <v>2.575573527384509</v>
       </c>
       <c r="H7" t="n">
-        <v>3.278818428196224</v>
+        <v>3.278818428196218</v>
       </c>
       <c r="I7" t="n">
-        <v>2.257439521778858</v>
+        <v>2.25743952177886</v>
       </c>
       <c r="J7" t="n">
         <v>2.176560176089642</v>
       </c>
       <c r="K7" t="n">
-        <v>2.057228448128176</v>
+        <v>2.057228448128179</v>
       </c>
       <c r="L7" t="n">
-        <v>3.045970742941343</v>
+        <v>3.045970742941344</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.761492356289808</v>
+        <v>3.761492356289809</v>
       </c>
       <c r="C8" t="n">
-        <v>5.605372388014422</v>
+        <v>5.60537238801443</v>
       </c>
       <c r="D8" t="n">
-        <v>6.551013332854904</v>
+        <v>6.551013332854913</v>
       </c>
       <c r="E8" t="n">
-        <v>5.169901042504548</v>
+        <v>5.16990104250455</v>
       </c>
       <c r="F8" t="n">
-        <v>4.063371165433042</v>
+        <v>4.063371165433047</v>
       </c>
       <c r="G8" t="n">
-        <v>5.930985521115486</v>
+        <v>5.930985521115502</v>
       </c>
       <c r="H8" t="n">
-        <v>6.634230421925549</v>
+        <v>6.634230421925547</v>
       </c>
       <c r="I8" t="n">
-        <v>5.612851515509841</v>
+        <v>5.612851515509849</v>
       </c>
       <c r="J8" t="n">
-        <v>5.532285678835168</v>
+        <v>5.532285678835171</v>
       </c>
       <c r="K8" t="n">
-        <v>3.787771692275165</v>
+        <v>3.787771692275169</v>
       </c>
       <c r="L8" t="n">
-        <v>8.067740562263847</v>
+        <v>8.067740562263857</v>
       </c>
     </row>
     <row r="9">
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91.6372670561412</v>
+        <v>91.63726705614121</v>
       </c>
       <c r="C9" t="n">
-        <v>116.8903361489345</v>
+        <v>116.8903361489344</v>
       </c>
       <c r="D9" t="n">
         <v>117.4975928940329</v>
@@ -813,7 +813,7 @@
         <v>117.2083474313831</v>
       </c>
       <c r="H9" t="n">
-        <v>117.9115923321949</v>
+        <v>117.9115923321948</v>
       </c>
       <c r="I9" t="n">
         <v>116.8902134257775</v>
@@ -822,7 +822,7 @@
         <v>116.8093340800881</v>
       </c>
       <c r="K9" t="n">
-        <v>85.21453941026073</v>
+        <v>85.2145394102607</v>
       </c>
       <c r="L9" t="n">
         <v>117.6787446469399</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.00722594657343</v>
+        <v>3.007225946573414</v>
       </c>
       <c r="C2" t="n">
-        <v>3.141343276769969</v>
+        <v>3.141343276770025</v>
       </c>
       <c r="D2" t="n">
-        <v>2.953935386609053</v>
+        <v>2.953935386609009</v>
       </c>
       <c r="E2" t="n">
-        <v>3.431709616498897</v>
+        <v>3.43170961649882</v>
       </c>
       <c r="F2" t="n">
-        <v>2.638728747130486</v>
+        <v>2.638728747130354</v>
       </c>
       <c r="G2" t="n">
-        <v>3.110621406913849</v>
+        <v>3.110621406913837</v>
       </c>
       <c r="H2" t="n">
-        <v>2.946616948728508</v>
+        <v>2.94661694872849</v>
       </c>
       <c r="I2" t="n">
-        <v>2.973404430548579</v>
+        <v>2.973404430548511</v>
       </c>
       <c r="J2" t="n">
-        <v>4.315441881135378</v>
+        <v>4.315441881135734</v>
       </c>
       <c r="K2" t="n">
-        <v>3.287755333027833</v>
+        <v>3.287755333027753</v>
       </c>
       <c r="L2" t="n">
-        <v>2.972728671856427</v>
+        <v>2.972728671856397</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.500102219702519</v>
+        <v>3.500102219702503</v>
       </c>
       <c r="C3" t="n">
-        <v>3.540487103635279</v>
+        <v>3.540487103635241</v>
       </c>
       <c r="D3" t="n">
-        <v>3.121312960924441</v>
+        <v>3.121312960924445</v>
       </c>
       <c r="E3" t="n">
-        <v>4.016048526736564</v>
+        <v>4.016048526736591</v>
       </c>
       <c r="F3" t="n">
-        <v>2.707055935165118</v>
+        <v>2.707055935164793</v>
       </c>
       <c r="G3" t="n">
-        <v>4.235399383528092</v>
+        <v>4.235399383528078</v>
       </c>
       <c r="H3" t="n">
-        <v>3.096657609927387</v>
+        <v>3.096657609927441</v>
       </c>
       <c r="I3" t="n">
-        <v>3.259559698893</v>
+        <v>3.259559698892934</v>
       </c>
       <c r="J3" t="n">
-        <v>5.58035906571382</v>
+        <v>5.580359065713012</v>
       </c>
       <c r="K3" t="n">
-        <v>3.785950883450704</v>
+        <v>3.785950883450711</v>
       </c>
       <c r="L3" t="n">
-        <v>3.280597389411766</v>
+        <v>3.280597389411738</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.316765672474105</v>
+        <v>3.316765672473904</v>
       </c>
       <c r="C4" t="n">
-        <v>2.723957303103719</v>
+        <v>2.723957303103673</v>
       </c>
       <c r="D4" t="n">
-        <v>2.714824282807095</v>
+        <v>2.714824282807198</v>
       </c>
       <c r="E4" t="n">
-        <v>2.795984097009956</v>
+        <v>2.795984097009887</v>
       </c>
       <c r="F4" t="n">
-        <v>2.795984097009974</v>
+        <v>2.795984097009888</v>
       </c>
       <c r="G4" t="n">
-        <v>4.482880024625585</v>
+        <v>4.482880024625473</v>
       </c>
       <c r="H4" t="n">
-        <v>2.677910670838448</v>
+        <v>2.6779106708384</v>
       </c>
       <c r="I4" t="n">
-        <v>2.923464407868313</v>
+        <v>2.923464407868332</v>
       </c>
       <c r="J4" t="n">
-        <v>3.146278422685535</v>
+        <v>3.146278422685623</v>
       </c>
       <c r="K4" t="n">
-        <v>2.952333435978795</v>
+        <v>2.952333435978854</v>
       </c>
       <c r="L4" t="n">
-        <v>2.96489008676299</v>
+        <v>2.96489008676298</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.06367802322258</v>
+        <v>22.06367802322255</v>
       </c>
       <c r="C5" t="n">
-        <v>15.73301562323812</v>
+        <v>15.73301562323809</v>
       </c>
       <c r="D5" t="n">
-        <v>12.21962749556886</v>
+        <v>12.21962749556872</v>
       </c>
       <c r="E5" t="n">
-        <v>15.73302301186249</v>
+        <v>15.73302301186236</v>
       </c>
       <c r="F5" t="n">
-        <v>15.73302301186249</v>
+        <v>15.73302301186236</v>
       </c>
       <c r="G5" t="n">
-        <v>41.34928514862026</v>
+        <v>41.34928514862019</v>
       </c>
       <c r="H5" t="n">
-        <v>12.9757982194191</v>
+        <v>12.97579821941864</v>
       </c>
       <c r="I5" t="n">
-        <v>15.73261469648451</v>
+        <v>15.73261469648449</v>
       </c>
       <c r="J5" t="n">
-        <v>20.92173831966482</v>
+        <v>20.92173831966259</v>
       </c>
       <c r="K5" t="n">
-        <v>15.51108641020023</v>
+        <v>15.51108641020015</v>
       </c>
       <c r="L5" t="n">
-        <v>19.03943957285883</v>
+        <v>19.03943957285858</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.042153807088144</v>
+        <v>4.042153807087961</v>
       </c>
       <c r="C6" t="n">
-        <v>3.580101098014864</v>
+        <v>3.580101098014842</v>
       </c>
       <c r="D6" t="n">
-        <v>5.965579810861835</v>
+        <v>5.965579810861676</v>
       </c>
       <c r="E6" t="n">
-        <v>3.517506875453761</v>
+        <v>3.51750687545373</v>
       </c>
       <c r="F6" t="n">
-        <v>3.641140379304812</v>
+        <v>3.641140379304879</v>
       </c>
       <c r="G6" t="n">
-        <v>7.606316162494299</v>
+        <v>7.606316162494271</v>
       </c>
       <c r="H6" t="n">
-        <v>6.332555393729323</v>
+        <v>6.332555393729557</v>
       </c>
       <c r="I6" t="n">
-        <v>3.648852542482538</v>
+        <v>3.648852542482568</v>
       </c>
       <c r="J6" t="n">
-        <v>3.91549758920047</v>
+        <v>3.915497589200478</v>
       </c>
       <c r="K6" t="n">
-        <v>3.644168156452893</v>
+        <v>3.644168156452874</v>
       </c>
       <c r="L6" t="n">
-        <v>3.671306271898352</v>
+        <v>3.671306271898149</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.202748274816485</v>
+        <v>4.202748274816307</v>
       </c>
       <c r="C7" t="n">
-        <v>3.809847936964568</v>
+        <v>3.809847936964448</v>
       </c>
       <c r="D7" t="n">
-        <v>3.600806181962282</v>
+        <v>3.60080618196215</v>
       </c>
       <c r="E7" t="n">
-        <v>3.796308645269256</v>
+        <v>3.796308645269252</v>
       </c>
       <c r="F7" t="n">
-        <v>3.796308645269231</v>
+        <v>3.796308645269252</v>
       </c>
       <c r="G7" t="n">
-        <v>5.368862626968064</v>
+        <v>5.368862626968021</v>
       </c>
       <c r="H7" t="n">
-        <v>3.563893273180901</v>
+        <v>3.563893273180771</v>
       </c>
       <c r="I7" t="n">
-        <v>3.809447010210815</v>
+        <v>3.809447010210834</v>
       </c>
       <c r="J7" t="n">
-        <v>4.03226102502826</v>
+        <v>4.032261025028085</v>
       </c>
       <c r="K7" t="n">
-        <v>3.838316038321442</v>
+        <v>3.83831603832135</v>
       </c>
       <c r="L7" t="n">
-        <v>3.850872689105465</v>
+        <v>3.850872689105379</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.183044249833452</v>
+        <v>6.183044249833299</v>
       </c>
       <c r="C8" t="n">
-        <v>7.945368153734792</v>
+        <v>7.945368153734854</v>
       </c>
       <c r="D8" t="n">
-        <v>8.198345849316517</v>
+        <v>8.198345849316652</v>
       </c>
       <c r="E8" t="n">
-        <v>7.353841305346746</v>
+        <v>7.353841305346469</v>
       </c>
       <c r="F8" t="n">
-        <v>5.850784692404185</v>
+        <v>5.850784692404078</v>
       </c>
       <c r="G8" t="n">
-        <v>9.516905210750773</v>
+        <v>9.516905210750615</v>
       </c>
       <c r="H8" t="n">
-        <v>7.711935856945793</v>
+        <v>7.711935856945724</v>
       </c>
       <c r="I8" t="n">
-        <v>7.957489593993424</v>
+        <v>7.957489593993477</v>
       </c>
       <c r="J8" t="n">
-        <v>8.180729625805741</v>
+        <v>8.180729625805682</v>
       </c>
       <c r="K8" t="n">
-        <v>5.77834500786485</v>
+        <v>5.778345007864719</v>
       </c>
       <c r="L8" t="n">
-        <v>10.2633078627639</v>
+        <v>10.26330786276394</v>
       </c>
     </row>
     <row r="9">
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82.49001045255329</v>
+        <v>82.49001045255315</v>
       </c>
       <c r="C9" t="n">
-        <v>104.1437068003921</v>
+        <v>104.1437068003922</v>
       </c>
       <c r="D9" t="n">
         <v>103.9346673774082</v>
@@ -1206,10 +1206,10 @@
         <v>104.1437141798311</v>
       </c>
       <c r="G9" t="n">
-        <v>105.7027214903957</v>
+        <v>105.7027214903955</v>
       </c>
       <c r="H9" t="n">
-        <v>103.8977521366085</v>
+        <v>103.8977521366084</v>
       </c>
       <c r="I9" t="n">
         <v>104.1433058736385</v>
@@ -1218,10 +1218,10 @@
         <v>104.366119888456</v>
       </c>
       <c r="K9" t="n">
-        <v>91.39829088347088</v>
+        <v>91.39829088347074</v>
       </c>
       <c r="L9" t="n">
-        <v>104.1847315525332</v>
+        <v>104.1847315525331</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.772294963007987</v>
+        <v>1.772294963008016</v>
       </c>
       <c r="C2" t="n">
-        <v>1.396332714307164</v>
+        <v>1.396332714307203</v>
       </c>
       <c r="D2" t="n">
-        <v>1.897544781008754</v>
+        <v>1.89754478100877</v>
       </c>
       <c r="E2" t="n">
-        <v>1.607010434533247</v>
+        <v>1.607010434533279</v>
       </c>
       <c r="F2" t="n">
-        <v>1.607040140493425</v>
+        <v>1.60704014049348</v>
       </c>
       <c r="G2" t="n">
-        <v>1.849190310165006</v>
+        <v>1.849190310165034</v>
       </c>
       <c r="H2" t="n">
-        <v>1.852680117210147</v>
+        <v>1.85268011721018</v>
       </c>
       <c r="I2" t="n">
-        <v>1.834887874986597</v>
+        <v>1.834887874986611</v>
       </c>
       <c r="J2" t="n">
-        <v>1.891709008692344</v>
+        <v>1.891709008692401</v>
       </c>
       <c r="K2" t="n">
-        <v>1.882237367056786</v>
+        <v>1.882237367056805</v>
       </c>
       <c r="L2" t="n">
-        <v>1.839178658042666</v>
+        <v>1.839178658042693</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.610726415972917</v>
+        <v>1.610726415972956</v>
       </c>
       <c r="C3" t="n">
-        <v>1.109633881999831</v>
+        <v>1.109633881999866</v>
       </c>
       <c r="D3" t="n">
-        <v>2.502649782466694</v>
+        <v>2.50264978246674</v>
       </c>
       <c r="E3" t="n">
-        <v>1.680403451326347</v>
+        <v>1.680403451326389</v>
       </c>
       <c r="F3" t="n">
-        <v>1.680433157286536</v>
+        <v>1.680433157286554</v>
       </c>
       <c r="G3" t="n">
-        <v>2.158902455435142</v>
+        <v>2.158902455435181</v>
       </c>
       <c r="H3" t="n">
-        <v>2.189883807154166</v>
+        <v>2.189883807154267</v>
       </c>
       <c r="I3" t="n">
-        <v>2.056567464168059</v>
+        <v>2.056567464168071</v>
       </c>
       <c r="J3" t="n">
-        <v>2.060466872530112</v>
+        <v>2.060466872530129</v>
       </c>
       <c r="K3" t="n">
-        <v>2.187886322831228</v>
+        <v>2.187886322831243</v>
       </c>
       <c r="L3" t="n">
-        <v>2.092611926697607</v>
+        <v>2.092611926697627</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8324032894806511</v>
+        <v>0.8324032894806721</v>
       </c>
       <c r="C4" t="n">
-        <v>0.961737534153176</v>
+        <v>0.9617375341532148</v>
       </c>
       <c r="D4" t="n">
-        <v>2.247157601562173</v>
+        <v>2.247157601562184</v>
       </c>
       <c r="E4" t="n">
-        <v>1.476744819943252</v>
+        <v>1.476744819943279</v>
       </c>
       <c r="F4" t="n">
-        <v>1.476744819943252</v>
+        <v>1.476744819943272</v>
       </c>
       <c r="G4" t="n">
-        <v>1.699907297668358</v>
+        <v>1.699907297668443</v>
       </c>
       <c r="H4" t="n">
-        <v>1.747384940798602</v>
+        <v>1.747384940798742</v>
       </c>
       <c r="I4" t="n">
-        <v>1.532727421001099</v>
+        <v>1.532727421001119</v>
       </c>
       <c r="J4" t="n">
-        <v>1.353067424541239</v>
+        <v>1.353067424541323</v>
       </c>
       <c r="K4" t="n">
-        <v>1.649334063761228</v>
+        <v>1.649334063761255</v>
       </c>
       <c r="L4" t="n">
-        <v>1.593257260417106</v>
+        <v>1.593257260417121</v>
       </c>
     </row>
     <row r="5">
@@ -1427,34 +1427,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-2.259854127041728</v>
+        <v>-2.259854127041736</v>
       </c>
       <c r="C5" t="n">
-        <v>2.045539579754418</v>
+        <v>2.045539579755288</v>
       </c>
       <c r="D5" t="n">
-        <v>22.98974912721001</v>
+        <v>22.98974912720965</v>
       </c>
       <c r="E5" t="n">
-        <v>10.41052612634473</v>
+        <v>10.4105261263454</v>
       </c>
       <c r="F5" t="n">
-        <v>10.41052612634473</v>
+        <v>10.41052612634552</v>
       </c>
       <c r="G5" t="n">
-        <v>13.56480917062619</v>
+        <v>13.56480917062729</v>
       </c>
       <c r="H5" t="n">
-        <v>15.67426335416228</v>
+        <v>15.67426335416333</v>
       </c>
       <c r="I5" t="n">
-        <v>10.41046869880595</v>
+        <v>10.41046869880712</v>
       </c>
       <c r="J5" t="n">
-        <v>7.286677389748745</v>
+        <v>7.286677389748894</v>
       </c>
       <c r="K5" t="n">
-        <v>12.33902929739643</v>
+        <v>12.33902929739647</v>
       </c>
       <c r="L5" t="n">
         <v>12.78854549269987</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.944571226001958</v>
+        <v>2.944571226001994</v>
       </c>
       <c r="C6" t="n">
-        <v>1.346102346385795</v>
+        <v>1.346102346385936</v>
       </c>
       <c r="D6" t="n">
-        <v>2.568020687805001</v>
+        <v>2.568020687805062</v>
       </c>
       <c r="E6" t="n">
-        <v>1.819175739524684</v>
+        <v>1.819175739524777</v>
       </c>
       <c r="F6" t="n">
-        <v>1.83976002021634</v>
+        <v>1.839760020216378</v>
       </c>
       <c r="G6" t="n">
-        <v>2.002469547446271</v>
+        <v>2.002469547446323</v>
       </c>
       <c r="H6" t="n">
-        <v>4.381265366053512</v>
+        <v>4.381265366053705</v>
       </c>
       <c r="I6" t="n">
-        <v>1.835289670778994</v>
+        <v>1.835289670779015</v>
       </c>
       <c r="J6" t="n">
-        <v>3.512052930276242</v>
+        <v>3.512052930276315</v>
       </c>
       <c r="K6" t="n">
-        <v>1.93944223541616</v>
+        <v>1.939442235416178</v>
       </c>
       <c r="L6" t="n">
-        <v>1.899877636627306</v>
+        <v>1.899877636627345</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.414380728184658</v>
+        <v>1.414380728184711</v>
       </c>
       <c r="C7" t="n">
-        <v>1.657239380921995</v>
+        <v>1.657239380921993</v>
       </c>
       <c r="D7" t="n">
-        <v>2.829133972350176</v>
+        <v>2.829133972350217</v>
       </c>
       <c r="E7" t="n">
-        <v>2.118201701209014</v>
+        <v>2.118201701209081</v>
       </c>
       <c r="F7" t="n">
-        <v>2.118201701209014</v>
+        <v>2.118201701209088</v>
       </c>
       <c r="G7" t="n">
-        <v>2.281884736372392</v>
+        <v>2.281884736372461</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3293623795026</v>
+        <v>2.329362379502756</v>
       </c>
       <c r="I7" t="n">
-        <v>2.114704859705132</v>
+        <v>2.114704859705155</v>
       </c>
       <c r="J7" t="n">
-        <v>1.935044863245257</v>
+        <v>1.935044863245312</v>
       </c>
       <c r="K7" t="n">
-        <v>2.231311502465223</v>
+        <v>2.231311502465273</v>
       </c>
       <c r="L7" t="n">
-        <v>2.175234699121107</v>
+        <v>2.175234699121152</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.043218715016854</v>
+        <v>3.043218715016886</v>
       </c>
       <c r="C8" t="n">
-        <v>4.735930857110566</v>
+        <v>4.735930857110789</v>
       </c>
       <c r="D8" t="n">
-        <v>6.204148051566723</v>
+        <v>6.204148051566826</v>
       </c>
       <c r="E8" t="n">
-        <v>4.797530647276368</v>
+        <v>4.797530647276354</v>
       </c>
       <c r="F8" t="n">
-        <v>3.791497516798267</v>
+        <v>3.791497516798386</v>
       </c>
       <c r="G8" t="n">
-        <v>5.357002263379675</v>
+        <v>5.357002263379904</v>
       </c>
       <c r="H8" t="n">
-        <v>5.404479906510913</v>
+        <v>5.404479906511236</v>
       </c>
       <c r="I8" t="n">
-        <v>5.189822386712395</v>
+        <v>5.189822386712448</v>
       </c>
       <c r="J8" t="n">
-        <v>5.010446625408917</v>
+        <v>5.010446625409164</v>
       </c>
       <c r="K8" t="n">
-        <v>3.833284104285877</v>
+        <v>3.833284104286009</v>
       </c>
       <c r="L8" t="n">
-        <v>6.761112141655226</v>
+        <v>6.761112141655325</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83.723507126244</v>
+        <v>83.72350712624403</v>
       </c>
       <c r="C9" t="n">
-        <v>106.9084070271864</v>
+        <v>106.9084070271866</v>
       </c>
       <c r="D9" t="n">
-        <v>108.0803031044677</v>
+        <v>108.0803031044678</v>
       </c>
       <c r="E9" t="n">
-        <v>133.8405593778909</v>
+        <v>133.8405593778911</v>
       </c>
       <c r="F9" t="n">
-        <v>107.3659298663149</v>
+        <v>107.365929866315</v>
       </c>
       <c r="G9" t="n">
-        <v>107.5330523826371</v>
+        <v>107.5330523826372</v>
       </c>
       <c r="H9" t="n">
-        <v>107.5805300257672</v>
+        <v>107.5805300257674</v>
       </c>
       <c r="I9" t="n">
         <v>107.3658725059698</v>
       </c>
       <c r="J9" t="n">
-        <v>107.1862125095099</v>
+        <v>107.18621250951</v>
       </c>
       <c r="K9" t="n">
-        <v>94.18977052495124</v>
+        <v>94.18977052495138</v>
       </c>
       <c r="L9" t="n">
-        <v>107.4264023453857</v>
+        <v>107.4264023453858</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.937592001108358</v>
+        <v>1.937592001108361</v>
       </c>
       <c r="C2" t="n">
         <v>1.521442119900674</v>
       </c>
       <c r="D2" t="n">
-        <v>2.068149181424319</v>
+        <v>2.068149181424325</v>
       </c>
       <c r="E2" t="n">
-        <v>1.790991015696335</v>
+        <v>1.790991015696333</v>
       </c>
       <c r="F2" t="n">
-        <v>1.791021560539828</v>
+        <v>1.791021560539829</v>
       </c>
       <c r="G2" t="n">
-        <v>2.011889343817621</v>
+        <v>2.011889343817622</v>
       </c>
       <c r="H2" t="n">
-        <v>1.972989363853962</v>
+        <v>1.972989363853957</v>
       </c>
       <c r="I2" t="n">
-        <v>2.00376240906474</v>
+        <v>2.003762409064736</v>
       </c>
       <c r="J2" t="n">
-        <v>2.067751517836616</v>
+        <v>2.067751517836619</v>
       </c>
       <c r="K2" t="n">
-        <v>2.121359276694321</v>
+        <v>2.121359276694313</v>
       </c>
       <c r="L2" t="n">
-        <v>2.011814713200061</v>
+        <v>2.011814713200055</v>
       </c>
     </row>
     <row r="3">
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.898130082930233</v>
+        <v>1.898130082930231</v>
       </c>
       <c r="C3" t="n">
-        <v>1.225991291601237</v>
+        <v>1.225991291601234</v>
       </c>
       <c r="D3" t="n">
-        <v>2.82761094868918</v>
+        <v>2.827610948689184</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0180548732323</v>
+        <v>2.018054873232296</v>
       </c>
       <c r="F3" t="n">
         <v>2.018085418075792</v>
@@ -1761,19 +1761,19 @@
         <v>2.427762795416994</v>
       </c>
       <c r="H3" t="n">
-        <v>2.159594853752808</v>
+        <v>2.159594853752807</v>
       </c>
       <c r="I3" t="n">
-        <v>2.369299043837365</v>
+        <v>2.369299043837366</v>
       </c>
       <c r="J3" t="n">
         <v>2.206264468286784</v>
       </c>
       <c r="K3" t="n">
-        <v>2.661057772503905</v>
+        <v>2.661057772503902</v>
       </c>
       <c r="L3" t="n">
-        <v>2.433425513283269</v>
+        <v>2.433425513283261</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.192960371537012</v>
+        <v>1.192960371537024</v>
       </c>
       <c r="C4" t="n">
-        <v>1.11727505515187</v>
+        <v>1.117275055151862</v>
       </c>
       <c r="D4" t="n">
-        <v>2.667663782475998</v>
+        <v>2.667663782475908</v>
       </c>
       <c r="E4" t="n">
-        <v>1.949332339744921</v>
+        <v>1.949332339744908</v>
       </c>
       <c r="F4" t="n">
-        <v>1.949332339744922</v>
+        <v>1.949332339744912</v>
       </c>
       <c r="G4" t="n">
-        <v>2.031254113060772</v>
+        <v>2.031254113060803</v>
       </c>
       <c r="H4" t="n">
-        <v>1.607186933703794</v>
+        <v>1.607186933703739</v>
       </c>
       <c r="I4" t="n">
-        <v>1.934566168274925</v>
+        <v>1.934566168274905</v>
       </c>
       <c r="J4" t="n">
-        <v>1.38544690121147</v>
+        <v>1.385446901211472</v>
       </c>
       <c r="K4" t="n">
-        <v>2.142221659576315</v>
+        <v>2.142221659576326</v>
       </c>
       <c r="L4" t="n">
-        <v>2.036340752378059</v>
+        <v>2.036340752377965</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.268630327898859</v>
+        <v>2.26863032789882</v>
       </c>
       <c r="C5" t="n">
-        <v>2.571011244961906</v>
+        <v>2.571011244961899</v>
       </c>
       <c r="D5" t="n">
-        <v>27.15293445477818</v>
+        <v>27.15293445477817</v>
       </c>
       <c r="E5" t="n">
-        <v>14.91611403114026</v>
+        <v>14.91611403114029</v>
       </c>
       <c r="F5" t="n">
-        <v>14.91611403114026</v>
+        <v>14.91611403114029</v>
       </c>
       <c r="G5" t="n">
-        <v>16.78367382931863</v>
+        <v>16.78367382931865</v>
       </c>
       <c r="H5" t="n">
-        <v>10.11822089881957</v>
+        <v>10.11822089881955</v>
       </c>
       <c r="I5" t="n">
-        <v>14.91607803058255</v>
+        <v>14.91607803058254</v>
       </c>
       <c r="J5" t="n">
-        <v>5.563627924972005</v>
+        <v>5.563627924971976</v>
       </c>
       <c r="K5" t="n">
-        <v>18.28901840831615</v>
+        <v>18.2890184083161</v>
       </c>
       <c r="L5" t="n">
-        <v>18.66072003385755</v>
+        <v>18.66072003385746</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.28534534031224</v>
+        <v>3.285345340312261</v>
       </c>
       <c r="C6" t="n">
-        <v>1.501171645169233</v>
+        <v>1.501171645169227</v>
       </c>
       <c r="D6" t="n">
-        <v>4.816557944208545</v>
+        <v>4.816557944208557</v>
       </c>
       <c r="E6" t="n">
-        <v>2.243516480402114</v>
+        <v>2.243516480402116</v>
       </c>
       <c r="F6" t="n">
-        <v>2.26037267361283</v>
+        <v>2.260372673612827</v>
       </c>
       <c r="G6" t="n">
-        <v>4.123639081835994</v>
+        <v>4.123639081836007</v>
       </c>
       <c r="H6" t="n">
-        <v>4.189083269738711</v>
+        <v>4.189083269738699</v>
       </c>
       <c r="I6" t="n">
-        <v>2.25166026891789</v>
+        <v>2.251660268917881</v>
       </c>
       <c r="J6" t="n">
-        <v>1.722041259511494</v>
+        <v>1.722041259511501</v>
       </c>
       <c r="K6" t="n">
-        <v>2.449221196197176</v>
+        <v>2.449221196197136</v>
       </c>
       <c r="L6" t="n">
-        <v>2.356463426463668</v>
+        <v>2.356463426463637</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.792207716528008</v>
+        <v>1.792207716527982</v>
       </c>
       <c r="C7" t="n">
-        <v>1.81872425666718</v>
+        <v>1.818724256667175</v>
       </c>
       <c r="D7" t="n">
-        <v>3.266907401089265</v>
+        <v>3.266907401089254</v>
       </c>
       <c r="E7" t="n">
-        <v>2.556228369978635</v>
+        <v>2.556228369978643</v>
       </c>
       <c r="F7" t="n">
-        <v>2.556228369978634</v>
+        <v>2.556228369978643</v>
       </c>
       <c r="G7" t="n">
-        <v>2.630501458051768</v>
+        <v>2.630501458051726</v>
       </c>
       <c r="H7" t="n">
-        <v>2.206434278694791</v>
+        <v>2.206434278694716</v>
       </c>
       <c r="I7" t="n">
-        <v>2.533813513265919</v>
+        <v>2.533813513265927</v>
       </c>
       <c r="J7" t="n">
-        <v>1.984694246202468</v>
+        <v>1.984694246202488</v>
       </c>
       <c r="K7" t="n">
-        <v>2.74146900456731</v>
+        <v>2.741469004567243</v>
       </c>
       <c r="L7" t="n">
-        <v>2.635588097369053</v>
+        <v>2.635588097369047</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.373812080225315</v>
+        <v>3.373812080225443</v>
       </c>
       <c r="C8" t="n">
-        <v>4.873017991469712</v>
+        <v>4.87301799146977</v>
       </c>
       <c r="D8" t="n">
-        <v>6.600399664008962</v>
+        <v>6.600399664008969</v>
       </c>
       <c r="E8" t="n">
-        <v>5.189011716930427</v>
+        <v>5.189011716930445</v>
       </c>
       <c r="F8" t="n">
-        <v>4.174800893449478</v>
+        <v>4.174800893449463</v>
       </c>
       <c r="G8" t="n">
-        <v>5.663113997042769</v>
+        <v>5.663113997042723</v>
       </c>
       <c r="H8" t="n">
-        <v>5.239046817683505</v>
+        <v>5.239046817683616</v>
       </c>
       <c r="I8" t="n">
-        <v>5.566426052256922</v>
+        <v>5.566426052256926</v>
       </c>
       <c r="J8" t="n">
-        <v>5.017591949128503</v>
+        <v>5.017591949128489</v>
       </c>
       <c r="K8" t="n">
-        <v>4.296120146459645</v>
+        <v>4.296120146459637</v>
       </c>
       <c r="L8" t="n">
-        <v>7.183900006177518</v>
+        <v>7.183900006177421</v>
       </c>
     </row>
     <row r="9">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.73995741705511</v>
+        <v>79.73995741705509</v>
       </c>
       <c r="C9" t="n">
         <v>101.5174750349464</v>
@@ -1992,25 +1992,25 @@
         <v>102.9656624804237</v>
       </c>
       <c r="E9" t="n">
-        <v>127.3327949047525</v>
+        <v>127.3327949047524</v>
       </c>
       <c r="F9" t="n">
-        <v>102.232600328228</v>
+        <v>102.2326003282279</v>
       </c>
       <c r="G9" t="n">
         <v>102.3292522363311</v>
       </c>
       <c r="H9" t="n">
-        <v>101.9051850569741</v>
+        <v>101.905185056974</v>
       </c>
       <c r="I9" t="n">
         <v>102.2325642915453</v>
       </c>
       <c r="J9" t="n">
-        <v>101.6834450244817</v>
+        <v>101.6834450244818</v>
       </c>
       <c r="K9" t="n">
-        <v>89.83760457732892</v>
+        <v>89.83760457732886</v>
       </c>
       <c r="L9" t="n">
         <v>102.3343388756483</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.989437071365105</v>
+        <v>1.989437071365183</v>
       </c>
       <c r="C2" t="n">
-        <v>1.56782597086129</v>
+        <v>1.567825970861295</v>
       </c>
       <c r="D2" t="n">
-        <v>2.121360496065476</v>
+        <v>2.121360496065551</v>
       </c>
       <c r="E2" t="n">
-        <v>1.845663378480743</v>
+        <v>1.845663378480831</v>
       </c>
       <c r="F2" t="n">
-        <v>1.845694469040583</v>
+        <v>1.845694469040637</v>
       </c>
       <c r="G2" t="n">
-        <v>2.064717272110185</v>
+        <v>2.064717272110248</v>
       </c>
       <c r="H2" t="n">
-        <v>2.002166648737079</v>
+        <v>2.002166648737083</v>
       </c>
       <c r="I2" t="n">
-        <v>2.045818387313133</v>
+        <v>2.04581838731319</v>
       </c>
       <c r="J2" t="n">
-        <v>2.129132556208221</v>
+        <v>2.129132556208252</v>
       </c>
       <c r="K2" t="n">
-        <v>2.220369328907213</v>
+        <v>2.220369328907244</v>
       </c>
       <c r="L2" t="n">
-        <v>2.085159045622216</v>
+        <v>2.085159045622221</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.994814399720846</v>
+        <v>1.994814399720871</v>
       </c>
       <c r="C3" t="n">
-        <v>1.267122051412741</v>
+        <v>1.267122051412746</v>
       </c>
       <c r="D3" t="n">
-        <v>2.933925819924446</v>
+        <v>2.933925819924495</v>
       </c>
       <c r="E3" t="n">
-        <v>2.065748033598122</v>
+        <v>2.06574803359814</v>
       </c>
       <c r="F3" t="n">
-        <v>2.065779124157901</v>
+        <v>2.065779124157945</v>
       </c>
       <c r="G3" t="n">
-        <v>2.53145768501934</v>
+        <v>2.531457685019364</v>
       </c>
       <c r="H3" t="n">
-        <v>2.096276024740953</v>
+        <v>2.096276024740959</v>
       </c>
       <c r="I3" t="n">
-        <v>2.396164167418507</v>
+        <v>2.396164167418521</v>
       </c>
       <c r="J3" t="n">
-        <v>2.22192751409542</v>
+        <v>2.221927514095499</v>
       </c>
       <c r="K3" t="n">
-        <v>2.877961809952951</v>
+        <v>2.877961809953029</v>
       </c>
       <c r="L3" t="n">
-        <v>2.683339784820585</v>
+        <v>2.683339784820592</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.32460227814599</v>
+        <v>1.324602278145908</v>
       </c>
       <c r="C4" t="n">
-        <v>1.155368637418115</v>
+        <v>1.155368637418123</v>
       </c>
       <c r="D4" t="n">
-        <v>2.814738047910189</v>
+        <v>2.814738047910228</v>
       </c>
       <c r="E4" t="n">
-        <v>1.998295180520536</v>
+        <v>1.998295180520531</v>
       </c>
       <c r="F4" t="n">
-        <v>1.998295180520538</v>
+        <v>1.99829518052053</v>
       </c>
       <c r="G4" t="n">
-        <v>2.173960208675793</v>
+        <v>2.173960208675788</v>
       </c>
       <c r="H4" t="n">
-        <v>1.486727809855513</v>
+        <v>1.486727809855425</v>
       </c>
       <c r="I4" t="n">
-        <v>1.955384882234536</v>
+        <v>1.955384882234545</v>
       </c>
       <c r="J4" t="n">
-        <v>1.317845038008809</v>
+        <v>1.317845038008937</v>
       </c>
       <c r="K4" t="n">
-        <v>2.361479400530393</v>
+        <v>2.361479400530397</v>
       </c>
       <c r="L4" t="n">
-        <v>2.408114624722344</v>
+        <v>2.408114624722371</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.154543853745926</v>
+        <v>4.154543853745832</v>
       </c>
       <c r="C5" t="n">
-        <v>2.775381738385766</v>
+        <v>2.775381738385791</v>
       </c>
       <c r="D5" t="n">
-        <v>29.24940054521898</v>
+        <v>29.24940054521891</v>
       </c>
       <c r="E5" t="n">
-        <v>14.87001224408493</v>
+        <v>14.87001224408497</v>
       </c>
       <c r="F5" t="n">
-        <v>14.87001224408493</v>
+        <v>14.87001224408497</v>
       </c>
       <c r="G5" t="n">
-        <v>18.86376162394719</v>
+        <v>18.86376162394718</v>
       </c>
       <c r="H5" t="n">
-        <v>7.356772689290605</v>
+        <v>7.356772689290765</v>
       </c>
       <c r="I5" t="n">
-        <v>14.86994849806581</v>
+        <v>14.86994849806584</v>
       </c>
       <c r="J5" t="n">
-        <v>3.932542106404494</v>
+        <v>3.932542106404683</v>
       </c>
       <c r="K5" t="n">
-        <v>21.62559058695332</v>
+        <v>21.62559058695334</v>
       </c>
       <c r="L5" t="n">
-        <v>25.44785751673864</v>
+        <v>25.44785751673867</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.658809398744791</v>
+        <v>1.658809398744888</v>
       </c>
       <c r="C6" t="n">
-        <v>1.550772959517152</v>
+        <v>1.55077295951717</v>
       </c>
       <c r="D6" t="n">
-        <v>3.165996968110802</v>
+        <v>3.165996968110798</v>
       </c>
       <c r="E6" t="n">
-        <v>2.280525053867934</v>
+        <v>2.280525053867946</v>
       </c>
       <c r="F6" t="n">
-        <v>2.299424618020414</v>
+        <v>2.299424618020431</v>
       </c>
       <c r="G6" t="n">
-        <v>4.311420104346106</v>
+        <v>4.311420104346152</v>
       </c>
       <c r="H6" t="n">
-        <v>4.110312331285845</v>
+        <v>4.110312331285896</v>
       </c>
       <c r="I6" t="n">
-        <v>4.092844777904886</v>
+        <v>4.092844777904909</v>
       </c>
       <c r="J6" t="n">
-        <v>3.511099485503396</v>
+        <v>3.511099485503346</v>
       </c>
       <c r="K6" t="n">
-        <v>2.687338989261427</v>
+        <v>2.687338989261438</v>
       </c>
       <c r="L6" t="n">
-        <v>2.746038045847419</v>
+        <v>2.746038045847433</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.941292062095784</v>
+        <v>1.941292062095821</v>
       </c>
       <c r="C7" t="n">
-        <v>1.871532085323154</v>
+        <v>1.871532085323162</v>
       </c>
       <c r="D7" t="n">
-        <v>3.431426074558253</v>
+        <v>3.431426074558386</v>
       </c>
       <c r="E7" t="n">
-        <v>2.603839429013044</v>
+        <v>2.60383942901306</v>
       </c>
       <c r="F7" t="n">
-        <v>2.603839429013044</v>
+        <v>2.60383942901306</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7906499926257</v>
+        <v>2.790649992625705</v>
       </c>
       <c r="H7" t="n">
-        <v>2.10341759380537</v>
+        <v>2.103417593805341</v>
       </c>
       <c r="I7" t="n">
-        <v>2.572074666184437</v>
+        <v>2.572074666184459</v>
       </c>
       <c r="J7" t="n">
-        <v>1.934534821958934</v>
+        <v>1.934534821958855</v>
       </c>
       <c r="K7" t="n">
-        <v>2.978169184480296</v>
+        <v>2.978169184480315</v>
       </c>
       <c r="L7" t="n">
-        <v>3.024804408672363</v>
+        <v>3.024804408672291</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.529020313152333</v>
+        <v>3.529020313152254</v>
       </c>
       <c r="C8" t="n">
-        <v>4.965002043603786</v>
+        <v>4.965002043603832</v>
       </c>
       <c r="D8" t="n">
-        <v>6.800180551658726</v>
+        <v>6.80018055165885</v>
       </c>
       <c r="E8" t="n">
-        <v>5.258930161393699</v>
+        <v>5.258930161393736</v>
       </c>
       <c r="F8" t="n">
-        <v>4.225538687861365</v>
+        <v>4.225538687861391</v>
       </c>
       <c r="G8" t="n">
-        <v>5.85352203722116</v>
+        <v>5.853522037221191</v>
       </c>
       <c r="H8" t="n">
-        <v>5.166289638399793</v>
+        <v>5.166289638399784</v>
       </c>
       <c r="I8" t="n">
-        <v>5.634946710779937</v>
+        <v>5.634946710779946</v>
       </c>
       <c r="J8" t="n">
-        <v>4.997696773571329</v>
+        <v>4.997696773571298</v>
       </c>
       <c r="K8" t="n">
-        <v>4.538495882275407</v>
+        <v>4.538495882275432</v>
       </c>
       <c r="L8" t="n">
-        <v>7.628587494266781</v>
+        <v>7.628587494266815</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.82351757743913</v>
+        <v>79.82351757743905</v>
       </c>
       <c r="C9" t="n">
-        <v>101.4954490601436</v>
+        <v>101.4954490601437</v>
       </c>
       <c r="D9" t="n">
         <v>103.0553454750924</v>
       </c>
       <c r="E9" t="n">
-        <v>127.2855070141484</v>
+        <v>127.2855070141485</v>
       </c>
       <c r="F9" t="n">
         <v>102.1960554486167</v>
       </c>
       <c r="G9" t="n">
-        <v>102.4145669674462</v>
+        <v>102.4145669674463</v>
       </c>
       <c r="H9" t="n">
-        <v>101.727334568626</v>
+        <v>101.7273345686259</v>
       </c>
       <c r="I9" t="n">
-        <v>102.195991641005</v>
+        <v>102.1959916410051</v>
       </c>
       <c r="J9" t="n">
         <v>101.5584517967794</v>
       </c>
       <c r="K9" t="n">
-        <v>89.49377982129151</v>
+        <v>89.4937798212915</v>
       </c>
       <c r="L9" t="n">
-        <v>102.6487213834927</v>
+        <v>102.6487213834929</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.919561962595367</v>
+        <v>1.919561962595396</v>
       </c>
       <c r="C2" t="n">
-        <v>1.494693253459964</v>
+        <v>1.494693253459994</v>
       </c>
       <c r="D2" t="n">
-        <v>2.045339154771771</v>
+        <v>2.045339154771812</v>
       </c>
       <c r="E2" t="n">
-        <v>1.764127840126369</v>
+        <v>1.764127840126431</v>
       </c>
       <c r="F2" t="n">
-        <v>1.764157294919545</v>
+        <v>1.764157294919621</v>
       </c>
       <c r="G2" t="n">
-        <v>2.001056116578809</v>
+        <v>2.001056116578829</v>
       </c>
       <c r="H2" t="n">
-        <v>1.972442615613486</v>
+        <v>1.972442615613534</v>
       </c>
       <c r="I2" t="n">
-        <v>1.989756661838153</v>
+        <v>1.989756661838251</v>
       </c>
       <c r="J2" t="n">
-        <v>2.033514949334591</v>
+        <v>2.033514949334594</v>
       </c>
       <c r="K2" t="n">
-        <v>2.068100375731222</v>
+        <v>2.068100375731411</v>
       </c>
       <c r="L2" t="n">
-        <v>1.994554044155844</v>
+        <v>1.994554044155916</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.867640036210311</v>
+        <v>1.867640036210276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.186613150167662</v>
+        <v>1.186613150167673</v>
       </c>
       <c r="D3" t="n">
-        <v>2.763118949684575</v>
+        <v>2.763118949684546</v>
       </c>
       <c r="E3" t="n">
-        <v>1.995040976326514</v>
+        <v>1.995040976326431</v>
       </c>
       <c r="F3" t="n">
-        <v>1.995070431119664</v>
+        <v>1.995070431119635</v>
       </c>
       <c r="G3" t="n">
-        <v>2.448613720038242</v>
+        <v>2.448613720038211</v>
       </c>
       <c r="H3" t="n">
-        <v>2.253514755166607</v>
+        <v>2.253514755166658</v>
       </c>
       <c r="I3" t="n">
-        <v>2.367514944691019</v>
+        <v>2.367514944690989</v>
       </c>
       <c r="J3" t="n">
-        <v>2.215755986912038</v>
+        <v>2.215755986911988</v>
       </c>
       <c r="K3" t="n">
-        <v>2.516751135648717</v>
+        <v>2.516751135649</v>
       </c>
       <c r="L3" t="n">
-        <v>2.408853833719458</v>
+        <v>2.408853833719492</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.117417564538238</v>
+        <v>1.117417564538236</v>
       </c>
       <c r="C4" t="n">
         <v>1.028123656193835</v>
       </c>
       <c r="D4" t="n">
-        <v>2.538128810537757</v>
+        <v>2.538128810537743</v>
       </c>
       <c r="E4" t="n">
-        <v>1.938802345707343</v>
+        <v>1.938802345707373</v>
       </c>
       <c r="F4" t="n">
-        <v>1.938802345707343</v>
+        <v>1.938802345707372</v>
       </c>
       <c r="G4" t="n">
-        <v>2.037006324069667</v>
+        <v>2.037006324069666</v>
       </c>
       <c r="H4" t="n">
-        <v>1.727620062632724</v>
+        <v>1.727620062632711</v>
       </c>
       <c r="I4" t="n">
-        <v>1.90445648708129</v>
+        <v>1.904456487081312</v>
       </c>
       <c r="J4" t="n">
-        <v>1.447238113840777</v>
+        <v>1.447238113840765</v>
       </c>
       <c r="K4" t="n">
-        <v>1.951715037977193</v>
+        <v>1.951715037977183</v>
       </c>
       <c r="L4" t="n">
-        <v>1.970442406413296</v>
+        <v>1.970442406413277</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.671848894221186</v>
+        <v>1.671848894221181</v>
       </c>
       <c r="C5" t="n">
-        <v>2.201799355062678</v>
+        <v>2.201799355062724</v>
       </c>
       <c r="D5" t="n">
-        <v>26.91836090958265</v>
+        <v>26.9183609095826</v>
       </c>
       <c r="E5" t="n">
-        <v>15.82102819341451</v>
+        <v>15.82102819341501</v>
       </c>
       <c r="F5" t="n">
-        <v>15.82102819341451</v>
+        <v>15.82102819341501</v>
       </c>
       <c r="G5" t="n">
-        <v>18.45045800610877</v>
+        <v>18.45045800610881</v>
       </c>
       <c r="H5" t="n">
-        <v>13.83029837622964</v>
+        <v>13.83029837622968</v>
       </c>
       <c r="I5" t="n">
-        <v>15.82097665989361</v>
+        <v>15.82097665989392</v>
       </c>
       <c r="J5" t="n">
-        <v>7.712141540403909</v>
+        <v>7.712141540403922</v>
       </c>
       <c r="K5" t="n">
-        <v>16.48799724004226</v>
+        <v>16.4879972400423</v>
       </c>
       <c r="L5" t="n">
-        <v>19.06082554437486</v>
+        <v>19.06082554437488</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.446514514614829</v>
+        <v>1.446514514614886</v>
       </c>
       <c r="C6" t="n">
-        <v>1.441516939793473</v>
+        <v>1.441516939793374</v>
       </c>
       <c r="D6" t="n">
-        <v>2.881963172557008</v>
+        <v>2.881963172557005</v>
       </c>
       <c r="E6" t="n">
-        <v>2.229119377418824</v>
+        <v>2.22911937741886</v>
       </c>
       <c r="F6" t="n">
-        <v>2.243987164975408</v>
+        <v>2.243987164975447</v>
       </c>
       <c r="G6" t="n">
-        <v>2.366103274146258</v>
+        <v>2.366103274146257</v>
       </c>
       <c r="H6" t="n">
-        <v>4.434065470391567</v>
+        <v>4.434065470391579</v>
       </c>
       <c r="I6" t="n">
-        <v>4.086746581466985</v>
+        <v>4.086746581467067</v>
       </c>
       <c r="J6" t="n">
-        <v>1.797254131087179</v>
+        <v>1.7972541310872</v>
       </c>
       <c r="K6" t="n">
-        <v>2.267342956288998</v>
+        <v>2.267342956289022</v>
       </c>
       <c r="L6" t="n">
-        <v>2.303710958284966</v>
+        <v>2.303710958284984</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.752887345456005</v>
+        <v>1.752887345456014</v>
       </c>
       <c r="C7" t="n">
-        <v>1.790664115749326</v>
+        <v>1.790664115749338</v>
       </c>
       <c r="D7" t="n">
-        <v>3.17359995559531</v>
+        <v>3.173599955595326</v>
       </c>
       <c r="E7" t="n">
-        <v>2.568432180675247</v>
+        <v>2.568432180675273</v>
       </c>
       <c r="F7" t="n">
-        <v>2.568432180675247</v>
+        <v>2.568432180675273</v>
       </c>
       <c r="G7" t="n">
-        <v>2.672476104987434</v>
+        <v>2.67247610498748</v>
       </c>
       <c r="H7" t="n">
-        <v>2.363089843550493</v>
+        <v>2.363089843550544</v>
       </c>
       <c r="I7" t="n">
-        <v>2.539926267999066</v>
+        <v>2.539926267999099</v>
       </c>
       <c r="J7" t="n">
-        <v>2.082707894758545</v>
+        <v>2.082707894758569</v>
       </c>
       <c r="K7" t="n">
-        <v>2.587184818894965</v>
+        <v>2.587184818894981</v>
       </c>
       <c r="L7" t="n">
-        <v>2.605912187331062</v>
+        <v>2.605912187331076</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.406674210047139</v>
+        <v>3.40667421004715</v>
       </c>
       <c r="C8" t="n">
-        <v>4.981501508125223</v>
+        <v>4.981501508125279</v>
       </c>
       <c r="D8" t="n">
-        <v>6.649967636289114</v>
+        <v>6.649967636289152</v>
       </c>
       <c r="E8" t="n">
-        <v>5.315063147084988</v>
+        <v>5.315063147084998</v>
       </c>
       <c r="F8" t="n">
-        <v>4.258589125296344</v>
+        <v>4.258589125296405</v>
       </c>
       <c r="G8" t="n">
-        <v>5.835827177438372</v>
+        <v>5.835827177438389</v>
       </c>
       <c r="H8" t="n">
-        <v>5.526440916000555</v>
+        <v>5.526440916000571</v>
       </c>
       <c r="I8" t="n">
-        <v>5.703277340450012</v>
+        <v>5.703277340450007</v>
       </c>
       <c r="J8" t="n">
-        <v>5.246355639431712</v>
+        <v>5.246355639431766</v>
       </c>
       <c r="K8" t="n">
-        <v>4.21293075330344</v>
+        <v>4.212930753303466</v>
       </c>
       <c r="L8" t="n">
-        <v>7.346129302303161</v>
+        <v>7.346129302303241</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.18399534640604</v>
+        <v>84.18399534640614</v>
       </c>
       <c r="C9" t="n">
-        <v>107.2181929647689</v>
+        <v>107.218192964769</v>
       </c>
       <c r="D9" t="n">
-        <v>108.6011280280001</v>
+        <v>108.6011280280002</v>
       </c>
       <c r="E9" t="n">
-        <v>134.5048892526721</v>
+        <v>134.5048892526722</v>
       </c>
       <c r="F9" t="n">
-        <v>107.9675066627352</v>
+        <v>107.9675066627353</v>
       </c>
       <c r="G9" t="n">
         <v>108.1000049540071</v>
       </c>
       <c r="H9" t="n">
-        <v>107.79061869257</v>
+        <v>107.7906186925701</v>
       </c>
       <c r="I9" t="n">
         <v>107.9674551170186</v>
       </c>
       <c r="J9" t="n">
-        <v>107.5102367437784</v>
+        <v>107.5102367437785</v>
       </c>
       <c r="K9" t="n">
-        <v>94.69049736173754</v>
+        <v>94.69049736173763</v>
       </c>
       <c r="L9" t="n">
-        <v>108.0334410363506</v>
+        <v>108.0334410363508</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.04069478697947</v>
+        <v>2.040694786979469</v>
       </c>
       <c r="C2" t="n">
-        <v>1.581517577693152</v>
+        <v>1.58151757769314</v>
       </c>
       <c r="D2" t="n">
-        <v>2.165774514490114</v>
+        <v>2.165774514490094</v>
       </c>
       <c r="E2" t="n">
         <v>1.87355422285623</v>
       </c>
       <c r="F2" t="n">
-        <v>1.873584819784228</v>
+        <v>1.873584819784219</v>
       </c>
       <c r="G2" t="n">
-        <v>2.11160984983024</v>
+        <v>2.111609849830232</v>
       </c>
       <c r="H2" t="n">
-        <v>2.029297574151531</v>
+        <v>2.029297574151526</v>
       </c>
       <c r="I2" t="n">
-        <v>2.089712685454777</v>
+        <v>2.089712685454771</v>
       </c>
       <c r="J2" t="n">
-        <v>2.149608066087261</v>
+        <v>2.149608066087242</v>
       </c>
       <c r="K2" t="n">
-        <v>2.247481203462237</v>
+        <v>2.247481203462238</v>
       </c>
       <c r="L2" t="n">
-        <v>2.129797306032992</v>
+        <v>2.129797306032984</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.147632073482424</v>
+        <v>2.147632073482407</v>
       </c>
       <c r="C3" t="n">
-        <v>1.271138146798536</v>
+        <v>1.271138146798527</v>
       </c>
       <c r="D3" t="n">
-        <v>3.037822524715679</v>
+        <v>3.03782252471567</v>
       </c>
       <c r="E3" t="n">
-        <v>2.139544961840199</v>
+        <v>2.13954496184018</v>
       </c>
       <c r="F3" t="n">
-        <v>2.139575558768195</v>
+        <v>2.139575558768178</v>
       </c>
       <c r="G3" t="n">
         <v>2.653127052384626</v>
       </c>
       <c r="H3" t="n">
-        <v>2.07840437726986</v>
+        <v>2.07840437726985</v>
       </c>
       <c r="I3" t="n">
-        <v>2.496389519928893</v>
+        <v>2.496389519928874</v>
       </c>
       <c r="J3" t="n">
-        <v>2.289079340448711</v>
+        <v>2.289079340448702</v>
       </c>
       <c r="K3" t="n">
-        <v>2.934921549791764</v>
+        <v>2.934921549791754</v>
       </c>
       <c r="L3" t="n">
-        <v>2.78976732534479</v>
+        <v>2.789767325344777</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.507905842299223</v>
+        <v>1.507905842299185</v>
       </c>
       <c r="C4" t="n">
-        <v>1.136520743110266</v>
+        <v>1.136520743110261</v>
       </c>
       <c r="D4" t="n">
-        <v>2.920738904049278</v>
+        <v>2.920738904049251</v>
       </c>
       <c r="E4" t="n">
-        <v>2.111542064756827</v>
+        <v>2.111542064756822</v>
       </c>
       <c r="F4" t="n">
-        <v>2.111542064756827</v>
+        <v>2.111542064756814</v>
       </c>
       <c r="G4" t="n">
-        <v>2.307923474670406</v>
+        <v>2.307923474670401</v>
       </c>
       <c r="H4" t="n">
-        <v>1.400645455971329</v>
+        <v>1.400645455971307</v>
       </c>
       <c r="I4" t="n">
-        <v>2.055247034705883</v>
+        <v>2.055247034705884</v>
       </c>
       <c r="J4" t="n">
-        <v>1.429204138670766</v>
+        <v>1.429204138670755</v>
       </c>
       <c r="K4" t="n">
-        <v>2.429525351683122</v>
+        <v>2.429525351683102</v>
       </c>
       <c r="L4" t="n">
-        <v>2.517442523588651</v>
+        <v>2.517442523588649</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.283039942954857</v>
+        <v>7.283039942954851</v>
       </c>
       <c r="C5" t="n">
-        <v>2.764749806435064</v>
+        <v>2.764749806435032</v>
       </c>
       <c r="D5" t="n">
-        <v>30.97068397229365</v>
+        <v>30.97068397229361</v>
       </c>
       <c r="E5" t="n">
-        <v>16.50686336096342</v>
+        <v>16.50686336096345</v>
       </c>
       <c r="F5" t="n">
-        <v>16.50686336096342</v>
+        <v>16.50686336096345</v>
       </c>
       <c r="G5" t="n">
-        <v>21.12321914447728</v>
+        <v>21.12321914447724</v>
       </c>
       <c r="H5" t="n">
-        <v>5.617212789020811</v>
+        <v>5.617212789020784</v>
       </c>
       <c r="I5" t="n">
-        <v>16.50678425585633</v>
+        <v>16.50678425585631</v>
       </c>
       <c r="J5" t="n">
-        <v>5.835364499551337</v>
+        <v>5.835364499551345</v>
       </c>
       <c r="K5" t="n">
         <v>22.7059635433207</v>
       </c>
       <c r="L5" t="n">
-        <v>27.48655066236026</v>
+        <v>27.48655066236017</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.84940340297582</v>
+        <v>1.849403402975793</v>
       </c>
       <c r="C6" t="n">
-        <v>1.553890467704712</v>
+        <v>1.553890467704699</v>
       </c>
       <c r="D6" t="n">
-        <v>5.126973276078086</v>
+        <v>5.126973276078131</v>
       </c>
       <c r="E6" t="n">
-        <v>2.387702915893747</v>
+        <v>2.387702915893741</v>
       </c>
       <c r="F6" t="n">
-        <v>2.406703719344311</v>
+        <v>2.406703719344306</v>
       </c>
       <c r="G6" t="n">
-        <v>2.649421035347007</v>
+        <v>2.649421035346999</v>
       </c>
       <c r="H6" t="n">
-        <v>4.037995561856617</v>
+        <v>4.03799556185661</v>
       </c>
       <c r="I6" t="n">
-        <v>4.200706316821976</v>
+        <v>4.200706316821949</v>
       </c>
       <c r="J6" t="n">
-        <v>3.631922528966369</v>
+        <v>3.631922528966347</v>
       </c>
       <c r="K6" t="n">
-        <v>2.764576434249932</v>
+        <v>2.764576434249906</v>
       </c>
       <c r="L6" t="n">
-        <v>2.86269198208333</v>
+        <v>2.862691982083323</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.133678099263868</v>
+        <v>2.133678099263857</v>
       </c>
       <c r="C7" t="n">
-        <v>1.884751704338143</v>
+        <v>1.884751704338124</v>
       </c>
       <c r="D7" t="n">
-        <v>3.546512349958814</v>
+        <v>3.546512349958804</v>
       </c>
       <c r="E7" t="n">
-        <v>2.71576958625843</v>
+        <v>2.715769586258422</v>
       </c>
       <c r="F7" t="n">
-        <v>2.71576958625843</v>
+        <v>2.715769586258422</v>
       </c>
       <c r="G7" t="n">
-        <v>2.933695731635065</v>
+        <v>2.933695731635038</v>
       </c>
       <c r="H7" t="n">
-        <v>2.026417712935979</v>
+        <v>2.026417712935975</v>
       </c>
       <c r="I7" t="n">
-        <v>2.681019291670542</v>
+        <v>2.681019291670526</v>
       </c>
       <c r="J7" t="n">
-        <v>2.054976395635417</v>
+        <v>2.054976395635409</v>
       </c>
       <c r="K7" t="n">
-        <v>3.055297608647776</v>
+        <v>3.055297608647766</v>
       </c>
       <c r="L7" t="n">
-        <v>3.143214780553303</v>
+        <v>3.143214780553281</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.73176049681684</v>
+        <v>3.731760496816822</v>
       </c>
       <c r="C8" t="n">
-        <v>5.001214787507017</v>
+        <v>5.001214787507036</v>
       </c>
       <c r="D8" t="n">
-        <v>6.937461409944184</v>
+        <v>6.937461409944132</v>
       </c>
       <c r="E8" t="n">
-        <v>5.387908910995786</v>
+        <v>5.387908910995757</v>
       </c>
       <c r="F8" t="n">
-        <v>4.346933854650473</v>
+        <v>4.346933854650494</v>
       </c>
       <c r="G8" t="n">
-        <v>6.016731272727076</v>
+        <v>6.016731272727029</v>
       </c>
       <c r="H8" t="n">
-        <v>5.109453254024685</v>
+        <v>5.109453254024692</v>
       </c>
       <c r="I8" t="n">
-        <v>5.764054832762557</v>
+        <v>5.764054832762602</v>
       </c>
       <c r="J8" t="n">
-        <v>5.1383037717353</v>
+        <v>5.138303771735301</v>
       </c>
       <c r="K8" t="n">
-        <v>4.625796239195459</v>
+        <v>4.625796239195416</v>
       </c>
       <c r="L8" t="n">
-        <v>7.777408049146159</v>
+        <v>7.777408049146079</v>
       </c>
     </row>
     <row r="9">
@@ -3177,16 +3177,16 @@
         <v>101.695172831694</v>
       </c>
       <c r="D9" t="n">
-        <v>103.3569330526894</v>
+        <v>103.3569330526893</v>
       </c>
       <c r="E9" t="n">
         <v>127.628868290314</v>
       </c>
       <c r="F9" t="n">
-        <v>102.4915196343953</v>
+        <v>102.4915196343952</v>
       </c>
       <c r="G9" t="n">
-        <v>102.7441168589909</v>
+        <v>102.7441168589908</v>
       </c>
       <c r="H9" t="n">
         <v>101.8368388402917</v>
@@ -3198,7 +3198,7 @@
         <v>101.865397522991</v>
       </c>
       <c r="K9" t="n">
-        <v>90.24444892654664</v>
+        <v>90.24444892654662</v>
       </c>
       <c r="L9" t="n">
         <v>102.953635907909</v>
@@ -3287,34 +3287,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.142958888695045</v>
+        <v>2.142958888695038</v>
       </c>
       <c r="C2" t="n">
-        <v>1.681956317098958</v>
+        <v>1.681956317098955</v>
       </c>
       <c r="D2" t="n">
-        <v>2.259388732483314</v>
+        <v>2.259388732483307</v>
       </c>
       <c r="E2" t="n">
         <v>1.980406555735123</v>
       </c>
       <c r="F2" t="n">
-        <v>1.980439703579328</v>
+        <v>1.980439703579326</v>
       </c>
       <c r="G2" t="n">
-        <v>2.212339897306332</v>
+        <v>2.212339897306328</v>
       </c>
       <c r="H2" t="n">
-        <v>2.120226104009111</v>
+        <v>2.12022610400911</v>
       </c>
       <c r="I2" t="n">
-        <v>2.175540507744903</v>
+        <v>2.175540507744898</v>
       </c>
       <c r="J2" t="n">
-        <v>2.30341105828705</v>
+        <v>2.303411058287044</v>
       </c>
       <c r="K2" t="n">
-        <v>2.385059117820312</v>
+        <v>2.385059117820308</v>
       </c>
       <c r="L2" t="n">
         <v>2.240418590026839</v>
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.311614151660407</v>
+        <v>2.311614151660401</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3683333757628</v>
+        <v>1.368333375762798</v>
       </c>
       <c r="D3" t="n">
-        <v>3.140048283792935</v>
+        <v>3.140048283792928</v>
       </c>
       <c r="E3" t="n">
-        <v>2.22102125804017</v>
+        <v>2.22102125804016</v>
       </c>
       <c r="F3" t="n">
-        <v>2.221054405884378</v>
+        <v>2.221054405884382</v>
       </c>
       <c r="G3" t="n">
         <v>2.80616249012456</v>
       </c>
       <c r="H3" t="n">
-        <v>2.163252007320234</v>
+        <v>2.163252007320231</v>
       </c>
       <c r="I3" t="n">
-        <v>2.543151244373677</v>
+        <v>2.543151244373675</v>
       </c>
       <c r="J3" t="n">
-        <v>2.461517916591307</v>
+        <v>2.461517916591301</v>
       </c>
       <c r="K3" t="n">
-        <v>3.125265273481516</v>
+        <v>3.125265273481522</v>
       </c>
       <c r="L3" t="n">
-        <v>3.014017422875131</v>
+        <v>3.014017422875128</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.747170824169849</v>
+        <v>1.747170824169767</v>
       </c>
       <c r="C4" t="n">
-        <v>1.215583709821896</v>
+        <v>1.215583709821878</v>
       </c>
       <c r="D4" t="n">
-        <v>3.062299470132635</v>
+        <v>3.062299470132571</v>
       </c>
       <c r="E4" t="n">
-        <v>2.140199371279196</v>
+        <v>2.140199371279165</v>
       </c>
       <c r="F4" t="n">
-        <v>2.140199371279195</v>
+        <v>2.140199371279174</v>
       </c>
       <c r="G4" t="n">
-        <v>2.529770261263925</v>
+        <v>2.529770261263765</v>
       </c>
       <c r="H4" t="n">
-        <v>1.514853182260052</v>
+        <v>1.514853182260113</v>
       </c>
       <c r="I4" t="n">
-        <v>2.108316175669285</v>
+        <v>2.108316175669291</v>
       </c>
       <c r="J4" t="n">
-        <v>1.510608924822334</v>
+        <v>1.51060892482228</v>
       </c>
       <c r="K4" t="n">
-        <v>2.603159410154907</v>
+        <v>2.603159410154902</v>
       </c>
       <c r="L4" t="n">
-        <v>2.850523882553603</v>
+        <v>2.850523882553654</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10.06884542717154</v>
+        <v>10.0688454271715</v>
       </c>
       <c r="C5" t="n">
-        <v>3.240426647614294</v>
+        <v>3.240426647614285</v>
       </c>
       <c r="D5" t="n">
         <v>32.0171968700262</v>
       </c>
       <c r="E5" t="n">
-        <v>16.0532280680224</v>
+        <v>16.05322806802223</v>
       </c>
       <c r="F5" t="n">
-        <v>16.0532280680224</v>
+        <v>16.05322806802223</v>
       </c>
       <c r="G5" t="n">
-        <v>23.60348936881753</v>
+        <v>23.6034893688175</v>
       </c>
       <c r="H5" t="n">
-        <v>6.267476456677367</v>
+        <v>6.267476456677332</v>
       </c>
       <c r="I5" t="n">
-        <v>16.05309501771544</v>
+        <v>16.05309501771525</v>
       </c>
       <c r="J5" t="n">
-        <v>5.858733742771178</v>
+        <v>5.858733742771176</v>
       </c>
       <c r="K5" t="n">
-        <v>24.30382947871693</v>
+        <v>24.30382947871695</v>
       </c>
       <c r="L5" t="n">
-        <v>32.41801719549652</v>
+        <v>32.4180171954965</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.020245446363542</v>
+        <v>4.020245446363568</v>
       </c>
       <c r="C6" t="n">
-        <v>1.705986062195034</v>
+        <v>1.705986062195026</v>
       </c>
       <c r="D6" t="n">
-        <v>3.469818044776952</v>
+        <v>3.469818044777028</v>
       </c>
       <c r="E6" t="n">
-        <v>2.477650185492671</v>
+        <v>2.477650185492656</v>
       </c>
       <c r="F6" t="n">
-        <v>2.510094807992902</v>
+        <v>2.510094807992886</v>
       </c>
       <c r="G6" t="n">
-        <v>4.802844883457505</v>
+        <v>4.802844883457572</v>
       </c>
       <c r="H6" t="n">
-        <v>1.904969112871789</v>
+        <v>1.904969112871757</v>
       </c>
       <c r="I6" t="n">
-        <v>4.381390797863129</v>
+        <v>4.381390797863093</v>
       </c>
       <c r="J6" t="n">
-        <v>1.927396154394219</v>
+        <v>1.927396154394166</v>
       </c>
       <c r="K6" t="n">
-        <v>2.993261082985886</v>
+        <v>2.993261082985883</v>
       </c>
       <c r="L6" t="n">
-        <v>3.248382243491263</v>
+        <v>3.248382243491296</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.402173197892723</v>
+        <v>2.402173197892716</v>
       </c>
       <c r="C7" t="n">
-        <v>2.021078351604566</v>
+        <v>2.021078351604553</v>
       </c>
       <c r="D7" t="n">
-        <v>3.717309455577059</v>
+        <v>3.717309455577084</v>
       </c>
       <c r="E7" t="n">
-        <v>2.792749473281801</v>
+        <v>2.79274947328179</v>
       </c>
       <c r="F7" t="n">
-        <v>2.792749473281801</v>
+        <v>2.792749473281787</v>
       </c>
       <c r="G7" t="n">
-        <v>3.184772634986723</v>
+        <v>3.18477263498671</v>
       </c>
       <c r="H7" t="n">
-        <v>2.169855555983009</v>
+        <v>2.169855555983067</v>
       </c>
       <c r="I7" t="n">
-        <v>2.763318549392265</v>
+        <v>2.763318549392245</v>
       </c>
       <c r="J7" t="n">
-        <v>2.165611298545238</v>
+        <v>2.165611298545232</v>
       </c>
       <c r="K7" t="n">
-        <v>3.258161783877789</v>
+        <v>3.258161783877854</v>
       </c>
       <c r="L7" t="n">
-        <v>3.505526256276564</v>
+        <v>3.505526256276611</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.035710162743844</v>
+        <v>4.035710162743883</v>
       </c>
       <c r="C8" t="n">
-        <v>5.241370567029243</v>
+        <v>5.241370567029204</v>
       </c>
       <c r="D8" t="n">
-        <v>7.232448585374788</v>
+        <v>7.232448585374816</v>
       </c>
       <c r="E8" t="n">
-        <v>5.554530290267392</v>
+        <v>5.554530290267374</v>
       </c>
       <c r="F8" t="n">
-        <v>4.46386221869341</v>
+        <v>4.463862218693393</v>
       </c>
       <c r="G8" t="n">
-        <v>6.376763755123005</v>
+        <v>6.376763755123016</v>
       </c>
       <c r="H8" t="n">
-        <v>5.361846676114507</v>
+        <v>5.361846676114479</v>
       </c>
       <c r="I8" t="n">
-        <v>5.955309669528586</v>
+        <v>5.955309669528559</v>
       </c>
       <c r="J8" t="n">
-        <v>5.357908697924035</v>
+        <v>5.357908697924065</v>
       </c>
       <c r="K8" t="n">
-        <v>4.862749662773676</v>
+        <v>4.862749662773731</v>
       </c>
       <c r="L8" t="n">
-        <v>8.325453055966239</v>
+        <v>8.325453055966291</v>
       </c>
     </row>
     <row r="9">
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.35793551547111</v>
+        <v>80.35793551547107</v>
       </c>
       <c r="C9" t="n">
-        <v>101.7624613952998</v>
+        <v>101.7624613952997</v>
       </c>
       <c r="D9" t="n">
-        <v>103.4586857642006</v>
+        <v>103.4586857642007</v>
       </c>
       <c r="E9" t="n">
-        <v>127.6449799569556</v>
+        <v>127.6449799569557</v>
       </c>
       <c r="F9" t="n">
         <v>102.5048347497411</v>
@@ -3594,10 +3594,10 @@
         <v>101.9069943422404</v>
       </c>
       <c r="K9" t="n">
-        <v>90.37687098883958</v>
+        <v>90.37687098883957</v>
       </c>
       <c r="L9" t="n">
-        <v>103.2469092999717</v>
+        <v>103.2469092999718</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.009175704834395</v>
+        <v>2.009175704835178</v>
       </c>
       <c r="C2" t="n">
-        <v>1.558594237844284</v>
+        <v>1.558594237845053</v>
       </c>
       <c r="D2" t="n">
-        <v>2.129377183808915</v>
+        <v>2.129377183808736</v>
       </c>
       <c r="E2" t="n">
-        <v>1.849257714759266</v>
+        <v>1.849257714760429</v>
       </c>
       <c r="F2" t="n">
-        <v>1.84928753407067</v>
+        <v>1.849287534071622</v>
       </c>
       <c r="G2" t="n">
-        <v>2.088518041022148</v>
+        <v>2.088518041022037</v>
       </c>
       <c r="H2" t="n">
-        <v>2.03510369374084</v>
+        <v>2.035103693741468</v>
       </c>
       <c r="I2" t="n">
-        <v>2.071769018118306</v>
+        <v>2.07176901811828</v>
       </c>
       <c r="J2" t="n">
-        <v>2.101169449555225</v>
+        <v>2.101169449555666</v>
       </c>
       <c r="K2" t="n">
-        <v>2.180448530347711</v>
+        <v>2.180448530348313</v>
       </c>
       <c r="L2" t="n">
-        <v>2.066333410197887</v>
+        <v>2.066333410197956</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.072386194003992</v>
+        <v>2.072386194004004</v>
       </c>
       <c r="C3" t="n">
-        <v>1.243310875637343</v>
+        <v>1.243310875637349</v>
       </c>
       <c r="D3" t="n">
-        <v>2.927929186876664</v>
+        <v>2.927929186876652</v>
       </c>
       <c r="E3" t="n">
-        <v>2.150610742052317</v>
+        <v>2.150610742052312</v>
       </c>
       <c r="F3" t="n">
-        <v>2.150640561363512</v>
+        <v>2.150640561363506</v>
       </c>
       <c r="G3" t="n">
-        <v>2.63800068994719</v>
+        <v>2.638000689947192</v>
       </c>
       <c r="H3" t="n">
-        <v>2.268237654527558</v>
+        <v>2.268237654527564</v>
       </c>
       <c r="I3" t="n">
-        <v>2.517943853522439</v>
+        <v>2.517943853522449</v>
       </c>
       <c r="J3" t="n">
-        <v>2.217651562918063</v>
+        <v>2.217651562918065</v>
       </c>
       <c r="K3" t="n">
-        <v>2.761475562511511</v>
+        <v>2.761475562511524</v>
       </c>
       <c r="L3" t="n">
-        <v>2.488356449965583</v>
+        <v>2.488356449965592</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.396633819100956</v>
+        <v>1.396633819100965</v>
       </c>
       <c r="C4" t="n">
-        <v>1.079197574878243</v>
+        <v>1.079197574878241</v>
       </c>
       <c r="D4" t="n">
-        <v>2.754364819519545</v>
+        <v>2.754364819519554</v>
       </c>
       <c r="E4" t="n">
-        <v>2.148667735646567</v>
+        <v>2.148667735646556</v>
       </c>
       <c r="F4" t="n">
-        <v>2.148667735646566</v>
+        <v>2.14866773564656</v>
       </c>
       <c r="G4" t="n">
-        <v>2.291900859700927</v>
+        <v>2.291900859700944</v>
       </c>
       <c r="H4" t="n">
-        <v>1.706917312547433</v>
+        <v>1.706917312547432</v>
       </c>
       <c r="I4" t="n">
-        <v>2.097688560822087</v>
+        <v>2.097688560822084</v>
       </c>
       <c r="J4" t="n">
-        <v>1.383359405768537</v>
+        <v>1.383359405768555</v>
       </c>
       <c r="K4" t="n">
-        <v>2.236393627387356</v>
+        <v>2.236393627387379</v>
       </c>
       <c r="L4" t="n">
-        <v>2.051619807400991</v>
+        <v>2.051619807401</v>
       </c>
     </row>
     <row r="5">
@@ -3803,13 +3803,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.936181379505296</v>
+        <v>5.936181379505299</v>
       </c>
       <c r="C5" t="n">
-        <v>2.446626000208407</v>
+        <v>2.446626000208416</v>
       </c>
       <c r="D5" t="n">
-        <v>29.93260421851417</v>
+        <v>29.93260421851415</v>
       </c>
       <c r="E5" t="n">
         <v>18.45077447916647</v>
@@ -3818,22 +3818,22 @@
         <v>18.45077447916647</v>
       </c>
       <c r="G5" t="n">
-        <v>22.26141600620851</v>
+        <v>22.26141600621035</v>
       </c>
       <c r="H5" t="n">
         <v>12.44608131875431</v>
       </c>
       <c r="I5" t="n">
-        <v>18.45069841986234</v>
+        <v>18.45069841986233</v>
       </c>
       <c r="J5" t="n">
-        <v>5.612683072015598</v>
+        <v>5.612683072015604</v>
       </c>
       <c r="K5" t="n">
-        <v>20.74340833750877</v>
+        <v>20.74340833750876</v>
       </c>
       <c r="L5" t="n">
-        <v>19.74179722163482</v>
+        <v>19.74179722163483</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.746436428510742</v>
+        <v>1.746436428510741</v>
       </c>
       <c r="C6" t="n">
-        <v>1.514759570891395</v>
+        <v>1.514759570891403</v>
       </c>
       <c r="D6" t="n">
-        <v>3.117340169839979</v>
+        <v>3.117340169839981</v>
       </c>
       <c r="E6" t="n">
-        <v>2.441228001773771</v>
+        <v>2.44122800177377</v>
       </c>
       <c r="F6" t="n">
-        <v>2.45832489581782</v>
+        <v>2.458324895817831</v>
       </c>
       <c r="G6" t="n">
-        <v>2.641703469110704</v>
+        <v>2.641703469110712</v>
       </c>
       <c r="H6" t="n">
-        <v>4.47278459634373</v>
+        <v>4.472784596343732</v>
       </c>
       <c r="I6" t="n">
-        <v>2.447491170231863</v>
+        <v>2.44749117023187</v>
       </c>
       <c r="J6" t="n">
-        <v>1.753558954076001</v>
+        <v>1.75355895407601</v>
       </c>
       <c r="K6" t="n">
-        <v>2.574177808426794</v>
+        <v>2.574177808426818</v>
       </c>
       <c r="L6" t="n">
-        <v>2.404117046365536</v>
+        <v>2.404117046365526</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.063140843841287</v>
+        <v>2.063140843841281</v>
       </c>
       <c r="C7" t="n">
-        <v>1.882708793525778</v>
+        <v>1.882708793525776</v>
       </c>
       <c r="D7" t="n">
-        <v>3.420875172857462</v>
+        <v>3.420875172857472</v>
       </c>
       <c r="E7" t="n">
-        <v>2.79756750257468</v>
+        <v>2.797567502574692</v>
       </c>
       <c r="F7" t="n">
-        <v>2.79756750257468</v>
+        <v>2.797567502574692</v>
       </c>
       <c r="G7" t="n">
-        <v>2.958407884441255</v>
+        <v>2.958407884441251</v>
       </c>
       <c r="H7" t="n">
-        <v>2.373424337287733</v>
+        <v>2.373424337287745</v>
       </c>
       <c r="I7" t="n">
-        <v>2.764195585562398</v>
+        <v>2.764195585562406</v>
       </c>
       <c r="J7" t="n">
-        <v>2.049866430508867</v>
+        <v>2.049866430508873</v>
       </c>
       <c r="K7" t="n">
-        <v>2.902900652127663</v>
+        <v>2.902900652127679</v>
       </c>
       <c r="L7" t="n">
-        <v>2.718126832141301</v>
+        <v>2.718126832141315</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.735310081679854</v>
+        <v>3.735310081679831</v>
       </c>
       <c r="C8" t="n">
-        <v>5.137706996172044</v>
+        <v>5.137706996172035</v>
       </c>
       <c r="D8" t="n">
-        <v>6.965302540440745</v>
+        <v>6.96530254044074</v>
       </c>
       <c r="E8" t="n">
-        <v>5.59177707301447</v>
+        <v>5.591777073014486</v>
       </c>
       <c r="F8" t="n">
-        <v>4.505456648111657</v>
+        <v>4.505456648111666</v>
       </c>
       <c r="G8" t="n">
-        <v>6.181288478903562</v>
+        <v>6.181288478903531</v>
       </c>
       <c r="H8" t="n">
-        <v>5.596304931747613</v>
+        <v>5.596304931747624</v>
       </c>
       <c r="I8" t="n">
-        <v>5.987076180024718</v>
+        <v>5.98707618002467</v>
       </c>
       <c r="J8" t="n">
-        <v>5.273051783645847</v>
+        <v>5.273051783645814</v>
       </c>
       <c r="K8" t="n">
-        <v>4.546264630376701</v>
+        <v>4.546264630376707</v>
       </c>
       <c r="L8" t="n">
-        <v>7.56085510654923</v>
+        <v>7.560855106549276</v>
       </c>
     </row>
     <row r="9">
@@ -3972,7 +3972,7 @@
         <v>108.9657259387013</v>
       </c>
       <c r="E9" t="n">
-        <v>134.8874329623252</v>
+        <v>134.8874329623253</v>
       </c>
       <c r="F9" t="n">
         <v>108.3091250722782</v>
@@ -3987,10 +3987,10 @@
         <v>108.3090489421086</v>
       </c>
       <c r="J9" t="n">
-        <v>107.594719787055</v>
+        <v>107.5947197870551</v>
       </c>
       <c r="K9" t="n">
-        <v>95.10298956119755</v>
+        <v>95.10298956119756</v>
       </c>
       <c r="L9" t="n">
         <v>108.2629801886874</v>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.324485404451763</v>
+        <v>2.324485404451725</v>
       </c>
       <c r="C2" t="n">
-        <v>1.798427838480095</v>
+        <v>1.798427838480101</v>
       </c>
       <c r="D2" t="n">
-        <v>2.39708496773736</v>
+        <v>2.397084967737328</v>
       </c>
       <c r="E2" t="n">
-        <v>2.152971531682257</v>
+        <v>2.15297153168223</v>
       </c>
       <c r="F2" t="n">
-        <v>2.153004405439015</v>
+        <v>2.153004405439005</v>
       </c>
       <c r="G2" t="n">
-        <v>2.373177692875399</v>
+        <v>2.373177692875362</v>
       </c>
       <c r="H2" t="n">
-        <v>2.260437402065861</v>
+        <v>2.260437402065873</v>
       </c>
       <c r="I2" t="n">
-        <v>2.344975305985646</v>
+        <v>2.344975305985616</v>
       </c>
       <c r="J2" t="n">
-        <v>2.464570505134691</v>
+        <v>2.464570505134674</v>
       </c>
       <c r="K2" t="n">
-        <v>2.566007469251197</v>
+        <v>2.566007469251191</v>
       </c>
       <c r="L2" t="n">
-        <v>2.36156874106114</v>
+        <v>2.36156874106115</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.744358438739562</v>
+        <v>2.744358438739545</v>
       </c>
       <c r="C3" t="n">
-        <v>1.47057454423976</v>
+        <v>1.470574544239768</v>
       </c>
       <c r="D3" t="n">
-        <v>3.260153863939713</v>
+        <v>3.260153863939699</v>
       </c>
       <c r="E3" t="n">
-        <v>2.572421761483219</v>
+        <v>2.572421761483224</v>
       </c>
       <c r="F3" t="n">
-        <v>2.572454635239987</v>
+        <v>2.572454635239991</v>
       </c>
       <c r="G3" t="n">
-        <v>3.091305989605996</v>
+        <v>3.091305989605984</v>
       </c>
       <c r="H3" t="n">
-        <v>2.303642370098916</v>
+        <v>2.303642370098921</v>
       </c>
       <c r="I3" t="n">
-        <v>2.889406460585554</v>
+        <v>2.889406460585545</v>
       </c>
       <c r="J3" t="n">
-        <v>2.722183754424604</v>
+        <v>2.722183754424595</v>
       </c>
       <c r="K3" t="n">
-        <v>3.418077837468691</v>
+        <v>3.41807783746869</v>
       </c>
       <c r="L3" t="n">
-        <v>3.019375959753951</v>
+        <v>3.019375959753955</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.332263804127045</v>
+        <v>2.332263804127052</v>
       </c>
       <c r="C4" t="n">
-        <v>1.33283444107782</v>
+        <v>1.332834441077772</v>
       </c>
       <c r="D4" t="n">
-        <v>3.152309268887081</v>
+        <v>3.152309268887099</v>
       </c>
       <c r="E4" t="n">
-        <v>2.639400508921482</v>
+        <v>2.63940050892148</v>
       </c>
       <c r="F4" t="n">
-        <v>2.639400508921484</v>
+        <v>2.639400508921481</v>
       </c>
       <c r="G4" t="n">
-        <v>2.881516130991556</v>
+        <v>2.88151613099157</v>
       </c>
       <c r="H4" t="n">
-        <v>1.637575666578102</v>
+        <v>1.637575666578115</v>
       </c>
       <c r="I4" t="n">
-        <v>2.559064902741676</v>
+        <v>2.559064902741682</v>
       </c>
       <c r="J4" t="n">
-        <v>1.810210036593373</v>
+        <v>1.810210036593391</v>
       </c>
       <c r="K4" t="n">
-        <v>2.902274043642612</v>
+        <v>2.902274043642621</v>
       </c>
       <c r="L4" t="n">
-        <v>2.761156162922878</v>
+        <v>2.761156162922895</v>
       </c>
     </row>
     <row r="5">
@@ -4202,34 +4202,34 @@
         <v>18.43439026695512</v>
       </c>
       <c r="C5" t="n">
-        <v>3.540442706393989</v>
+        <v>3.540442706393919</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71975762396753</v>
+        <v>31.71975762396758</v>
       </c>
       <c r="E5" t="n">
-        <v>21.90692967161911</v>
+        <v>21.90692967161916</v>
       </c>
       <c r="F5" t="n">
-        <v>21.90692967161911</v>
+        <v>21.90692967161916</v>
       </c>
       <c r="G5" t="n">
-        <v>27.86504088771451</v>
+        <v>27.86504088771465</v>
       </c>
       <c r="H5" t="n">
-        <v>6.546677924053694</v>
+        <v>6.546677924053756</v>
       </c>
       <c r="I5" t="n">
-        <v>21.90680711870349</v>
+        <v>21.90680711870353</v>
       </c>
       <c r="J5" t="n">
-        <v>9.282994627220129</v>
+        <v>9.282994627220168</v>
       </c>
       <c r="K5" t="n">
         <v>27.57324622316689</v>
       </c>
       <c r="L5" t="n">
-        <v>28.56369708073863</v>
+        <v>28.56369708073873</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.693104479808857</v>
+        <v>4.69310447980885</v>
       </c>
       <c r="C6" t="n">
-        <v>1.847986319798669</v>
+        <v>1.847986319798609</v>
       </c>
       <c r="D6" t="n">
-        <v>3.576318049493132</v>
+        <v>3.576318049493135</v>
       </c>
       <c r="E6" t="n">
-        <v>2.961466153310595</v>
+        <v>2.961466153310607</v>
       </c>
       <c r="F6" t="n">
-        <v>2.991331990430368</v>
+        <v>2.991331990430381</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3041578673719</v>
+        <v>3.304157867371925</v>
       </c>
       <c r="H6" t="n">
-        <v>4.493055904569099</v>
+        <v>4.493055904569144</v>
       </c>
       <c r="I6" t="n">
-        <v>4.919905578423485</v>
+        <v>4.919905578423482</v>
       </c>
       <c r="J6" t="n">
-        <v>2.256671644582392</v>
+        <v>2.256671644582389</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3189326237456</v>
+        <v>3.318932623745599</v>
       </c>
       <c r="L6" t="n">
-        <v>3.182557034710829</v>
+        <v>3.182557034710833</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.052070411086335</v>
+        <v>3.052070411086314</v>
       </c>
       <c r="C7" t="n">
-        <v>2.210630975168582</v>
+        <v>2.210630975168535</v>
       </c>
       <c r="D7" t="n">
-        <v>3.872123410434744</v>
+        <v>3.872123410434756</v>
       </c>
       <c r="E7" t="n">
-        <v>3.321216680881342</v>
+        <v>3.321216680881353</v>
       </c>
       <c r="F7" t="n">
-        <v>3.321216680881343</v>
+        <v>3.321216680881353</v>
       </c>
       <c r="G7" t="n">
-        <v>3.601322737950822</v>
+        <v>3.601322737950839</v>
       </c>
       <c r="H7" t="n">
-        <v>2.357382273537421</v>
+        <v>2.357382273537378</v>
       </c>
       <c r="I7" t="n">
-        <v>3.278871509700961</v>
+        <v>3.278871509700958</v>
       </c>
       <c r="J7" t="n">
-        <v>2.530016643552678</v>
+        <v>2.530016643552673</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6220806506019</v>
+        <v>3.622080650601903</v>
       </c>
       <c r="L7" t="n">
-        <v>3.480962769882186</v>
+        <v>3.480962769882173</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.724247168619905</v>
+        <v>4.724247168619956</v>
       </c>
       <c r="C8" t="n">
-        <v>5.562994114502457</v>
+        <v>5.56299411450246</v>
       </c>
       <c r="D8" t="n">
-        <v>7.523778426467109</v>
+        <v>7.523778426467177</v>
       </c>
       <c r="E8" t="n">
-        <v>6.178670076197256</v>
+        <v>6.178670076197341</v>
       </c>
       <c r="F8" t="n">
-        <v>5.028324436742619</v>
+        <v>5.028324436742634</v>
       </c>
       <c r="G8" t="n">
-        <v>6.913020026150298</v>
+        <v>6.913020026150324</v>
       </c>
       <c r="H8" t="n">
-        <v>5.66907956172442</v>
+        <v>5.669079561724494</v>
       </c>
       <c r="I8" t="n">
-        <v>6.59056879790041</v>
+        <v>6.590568797900446</v>
       </c>
       <c r="J8" t="n">
-        <v>5.842036142819273</v>
+        <v>5.84203614281941</v>
       </c>
       <c r="K8" t="n">
-        <v>5.263802472569955</v>
+        <v>5.263802472569965</v>
       </c>
       <c r="L8" t="n">
-        <v>8.505276345405342</v>
+        <v>8.505276345405452</v>
       </c>
     </row>
     <row r="9">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.20963947266898</v>
+        <v>81.20963947266901</v>
       </c>
       <c r="C9" t="n">
         <v>102.2342296803132</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.453811580503018</v>
+        <v>2.453811580503015</v>
       </c>
       <c r="C2" t="n">
-        <v>1.950331742748079</v>
+        <v>1.95033174274808</v>
       </c>
       <c r="D2" t="n">
-        <v>2.54089987432641</v>
+        <v>2.5408998743264</v>
       </c>
       <c r="E2" t="n">
-        <v>2.298450213926274</v>
+        <v>2.298450213926282</v>
       </c>
       <c r="F2" t="n">
-        <v>2.298487759418436</v>
+        <v>2.298487759418435</v>
       </c>
       <c r="G2" t="n">
-        <v>2.514567015680354</v>
+        <v>2.514567015680336</v>
       </c>
       <c r="H2" t="n">
-        <v>2.407151301194206</v>
+        <v>2.407151301194207</v>
       </c>
       <c r="I2" t="n">
-        <v>2.475827953177876</v>
+        <v>2.475827953177866</v>
       </c>
       <c r="J2" t="n">
-        <v>2.72274685116534</v>
+        <v>2.722746851165342</v>
       </c>
       <c r="K2" t="n">
-        <v>2.744965049187179</v>
+        <v>2.744965049187191</v>
       </c>
       <c r="L2" t="n">
-        <v>2.523216797397982</v>
+        <v>2.523216797397985</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.749636331424294</v>
+        <v>2.749636331424295</v>
       </c>
       <c r="C3" t="n">
-        <v>1.603958597982812</v>
+        <v>1.603958597982811</v>
       </c>
       <c r="D3" t="n">
         <v>3.368803895443079</v>
       </c>
       <c r="E3" t="n">
-        <v>2.612862506258287</v>
+        <v>2.61286250625827</v>
       </c>
       <c r="F3" t="n">
-        <v>2.612900051750431</v>
+        <v>2.612900051750425</v>
       </c>
       <c r="G3" t="n">
-        <v>3.182642190705077</v>
+        <v>3.182642190705081</v>
       </c>
       <c r="H3" t="n">
-        <v>2.433456082747488</v>
+        <v>2.43345608274749</v>
       </c>
       <c r="I3" t="n">
-        <v>2.905687957412448</v>
+        <v>2.905687957412435</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05851703814486</v>
+        <v>3.058517038144861</v>
       </c>
       <c r="K3" t="n">
-        <v>3.573578481045022</v>
+        <v>3.573578481045012</v>
       </c>
       <c r="L3" t="n">
-        <v>3.254536948710795</v>
+        <v>3.254536948710796</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.294392843029729</v>
+        <v>2.294392843029699</v>
       </c>
       <c r="C4" t="n">
-        <v>1.447596892786807</v>
+        <v>1.447596892786806</v>
       </c>
       <c r="D4" t="n">
-        <v>3.278095184359378</v>
+        <v>3.27809518435934</v>
       </c>
       <c r="E4" t="n">
-        <v>2.552394597445951</v>
+        <v>2.552394597445953</v>
       </c>
       <c r="F4" t="n">
-        <v>2.552394597445951</v>
+        <v>2.552394597445953</v>
       </c>
       <c r="G4" t="n">
-        <v>2.979836558186904</v>
+        <v>2.979836558186888</v>
       </c>
       <c r="H4" t="n">
-        <v>1.796910150030731</v>
+        <v>1.796910150030719</v>
       </c>
       <c r="I4" t="n">
-        <v>2.538112931136198</v>
+        <v>2.538112931136206</v>
       </c>
       <c r="J4" t="n">
-        <v>2.016096681507721</v>
+        <v>2.016096681507674</v>
       </c>
       <c r="K4" t="n">
-        <v>3.005032800409199</v>
+        <v>3.005032800409149</v>
       </c>
       <c r="L4" t="n">
-        <v>3.08580493873637</v>
+        <v>3.085804938736324</v>
       </c>
     </row>
     <row r="5">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.37573012114525</v>
+        <v>15.37573012114522</v>
       </c>
       <c r="C5" t="n">
-        <v>3.755435876975678</v>
+        <v>3.755435876975655</v>
       </c>
       <c r="D5" t="n">
-        <v>31.53768118934816</v>
+        <v>31.53768118934818</v>
       </c>
       <c r="E5" t="n">
         <v>19.20948351732483</v>
@@ -4610,22 +4610,22 @@
         <v>19.20948351732483</v>
       </c>
       <c r="G5" t="n">
-        <v>27.19711545813644</v>
+        <v>27.19711545813654</v>
       </c>
       <c r="H5" t="n">
-        <v>6.977178593329095</v>
+        <v>6.977178593329061</v>
       </c>
       <c r="I5" t="n">
-        <v>19.2093205512726</v>
+        <v>19.20932055127258</v>
       </c>
       <c r="J5" t="n">
-        <v>10.51902488277705</v>
+        <v>10.51902488277704</v>
       </c>
       <c r="K5" t="n">
-        <v>26.99727553503199</v>
+        <v>26.99727553503202</v>
       </c>
       <c r="L5" t="n">
-        <v>32.22616442532969</v>
+        <v>32.22616442532949</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.843587973279688</v>
+        <v>4.843587973279619</v>
       </c>
       <c r="C6" t="n">
-        <v>2.064963579317471</v>
+        <v>2.064963579317455</v>
       </c>
       <c r="D6" t="n">
-        <v>3.778109550622033</v>
+        <v>3.778109550621977</v>
       </c>
       <c r="E6" t="n">
-        <v>2.98579018465833</v>
+        <v>2.985790184658332</v>
       </c>
       <c r="F6" t="n">
-        <v>3.037025861498426</v>
+        <v>3.037025861498429</v>
       </c>
       <c r="G6" t="n">
-        <v>3.473001320868691</v>
+        <v>3.473001320868636</v>
       </c>
       <c r="H6" t="n">
-        <v>4.846877934462817</v>
+        <v>4.846877934462788</v>
       </c>
       <c r="I6" t="n">
-        <v>3.031277693817951</v>
+        <v>3.031277693817952</v>
       </c>
       <c r="J6" t="n">
-        <v>4.657677944273111</v>
+        <v>4.657677944273066</v>
       </c>
       <c r="K6" t="n">
-        <v>3.495605423424457</v>
+        <v>3.495605423424388</v>
       </c>
       <c r="L6" t="n">
-        <v>3.578817177373744</v>
+        <v>3.578817177373724</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.044478392192426</v>
+        <v>3.044478392192373</v>
       </c>
       <c r="C7" t="n">
-        <v>2.389626668564078</v>
+        <v>2.389626668564126</v>
       </c>
       <c r="D7" t="n">
-        <v>4.028195817813881</v>
+        <v>4.02819581781386</v>
       </c>
       <c r="E7" t="n">
-        <v>3.31359454132119</v>
+        <v>3.313594541321193</v>
       </c>
       <c r="F7" t="n">
-        <v>3.31359454132119</v>
+        <v>3.313594541321193</v>
       </c>
       <c r="G7" t="n">
-        <v>3.729922107349589</v>
+        <v>3.72992210734956</v>
       </c>
       <c r="H7" t="n">
-        <v>2.546995699193438</v>
+        <v>2.546995699193391</v>
       </c>
       <c r="I7" t="n">
-        <v>3.288198480298876</v>
+        <v>3.288198480298879</v>
       </c>
       <c r="J7" t="n">
-        <v>2.766182230670376</v>
+        <v>2.766182230670348</v>
       </c>
       <c r="K7" t="n">
-        <v>3.755118349571882</v>
+        <v>3.755118349571821</v>
       </c>
       <c r="L7" t="n">
-        <v>3.835890487899033</v>
+        <v>3.835890487898997</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.780808524789852</v>
+        <v>4.780808524789809</v>
       </c>
       <c r="C8" t="n">
-        <v>5.909855976454936</v>
+        <v>5.909855976454955</v>
       </c>
       <c r="D8" t="n">
-        <v>7.888799836524732</v>
+        <v>7.888799836524716</v>
       </c>
       <c r="E8" t="n">
-        <v>6.324816435173627</v>
+        <v>6.324816435173634</v>
       </c>
       <c r="F8" t="n">
-        <v>5.095507342135086</v>
+        <v>5.095507342135075</v>
       </c>
       <c r="G8" t="n">
-        <v>7.225706837882294</v>
+        <v>7.225706837882288</v>
       </c>
       <c r="H8" t="n">
-        <v>6.042780429711741</v>
+        <v>6.042780429711727</v>
       </c>
       <c r="I8" t="n">
-        <v>6.783983210831594</v>
+        <v>6.783983210831595</v>
       </c>
       <c r="J8" t="n">
-        <v>6.262312741209371</v>
+        <v>6.26231274120931</v>
       </c>
       <c r="K8" t="n">
-        <v>5.458765709867918</v>
+        <v>5.458765709867865</v>
       </c>
       <c r="L8" t="n">
-        <v>9.169572666292593</v>
+        <v>9.169572666292535</v>
       </c>
     </row>
     <row r="9">
@@ -4782,7 +4782,7 @@
         <v>102.6471635038326</v>
       </c>
       <c r="K9" t="n">
-        <v>90.45518149314476</v>
+        <v>90.45518149314474</v>
       </c>
       <c r="L9" t="n">
         <v>103.7168717610613</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.186412480120625</v>
+        <v>2.186412480120591</v>
       </c>
       <c r="C2" t="n">
-        <v>2.056321765943951</v>
+        <v>2.056321765943913</v>
       </c>
       <c r="D2" t="n">
-        <v>2.288635279618303</v>
+        <v>2.288635279618302</v>
       </c>
       <c r="E2" t="n">
-        <v>2.210604090154175</v>
+        <v>2.210604090153959</v>
       </c>
       <c r="F2" t="n">
-        <v>1.808291183717773</v>
+        <v>1.808291183717757</v>
       </c>
       <c r="G2" t="n">
-        <v>2.245008124461318</v>
+        <v>2.245008124461273</v>
       </c>
       <c r="H2" t="n">
-        <v>2.288635323309075</v>
+        <v>2.288635323309052</v>
       </c>
       <c r="I2" t="n">
-        <v>2.210842148542885</v>
+        <v>2.210842148542862</v>
       </c>
       <c r="J2" t="n">
-        <v>2.641844413366441</v>
+        <v>2.641844413365723</v>
       </c>
       <c r="K2" t="n">
-        <v>2.102277483678052</v>
+        <v>2.10227748367805</v>
       </c>
       <c r="L2" t="n">
-        <v>2.277467509755342</v>
+        <v>2.2774675097553</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.28212779430367</v>
+        <v>2.282127794303641</v>
       </c>
       <c r="C3" t="n">
-        <v>2.202093015901323</v>
+        <v>2.202093015901209</v>
       </c>
       <c r="D3" t="n">
-        <v>3.009641643804626</v>
+        <v>3.009641643804621</v>
       </c>
       <c r="E3" t="n">
-        <v>2.455081289418647</v>
+        <v>2.455081289418468</v>
       </c>
       <c r="F3" t="n">
-        <v>1.790966757787572</v>
+        <v>1.790966757787509</v>
       </c>
       <c r="G3" t="n">
-        <v>2.699914038867654</v>
+        <v>2.699914038867609</v>
       </c>
       <c r="H3" t="n">
-        <v>3.018491658897884</v>
+        <v>3.018491658897858</v>
       </c>
       <c r="I3" t="n">
-        <v>2.455477187139466</v>
+        <v>2.455477187139453</v>
       </c>
       <c r="J3" t="n">
-        <v>3.165747554973916</v>
+        <v>3.165747554973667</v>
       </c>
       <c r="K3" t="n">
-        <v>2.230742142159478</v>
+        <v>2.230742142159428</v>
       </c>
       <c r="L3" t="n">
-        <v>2.937762591272028</v>
+        <v>2.937762591271987</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.574964347321575</v>
+        <v>1.574964347321443</v>
       </c>
       <c r="C4" t="n">
-        <v>1.633619886558799</v>
+        <v>1.633619886558796</v>
       </c>
       <c r="D4" t="n">
-        <v>2.729617892458904</v>
+        <v>2.729617892458728</v>
       </c>
       <c r="E4" t="n">
-        <v>1.68466480606205</v>
+        <v>1.684664806062035</v>
       </c>
       <c r="F4" t="n">
-        <v>1.68466480606205</v>
+        <v>1.684664806062035</v>
       </c>
       <c r="G4" t="n">
-        <v>2.235934510848354</v>
+        <v>2.23593451084834</v>
       </c>
       <c r="H4" t="n">
-        <v>2.735307098841018</v>
+        <v>2.735307098840903</v>
       </c>
       <c r="I4" t="n">
-        <v>1.845461729283947</v>
+        <v>1.845461729283873</v>
       </c>
       <c r="J4" t="n">
-        <v>1.845081666939057</v>
+        <v>1.845081666938995</v>
       </c>
       <c r="K4" t="n">
-        <v>1.755497690204746</v>
+        <v>1.755497690204588</v>
       </c>
       <c r="L4" t="n">
-        <v>2.60450617490707</v>
+        <v>2.604506174906895</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.018627863754572</v>
+        <v>6.01862786375443</v>
       </c>
       <c r="C5" t="n">
-        <v>10.67116399111746</v>
+        <v>10.67116399111742</v>
       </c>
       <c r="D5" t="n">
-        <v>26.70761011495779</v>
+        <v>26.70761011495756</v>
       </c>
       <c r="E5" t="n">
-        <v>10.67117175012468</v>
+        <v>10.67117175012456</v>
       </c>
       <c r="F5" t="n">
-        <v>10.67117175012468</v>
+        <v>10.67117175012459</v>
       </c>
       <c r="G5" t="n">
-        <v>18.30207855954085</v>
+        <v>18.30207855954051</v>
       </c>
       <c r="H5" t="n">
-        <v>30.01801270284707</v>
+        <v>30.01801270284685</v>
       </c>
       <c r="I5" t="n">
-        <v>10.67101606401553</v>
+        <v>10.67101606401546</v>
       </c>
       <c r="J5" t="n">
-        <v>11.48532497882977</v>
+        <v>11.48532497882898</v>
       </c>
       <c r="K5" t="n">
-        <v>9.324759110792492</v>
+        <v>9.324759110792513</v>
       </c>
       <c r="L5" t="n">
-        <v>7.693210809982289</v>
+        <v>7.693210809982021</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.976679860822631</v>
+        <v>1.976679860822415</v>
       </c>
       <c r="C6" t="n">
-        <v>2.209478185308533</v>
+        <v>2.209478185308527</v>
       </c>
       <c r="D6" t="n">
-        <v>3.211558908462123</v>
+        <v>3.211558908462048</v>
       </c>
       <c r="E6" t="n">
-        <v>2.194147699079455</v>
+        <v>2.194147699079439</v>
       </c>
       <c r="F6" t="n">
-        <v>2.245104751988136</v>
+        <v>2.245104751988109</v>
       </c>
       <c r="G6" t="n">
-        <v>2.637650024349402</v>
+        <v>2.63765002434938</v>
       </c>
       <c r="H6" t="n">
-        <v>5.735810470898129</v>
+        <v>5.735810470898098</v>
       </c>
       <c r="I6" t="n">
-        <v>4.265174669008928</v>
+        <v>4.265174669008878</v>
       </c>
       <c r="J6" t="n">
-        <v>2.275298227424139</v>
+        <v>2.27529822742408</v>
       </c>
       <c r="K6" t="n">
-        <v>2.122859542341955</v>
+        <v>2.122859542342093</v>
       </c>
       <c r="L6" t="n">
-        <v>3.00931728519178</v>
+        <v>3.00931728519159</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.279285264380589</v>
+        <v>2.279285264380667</v>
       </c>
       <c r="C7" t="n">
-        <v>2.549930573445066</v>
+        <v>2.549930573445073</v>
       </c>
       <c r="D7" t="n">
-        <v>3.433952850035303</v>
+        <v>3.433952850035079</v>
       </c>
       <c r="E7" t="n">
-        <v>2.524362120422725</v>
+        <v>2.524362120422685</v>
       </c>
       <c r="F7" t="n">
-        <v>2.524362120422725</v>
+        <v>2.524362120422671</v>
       </c>
       <c r="G7" t="n">
-        <v>2.940255427907527</v>
+        <v>2.94025542790757</v>
       </c>
       <c r="H7" t="n">
-        <v>3.439628015900031</v>
+        <v>3.439628015900166</v>
       </c>
       <c r="I7" t="n">
-        <v>2.549782646343132</v>
+        <v>2.5497826463431</v>
       </c>
       <c r="J7" t="n">
-        <v>2.549402583998182</v>
+        <v>2.549402583998232</v>
       </c>
       <c r="K7" t="n">
-        <v>2.459818607263763</v>
+        <v>2.459818607263791</v>
       </c>
       <c r="L7" t="n">
-        <v>3.30882709196603</v>
+        <v>3.308827091966116</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.047070991288758</v>
+        <v>4.047070991288549</v>
       </c>
       <c r="C8" t="n">
-        <v>6.002727961489911</v>
+        <v>6.002727961489954</v>
       </c>
       <c r="D8" t="n">
-        <v>7.265276363540244</v>
+        <v>7.265276363539964</v>
       </c>
       <c r="E8" t="n">
-        <v>5.53786273921551</v>
+        <v>5.537862739215429</v>
       </c>
       <c r="F8" t="n">
-        <v>4.356635607937741</v>
+        <v>4.356635607937605</v>
       </c>
       <c r="G8" t="n">
-        <v>6.417189863249214</v>
+        <v>6.417189863248917</v>
       </c>
       <c r="H8" t="n">
-        <v>6.916562451230325</v>
+        <v>6.916562451229843</v>
       </c>
       <c r="I8" t="n">
-        <v>6.026717081684718</v>
+        <v>6.026717081684603</v>
       </c>
       <c r="J8" t="n">
-        <v>6.026672913663522</v>
+        <v>6.02667291366327</v>
       </c>
       <c r="K8" t="n">
-        <v>4.195856019638637</v>
+        <v>4.195856019638507</v>
       </c>
       <c r="L8" t="n">
-        <v>8.571110267721862</v>
+        <v>8.571110267721931</v>
       </c>
     </row>
     <row r="9">
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.09007222973629</v>
+        <v>86.09007222973612</v>
       </c>
       <c r="C9" t="n">
         <v>109.7940385802185</v>
@@ -5160,25 +5160,25 @@
         <v>110.6780473318267</v>
       </c>
       <c r="E9" t="n">
-        <v>136.8356021355275</v>
+        <v>136.8356021355274</v>
       </c>
       <c r="F9" t="n">
         <v>109.7940461113435</v>
       </c>
       <c r="G9" t="n">
-        <v>110.1843634346812</v>
+        <v>110.1843634346811</v>
       </c>
       <c r="H9" t="n">
-        <v>110.6837360226735</v>
+        <v>110.6837360226736</v>
       </c>
       <c r="I9" t="n">
         <v>109.7938906531169</v>
       </c>
       <c r="J9" t="n">
-        <v>109.7935105907717</v>
+        <v>109.7935105907715</v>
       </c>
       <c r="K9" t="n">
-        <v>96.1265685897166</v>
+        <v>96.12656858971638</v>
       </c>
       <c r="L9" t="n">
         <v>110.5529350987395</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.48137007097328</v>
+        <v>2.481370070973281</v>
       </c>
       <c r="C2" t="n">
         <v>2.511389919554013</v>
@@ -5276,28 +5276,28 @@
         <v>2.57915670005084</v>
       </c>
       <c r="E2" t="n">
-        <v>2.731784777107086</v>
+        <v>2.731784777107085</v>
       </c>
       <c r="F2" t="n">
-        <v>2.137746239496603</v>
+        <v>2.137746239496601</v>
       </c>
       <c r="G2" t="n">
-        <v>2.541926796360383</v>
+        <v>2.541926796360381</v>
       </c>
       <c r="H2" t="n">
-        <v>2.570097814073917</v>
+        <v>2.570097814073919</v>
       </c>
       <c r="I2" t="n">
-        <v>2.49761859178715</v>
+        <v>2.497618591787151</v>
       </c>
       <c r="J2" t="n">
-        <v>3.377570442099203</v>
+        <v>3.3775704420992</v>
       </c>
       <c r="K2" t="n">
-        <v>2.628863880071552</v>
+        <v>2.628863880071555</v>
       </c>
       <c r="L2" t="n">
-        <v>2.558159889118463</v>
+        <v>2.558159889118466</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.580818684540833</v>
+        <v>2.580818684540834</v>
       </c>
       <c r="C3" t="n">
         <v>2.720543947508868</v>
       </c>
       <c r="D3" t="n">
-        <v>3.276029446226292</v>
+        <v>3.276029446226294</v>
       </c>
       <c r="E3" t="n">
-        <v>3.082263187950501</v>
+        <v>3.0822631879505</v>
       </c>
       <c r="F3" t="n">
-        <v>2.101666242437226</v>
+        <v>2.101666242437224</v>
       </c>
       <c r="G3" t="n">
         <v>3.01222045137372</v>
       </c>
       <c r="H3" t="n">
-        <v>3.224141191460485</v>
+        <v>3.224141191460487</v>
       </c>
       <c r="I3" t="n">
         <v>2.69574642978455</v>
       </c>
       <c r="J3" t="n">
-        <v>4.156890989262109</v>
+        <v>4.156890989262111</v>
       </c>
       <c r="K3" t="n">
         <v>2.96495890472744</v>
       </c>
       <c r="L3" t="n">
-        <v>3.137489176817766</v>
+        <v>3.137489176817769</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.001919714092069</v>
+        <v>2.001919714092016</v>
       </c>
       <c r="C4" t="n">
-        <v>1.995898484991012</v>
+        <v>1.99589848499101</v>
       </c>
       <c r="D4" t="n">
-        <v>3.106464673595036</v>
+        <v>3.106464673594888</v>
       </c>
       <c r="E4" t="n">
-        <v>2.053141347056841</v>
+        <v>2.05314134705683</v>
       </c>
       <c r="F4" t="n">
-        <v>2.053141347056839</v>
+        <v>2.053141347056831</v>
       </c>
       <c r="G4" t="n">
-        <v>2.68490194941189</v>
+        <v>2.684901949411717</v>
       </c>
       <c r="H4" t="n">
-        <v>3.015573768511747</v>
+        <v>3.015573768511521</v>
       </c>
       <c r="I4" t="n">
-        <v>2.179103209715992</v>
+        <v>2.179103209715984</v>
       </c>
       <c r="J4" t="n">
-        <v>2.199400736713259</v>
+        <v>2.199400736713224</v>
       </c>
       <c r="K4" t="n">
-        <v>2.294647585190067</v>
+        <v>2.294647585189967</v>
       </c>
       <c r="L4" t="n">
-        <v>2.875313978316906</v>
+        <v>2.875313978316741</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.686651273392665</v>
+        <v>7.686651273392429</v>
       </c>
       <c r="C5" t="n">
-        <v>10.38828334114225</v>
+        <v>10.38828334114228</v>
       </c>
       <c r="D5" t="n">
-        <v>25.82455192924635</v>
+        <v>25.8245519292464</v>
       </c>
       <c r="E5" t="n">
-        <v>10.38829061627438</v>
+        <v>10.38829061627439</v>
       </c>
       <c r="F5" t="n">
         <v>10.38829061627439</v>
       </c>
       <c r="G5" t="n">
-        <v>19.3717884518394</v>
+        <v>19.37178845183927</v>
       </c>
       <c r="H5" t="n">
-        <v>27.61317232958252</v>
+        <v>27.61317232958227</v>
       </c>
       <c r="I5" t="n">
-        <v>10.38810112225677</v>
+        <v>10.38810112225679</v>
       </c>
       <c r="J5" t="n">
         <v>11.59927519793571</v>
       </c>
       <c r="K5" t="n">
-        <v>12.0828367909399</v>
+        <v>12.08283679093963</v>
       </c>
       <c r="L5" t="n">
-        <v>10.99280833281553</v>
+        <v>10.99280833281539</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.479038427848697</v>
+        <v>2.479038427848636</v>
       </c>
       <c r="C6" t="n">
-        <v>2.61883779207824</v>
+        <v>2.618837792078236</v>
       </c>
       <c r="D6" t="n">
-        <v>3.652013036944563</v>
+        <v>3.652013036944105</v>
       </c>
       <c r="E6" t="n">
-        <v>2.585257109066446</v>
+        <v>2.585257109066444</v>
       </c>
       <c r="F6" t="n">
         <v>2.65391619468505</v>
       </c>
       <c r="G6" t="n">
-        <v>3.162020663168342</v>
+        <v>3.162020663168158</v>
       </c>
       <c r="H6" t="n">
-        <v>6.087308922983087</v>
+        <v>6.087308922982957</v>
       </c>
       <c r="I6" t="n">
-        <v>4.744960696667844</v>
+        <v>4.744960696667824</v>
       </c>
       <c r="J6" t="n">
-        <v>2.707895850914821</v>
+        <v>2.707895850914737</v>
       </c>
       <c r="K6" t="n">
-        <v>2.732865696049777</v>
+        <v>2.732865696049473</v>
       </c>
       <c r="L6" t="n">
-        <v>3.346851165628586</v>
+        <v>3.346851165628319</v>
       </c>
     </row>
     <row r="7">
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.742213678947949</v>
+        <v>2.742213678947669</v>
       </c>
       <c r="C7" t="n">
-        <v>2.919579393457308</v>
+        <v>2.919579393457302</v>
       </c>
       <c r="D7" t="n">
-        <v>3.846760148323903</v>
+        <v>3.846760148323815</v>
       </c>
       <c r="E7" t="n">
         <v>2.902785722584101</v>
@@ -5482,22 +5482,22 @@
         <v>2.902785722584101</v>
       </c>
       <c r="G7" t="n">
-        <v>3.425195914267634</v>
+        <v>3.425195914267588</v>
       </c>
       <c r="H7" t="n">
-        <v>3.755867733367681</v>
+        <v>3.755867733367338</v>
       </c>
       <c r="I7" t="n">
-        <v>2.919397174571821</v>
+        <v>2.919397174571822</v>
       </c>
       <c r="J7" t="n">
-        <v>2.939694701569085</v>
+        <v>2.939694701568925</v>
       </c>
       <c r="K7" t="n">
-        <v>3.034941550046011</v>
+        <v>3.034941550045678</v>
       </c>
       <c r="L7" t="n">
-        <v>3.615607943172785</v>
+        <v>3.615607943172658</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.507177274562327</v>
+        <v>4.507177274562149</v>
       </c>
       <c r="C8" t="n">
-        <v>6.491504729006409</v>
+        <v>6.491504729006396</v>
       </c>
       <c r="D8" t="n">
-        <v>7.812332804698715</v>
+        <v>7.812332804698409</v>
       </c>
       <c r="E8" t="n">
-        <v>5.994693584632819</v>
+        <v>5.994693584632804</v>
       </c>
       <c r="F8" t="n">
-        <v>4.732302560586297</v>
+        <v>4.732302560586279</v>
       </c>
       <c r="G8" t="n">
-        <v>7.012827913701139</v>
+        <v>7.01282791370119</v>
       </c>
       <c r="H8" t="n">
-        <v>7.343499732778538</v>
+        <v>7.343499732778309</v>
       </c>
       <c r="I8" t="n">
-        <v>6.507029174005425</v>
+        <v>6.507029174005435</v>
       </c>
       <c r="J8" t="n">
-        <v>6.527684902767516</v>
+        <v>6.527684902767469</v>
       </c>
       <c r="K8" t="n">
-        <v>4.766048144753142</v>
+        <v>4.766048144752916</v>
       </c>
       <c r="L8" t="n">
-        <v>9.107169494863928</v>
+        <v>9.107169494863673</v>
       </c>
     </row>
     <row r="9">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80.77530287858922</v>
+        <v>80.77530287858896</v>
       </c>
       <c r="C9" t="n">
         <v>102.8383281738168</v>
       </c>
       <c r="D9" t="n">
-        <v>103.7655080718844</v>
+        <v>103.7655080718842</v>
       </c>
       <c r="E9" t="n">
         <v>128.0939228763577</v>
@@ -5565,16 +5565,16 @@
         <v>103.343944694627</v>
       </c>
       <c r="H9" t="n">
-        <v>103.6746165137269</v>
+        <v>103.6746165137268</v>
       </c>
       <c r="I9" t="n">
         <v>102.8381459549314</v>
       </c>
       <c r="J9" t="n">
-        <v>102.8584434819284</v>
+        <v>102.8584434819283</v>
       </c>
       <c r="K9" t="n">
-        <v>90.27305349239795</v>
+        <v>90.27305349239774</v>
       </c>
       <c r="L9" t="n">
         <v>103.5343567235322</v>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.66741859014407</v>
+        <v>2.667418590144071</v>
       </c>
       <c r="C2" t="n">
         <v>2.820870460774244</v>
       </c>
       <c r="D2" t="n">
-        <v>2.755729084366104</v>
+        <v>2.755729084366111</v>
       </c>
       <c r="E2" t="n">
-        <v>3.084671145759667</v>
+        <v>3.084671145759671</v>
       </c>
       <c r="F2" t="n">
-        <v>2.367982382428724</v>
+        <v>2.367982382428725</v>
       </c>
       <c r="G2" t="n">
-        <v>2.736016683488532</v>
+        <v>2.736016683488538</v>
       </c>
       <c r="H2" t="n">
-        <v>2.743023548966368</v>
+        <v>2.74302354896637</v>
       </c>
       <c r="I2" t="n">
-        <v>2.688782830512921</v>
+        <v>2.688782830512927</v>
       </c>
       <c r="J2" t="n">
-        <v>3.864015363592732</v>
+        <v>3.864015363592733</v>
       </c>
       <c r="K2" t="n">
-        <v>2.991183108464239</v>
+        <v>2.991183108464238</v>
       </c>
       <c r="L2" t="n">
-        <v>2.739388032479699</v>
+        <v>2.739388032479701</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.746360715353101</v>
+        <v>2.746360715353104</v>
       </c>
       <c r="C3" t="n">
-        <v>3.117959548399251</v>
+        <v>3.117959548399253</v>
       </c>
       <c r="D3" t="n">
-        <v>3.37313060059005</v>
+        <v>3.373130600590055</v>
       </c>
       <c r="E3" t="n">
-        <v>3.551110109329896</v>
+        <v>3.551110109329895</v>
       </c>
       <c r="F3" t="n">
-        <v>2.368054601590151</v>
+        <v>2.368054601590149</v>
       </c>
       <c r="G3" t="n">
-        <v>3.23447884779328</v>
+        <v>3.234478847793286</v>
       </c>
       <c r="H3" t="n">
         <v>3.297094257119677</v>
       </c>
       <c r="I3" t="n">
-        <v>2.897656441219409</v>
+        <v>2.897656441219402</v>
       </c>
       <c r="J3" t="n">
-        <v>4.823771121199623</v>
+        <v>4.823771121199618</v>
       </c>
       <c r="K3" t="n">
-        <v>3.424287836689051</v>
+        <v>3.424287836689056</v>
       </c>
       <c r="L3" t="n">
-        <v>3.270293346373867</v>
+        <v>3.27029334637387</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.280503959169972</v>
+        <v>2.280503959169979</v>
       </c>
       <c r="C4" t="n">
-        <v>2.405454653478035</v>
+        <v>2.405454653478034</v>
       </c>
       <c r="D4" t="n">
-        <v>3.278011616242277</v>
+        <v>3.278011616242285</v>
       </c>
       <c r="E4" t="n">
-        <v>2.463976767189663</v>
+        <v>2.463976767189661</v>
       </c>
       <c r="F4" t="n">
-        <v>2.463976767189661</v>
+        <v>2.46397676718966</v>
       </c>
       <c r="G4" t="n">
         <v>3.054143761666807</v>
       </c>
       <c r="H4" t="n">
-        <v>3.150842965502212</v>
+        <v>3.150842965502223</v>
       </c>
       <c r="I4" t="n">
-        <v>2.514307081707243</v>
+        <v>2.514307081707251</v>
       </c>
       <c r="J4" t="n">
-        <v>2.48846046362836</v>
+        <v>2.488460463628367</v>
       </c>
       <c r="K4" t="n">
-        <v>2.580628353765112</v>
+        <v>2.58062835376512</v>
       </c>
       <c r="L4" t="n">
-        <v>3.103076133979323</v>
+        <v>3.103076133979329</v>
       </c>
     </row>
     <row r="5">
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.34807454134514</v>
+        <v>8.348074541345156</v>
       </c>
       <c r="C5" t="n">
-        <v>11.99636957330163</v>
+        <v>11.99636957330161</v>
       </c>
       <c r="D5" t="n">
-        <v>24.17348113933751</v>
+        <v>24.1734811393375</v>
       </c>
       <c r="E5" t="n">
         <v>11.99637460550879</v>
@@ -5798,22 +5798,22 @@
         <v>11.99637460550879</v>
       </c>
       <c r="G5" t="n">
-        <v>21.28958765331613</v>
+        <v>21.28958765331626</v>
       </c>
       <c r="H5" t="n">
-        <v>24.91054735711251</v>
+        <v>24.91054735711249</v>
       </c>
       <c r="I5" t="n">
-        <v>11.99618060958345</v>
+        <v>11.99618060958344</v>
       </c>
       <c r="J5" t="n">
         <v>12.6484729576762</v>
       </c>
       <c r="K5" t="n">
-        <v>12.47461039271266</v>
+        <v>12.47461039271268</v>
       </c>
       <c r="L5" t="n">
-        <v>9.993050151228156</v>
+        <v>9.993050151228195</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.832403660057061</v>
+        <v>2.832403660057059</v>
       </c>
       <c r="C6" t="n">
         <v>3.040521079404148</v>
       </c>
       <c r="D6" t="n">
-        <v>3.890031515975434</v>
+        <v>3.890031515975437</v>
       </c>
       <c r="E6" t="n">
         <v>2.99297048493203</v>
       </c>
       <c r="F6" t="n">
-        <v>3.069817072691805</v>
+        <v>3.069817072691808</v>
       </c>
       <c r="G6" t="n">
-        <v>5.826666520327691</v>
+        <v>5.826666520327719</v>
       </c>
       <c r="H6" t="n">
-        <v>6.418019055012863</v>
+        <v>6.418019055012872</v>
       </c>
       <c r="I6" t="n">
-        <v>3.066206782594345</v>
+        <v>3.066206782594344</v>
       </c>
       <c r="J6" t="n">
-        <v>5.363332913399389</v>
+        <v>5.363332913399399</v>
       </c>
       <c r="K6" t="n">
-        <v>3.092001948286935</v>
+        <v>3.092001948286938</v>
       </c>
       <c r="L6" t="n">
-        <v>3.646380391178618</v>
+        <v>3.646380391178622</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.089297085161383</v>
+        <v>3.089297085161386</v>
       </c>
       <c r="C7" t="n">
-        <v>3.323289171416827</v>
+        <v>3.32328917141683</v>
       </c>
       <c r="D7" t="n">
-        <v>4.086790376647595</v>
+        <v>4.086790376647607</v>
       </c>
       <c r="E7" t="n">
-        <v>3.328879754483184</v>
+        <v>3.328879754483185</v>
       </c>
       <c r="F7" t="n">
-        <v>3.328879754483184</v>
+        <v>3.328879754483185</v>
       </c>
       <c r="G7" t="n">
-        <v>3.862936887658206</v>
+        <v>3.862936887658224</v>
       </c>
       <c r="H7" t="n">
-        <v>3.959636091493626</v>
+        <v>3.959636091493627</v>
       </c>
       <c r="I7" t="n">
-        <v>3.323100207698665</v>
+        <v>3.323100207698668</v>
       </c>
       <c r="J7" t="n">
-        <v>3.297253589619772</v>
+        <v>3.297253589619774</v>
       </c>
       <c r="K7" t="n">
-        <v>3.389421479756523</v>
+        <v>3.389421479756527</v>
       </c>
       <c r="L7" t="n">
-        <v>3.911869259970734</v>
+        <v>3.911869259970736</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.928655885086526</v>
+        <v>4.928655885086534</v>
       </c>
       <c r="C8" t="n">
-        <v>7.140927941839175</v>
+        <v>7.140927941839185</v>
       </c>
       <c r="D8" t="n">
-        <v>8.307707626658972</v>
+        <v>8.307707626658967</v>
       </c>
       <c r="E8" t="n">
-        <v>6.600845757043336</v>
+        <v>6.600845757043341</v>
       </c>
       <c r="F8" t="n">
-        <v>5.228519709389264</v>
+        <v>5.228519709389261</v>
       </c>
       <c r="G8" t="n">
-        <v>7.674823318420337</v>
+        <v>7.674823318420334</v>
       </c>
       <c r="H8" t="n">
-        <v>7.771522522231915</v>
+        <v>7.77152252223195</v>
       </c>
       <c r="I8" t="n">
-        <v>7.134986638460771</v>
+        <v>7.134986638460775</v>
       </c>
       <c r="J8" t="n">
-        <v>7.109527672331359</v>
+        <v>7.109527672331368</v>
       </c>
       <c r="K8" t="n">
-        <v>5.192139566842291</v>
+        <v>5.192139566842302</v>
       </c>
       <c r="L8" t="n">
-        <v>9.784225735239302</v>
+        <v>9.784225735239319</v>
       </c>
     </row>
     <row r="9">
@@ -5943,10 +5943,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.05912021638358</v>
+        <v>81.0591202163836</v>
       </c>
       <c r="C9" t="n">
-        <v>103.2059276128074</v>
+        <v>103.2059276128075</v>
       </c>
       <c r="D9" t="n">
         <v>103.9694439449003</v>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.575539149645702</v>
+        <v>2.575539149645699</v>
       </c>
       <c r="C2" t="n">
-        <v>2.594641470816309</v>
+        <v>2.59464147081631</v>
       </c>
       <c r="D2" t="n">
         <v>2.596429670088433</v>
       </c>
       <c r="E2" t="n">
-        <v>2.81978275187267</v>
+        <v>2.819782751872674</v>
       </c>
       <c r="F2" t="n">
-        <v>2.215611782808611</v>
+        <v>2.215611782808614</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67297319734695</v>
+        <v>2.672973197346947</v>
       </c>
       <c r="H2" t="n">
         <v>2.602088365237283</v>
       </c>
       <c r="I2" t="n">
-        <v>2.579617180714953</v>
+        <v>2.579617180714952</v>
       </c>
       <c r="J2" t="n">
-        <v>3.495278964831739</v>
+        <v>3.495278964831732</v>
       </c>
       <c r="K2" t="n">
-        <v>2.731861591005939</v>
+        <v>2.731861591005934</v>
       </c>
       <c r="L2" t="n">
         <v>2.575633389051221</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.699182962392957</v>
+        <v>2.699182962392956</v>
       </c>
       <c r="C3" t="n">
-        <v>2.755474067125283</v>
+        <v>2.755474067125282</v>
       </c>
       <c r="D3" t="n">
-        <v>2.846710488814306</v>
+        <v>2.846710488814308</v>
       </c>
       <c r="E3" t="n">
-        <v>3.124449606801837</v>
+        <v>3.124449606801849</v>
       </c>
       <c r="F3" t="n">
-        <v>2.127127784593178</v>
+        <v>2.127127784593177</v>
       </c>
       <c r="G3" t="n">
-        <v>3.391290241053145</v>
+        <v>3.39129024105314</v>
       </c>
       <c r="H3" t="n">
-        <v>2.903710596737839</v>
+        <v>2.903710596737838</v>
       </c>
       <c r="I3" t="n">
-        <v>2.728045627665201</v>
+        <v>2.728045627665196</v>
       </c>
       <c r="J3" t="n">
-        <v>4.276971323894783</v>
+        <v>4.276971323894804</v>
       </c>
       <c r="K3" t="n">
-        <v>3.037006080456594</v>
+        <v>3.037006080456587</v>
       </c>
       <c r="L3" t="n">
-        <v>2.716368994467784</v>
+        <v>2.716368994467785</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.226448187841719</v>
+        <v>2.226448187841727</v>
       </c>
       <c r="C4" t="n">
-        <v>2.111448645278813</v>
+        <v>2.111448645278832</v>
       </c>
       <c r="D4" t="n">
-        <v>2.462416226356556</v>
+        <v>2.462416226356565</v>
       </c>
       <c r="E4" t="n">
-        <v>2.170580915708837</v>
+        <v>2.17058091570883</v>
       </c>
       <c r="F4" t="n">
-        <v>2.170580915708837</v>
+        <v>2.170580915708829</v>
       </c>
       <c r="G4" t="n">
-        <v>3.325606166714297</v>
+        <v>3.325606166714302</v>
       </c>
       <c r="H4" t="n">
-        <v>2.552624609940636</v>
+        <v>2.552624609940631</v>
       </c>
       <c r="I4" t="n">
-        <v>2.263673653496913</v>
+        <v>2.263673653496927</v>
       </c>
       <c r="J4" t="n">
-        <v>2.34653870727097</v>
+        <v>2.346538707270973</v>
       </c>
       <c r="K4" t="n">
-        <v>2.392550164870248</v>
+        <v>2.392550164870251</v>
       </c>
       <c r="L4" t="n">
-        <v>2.25348968083884</v>
+        <v>2.253489680838849</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.651762061742106</v>
+        <v>9.65176206174208</v>
       </c>
       <c r="C5" t="n">
-        <v>10.37934450010717</v>
+        <v>10.37934450010716</v>
       </c>
       <c r="D5" t="n">
-        <v>13.2407316603707</v>
+        <v>13.24073166037068</v>
       </c>
       <c r="E5" t="n">
-        <v>10.37935042846475</v>
+        <v>10.37935042846473</v>
       </c>
       <c r="F5" t="n">
-        <v>10.37935042846475</v>
+        <v>10.37935042846473</v>
       </c>
       <c r="G5" t="n">
-        <v>28.63307253781983</v>
+        <v>28.63307253781984</v>
       </c>
       <c r="H5" t="n">
-        <v>16.24187849739309</v>
+        <v>16.24187849739304</v>
       </c>
       <c r="I5" t="n">
-        <v>10.37904683557468</v>
+        <v>10.37904683557469</v>
       </c>
       <c r="J5" t="n">
-        <v>12.62302588992284</v>
+        <v>12.62302588992286</v>
       </c>
       <c r="K5" t="n">
-        <v>12.29531371316724</v>
+        <v>12.29531371316719</v>
       </c>
       <c r="L5" t="n">
-        <v>11.49760712547457</v>
+        <v>11.49760712547456</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.168586725681795</v>
+        <v>5.168586725681774</v>
       </c>
       <c r="C6" t="n">
-        <v>2.769575898157138</v>
+        <v>2.769575898157121</v>
       </c>
       <c r="D6" t="n">
-        <v>5.499809784182991</v>
+        <v>5.499809784182982</v>
       </c>
       <c r="E6" t="n">
-        <v>2.73132875946769</v>
+        <v>2.731328759467695</v>
       </c>
       <c r="F6" t="n">
-        <v>2.81895928880963</v>
+        <v>2.818959288809618</v>
       </c>
       <c r="G6" t="n">
-        <v>6.267744704554372</v>
+        <v>6.267744704554354</v>
       </c>
       <c r="H6" t="n">
-        <v>3.109409762223642</v>
+        <v>3.109409762223641</v>
       </c>
       <c r="I6" t="n">
-        <v>5.205812191336979</v>
+        <v>5.205812191336965</v>
       </c>
       <c r="J6" t="n">
-        <v>5.358398784956208</v>
+        <v>5.358398784956212</v>
       </c>
       <c r="K6" t="n">
-        <v>2.912955287354285</v>
+        <v>2.912955287354283</v>
       </c>
       <c r="L6" t="n">
-        <v>2.800332463936307</v>
+        <v>2.800332463936305</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.100975396758398</v>
+        <v>3.100975396758399</v>
       </c>
       <c r="C7" t="n">
-        <v>3.138498526946075</v>
+        <v>3.138498526946029</v>
       </c>
       <c r="D7" t="n">
-        <v>3.336932373784399</v>
+        <v>3.336932373784397</v>
       </c>
       <c r="E7" t="n">
-        <v>3.135157506124906</v>
+        <v>3.135157506124919</v>
       </c>
       <c r="F7" t="n">
-        <v>3.135157506124909</v>
+        <v>3.135157506124923</v>
       </c>
       <c r="G7" t="n">
-        <v>4.200133375630977</v>
+        <v>4.200133375630973</v>
       </c>
       <c r="H7" t="n">
-        <v>3.427151818857315</v>
+        <v>3.427151818857311</v>
       </c>
       <c r="I7" t="n">
-        <v>3.138200862413588</v>
+        <v>3.138200862413578</v>
       </c>
       <c r="J7" t="n">
-        <v>3.221065916187647</v>
+        <v>3.221065916187653</v>
       </c>
       <c r="K7" t="n">
-        <v>3.267077373786926</v>
+        <v>3.267077373786924</v>
       </c>
       <c r="L7" t="n">
         <v>3.128016889755515</v>
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.085196102485798</v>
+        <v>5.085196102485781</v>
       </c>
       <c r="C8" t="n">
-        <v>7.191253112582442</v>
+        <v>7.191253112582436</v>
       </c>
       <c r="D8" t="n">
-        <v>7.821969118494453</v>
+        <v>7.821969118494456</v>
       </c>
       <c r="E8" t="n">
-        <v>6.625060674272796</v>
+        <v>6.625060674272769</v>
       </c>
       <c r="F8" t="n">
-        <v>5.186392351725754</v>
+        <v>5.186392351725786</v>
       </c>
       <c r="G8" t="n">
-        <v>8.255660234877626</v>
+        <v>8.255660234877586</v>
       </c>
       <c r="H8" t="n">
-        <v>7.482678678087723</v>
+        <v>7.482678678087735</v>
       </c>
       <c r="I8" t="n">
-        <v>7.193727721660218</v>
+        <v>7.193727721660193</v>
       </c>
       <c r="J8" t="n">
-        <v>7.276999841649992</v>
+        <v>7.276999841650051</v>
       </c>
       <c r="K8" t="n">
-        <v>5.212822504766479</v>
+        <v>5.212822504766462</v>
       </c>
       <c r="L8" t="n">
-        <v>9.347196221573173</v>
+        <v>9.347196221573226</v>
       </c>
     </row>
     <row r="9">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87.16221564071043</v>
+        <v>87.16221564071039</v>
       </c>
       <c r="C9" t="n">
         <v>110.8000974239281</v>
@@ -6348,13 +6348,13 @@
         <v>110.9985434856814</v>
       </c>
       <c r="E9" t="n">
-        <v>138.0344177773745</v>
+        <v>138.0344177773744</v>
       </c>
       <c r="F9" t="n">
         <v>110.8001032764967</v>
       </c>
       <c r="G9" t="n">
-        <v>111.8617322726128</v>
+        <v>111.8617322726129</v>
       </c>
       <c r="H9" t="n">
         <v>111.0887507158393</v>
@@ -6363,13 +6363,13 @@
         <v>110.7997997593955</v>
       </c>
       <c r="J9" t="n">
-        <v>110.8826648131695</v>
+        <v>110.8826648131694</v>
       </c>
       <c r="K9" t="n">
         <v>97.25453626656703</v>
       </c>
       <c r="L9" t="n">
-        <v>110.7896157867372</v>
+        <v>110.7896157867371</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.243627526575014</v>
+        <v>3.243627526574931</v>
       </c>
       <c r="C2" t="n">
-        <v>3.281041143868645</v>
+        <v>3.28104114386859</v>
       </c>
       <c r="D2" t="n">
-        <v>3.067996740591123</v>
+        <v>3.067996740591055</v>
       </c>
       <c r="E2" t="n">
-        <v>3.579450248218374</v>
+        <v>3.579450248218333</v>
       </c>
       <c r="F2" t="n">
-        <v>2.763031492617896</v>
+        <v>2.763031492617829</v>
       </c>
       <c r="G2" t="n">
-        <v>3.270995287611761</v>
+        <v>3.270995287611679</v>
       </c>
       <c r="H2" t="n">
-        <v>3.059024692965955</v>
+        <v>3.059024692965895</v>
       </c>
       <c r="I2" t="n">
-        <v>3.101470424796838</v>
+        <v>3.101470424796796</v>
       </c>
       <c r="J2" t="n">
-        <v>4.491902618235989</v>
+        <v>4.491902618235921</v>
       </c>
       <c r="K2" t="n">
-        <v>3.542545209151462</v>
+        <v>3.542545209151413</v>
       </c>
       <c r="L2" t="n">
-        <v>3.059709468406917</v>
+        <v>3.059709468406862</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.43710233700309</v>
+        <v>4.43710233700303</v>
       </c>
       <c r="C3" t="n">
-        <v>3.72599260691097</v>
+        <v>3.725992606910913</v>
       </c>
       <c r="D3" t="n">
-        <v>3.187605028305518</v>
+        <v>3.187605028305482</v>
       </c>
       <c r="E3" t="n">
-        <v>4.214274831428244</v>
+        <v>4.214274831428199</v>
       </c>
       <c r="F3" t="n">
-        <v>2.866592949124765</v>
+        <v>2.866592949124725</v>
       </c>
       <c r="G3" t="n">
-        <v>4.627841264828061</v>
+        <v>4.627841264828006</v>
       </c>
       <c r="H3" t="n">
-        <v>3.154695448185691</v>
+        <v>3.154695448185628</v>
       </c>
       <c r="I3" t="n">
-        <v>3.425311040280732</v>
+        <v>3.4253110402807</v>
       </c>
       <c r="J3" t="n">
-        <v>5.853525596275559</v>
+        <v>5.853525596275514</v>
       </c>
       <c r="K3" t="n">
-        <v>4.573996153646988</v>
+        <v>4.573996153646945</v>
       </c>
       <c r="L3" t="n">
-        <v>3.159731511361637</v>
+        <v>3.159731511361596</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.748579597815481</v>
+        <v>4.748579597815611</v>
       </c>
       <c r="C4" t="n">
-        <v>2.897215249642527</v>
+        <v>2.897215249642482</v>
       </c>
       <c r="D4" t="n">
-        <v>2.764749075974222</v>
+        <v>2.764749075974366</v>
       </c>
       <c r="E4" t="n">
-        <v>2.974554740740912</v>
+        <v>2.974554740740901</v>
       </c>
       <c r="F4" t="n">
-        <v>2.974554740740929</v>
+        <v>2.974554740740901</v>
       </c>
       <c r="G4" t="n">
-        <v>5.055672996326772</v>
+        <v>5.055672996326719</v>
       </c>
       <c r="H4" t="n">
-        <v>2.717343238703238</v>
+        <v>2.717343238703305</v>
       </c>
       <c r="I4" t="n">
-        <v>3.129927623830139</v>
+        <v>3.12992762383007</v>
       </c>
       <c r="J4" t="n">
-        <v>3.413236005204879</v>
+        <v>3.41323600520495</v>
       </c>
       <c r="K4" t="n">
-        <v>4.016691107966739</v>
+        <v>4.016691107966907</v>
       </c>
       <c r="L4" t="n">
-        <v>2.722687955192409</v>
+        <v>2.722687955192411</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44.34560704856756</v>
+        <v>44.34560704856768</v>
       </c>
       <c r="C5" t="n">
-        <v>17.37957297372431</v>
+        <v>17.37957297372424</v>
       </c>
       <c r="D5" t="n">
-        <v>11.32516058740015</v>
+        <v>11.32516058740014</v>
       </c>
       <c r="E5" t="n">
-        <v>17.37958133245415</v>
+        <v>17.37958133245409</v>
       </c>
       <c r="F5" t="n">
-        <v>17.37958133245415</v>
+        <v>17.37958133245409</v>
       </c>
       <c r="G5" t="n">
-        <v>47.43441424144682</v>
+        <v>47.43441424144588</v>
       </c>
       <c r="H5" t="n">
-        <v>11.42936556649446</v>
+        <v>11.42936556649451</v>
       </c>
       <c r="I5" t="n">
-        <v>17.37908099850204</v>
+        <v>17.37908099850199</v>
       </c>
       <c r="J5" t="n">
-        <v>23.06619348474317</v>
+        <v>23.06619348474327</v>
       </c>
       <c r="K5" t="n">
-        <v>30.86416660095262</v>
+        <v>30.86416660095272</v>
       </c>
       <c r="L5" t="n">
-        <v>6.978037266621136</v>
+        <v>6.97803726662133</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.036078820485491</v>
+        <v>8.036078820485651</v>
       </c>
       <c r="C6" t="n">
-        <v>3.834738106640029</v>
+        <v>3.83473810663997</v>
       </c>
       <c r="D6" t="n">
-        <v>3.535634756353013</v>
+        <v>3.535634756352981</v>
       </c>
       <c r="E6" t="n">
-        <v>3.767148681178561</v>
+        <v>3.767148681178512</v>
       </c>
       <c r="F6" t="n">
-        <v>3.910451174397523</v>
+        <v>3.910451174397453</v>
       </c>
       <c r="G6" t="n">
-        <v>8.343172218996546</v>
+        <v>8.343172218996807</v>
       </c>
       <c r="H6" t="n">
-        <v>6.625640562077613</v>
+        <v>6.625640562077639</v>
       </c>
       <c r="I6" t="n">
-        <v>6.417426846500178</v>
+        <v>6.417426846500122</v>
       </c>
       <c r="J6" t="n">
-        <v>4.252484917480051</v>
+        <v>4.252484917480108</v>
       </c>
       <c r="K6" t="n">
-        <v>4.805477434928227</v>
+        <v>4.805477434928274</v>
       </c>
       <c r="L6" t="n">
-        <v>3.491524467094428</v>
+        <v>3.491524467094421</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.683933006928272</v>
+        <v>5.683933006928427</v>
       </c>
       <c r="C7" t="n">
-        <v>4.065773008165104</v>
+        <v>4.065773008165028</v>
       </c>
       <c r="D7" t="n">
         <v>3.700106422375859</v>
       </c>
       <c r="E7" t="n">
-        <v>4.045505132741617</v>
+        <v>4.04550513274156</v>
       </c>
       <c r="F7" t="n">
-        <v>4.045505132741622</v>
+        <v>4.04550513274156</v>
       </c>
       <c r="G7" t="n">
-        <v>5.991026405439507</v>
+        <v>5.991026405439395</v>
       </c>
       <c r="H7" t="n">
-        <v>3.652696647816013</v>
+        <v>3.652696647815957</v>
       </c>
       <c r="I7" t="n">
-        <v>4.065281032942832</v>
+        <v>4.065281032942789</v>
       </c>
       <c r="J7" t="n">
-        <v>4.348589414317668</v>
+        <v>4.348589414317616</v>
       </c>
       <c r="K7" t="n">
-        <v>4.952044517079505</v>
+        <v>4.952044517079569</v>
       </c>
       <c r="L7" t="n">
-        <v>3.658041364305022</v>
+        <v>3.658041364305069</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.730551268626462</v>
+        <v>7.730551268626335</v>
       </c>
       <c r="C8" t="n">
-        <v>8.355534604593087</v>
+        <v>8.35553460459305</v>
       </c>
       <c r="D8" t="n">
-        <v>8.477866584956805</v>
+        <v>8.477866584956823</v>
       </c>
       <c r="E8" t="n">
-        <v>7.738889368997549</v>
+        <v>7.738889368997485</v>
       </c>
       <c r="F8" t="n">
-        <v>6.172006201010722</v>
+        <v>6.172006201010673</v>
       </c>
       <c r="G8" t="n">
         <v>10.29973196788434</v>
       </c>
       <c r="H8" t="n">
-        <v>7.961402210261873</v>
+        <v>7.96140221026193</v>
       </c>
       <c r="I8" t="n">
-        <v>8.373986595387759</v>
+        <v>8.373986595387738</v>
       </c>
       <c r="J8" t="n">
-        <v>8.657739534173913</v>
+        <v>8.657739534174166</v>
       </c>
       <c r="K8" t="n">
-        <v>6.956643346538065</v>
+        <v>6.956643346538135</v>
       </c>
       <c r="L8" t="n">
-        <v>10.32968625782417</v>
+        <v>10.32968625782429</v>
       </c>
     </row>
     <row r="9">
@@ -6735,16 +6735,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84.28146080107308</v>
+        <v>84.28146080107312</v>
       </c>
       <c r="C9" t="n">
-        <v>104.818423067763</v>
+        <v>104.8184230677629</v>
       </c>
       <c r="D9" t="n">
-        <v>104.4527544817817</v>
+        <v>104.4527544817818</v>
       </c>
       <c r="E9" t="n">
-        <v>130.3849745663387</v>
+        <v>130.3849745663386</v>
       </c>
       <c r="F9" t="n">
         <v>104.8184314736133</v>
@@ -6753,19 +6753,19 @@
         <v>106.7436764650375</v>
       </c>
       <c r="H9" t="n">
-        <v>104.4053467074141</v>
+        <v>104.405346707414</v>
       </c>
       <c r="I9" t="n">
-        <v>104.8179310925408</v>
+        <v>104.8179310925407</v>
       </c>
       <c r="J9" t="n">
-        <v>105.1012394739157</v>
+        <v>105.1012394739158</v>
       </c>
       <c r="K9" t="n">
-        <v>92.8679305409278</v>
+        <v>92.86793054092774</v>
       </c>
       <c r="L9" t="n">
-        <v>104.4106914239029</v>
+        <v>104.410691423903</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.502524713190255</v>
+        <v>3.502524713190241</v>
       </c>
       <c r="C2" t="n">
-        <v>3.512691648452546</v>
+        <v>3.512691648452543</v>
       </c>
       <c r="D2" t="n">
-        <v>3.215200631647173</v>
+        <v>3.21520063164716</v>
       </c>
       <c r="E2" t="n">
-        <v>3.842666548900696</v>
+        <v>3.842666548900685</v>
       </c>
       <c r="F2" t="n">
-        <v>2.933311323701778</v>
+        <v>2.933311323701762</v>
       </c>
       <c r="G2" t="n">
-        <v>3.404788987326452</v>
+        <v>3.404788987326439</v>
       </c>
       <c r="H2" t="n">
-        <v>3.179707132314693</v>
+        <v>3.179707132314703</v>
       </c>
       <c r="I2" t="n">
         <v>3.248270199275821</v>
       </c>
       <c r="J2" t="n">
-        <v>4.859535671432601</v>
+        <v>4.859535671432594</v>
       </c>
       <c r="K2" t="n">
-        <v>3.744006339698271</v>
+        <v>3.744006339698273</v>
       </c>
       <c r="L2" t="n">
-        <v>3.211331184641697</v>
+        <v>3.211331184641695</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.45031030193956</v>
+        <v>5.450310301939566</v>
       </c>
       <c r="C3" t="n">
-        <v>4.08427373810933</v>
+        <v>4.084273738109321</v>
       </c>
       <c r="D3" t="n">
-        <v>3.408457612007028</v>
+        <v>3.408457612007027</v>
       </c>
       <c r="E3" t="n">
-        <v>4.624555508879479</v>
+        <v>4.624555508879512</v>
       </c>
       <c r="F3" t="n">
-        <v>3.123462404271839</v>
+        <v>3.123462404271808</v>
       </c>
       <c r="G3" t="n">
-        <v>4.755676241933158</v>
+        <v>4.755676241933133</v>
       </c>
       <c r="H3" t="n">
-        <v>3.188984345496258</v>
+        <v>3.188984345496245</v>
       </c>
       <c r="I3" t="n">
-        <v>3.643422924474266</v>
+        <v>3.643422924474259</v>
       </c>
       <c r="J3" t="n">
-        <v>6.472508555605565</v>
+        <v>6.472508555605519</v>
       </c>
       <c r="K3" t="n">
-        <v>4.765212499541765</v>
+        <v>4.765212499541758</v>
       </c>
       <c r="L3" t="n">
-        <v>3.412374495577732</v>
+        <v>3.412374495577723</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.328824609832988</v>
+        <v>6.328824609832749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.174738901144815</v>
+        <v>3.174738901144835</v>
       </c>
       <c r="D4" t="n">
-        <v>3.083366933196231</v>
+        <v>3.083366933196064</v>
       </c>
       <c r="E4" t="n">
-        <v>3.261113012441065</v>
+        <v>3.261113012441084</v>
       </c>
       <c r="F4" t="n">
-        <v>3.261113012441064</v>
+        <v>3.261113012441084</v>
       </c>
       <c r="G4" t="n">
-        <v>5.222890320741079</v>
+        <v>5.222890320740963</v>
       </c>
       <c r="H4" t="n">
-        <v>2.739035673250259</v>
+        <v>2.739035673250088</v>
       </c>
       <c r="I4" t="n">
-        <v>3.444542603606113</v>
+        <v>3.444542603606098</v>
       </c>
       <c r="J4" t="n">
-        <v>3.801372651265292</v>
+        <v>3.801372651265093</v>
       </c>
       <c r="K4" t="n">
-        <v>4.091106800539849</v>
+        <v>4.091106800539597</v>
       </c>
       <c r="L4" t="n">
-        <v>3.089393939951008</v>
+        <v>3.08939393995082</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.21161807079372</v>
+        <v>67.21161807079352</v>
       </c>
       <c r="C5" t="n">
-        <v>20.41597283961327</v>
+        <v>20.41597283961332</v>
       </c>
       <c r="D5" t="n">
-        <v>14.36740607973177</v>
+        <v>14.36740607973157</v>
       </c>
       <c r="E5" t="n">
-        <v>20.41598234588812</v>
+        <v>20.41598234588828</v>
       </c>
       <c r="F5" t="n">
-        <v>20.41598234588812</v>
+        <v>20.41598234588828</v>
       </c>
       <c r="G5" t="n">
-        <v>49.19251314721822</v>
+        <v>49.19251314721812</v>
       </c>
       <c r="H5" t="n">
-        <v>9.885032428889767</v>
+        <v>9.885032428889383</v>
       </c>
       <c r="I5" t="n">
-        <v>20.41551993015908</v>
+        <v>20.41551993015927</v>
       </c>
       <c r="J5" t="n">
-        <v>27.59991339565536</v>
+        <v>27.59991339565504</v>
       </c>
       <c r="K5" t="n">
-        <v>29.28400078164231</v>
+        <v>29.28400078164226</v>
       </c>
       <c r="L5" t="n">
-        <v>27.02850559317512</v>
+        <v>27.02850559317499</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.204612898139715</v>
+        <v>7.204612898139535</v>
       </c>
       <c r="C6" t="n">
-        <v>4.21458672551312</v>
+        <v>4.214586725513142</v>
       </c>
       <c r="D6" t="n">
-        <v>3.917261072258426</v>
+        <v>3.917261072258203</v>
       </c>
       <c r="E6" t="n">
-        <v>4.136487868064568</v>
+        <v>4.136487868064594</v>
       </c>
       <c r="F6" t="n">
-        <v>4.292073508214626</v>
+        <v>4.292073508214618</v>
       </c>
       <c r="G6" t="n">
-        <v>6.09867860904781</v>
+        <v>6.098678609047612</v>
       </c>
       <c r="H6" t="n">
-        <v>6.856448914586919</v>
+        <v>6.856448914586491</v>
       </c>
       <c r="I6" t="n">
-        <v>4.320330891912789</v>
+        <v>4.3203308919128</v>
       </c>
       <c r="J6" t="n">
-        <v>4.714174860130197</v>
+        <v>4.71417486012993</v>
       </c>
       <c r="K6" t="n">
-        <v>4.942886377027049</v>
+        <v>4.942886377026674</v>
       </c>
       <c r="L6" t="n">
-        <v>3.925138607534376</v>
+        <v>3.925138607534104</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7.293951797977127</v>
+        <v>7.293951797976692</v>
       </c>
       <c r="C7" t="n">
-        <v>4.41012270120433</v>
+        <v>4.410122701204261</v>
       </c>
       <c r="D7" t="n">
-        <v>4.048503041220347</v>
+        <v>4.048503041220203</v>
       </c>
       <c r="E7" t="n">
-        <v>4.381320446893894</v>
+        <v>4.381320446893862</v>
       </c>
       <c r="F7" t="n">
-        <v>4.381320446893894</v>
+        <v>4.381320446893862</v>
       </c>
       <c r="G7" t="n">
-        <v>6.188017508885211</v>
+        <v>6.188017508885014</v>
       </c>
       <c r="H7" t="n">
-        <v>3.704162861394409</v>
+        <v>3.704162861394132</v>
       </c>
       <c r="I7" t="n">
-        <v>4.409669791750146</v>
+        <v>4.409669791750171</v>
       </c>
       <c r="J7" t="n">
-        <v>4.766499839409407</v>
+        <v>4.766499839409169</v>
       </c>
       <c r="K7" t="n">
-        <v>5.056233988683783</v>
+        <v>5.056233988683691</v>
       </c>
       <c r="L7" t="n">
-        <v>4.054521128095149</v>
+        <v>4.054521128094686</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.398165572841288</v>
+        <v>9.398165572841162</v>
       </c>
       <c r="C8" t="n">
-        <v>8.858265243823675</v>
+        <v>8.858265243823629</v>
       </c>
       <c r="D8" t="n">
-        <v>9.015375201894715</v>
+        <v>9.015375201894537</v>
       </c>
       <c r="E8" t="n">
-        <v>8.212695776041228</v>
+        <v>8.212695776041189</v>
       </c>
       <c r="F8" t="n">
-        <v>6.572310748469461</v>
+        <v>6.572310748469531</v>
       </c>
       <c r="G8" t="n">
-        <v>10.66325199900083</v>
+        <v>10.66325199900055</v>
       </c>
       <c r="H8" t="n">
-        <v>8.179397351521841</v>
+        <v>8.179397351521638</v>
       </c>
       <c r="I8" t="n">
-        <v>8.884904281865909</v>
+        <v>8.884904281865673</v>
       </c>
       <c r="J8" t="n">
-        <v>9.242200294055079</v>
+        <v>9.242200294055051</v>
       </c>
       <c r="K8" t="n">
-        <v>7.116404837342204</v>
+        <v>7.116404837342122</v>
       </c>
       <c r="L8" t="n">
-        <v>11.00648500824811</v>
+        <v>11.006485008248</v>
       </c>
     </row>
     <row r="9">
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85.72945398491764</v>
+        <v>85.7294539849174</v>
       </c>
       <c r="C9" t="n">
-        <v>104.9874233932719</v>
+        <v>104.9874233932718</v>
       </c>
       <c r="D9" t="n">
-        <v>104.6257968310583</v>
+        <v>104.6257968310582</v>
       </c>
       <c r="E9" t="n">
         <v>130.5386008301334</v>
@@ -7146,10 +7146,10 @@
         <v>104.9874329905302</v>
       </c>
       <c r="G9" t="n">
-        <v>106.7653182009528</v>
+        <v>106.7653182009527</v>
       </c>
       <c r="H9" t="n">
-        <v>104.2814635534618</v>
+        <v>104.2814635534617</v>
       </c>
       <c r="I9" t="n">
         <v>104.9869704838178</v>
@@ -7158,10 +7158,10 @@
         <v>105.3438005314769</v>
       </c>
       <c r="K9" t="n">
-        <v>92.28399990888971</v>
+        <v>92.28399990888963</v>
       </c>
       <c r="L9" t="n">
-        <v>104.6318218201625</v>
+        <v>104.6318218201624</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.365731899565676</v>
+        <v>2.365731899565596</v>
       </c>
       <c r="C2" t="n">
-        <v>2.244522307314802</v>
+        <v>2.244522307314761</v>
       </c>
       <c r="D2" t="n">
-        <v>2.444110034497397</v>
+        <v>2.444110034497359</v>
       </c>
       <c r="E2" t="n">
-        <v>2.420670749150823</v>
+        <v>2.420670749150704</v>
       </c>
       <c r="F2" t="n">
-        <v>1.957289265669868</v>
+        <v>1.957289265669789</v>
       </c>
       <c r="G2" t="n">
-        <v>2.44843506135685</v>
+        <v>2.448435061356764</v>
       </c>
       <c r="H2" t="n">
-        <v>2.473662602708226</v>
+        <v>2.473662602708145</v>
       </c>
       <c r="I2" t="n">
-        <v>2.358915588919579</v>
+        <v>2.358915588919495</v>
       </c>
       <c r="J2" t="n">
-        <v>2.912995251630631</v>
+        <v>2.912995251630189</v>
       </c>
       <c r="K2" t="n">
-        <v>2.310837346447159</v>
+        <v>2.310837346446885</v>
       </c>
       <c r="L2" t="n">
-        <v>2.417154442280834</v>
+        <v>2.417154442280721</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.587361297968568</v>
+        <v>2.587361297968487</v>
       </c>
       <c r="C3" t="n">
-        <v>2.352347336043604</v>
+        <v>2.352347336043584</v>
       </c>
       <c r="D3" t="n">
-        <v>3.143707342781675</v>
+        <v>3.143707342781699</v>
       </c>
       <c r="E3" t="n">
-        <v>2.640726843973155</v>
+        <v>2.64072684397334</v>
       </c>
       <c r="F3" t="n">
-        <v>1.875806204502014</v>
+        <v>1.875806204501996</v>
       </c>
       <c r="G3" t="n">
-        <v>3.176120835228071</v>
+        <v>3.176120835228039</v>
       </c>
       <c r="H3" t="n">
-        <v>3.364577543856208</v>
+        <v>3.364577543856135</v>
       </c>
       <c r="I3" t="n">
-        <v>2.538802665367113</v>
+        <v>2.538802665367112</v>
       </c>
       <c r="J3" t="n">
-        <v>3.428191948041207</v>
+        <v>3.428191948040409</v>
       </c>
       <c r="K3" t="n">
-        <v>2.403940686465435</v>
+        <v>2.403940686464858</v>
       </c>
       <c r="L3" t="n">
-        <v>2.967294929057807</v>
+        <v>2.96729492905774</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.01969082047271</v>
+        <v>2.019690820472618</v>
       </c>
       <c r="C4" t="n">
-        <v>1.746856552658335</v>
+        <v>1.746856552658279</v>
       </c>
       <c r="D4" t="n">
-        <v>2.905007910249942</v>
+        <v>2.905007910249842</v>
       </c>
       <c r="E4" t="n">
-        <v>1.799752646912045</v>
+        <v>1.799752646911987</v>
       </c>
       <c r="F4" t="n">
-        <v>1.799752646912045</v>
+        <v>1.799752646911983</v>
       </c>
       <c r="G4" t="n">
-        <v>2.952506510194436</v>
+        <v>2.952506510194359</v>
       </c>
       <c r="H4" t="n">
-        <v>3.250428090001255</v>
+        <v>3.250428090001048</v>
       </c>
       <c r="I4" t="n">
-        <v>1.934163333799773</v>
+        <v>1.934163333799617</v>
       </c>
       <c r="J4" t="n">
-        <v>1.887908749272822</v>
+        <v>1.887908749272748</v>
       </c>
       <c r="K4" t="n">
-        <v>1.827285579604092</v>
+        <v>1.827285579603904</v>
       </c>
       <c r="L4" t="n">
-        <v>2.614401531052374</v>
+        <v>2.614401531052299</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.08415081606257</v>
+        <v>11.08415081606233</v>
       </c>
       <c r="C5" t="n">
-        <v>9.670007491268406</v>
+        <v>9.670007491268251</v>
       </c>
       <c r="D5" t="n">
-        <v>26.13148657183739</v>
+        <v>26.13148657183721</v>
       </c>
       <c r="E5" t="n">
-        <v>9.670014446066535</v>
+        <v>9.670014446066716</v>
       </c>
       <c r="F5" t="n">
-        <v>9.670014446066535</v>
+        <v>9.670014446066716</v>
       </c>
       <c r="G5" t="n">
-        <v>27.91340979082069</v>
+        <v>27.91340979082046</v>
       </c>
       <c r="H5" t="n">
-        <v>34.68923551258133</v>
+        <v>34.68923551258128</v>
       </c>
       <c r="I5" t="n">
-        <v>9.669729443342337</v>
+        <v>9.669729443342089</v>
       </c>
       <c r="J5" t="n">
-        <v>9.41594500929588</v>
+        <v>9.415945009293724</v>
       </c>
       <c r="K5" t="n">
-        <v>7.805934867410041</v>
+        <v>7.805934867409847</v>
       </c>
       <c r="L5" t="n">
-        <v>6.096473655408602</v>
+        <v>6.096473655408672</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.470398694712343</v>
+        <v>2.470398694712207</v>
       </c>
       <c r="C6" t="n">
-        <v>2.330222114484422</v>
+        <v>2.330222114484356</v>
       </c>
       <c r="D6" t="n">
-        <v>3.423187537007972</v>
+        <v>3.423187537007931</v>
       </c>
       <c r="E6" t="n">
-        <v>2.307804883816006</v>
+        <v>2.307804883815923</v>
       </c>
       <c r="F6" t="n">
-        <v>2.376216759775054</v>
+        <v>2.376216759775018</v>
       </c>
       <c r="G6" t="n">
-        <v>5.519047150854671</v>
+        <v>5.519047150854601</v>
       </c>
       <c r="H6" t="n">
-        <v>6.436105510134664</v>
+        <v>6.436105510134276</v>
       </c>
       <c r="I6" t="n">
-        <v>4.500703974459959</v>
+        <v>4.500703974459919</v>
       </c>
       <c r="J6" t="n">
-        <v>4.585471454816214</v>
+        <v>4.585471454816038</v>
       </c>
       <c r="K6" t="n">
-        <v>2.224153303922356</v>
+        <v>2.224153303922372</v>
       </c>
       <c r="L6" t="n">
-        <v>3.05892619389315</v>
+        <v>3.058926193893168</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.775833522793662</v>
+        <v>2.775833522793685</v>
       </c>
       <c r="C7" t="n">
-        <v>2.690584084046879</v>
+        <v>2.690584084046767</v>
       </c>
       <c r="D7" t="n">
-        <v>3.661154105486091</v>
+        <v>3.661154105486011</v>
       </c>
       <c r="E7" t="n">
-        <v>2.674380367608387</v>
+        <v>2.674380367608245</v>
       </c>
       <c r="F7" t="n">
-        <v>2.674380367608387</v>
+        <v>2.674380367608244</v>
       </c>
       <c r="G7" t="n">
-        <v>3.70864921251552</v>
+        <v>3.708649212515322</v>
       </c>
       <c r="H7" t="n">
-        <v>4.006570792322166</v>
+        <v>4.006570792322194</v>
       </c>
       <c r="I7" t="n">
-        <v>2.690306036120794</v>
+        <v>2.690306036120634</v>
       </c>
       <c r="J7" t="n">
-        <v>2.644051451593748</v>
+        <v>2.644051451593834</v>
       </c>
       <c r="K7" t="n">
-        <v>2.583428281925072</v>
+        <v>2.583428281925003</v>
       </c>
       <c r="L7" t="n">
-        <v>3.370544233373325</v>
+        <v>3.370544233373393</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.622940380232438</v>
+        <v>4.622940380232236</v>
       </c>
       <c r="C8" t="n">
-        <v>6.352125943523443</v>
+        <v>6.352125943522365</v>
       </c>
       <c r="D8" t="n">
-        <v>7.717209886503674</v>
+        <v>7.717209886502853</v>
       </c>
       <c r="E8" t="n">
-        <v>5.853364873182529</v>
+        <v>5.853364873182784</v>
       </c>
       <c r="F8" t="n">
-        <v>4.586020146582821</v>
+        <v>4.586020146582688</v>
       </c>
       <c r="G8" t="n">
-        <v>7.385333655601377</v>
+        <v>7.385333655600875</v>
       </c>
       <c r="H8" t="n">
-        <v>7.683255235399801</v>
+        <v>7.683255235399225</v>
       </c>
       <c r="I8" t="n">
-        <v>6.366990479206686</v>
+        <v>6.366990479206277</v>
       </c>
       <c r="J8" t="n">
-        <v>6.321095456014146</v>
+        <v>6.321095456014152</v>
       </c>
       <c r="K8" t="n">
-        <v>4.396549796683611</v>
+        <v>4.396549796683535</v>
       </c>
       <c r="L8" t="n">
-        <v>8.958375448530182</v>
+        <v>8.95837544853002</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86.79118257175729</v>
+        <v>86.79118257175728</v>
       </c>
       <c r="C9" t="n">
-        <v>110.22630704921</v>
+        <v>110.2263070492098</v>
       </c>
       <c r="D9" t="n">
-        <v>111.1968743370014</v>
+        <v>111.1968743370013</v>
       </c>
       <c r="E9" t="n">
         <v>137.3683270464699</v>
       </c>
       <c r="F9" t="n">
-        <v>110.2263136594482</v>
+        <v>110.2263136594479</v>
       </c>
       <c r="G9" t="n">
-        <v>111.2443721776787</v>
+        <v>111.2443721776786</v>
       </c>
       <c r="H9" t="n">
-        <v>111.5422937574854</v>
+        <v>111.5422937574855</v>
       </c>
       <c r="I9" t="n">
-        <v>110.226029001284</v>
+        <v>110.2260290012837</v>
       </c>
       <c r="J9" t="n">
-        <v>110.179774416757</v>
+        <v>110.1797744167566</v>
       </c>
       <c r="K9" t="n">
-        <v>96.49135454774844</v>
+        <v>96.49135454774834</v>
       </c>
       <c r="L9" t="n">
-        <v>110.9062671985364</v>
+        <v>110.9062671985363</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.86657960124458</v>
+        <v>2.866579601244528</v>
       </c>
       <c r="C2" t="n">
-        <v>2.863100221457772</v>
+        <v>2.863100221457754</v>
       </c>
       <c r="D2" t="n">
-        <v>2.86875532161723</v>
+        <v>2.86875532161721</v>
       </c>
       <c r="E2" t="n">
-        <v>3.11759724438665</v>
+        <v>3.117597244386646</v>
       </c>
       <c r="F2" t="n">
-        <v>2.428726431143924</v>
+        <v>2.428726431143902</v>
       </c>
       <c r="G2" t="n">
-        <v>2.969187754103729</v>
+        <v>2.969187754103697</v>
       </c>
       <c r="H2" t="n">
-        <v>2.814457181872804</v>
+        <v>2.814457181872785</v>
       </c>
       <c r="I2" t="n">
-        <v>2.803223880831255</v>
+        <v>2.803223880831236</v>
       </c>
       <c r="J2" t="n">
-        <v>3.910958496440774</v>
+        <v>3.910958496440773</v>
       </c>
       <c r="K2" t="n">
-        <v>2.98984903413485</v>
+        <v>2.989849034134836</v>
       </c>
       <c r="L2" t="n">
-        <v>2.847200094433782</v>
+        <v>2.847200094433787</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.422214422749116</v>
+        <v>3.422214422749101</v>
       </c>
       <c r="C3" t="n">
-        <v>3.073900952439436</v>
+        <v>3.073900952439439</v>
       </c>
       <c r="D3" t="n">
-        <v>3.435403683904058</v>
+        <v>3.435403683904034</v>
       </c>
       <c r="E3" t="n">
-        <v>3.490228687336907</v>
+        <v>3.490228687336906</v>
       </c>
       <c r="F3" t="n">
-        <v>2.353090902024408</v>
+        <v>2.353090902024415</v>
       </c>
       <c r="G3" t="n">
-        <v>4.150479392787475</v>
+        <v>4.150479392787502</v>
       </c>
       <c r="H3" t="n">
-        <v>3.076628100520431</v>
+        <v>3.076628100520436</v>
       </c>
       <c r="I3" t="n">
-        <v>2.971319860317506</v>
+        <v>2.971319860317512</v>
       </c>
       <c r="J3" t="n">
-        <v>5.011928329265666</v>
+        <v>5.011928329265682</v>
       </c>
       <c r="K3" t="n">
-        <v>3.335977049171766</v>
+        <v>3.33597704917175</v>
       </c>
       <c r="L3" t="n">
-        <v>3.308795621125664</v>
+        <v>3.308795621125655</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.186658525543561</v>
+        <v>3.186658525543659</v>
       </c>
       <c r="C4" t="n">
-        <v>2.241293482235605</v>
+        <v>2.241293482235616</v>
       </c>
       <c r="D4" t="n">
-        <v>3.211234288033848</v>
+        <v>3.211234288033588</v>
       </c>
       <c r="E4" t="n">
-        <v>2.307720294430245</v>
+        <v>2.30772029443024</v>
       </c>
       <c r="F4" t="n">
-        <v>2.307720294430236</v>
+        <v>2.30772029443024</v>
       </c>
       <c r="G4" t="n">
-        <v>4.343650007305279</v>
+        <v>4.343650007305237</v>
       </c>
       <c r="H4" t="n">
-        <v>2.641258574761686</v>
+        <v>2.641258574762031</v>
       </c>
       <c r="I4" t="n">
-        <v>2.458155427763822</v>
+        <v>2.45815542776383</v>
       </c>
       <c r="J4" t="n">
-        <v>2.903382715492835</v>
+        <v>2.90338271549298</v>
       </c>
       <c r="K4" t="n">
-        <v>2.588918719635676</v>
+        <v>2.588918719635924</v>
       </c>
       <c r="L4" t="n">
-        <v>3.002075518970744</v>
+        <v>3.002075518971068</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.33513826062912</v>
+        <v>23.33513826062897</v>
       </c>
       <c r="C5" t="n">
-        <v>11.32809138578557</v>
+        <v>11.32809138578559</v>
       </c>
       <c r="D5" t="n">
-        <v>22.55769251070133</v>
+        <v>22.55769251070118</v>
       </c>
       <c r="E5" t="n">
-        <v>11.32809924973417</v>
+        <v>11.32809924973416</v>
       </c>
       <c r="F5" t="n">
-        <v>11.32809924973417</v>
+        <v>11.32809924973416</v>
       </c>
       <c r="G5" t="n">
-        <v>41.73090357033798</v>
+        <v>41.73090357033545</v>
       </c>
       <c r="H5" t="n">
-        <v>15.17242575125963</v>
+        <v>15.17242575125948</v>
       </c>
       <c r="I5" t="n">
-        <v>11.32761846983871</v>
+        <v>11.32761846983873</v>
       </c>
       <c r="J5" t="n">
-        <v>20.06952359067639</v>
+        <v>20.06952359067638</v>
       </c>
       <c r="K5" t="n">
-        <v>13.08164974847165</v>
+        <v>13.08164974847169</v>
       </c>
       <c r="L5" t="n">
-        <v>23.30853376446682</v>
+        <v>23.30853376446688</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.097671738106554</v>
+        <v>6.097671738106644</v>
       </c>
       <c r="C6" t="n">
-        <v>2.98919412364258</v>
+        <v>2.989194123642581</v>
       </c>
       <c r="D6" t="n">
-        <v>3.847046322760681</v>
+        <v>3.847046322760658</v>
       </c>
       <c r="E6" t="n">
-        <v>2.943075626624626</v>
+        <v>2.943075626624616</v>
       </c>
       <c r="F6" t="n">
-        <v>3.056751731048829</v>
+        <v>3.05675173104883</v>
       </c>
       <c r="G6" t="n">
-        <v>7.254663219868656</v>
+        <v>7.254663219868241</v>
       </c>
       <c r="H6" t="n">
-        <v>6.080449879936689</v>
+        <v>6.080449879936761</v>
       </c>
       <c r="I6" t="n">
-        <v>5.369168640326971</v>
+        <v>5.369168640326976</v>
       </c>
       <c r="J6" t="n">
-        <v>3.549954049562998</v>
+        <v>3.549954049562984</v>
       </c>
       <c r="K6" t="n">
-        <v>3.143634347914221</v>
+        <v>3.143634347914062</v>
       </c>
       <c r="L6" t="n">
-        <v>3.597510320763806</v>
+        <v>3.597510320763834</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.026551550325677</v>
+        <v>4.026551550325553</v>
       </c>
       <c r="C7" t="n">
-        <v>3.298521368492718</v>
+        <v>3.298521368492714</v>
       </c>
       <c r="D7" t="n">
-        <v>4.051130052978659</v>
+        <v>4.051130052978547</v>
       </c>
       <c r="E7" t="n">
-        <v>3.278980204395328</v>
+        <v>3.278980204395368</v>
       </c>
       <c r="F7" t="n">
-        <v>3.278980204395328</v>
+        <v>3.278980204395368</v>
       </c>
       <c r="G7" t="n">
-        <v>5.183543032087414</v>
+        <v>5.183543032087253</v>
       </c>
       <c r="H7" t="n">
-        <v>3.481151599543886</v>
+        <v>3.481151599544025</v>
       </c>
       <c r="I7" t="n">
-        <v>3.298048452545852</v>
+        <v>3.298048452545876</v>
       </c>
       <c r="J7" t="n">
-        <v>3.74327574027481</v>
+        <v>3.743275740274947</v>
       </c>
       <c r="K7" t="n">
-        <v>3.428811744417933</v>
+        <v>3.428811744417881</v>
       </c>
       <c r="L7" t="n">
-        <v>3.841968543753112</v>
+        <v>3.841968543753012</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.95087585439688</v>
+        <v>5.950875854396772</v>
       </c>
       <c r="C8" t="n">
-        <v>7.252569090702395</v>
+        <v>7.252569090702387</v>
       </c>
       <c r="D8" t="n">
-        <v>8.448135208471079</v>
+        <v>8.448135208470919</v>
       </c>
       <c r="E8" t="n">
-        <v>6.694402388640485</v>
+        <v>6.694402388640619</v>
       </c>
       <c r="F8" t="n">
-        <v>5.276108857127985</v>
+        <v>5.27610885712799</v>
       </c>
       <c r="G8" t="n">
-        <v>9.155881789626545</v>
+        <v>9.15588178962647</v>
       </c>
       <c r="H8" t="n">
-        <v>7.453490357066752</v>
+        <v>7.453490357066804</v>
       </c>
       <c r="I8" t="n">
-        <v>7.270387210085107</v>
+        <v>7.27038721008502</v>
       </c>
       <c r="J8" t="n">
-        <v>7.716016985414381</v>
+        <v>7.716016985414275</v>
       </c>
       <c r="K8" t="n">
-        <v>5.315093129128809</v>
+        <v>5.315093129128739</v>
       </c>
       <c r="L8" t="n">
-        <v>9.953629644466483</v>
+        <v>9.953629644466359</v>
       </c>
     </row>
     <row r="9">
@@ -7932,25 +7932,25 @@
         <v>104.5414576124159</v>
       </c>
       <c r="E9" t="n">
-        <v>129.2361649918869</v>
+        <v>129.2361649918868</v>
       </c>
       <c r="F9" t="n">
-        <v>103.7888578730755</v>
+        <v>103.7888578730754</v>
       </c>
       <c r="G9" t="n">
         <v>105.6738717342538</v>
       </c>
       <c r="H9" t="n">
-        <v>103.9714803017102</v>
+        <v>103.9714803017103</v>
       </c>
       <c r="I9" t="n">
-        <v>103.7883771547122</v>
+        <v>103.7883771547121</v>
       </c>
       <c r="J9" t="n">
-        <v>104.2336044424411</v>
+        <v>104.2336044424412</v>
       </c>
       <c r="K9" t="n">
-        <v>91.142243570669</v>
+        <v>91.14224357066885</v>
       </c>
       <c r="L9" t="n">
         <v>104.3322972459193</v>
